--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-02</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-07-31</t>
         </is>
       </c>
     </row>
@@ -604,10 +604,10 @@
         <v>5</v>
       </c>
       <c r="N5" t="n">
-        <v>74676.65579999999</v>
+        <v>74676.65634615401</v>
       </c>
       <c r="O5" t="n">
-        <v>373383.279</v>
+        <v>373383.28173077</v>
       </c>
       <c r="P5" t="n">
         <v>144900</v>
@@ -1155,10 +1155,10 @@
         <v>324</v>
       </c>
       <c r="N18" t="n">
-        <v>3926.8371355499</v>
+        <v>3926.8371399387</v>
       </c>
       <c r="O18" t="n">
-        <v>1272295.231918168</v>
+        <v>1272295.233340139</v>
       </c>
       <c r="P18" t="n">
         <v>4800</v>
@@ -1358,10 +1358,10 @@
         <v>21</v>
       </c>
       <c r="N23" t="n">
-        <v>3910.628317757</v>
+        <v>3910.6283208955</v>
       </c>
       <c r="O23" t="n">
-        <v>82123.19467289699</v>
+        <v>82123.1947388055</v>
       </c>
       <c r="P23" t="n">
         <v>9100</v>
@@ -1442,10 +1442,10 @@
         <v>2</v>
       </c>
       <c r="N25" t="n">
-        <v>30708.904814815</v>
+        <v>30708.906428571</v>
       </c>
       <c r="O25" t="n">
-        <v>61417.80962963</v>
+        <v>61417.812857142</v>
       </c>
       <c r="P25" t="n">
         <v>53500</v>
@@ -1526,10 +1526,10 @@
         <v>6</v>
       </c>
       <c r="N27" t="n">
-        <v>17085.656666667</v>
+        <v>17085.657567568</v>
       </c>
       <c r="O27" t="n">
-        <v>102513.940000002</v>
+        <v>102513.945405408</v>
       </c>
       <c r="P27" t="n">
         <v>29200</v>
@@ -1568,10 +1568,10 @@
         <v>16</v>
       </c>
       <c r="N28" t="n">
-        <v>16486.41027027</v>
+        <v>16486.4104</v>
       </c>
       <c r="O28" t="n">
-        <v>263782.56432432</v>
+        <v>263782.5664</v>
       </c>
       <c r="P28" t="n">
         <v>30500</v>
@@ -1610,10 +1610,10 @@
         <v>42</v>
       </c>
       <c r="N29" t="n">
-        <v>15711.966441948</v>
+        <v>15711.966494465</v>
       </c>
       <c r="O29" t="n">
-        <v>659902.590561816</v>
+        <v>659902.59276753</v>
       </c>
       <c r="P29" t="n">
         <v>28500</v>
@@ -1790,10 +1790,10 @@
         <v>6</v>
       </c>
       <c r="N33" t="n">
-        <v>36574.852</v>
+        <v>36574.851914894</v>
       </c>
       <c r="O33" t="n">
-        <v>219449.112</v>
+        <v>219449.111489364</v>
       </c>
       <c r="P33" t="n">
         <v>65900</v>
@@ -1973,10 +1973,10 @@
         <v>58</v>
       </c>
       <c r="N37" t="n">
-        <v>141416.88438871</v>
+        <v>141416.88436137</v>
       </c>
       <c r="O37" t="n">
-        <v>8202179.294545179</v>
+        <v>8202179.29295946</v>
       </c>
       <c r="P37" t="n">
         <v>251900</v>
@@ -2015,10 +2015,10 @@
         <v>36</v>
       </c>
       <c r="N38" t="n">
-        <v>200072.19883562</v>
+        <v>200072.19865772</v>
       </c>
       <c r="O38" t="n">
-        <v>7202599.158082319</v>
+        <v>7202599.15167792</v>
       </c>
       <c r="P38" t="n">
         <v>312000</v>
@@ -2151,10 +2151,10 @@
         <v>6</v>
       </c>
       <c r="N41" t="n">
-        <v>344599.17885246</v>
+        <v>344599.17888889</v>
       </c>
       <c r="O41" t="n">
-        <v>2067595.07311476</v>
+        <v>2067595.07333334</v>
       </c>
       <c r="P41" t="n">
         <v>532900</v>
@@ -2431,10 +2431,10 @@
         <v>24</v>
       </c>
       <c r="N48" t="n">
-        <v>4878.2852688172</v>
+        <v>4878.2851851852</v>
       </c>
       <c r="O48" t="n">
-        <v>117078.8464516128</v>
+        <v>117078.8444444448</v>
       </c>
       <c r="P48" t="n">
         <v>13500</v>
@@ -2472,10 +2472,10 @@
         <v>12</v>
       </c>
       <c r="N49" t="n">
-        <v>7394.9353846154</v>
+        <v>7394.9353551913</v>
       </c>
       <c r="O49" t="n">
-        <v>88739.2246153848</v>
+        <v>88739.2242622956</v>
       </c>
       <c r="P49" t="n">
         <v>17900</v>
@@ -2667,10 +2667,10 @@
         <v>264</v>
       </c>
       <c r="N54" t="n">
-        <v>3340.6800775194</v>
+        <v>3340.6800773694</v>
       </c>
       <c r="O54" t="n">
-        <v>881939.5404651216</v>
+        <v>881939.5404255216</v>
       </c>
       <c r="P54" t="n">
         <v>7100</v>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-07-31</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-03</t>
         </is>
       </c>
     </row>
@@ -604,10 +604,10 @@
         <v>5</v>
       </c>
       <c r="N5" t="n">
-        <v>74676.65634615401</v>
+        <v>74676.65579999999</v>
       </c>
       <c r="O5" t="n">
-        <v>373383.28173077</v>
+        <v>373383.279</v>
       </c>
       <c r="P5" t="n">
         <v>144900</v>
@@ -1155,10 +1155,10 @@
         <v>324</v>
       </c>
       <c r="N18" t="n">
-        <v>3926.8371399387</v>
+        <v>3926.8371355499</v>
       </c>
       <c r="O18" t="n">
-        <v>1272295.233340139</v>
+        <v>1272295.231918168</v>
       </c>
       <c r="P18" t="n">
         <v>4800</v>
@@ -1358,10 +1358,10 @@
         <v>21</v>
       </c>
       <c r="N23" t="n">
-        <v>3910.6283208955</v>
+        <v>3910.628317757</v>
       </c>
       <c r="O23" t="n">
-        <v>82123.1947388055</v>
+        <v>82123.19467289699</v>
       </c>
       <c r="P23" t="n">
         <v>9100</v>
@@ -1442,10 +1442,10 @@
         <v>2</v>
       </c>
       <c r="N25" t="n">
-        <v>30708.906428571</v>
+        <v>30708.904814815</v>
       </c>
       <c r="O25" t="n">
-        <v>61417.812857142</v>
+        <v>61417.80962963</v>
       </c>
       <c r="P25" t="n">
         <v>53500</v>
@@ -1526,10 +1526,10 @@
         <v>6</v>
       </c>
       <c r="N27" t="n">
-        <v>17085.657567568</v>
+        <v>17085.656666667</v>
       </c>
       <c r="O27" t="n">
-        <v>102513.945405408</v>
+        <v>102513.940000002</v>
       </c>
       <c r="P27" t="n">
         <v>29200</v>
@@ -1568,10 +1568,10 @@
         <v>16</v>
       </c>
       <c r="N28" t="n">
-        <v>16486.4104</v>
+        <v>16486.41027027</v>
       </c>
       <c r="O28" t="n">
-        <v>263782.5664</v>
+        <v>263782.56432432</v>
       </c>
       <c r="P28" t="n">
         <v>30500</v>
@@ -1610,10 +1610,10 @@
         <v>42</v>
       </c>
       <c r="N29" t="n">
-        <v>15711.966494465</v>
+        <v>15711.966441948</v>
       </c>
       <c r="O29" t="n">
-        <v>659902.59276753</v>
+        <v>659902.590561816</v>
       </c>
       <c r="P29" t="n">
         <v>28500</v>
@@ -1790,10 +1790,10 @@
         <v>6</v>
       </c>
       <c r="N33" t="n">
-        <v>36574.851914894</v>
+        <v>36574.852</v>
       </c>
       <c r="O33" t="n">
-        <v>219449.111489364</v>
+        <v>219449.112</v>
       </c>
       <c r="P33" t="n">
         <v>65900</v>
@@ -1973,10 +1973,10 @@
         <v>58</v>
       </c>
       <c r="N37" t="n">
-        <v>141416.88436137</v>
+        <v>141416.88438871</v>
       </c>
       <c r="O37" t="n">
-        <v>8202179.29295946</v>
+        <v>8202179.294545179</v>
       </c>
       <c r="P37" t="n">
         <v>251900</v>
@@ -2015,10 +2015,10 @@
         <v>36</v>
       </c>
       <c r="N38" t="n">
-        <v>200072.19865772</v>
+        <v>200072.19883562</v>
       </c>
       <c r="O38" t="n">
-        <v>7202599.15167792</v>
+        <v>7202599.158082319</v>
       </c>
       <c r="P38" t="n">
         <v>312000</v>
@@ -2151,10 +2151,10 @@
         <v>6</v>
       </c>
       <c r="N41" t="n">
-        <v>344599.17888889</v>
+        <v>344599.17885246</v>
       </c>
       <c r="O41" t="n">
-        <v>2067595.07333334</v>
+        <v>2067595.07311476</v>
       </c>
       <c r="P41" t="n">
         <v>532900</v>
@@ -2431,10 +2431,10 @@
         <v>24</v>
       </c>
       <c r="N48" t="n">
-        <v>4878.2851851852</v>
+        <v>4878.2852688172</v>
       </c>
       <c r="O48" t="n">
-        <v>117078.8444444448</v>
+        <v>117078.8464516128</v>
       </c>
       <c r="P48" t="n">
         <v>13500</v>
@@ -2472,10 +2472,10 @@
         <v>12</v>
       </c>
       <c r="N49" t="n">
-        <v>7394.9353551913</v>
+        <v>7394.9353846154</v>
       </c>
       <c r="O49" t="n">
-        <v>88739.2242622956</v>
+        <v>88739.2246153848</v>
       </c>
       <c r="P49" t="n">
         <v>17900</v>
@@ -2667,10 +2667,10 @@
         <v>264</v>
       </c>
       <c r="N54" t="n">
-        <v>3340.6800773694</v>
+        <v>3340.6800775194</v>
       </c>
       <c r="O54" t="n">
-        <v>881939.5404255216</v>
+        <v>881939.5404651216</v>
       </c>
       <c r="P54" t="n">
         <v>7100</v>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-03</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-04</t>
         </is>
       </c>
     </row>
@@ -604,10 +604,10 @@
         <v>5</v>
       </c>
       <c r="N5" t="n">
-        <v>74676.65579999999</v>
+        <v>74676.655510204</v>
       </c>
       <c r="O5" t="n">
-        <v>373383.279</v>
+        <v>373383.27755102</v>
       </c>
       <c r="P5" t="n">
         <v>144900</v>
@@ -1155,10 +1155,10 @@
         <v>324</v>
       </c>
       <c r="N18" t="n">
-        <v>3926.8371355499</v>
+        <v>3926.8371340839</v>
       </c>
       <c r="O18" t="n">
-        <v>1272295.231918168</v>
+        <v>1272295.231443183</v>
       </c>
       <c r="P18" t="n">
         <v>4800</v>
@@ -1319,10 +1319,10 @@
         <v>13</v>
       </c>
       <c r="N22" t="n">
-        <v>15403.520437158</v>
+        <v>15403.520494505</v>
       </c>
       <c r="O22" t="n">
-        <v>200245.765683054</v>
+        <v>200245.766428565</v>
       </c>
       <c r="P22" t="n">
         <v>33500</v>
@@ -1484,10 +1484,10 @@
         <v>12</v>
       </c>
       <c r="N26" t="n">
-        <v>12837.964266667</v>
+        <v>12837.964861111</v>
       </c>
       <c r="O26" t="n">
-        <v>154055.571200004</v>
+        <v>154055.578333332</v>
       </c>
       <c r="P26" t="n">
         <v>22900</v>
@@ -1610,10 +1610,10 @@
         <v>42</v>
       </c>
       <c r="N29" t="n">
-        <v>15711.966441948</v>
+        <v>15711.966415094</v>
       </c>
       <c r="O29" t="n">
-        <v>659902.590561816</v>
+        <v>659902.589433948</v>
       </c>
       <c r="P29" t="n">
         <v>28500</v>
@@ -1657,10 +1657,10 @@
         <v>12</v>
       </c>
       <c r="N30" t="n">
-        <v>30238.812195122</v>
+        <v>30238.812222222</v>
       </c>
       <c r="O30" t="n">
-        <v>362865.746341464</v>
+        <v>362865.746666664</v>
       </c>
       <c r="P30" t="n">
         <v>51100</v>
@@ -1973,10 +1973,10 @@
         <v>58</v>
       </c>
       <c r="N37" t="n">
-        <v>141416.88438871</v>
+        <v>141416.8844164</v>
       </c>
       <c r="O37" t="n">
-        <v>8202179.294545179</v>
+        <v>8202179.296151199</v>
       </c>
       <c r="P37" t="n">
         <v>251900</v>
@@ -2015,10 +2015,10 @@
         <v>36</v>
       </c>
       <c r="N38" t="n">
-        <v>200072.19883562</v>
+        <v>200072.19889655</v>
       </c>
       <c r="O38" t="n">
-        <v>7202599.158082319</v>
+        <v>7202599.1602758</v>
       </c>
       <c r="P38" t="n">
         <v>312000</v>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q77"/>
+  <dimension ref="A1:Q76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-04</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-05</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -554,19 +554,19 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N4" t="n">
-        <v>96741.40686747</v>
+        <v>96741.40695121999</v>
       </c>
       <c r="O4" t="n">
-        <v>1257638.28927711</v>
+        <v>1160896.88341464</v>
       </c>
       <c r="P4" t="n">
         <v>188900</v>
       </c>
       <c r="Q4" t="n">
-        <v>2455700</v>
+        <v>2266800</v>
       </c>
     </row>
     <row r="5">
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -601,19 +601,19 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N5" t="n">
-        <v>74676.655510204</v>
+        <v>74676.654222222</v>
       </c>
       <c r="O5" t="n">
-        <v>373383.27755102</v>
+        <v>149353.308444444</v>
       </c>
       <c r="P5" t="n">
         <v>144900</v>
       </c>
       <c r="Q5" t="n">
-        <v>724500</v>
+        <v>289800</v>
       </c>
     </row>
     <row r="6">
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -1397,19 +1397,19 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="N24" t="n">
-        <v>21338.138571429</v>
+        <v>21338.01</v>
       </c>
       <c r="O24" t="n">
-        <v>149366.970000003</v>
+        <v>21338.01</v>
       </c>
       <c r="P24" t="n">
         <v>37100</v>
       </c>
       <c r="Q24" t="n">
-        <v>259700</v>
+        <v>37100</v>
       </c>
     </row>
     <row r="25">
@@ -1498,14 +1498,14 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>51026</v>
+        <v>51104</v>
       </c>
       <c r="B27" t="n">
-        <v>6941607325452</v>
+        <v>6942138915815</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>51026 PISCINA DE JUEGOS</t>
+          <t>PISCINA VERANO 102 X25 CM</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1514,7 +1514,7 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -1523,31 +1523,31 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="N27" t="n">
-        <v>17085.656666667</v>
+        <v>16486.41027027</v>
       </c>
       <c r="O27" t="n">
-        <v>102513.940000002</v>
+        <v>263782.56432432</v>
       </c>
       <c r="P27" t="n">
-        <v>29200</v>
+        <v>30500</v>
       </c>
       <c r="Q27" t="n">
-        <v>175200</v>
+        <v>488000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>51104</v>
+        <v>51124</v>
       </c>
       <c r="B28" t="n">
-        <v>6942138915815</v>
+        <v>6941607325032</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>PISCINA VERANO 102 X25 CM</t>
+          <t>51124 COMBO DE PISCINA Y BALON</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1556,7 +1556,7 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -1565,40 +1565,45 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="N28" t="n">
-        <v>16486.41027027</v>
+        <v>15711.966317829</v>
       </c>
       <c r="O28" t="n">
-        <v>263782.56432432</v>
+        <v>565630.787441844</v>
       </c>
       <c r="P28" t="n">
-        <v>30500</v>
+        <v>28500</v>
       </c>
       <c r="Q28" t="n">
-        <v>488000</v>
+        <v>1026000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>51124</v>
+        <v>51203</v>
       </c>
       <c r="B29" t="n">
-        <v>6941607325032</v>
+        <v>6941607325544</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>51124 COMBO DE PISCINA Y BALON</t>
+          <t>51203 PISCINA 3 AROS BESTWAY Φ1.68m x H38cm</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -1607,45 +1612,37 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="N29" t="n">
-        <v>15711.966415094</v>
+        <v>30238.812278481</v>
       </c>
       <c r="O29" t="n">
-        <v>659902.589433948</v>
+        <v>302388.12278481</v>
       </c>
       <c r="P29" t="n">
-        <v>28500</v>
+        <v>51100</v>
       </c>
       <c r="Q29" t="n">
-        <v>1197000</v>
+        <v>511000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>51203</v>
-      </c>
-      <c r="B30" t="n">
-        <v>6941607325544</v>
+        <v>52331</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>51203 PISCINA 3 AROS BESTWAY Φ1.68m x H38cm</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>PISCINA CANOPY FRUTICAS 8 PCS</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>12</v>
+        <v>75</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -1654,28 +1651,36 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>12</v>
+        <v>75</v>
       </c>
       <c r="N30" t="n">
-        <v>30238.812222222</v>
+        <v>20195.32</v>
       </c>
       <c r="O30" t="n">
-        <v>362865.746666664</v>
+        <v>1514649</v>
       </c>
       <c r="P30" t="n">
-        <v>51100</v>
+        <v>45900</v>
       </c>
       <c r="Q30" t="n">
-        <v>613200</v>
+        <v>3442500</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>52331</v>
+        <v>52637</v>
+      </c>
+      <c r="B31" t="n">
+        <v>6941607352212</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>PISCINA CANOPY FRUTICAS 8 PCS</t>
+          <t>52637 PISCINA TECHADA SUNNY BESTWAY</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1684,7 +1689,7 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>75</v>
+        <v>4</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -1693,31 +1698,31 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>75</v>
+        <v>4</v>
       </c>
       <c r="N31" t="n">
-        <v>20195.32</v>
+        <v>22267.551785714</v>
       </c>
       <c r="O31" t="n">
-        <v>1514649</v>
+        <v>89070.207142856</v>
       </c>
       <c r="P31" t="n">
-        <v>45900</v>
+        <v>46300</v>
       </c>
       <c r="Q31" t="n">
-        <v>3442500</v>
+        <v>185200</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>52637</v>
+        <v>53157</v>
       </c>
       <c r="B32" t="n">
-        <v>6941607352212</v>
+        <v>6941607352137</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>52637 PISCINA TECHADA SUNNY BESTWAY</t>
+          <t>53157 PISCINA FUENTE SHARK BESTWAY</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1743,33 +1748,28 @@
         <v>4</v>
       </c>
       <c r="N32" t="n">
-        <v>22267.551785714</v>
+        <v>36574.852142857</v>
       </c>
       <c r="O32" t="n">
-        <v>89070.207142856</v>
+        <v>146299.408571428</v>
       </c>
       <c r="P32" t="n">
-        <v>46300</v>
+        <v>65900</v>
       </c>
       <c r="Q32" t="n">
-        <v>185200</v>
+        <v>263600</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>53157</v>
+        <v>54150</v>
       </c>
       <c r="B33" t="n">
-        <v>6941607352137</v>
+        <v>6942138968279</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>53157 PISCINA FUENTE SHARK BESTWAY</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>54150 Piscina familiar rectangular</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -1787,31 +1787,36 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N33" t="n">
-        <v>36574.852</v>
+        <v>80027.73</v>
       </c>
       <c r="O33" t="n">
-        <v>219449.112</v>
+        <v>320110.92</v>
       </c>
       <c r="P33" t="n">
-        <v>65900</v>
+        <v>129900</v>
       </c>
       <c r="Q33" t="n">
-        <v>395400</v>
+        <v>519600</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>54150</v>
+        <v>54370</v>
       </c>
       <c r="B34" t="n">
-        <v>6942138968279</v>
+        <v>6941607312643</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>54150 Piscina familiar rectangular</t>
+          <t>PISCINA CAPITAN 213 X155 X 132CM</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1832,28 +1837,28 @@
         <v>4</v>
       </c>
       <c r="N34" t="n">
-        <v>80027.73</v>
+        <v>103298.75</v>
       </c>
       <c r="O34" t="n">
-        <v>320110.92</v>
+        <v>413195</v>
       </c>
       <c r="P34" t="n">
-        <v>129900</v>
+        <v>178900</v>
       </c>
       <c r="Q34" t="n">
-        <v>519600</v>
+        <v>715600</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>54370</v>
+        <v>55031</v>
       </c>
       <c r="B35" t="n">
-        <v>6941607312643</v>
+        <v>6942138913781</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>PISCINA CAPITAN 213 X155 X 132CM</t>
+          <t>55031 PISCINA DELFIN 2.44mx46cm</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1867,7 +1872,7 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -1876,31 +1881,31 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N35" t="n">
-        <v>103298.75</v>
+        <v>56906.800422535</v>
       </c>
       <c r="O35" t="n">
-        <v>413195</v>
+        <v>56906.800422535</v>
       </c>
       <c r="P35" t="n">
-        <v>178900</v>
+        <v>95900</v>
       </c>
       <c r="Q35" t="n">
-        <v>715600</v>
+        <v>95900</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>55031</v>
+        <v>56401</v>
       </c>
       <c r="B36" t="n">
-        <v>6942138913781</v>
+        <v>6941607327951</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>55031 PISCINA DELFIN 2.44mx46cm</t>
+          <t>56401 PISCINA ESTRUCTURAL RECTANGULAR BESTWAY</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1914,7 +1919,7 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -1923,45 +1928,40 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="N36" t="n">
-        <v>56906.799135802</v>
+        <v>141416.8844586</v>
       </c>
       <c r="O36" t="n">
-        <v>625974.790493822</v>
+        <v>7919345.5296816</v>
       </c>
       <c r="P36" t="n">
-        <v>95900</v>
+        <v>251900</v>
       </c>
       <c r="Q36" t="n">
-        <v>1054900</v>
+        <v>14106400</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>56401</v>
+        <v>56403</v>
       </c>
       <c r="B37" t="n">
-        <v>6941607327951</v>
+        <v>6941607327982</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>56401 PISCINA ESTRUCTURAL RECTANGULAR BESTWAY</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>PISCINA ESTRUCTURAL 2.59m x 1.70m x 61cm BESTWAY</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -1970,40 +1970,40 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="N37" t="n">
-        <v>141416.8844164</v>
+        <v>200072.19902098</v>
       </c>
       <c r="O37" t="n">
-        <v>8202179.296151199</v>
+        <v>6802454.76671332</v>
       </c>
       <c r="P37" t="n">
-        <v>251900</v>
+        <v>312000</v>
       </c>
       <c r="Q37" t="n">
-        <v>14610200</v>
+        <v>10608000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>56403</v>
+        <v>56404</v>
       </c>
       <c r="B38" t="n">
-        <v>6941607327982</v>
+        <v>6941607327999</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>PISCINA ESTRUCTURAL 2.59m x 1.70m x 61cm BESTWAY</t>
+          <t>56404 PISCINA ESTRUCTURAL RECTANGULAR BESTWAY</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -2012,40 +2012,45 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="N38" t="n">
-        <v>200072.19889655</v>
+        <v>174389.78625</v>
       </c>
       <c r="O38" t="n">
-        <v>7202599.1602758</v>
+        <v>2790236.58</v>
       </c>
       <c r="P38" t="n">
-        <v>312000</v>
+        <v>368200</v>
       </c>
       <c r="Q38" t="n">
-        <v>11232000</v>
+        <v>5891200</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>56404</v>
+        <v>56405</v>
       </c>
       <c r="B39" t="n">
-        <v>6941607327999</v>
+        <v>6941607328002</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>56404 PISCINA ESTRUCTURAL RECTANGULAR BESTWAY</t>
+          <t>PISCINA ESTRUCTURAL RECTAGULAR BESTWAY 4.00mX2.11mX81cm</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -2054,31 +2059,31 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="N39" t="n">
-        <v>174389.78511628</v>
+        <v>251809.29411765</v>
       </c>
       <c r="O39" t="n">
-        <v>3313405.91720932</v>
+        <v>1510855.7647059</v>
       </c>
       <c r="P39" t="n">
-        <v>368200</v>
+        <v>584000</v>
       </c>
       <c r="Q39" t="n">
-        <v>6995800</v>
+        <v>3504000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>56405</v>
+        <v>56417</v>
       </c>
       <c r="B40" t="n">
-        <v>6941607328002</v>
+        <v>6942138981902</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>PISCINA ESTRUCTURAL RECTAGULAR BESTWAY 4.00mX2.11mX81cm</t>
+          <t>Piscina Estructural Redonda 366 x 76 cm Bomba/Filtro 56417</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2104,38 +2109,30 @@
         <v>6</v>
       </c>
       <c r="N40" t="n">
-        <v>251809.29411765</v>
+        <v>344599.17885246</v>
       </c>
       <c r="O40" t="n">
-        <v>1510855.7647059</v>
+        <v>2067595.07311476</v>
       </c>
       <c r="P40" t="n">
-        <v>584000</v>
+        <v>532900</v>
       </c>
       <c r="Q40" t="n">
-        <v>3504000</v>
+        <v>3197400</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>56417</v>
-      </c>
-      <c r="B41" t="n">
-        <v>6942138981902</v>
+        <v>62068</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Piscina Estructural Redonda 366 x 76 cm Bomba/Filtro 56417</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>PARCHE PISCINA EXTERIOR BESTWAY</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J41" t="n">
@@ -2151,25 +2148,25 @@
         <v>6</v>
       </c>
       <c r="N41" t="n">
-        <v>344599.17885246</v>
+        <v>1977.88</v>
       </c>
       <c r="O41" t="n">
-        <v>2067595.07311476</v>
+        <v>11867.28</v>
       </c>
       <c r="P41" t="n">
-        <v>532900</v>
+        <v>2900</v>
       </c>
       <c r="Q41" t="n">
-        <v>3197400</v>
+        <v>17400</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>62068</v>
+        <v>62091</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>PARCHE PISCINA EXTERIOR BESTWAY</t>
+          <t>PARCHE PISCINA A PRUEBA DE AGUA BESTWAY</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2178,7 +2175,7 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>6</v>
+        <v>217</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -2187,28 +2184,28 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>6</v>
+        <v>217</v>
       </c>
       <c r="N42" t="n">
-        <v>1977.88</v>
+        <v>1141.57</v>
       </c>
       <c r="O42" t="n">
-        <v>11867.28</v>
+        <v>247720.69</v>
       </c>
       <c r="P42" t="n">
-        <v>2900</v>
+        <v>3900</v>
       </c>
       <c r="Q42" t="n">
-        <v>17400</v>
+        <v>846300</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>62091</v>
+        <v>67001</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>PARCHE PISCINA A PRUEBA DE AGUA BESTWAY</t>
+          <t>COLCHON INFLABLE SENCILLO BESTWAY 1.88 X 99 CM</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2217,7 +2214,7 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>217</v>
+        <v>3</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -2226,28 +2223,28 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>217</v>
+        <v>3</v>
       </c>
       <c r="N43" t="n">
-        <v>1141.57</v>
+        <v>26280.41</v>
       </c>
       <c r="O43" t="n">
-        <v>247720.69</v>
+        <v>78841.23</v>
       </c>
       <c r="P43" t="n">
-        <v>3900</v>
+        <v>46500</v>
       </c>
       <c r="Q43" t="n">
-        <v>846300</v>
+        <v>139500</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>67001</v>
+        <v>67374</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>COLCHON INFLABLE SENCILLO BESTWAY 1.88 X 99 CM</t>
+          <t>COLCHON INFLABLE DOBLE+ALMOHADAS BESTWAY 2.03mx1.52mx22cm</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2256,7 +2253,7 @@
         </is>
       </c>
       <c r="J44" t="n">
-        <v>3</v>
+        <v>67</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -2265,28 +2262,28 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3</v>
+        <v>67</v>
       </c>
       <c r="N44" t="n">
-        <v>26280.41</v>
+        <v>61666.873842239</v>
       </c>
       <c r="O44" t="n">
-        <v>78841.23</v>
+        <v>4131680.547430013</v>
       </c>
       <c r="P44" t="n">
-        <v>46500</v>
+        <v>98900</v>
       </c>
       <c r="Q44" t="n">
-        <v>139500</v>
+        <v>6626300</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>67374</v>
+        <v>91004</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>COLCHON INFLABLE DOBLE+ALMOHADAS BESTWAY 2.03mx1.52mx22cm</t>
+          <t>FLOTADOR DISNEY 56CM 24PCS</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2295,7 +2292,7 @@
         </is>
       </c>
       <c r="J45" t="n">
-        <v>67</v>
+        <v>340</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -2304,28 +2301,28 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>67</v>
+        <v>340</v>
       </c>
       <c r="N45" t="n">
-        <v>61666.873832487</v>
+        <v>3865.67</v>
       </c>
       <c r="O45" t="n">
-        <v>4131680.546776629</v>
+        <v>1314327.8</v>
       </c>
       <c r="P45" t="n">
-        <v>98900</v>
+        <v>5500</v>
       </c>
       <c r="Q45" t="n">
-        <v>6626300</v>
+        <v>1870000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>91004</v>
+        <v>91007</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>FLOTADOR DISNEY 56CM 24PCS</t>
+          <t>PISCINA DISNEY 122X25CM 12 PCS</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2334,7 +2331,7 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>340</v>
+        <v>24</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -2343,28 +2340,35 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>340</v>
+        <v>24</v>
       </c>
       <c r="N46" t="n">
-        <v>3865.67</v>
+        <v>16010.3</v>
       </c>
       <c r="O46" t="n">
-        <v>1314327.8</v>
+        <v>384247.2</v>
       </c>
       <c r="P46" t="n">
-        <v>5500</v>
+        <v>30500</v>
       </c>
       <c r="Q46" t="n">
-        <v>1870000</v>
+        <v>732000</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="n">
-        <v>91007</v>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>9103C</t>
+        </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>PISCINA DISNEY 122X25CM 12 PCS</t>
+          <t>9103C GAFA ACUATICA SIRENITA BESTWAY</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2385,32 +2389,27 @@
         <v>24</v>
       </c>
       <c r="N47" t="n">
-        <v>16010.3</v>
+        <v>4878.2852688172</v>
       </c>
       <c r="O47" t="n">
-        <v>384247.2</v>
+        <v>117078.8464516128</v>
       </c>
       <c r="P47" t="n">
-        <v>30500</v>
+        <v>13500</v>
       </c>
       <c r="Q47" t="n">
-        <v>732000</v>
+        <v>324000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>9103C</t>
+          <t>9103D</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>9103C GAFA ACUATICA SIRENITA BESTWAY</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>9103D CARETA ACUATICA SIRENITA BESTWAY</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2419,7 +2418,7 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
@@ -2428,30 +2427,28 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="N48" t="n">
-        <v>4878.2852688172</v>
+        <v>7394.9353846154</v>
       </c>
       <c r="O48" t="n">
-        <v>117078.8464516128</v>
+        <v>88739.2246153848</v>
       </c>
       <c r="P48" t="n">
-        <v>13500</v>
+        <v>17900</v>
       </c>
       <c r="Q48" t="n">
-        <v>324000</v>
+        <v>214800</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>9103D</t>
-        </is>
+      <c r="A49" t="n">
+        <v>91040</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>9103D CARETA ACUATICA SIRENITA BESTWAY</t>
+          <t>FLOTADOR MINNIE 56CM 24 PCS</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2460,7 +2457,7 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>12</v>
+        <v>402</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -2469,28 +2466,28 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>12</v>
+        <v>402</v>
       </c>
       <c r="N49" t="n">
-        <v>7394.9353846154</v>
+        <v>3114.49</v>
       </c>
       <c r="O49" t="n">
-        <v>88739.2246153848</v>
+        <v>1252024.98</v>
       </c>
       <c r="P49" t="n">
-        <v>17900</v>
+        <v>5500</v>
       </c>
       <c r="Q49" t="n">
-        <v>214800</v>
+        <v>2211000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>91040</v>
+        <v>91042</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>FLOTADOR MINNIE 56CM 24 PCS</t>
+          <t>PELOTA PISCINA PRINCESAS 24 PCS</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2499,7 +2496,7 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>402</v>
+        <v>120</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -2508,28 +2505,28 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>402</v>
+        <v>120</v>
       </c>
       <c r="N50" t="n">
-        <v>3114.49</v>
+        <v>2791.02</v>
       </c>
       <c r="O50" t="n">
-        <v>1252024.98</v>
+        <v>334922.4</v>
       </c>
       <c r="P50" t="n">
-        <v>5500</v>
+        <v>3900</v>
       </c>
       <c r="Q50" t="n">
-        <v>2211000</v>
+        <v>468000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>91042</v>
+        <v>91043</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>PELOTA PISCINA PRINCESAS 24 PCS</t>
+          <t>FLOTADOR PRINCESAS 56CM 24PCS</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2538,7 +2535,7 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>120</v>
+        <v>58</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
@@ -2547,28 +2544,28 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>120</v>
+        <v>58</v>
       </c>
       <c r="N51" t="n">
-        <v>2791.02</v>
+        <v>3564.14</v>
       </c>
       <c r="O51" t="n">
-        <v>334922.4</v>
+        <v>206720.12</v>
       </c>
       <c r="P51" t="n">
-        <v>3900</v>
+        <v>5500</v>
       </c>
       <c r="Q51" t="n">
-        <v>468000</v>
+        <v>319000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>91043</v>
+        <v>91098</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>FLOTADOR PRINCESAS 56CM 24PCS</t>
+          <t>BALON INFLABLE MICKEY 51CM</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2577,7 +2574,7 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>58</v>
+        <v>183</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
@@ -2586,28 +2583,28 @@
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>58</v>
+        <v>183</v>
       </c>
       <c r="N52" t="n">
-        <v>3564.14</v>
+        <v>4378</v>
       </c>
       <c r="O52" t="n">
-        <v>206720.12</v>
+        <v>801174</v>
       </c>
       <c r="P52" t="n">
-        <v>5500</v>
+        <v>3900</v>
       </c>
       <c r="Q52" t="n">
-        <v>319000</v>
+        <v>713700</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>91098</v>
+        <v>98002</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>BALON INFLABLE MICKEY 51CM</t>
+          <t>PELOTA PISCINA SIPDERMAN  51CM</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2616,7 +2613,7 @@
         </is>
       </c>
       <c r="J53" t="n">
-        <v>183</v>
+        <v>264</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
@@ -2625,28 +2622,28 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>183</v>
+        <v>264</v>
       </c>
       <c r="N53" t="n">
-        <v>4378</v>
+        <v>3340.6800784314</v>
       </c>
       <c r="O53" t="n">
-        <v>801174</v>
+        <v>881939.5407058896</v>
       </c>
       <c r="P53" t="n">
-        <v>3900</v>
+        <v>7100</v>
       </c>
       <c r="Q53" t="n">
-        <v>713700</v>
+        <v>1874400</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>98002</v>
+        <v>98003</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>PELOTA PISCINA SIPDERMAN  51CM</t>
+          <t>FLOTADOR SPIDER MAN 56CM 24 PCS</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2655,7 +2652,7 @@
         </is>
       </c>
       <c r="J54" t="n">
-        <v>264</v>
+        <v>67</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
@@ -2664,28 +2661,35 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>264</v>
+        <v>67</v>
       </c>
       <c r="N54" t="n">
-        <v>3340.6800775194</v>
+        <v>2903.52</v>
       </c>
       <c r="O54" t="n">
-        <v>881939.5404651216</v>
+        <v>194535.84</v>
       </c>
       <c r="P54" t="n">
         <v>7100</v>
       </c>
       <c r="Q54" t="n">
-        <v>1874400</v>
+        <v>475700</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="n">
-        <v>98003</v>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>C105</t>
+        </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>FLOTADOR SPIDER MAN 56CM 24 PCS</t>
+          <t>SCOOTER COLORES</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2694,7 +2698,7 @@
         </is>
       </c>
       <c r="J55" t="n">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
@@ -2703,30 +2707,30 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="N55" t="n">
-        <v>2903.52</v>
+        <v>39171.85</v>
       </c>
       <c r="O55" t="n">
-        <v>194535.84</v>
+        <v>705093.2999999999</v>
       </c>
       <c r="P55" t="n">
-        <v>7100</v>
+        <v>68900</v>
       </c>
       <c r="Q55" t="n">
-        <v>475700</v>
+        <v>1240200</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C1370</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>SCOOTER COLORES</t>
+          <t>LLAVERO PELUCHES STD C1370</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2736,11 +2740,11 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -2749,44 +2753,39 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="N56" t="n">
-        <v>39171.85</v>
+        <v>3472</v>
       </c>
       <c r="O56" t="n">
-        <v>705093.2999999999</v>
+        <v>868000</v>
       </c>
       <c r="P56" t="n">
-        <v>68900</v>
+        <v>4800</v>
       </c>
       <c r="Q56" t="n">
-        <v>1240200</v>
+        <v>1200000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>C1370</t>
+          <t>C1717</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>LLAVERO PELUCHES STD C1370</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>ESPADA CON LUZ Y SONIDO</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>250</v>
+        <v>432</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
@@ -2795,30 +2794,38 @@
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>250</v>
+        <v>432</v>
       </c>
       <c r="N57" t="n">
-        <v>3472</v>
+        <v>4443</v>
       </c>
       <c r="O57" t="n">
-        <v>868000</v>
+        <v>1919376</v>
       </c>
       <c r="P57" t="n">
-        <v>4800</v>
+        <v>6300</v>
       </c>
       <c r="Q57" t="n">
-        <v>1200000</v>
+        <v>2721600</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>C1717</t>
-        </is>
+          <t>C1758</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>6914919067549</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ESPADA CON LUZ Y SONIDO</t>
+          <t>MULA BLISTER SURTIDA</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -2827,7 +2834,7 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>432</v>
+        <v>180</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
@@ -2836,33 +2843,33 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>432</v>
+        <v>180</v>
       </c>
       <c r="N58" t="n">
-        <v>4443</v>
+        <v>4648.6</v>
       </c>
       <c r="O58" t="n">
-        <v>1919376</v>
+        <v>836748.0000000001</v>
       </c>
       <c r="P58" t="n">
-        <v>6300</v>
+        <v>8900</v>
       </c>
       <c r="Q58" t="n">
-        <v>2721600</v>
+        <v>1602000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>C1758</t>
+          <t>C1897</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>6914919067549</v>
+        <v>6914919086373</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MULA BLISTER SURTIDA</t>
+          <t>MULA DIDACTICA</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2876,7 +2883,7 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
@@ -2885,38 +2892,30 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="N59" t="n">
-        <v>4648.6</v>
+        <v>16897</v>
       </c>
       <c r="O59" t="n">
-        <v>836748.0000000001</v>
+        <v>2838696</v>
       </c>
       <c r="P59" t="n">
-        <v>8900</v>
+        <v>27900</v>
       </c>
       <c r="Q59" t="n">
-        <v>1602000</v>
+        <v>4687200</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>C1897</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>6914919086373</v>
+          <t>C2117</t>
+        </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MULA DIDACTICA</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>DISPLAY CARTÓN PEGAJOSOS X 20</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -2925,7 +2924,7 @@
         </is>
       </c>
       <c r="J60" t="n">
-        <v>168</v>
+        <v>1400</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
@@ -2934,30 +2933,38 @@
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>168</v>
+        <v>1400</v>
       </c>
       <c r="N60" t="n">
-        <v>16897</v>
+        <v>3751</v>
       </c>
       <c r="O60" t="n">
-        <v>2838696</v>
+        <v>5251400</v>
       </c>
       <c r="P60" t="n">
-        <v>27900</v>
+        <v>6400</v>
       </c>
       <c r="Q60" t="n">
-        <v>4687200</v>
+        <v>8960000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>C2117</t>
-        </is>
+          <t>C342</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>6914919018374</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>DISPLAY CARTÓN PEGAJOSOS X 20</t>
+          <t>COCINA CON VAPOR DE AGUA</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -2966,7 +2973,7 @@
         </is>
       </c>
       <c r="J61" t="n">
-        <v>1400</v>
+        <v>24</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
@@ -2975,38 +2982,30 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>1400</v>
+        <v>24</v>
       </c>
       <c r="N61" t="n">
-        <v>3751</v>
+        <v>24538.02</v>
       </c>
       <c r="O61" t="n">
-        <v>5251400</v>
+        <v>588912.48</v>
       </c>
       <c r="P61" t="n">
-        <v>6400</v>
+        <v>52900</v>
       </c>
       <c r="Q61" t="n">
-        <v>8960000</v>
+        <v>1269600</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>C342</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>6914919018374</v>
+          <t>C3455</t>
+        </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>COCINA CON VAPOR DE AGUA</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>DINOSAURIO BOLSA</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3015,7 +3014,7 @@
         </is>
       </c>
       <c r="J62" t="n">
-        <v>24</v>
+        <v>288</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
@@ -3024,30 +3023,35 @@
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>24</v>
+        <v>288</v>
       </c>
       <c r="N62" t="n">
-        <v>24538.02</v>
+        <v>5894.64</v>
       </c>
       <c r="O62" t="n">
-        <v>588912.48</v>
+        <v>1697656.32</v>
       </c>
       <c r="P62" t="n">
-        <v>52900</v>
+        <v>11000</v>
       </c>
       <c r="Q62" t="n">
-        <v>1269600</v>
+        <v>3168000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>C3455</t>
+          <t>C3638</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>DINOSAURIO BOLSA</t>
+          <t>INFLABLE DONA</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3056,7 +3060,7 @@
         </is>
       </c>
       <c r="J63" t="n">
-        <v>288</v>
+        <v>683</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
@@ -3065,30 +3069,30 @@
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>288</v>
+        <v>683</v>
       </c>
       <c r="N63" t="n">
-        <v>5894.64</v>
+        <v>3877.89</v>
       </c>
       <c r="O63" t="n">
-        <v>1697656.32</v>
+        <v>2648598.87</v>
       </c>
       <c r="P63" t="n">
-        <v>11000</v>
+        <v>6500</v>
       </c>
       <c r="Q63" t="n">
-        <v>3168000</v>
+        <v>4439500</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>C3638</t>
+          <t>C3700</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>INFLABLE DONA</t>
+          <t>MUNECA CON CARRO RECARGABLE DE CONTROL REMOTO</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3102,7 +3106,7 @@
         </is>
       </c>
       <c r="J64" t="n">
-        <v>683</v>
+        <v>6</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -3111,30 +3115,30 @@
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>683</v>
+        <v>6</v>
       </c>
       <c r="N64" t="n">
-        <v>3877.89</v>
+        <v>60174</v>
       </c>
       <c r="O64" t="n">
-        <v>2648598.87</v>
+        <v>361044</v>
       </c>
       <c r="P64" t="n">
-        <v>6500</v>
+        <v>96900</v>
       </c>
       <c r="Q64" t="n">
-        <v>4439500</v>
+        <v>581400</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>C3700</t>
+          <t>C3970</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MUNECA CON CARRO RECARGABLE DE CONTROL REMOTO</t>
+          <t>GUITARRAS C3970</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3144,11 +3148,11 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J65" t="n">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
@@ -3157,44 +3161,39 @@
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="N65" t="n">
-        <v>60174</v>
+        <v>26854</v>
       </c>
       <c r="O65" t="n">
-        <v>361044</v>
+        <v>1288992</v>
       </c>
       <c r="P65" t="n">
-        <v>96900</v>
+        <v>43900</v>
       </c>
       <c r="Q65" t="n">
-        <v>581400</v>
+        <v>2107200</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>C3970</t>
+          <t>C3988</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>GUITARRAS C3970</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>DRAGÓN CAMINA CON LUZ Y SONIDO</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J66" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>
@@ -3203,39 +3202,44 @@
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="N66" t="n">
-        <v>26854</v>
+        <v>29700</v>
       </c>
       <c r="O66" t="n">
-        <v>1288992</v>
+        <v>356400</v>
       </c>
       <c r="P66" t="n">
-        <v>43900</v>
+        <v>50500</v>
       </c>
       <c r="Q66" t="n">
-        <v>2107200</v>
+        <v>606000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>C3988</t>
+          <t>C4303</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>DRAGÓN CAMINA CON LUZ Y SONIDO</t>
+          <t>BEBE CON PIJAMA MED BOLSA PVC C4303</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J67" t="n">
-        <v>12</v>
+        <v>300</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
@@ -3244,30 +3248,30 @@
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>12</v>
+        <v>300</v>
       </c>
       <c r="N67" t="n">
-        <v>29700</v>
+        <v>18016</v>
       </c>
       <c r="O67" t="n">
-        <v>356400</v>
+        <v>5404800</v>
       </c>
       <c r="P67" t="n">
-        <v>50500</v>
+        <v>29900</v>
       </c>
       <c r="Q67" t="n">
-        <v>606000</v>
+        <v>8970000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>C4303</t>
+          <t>C4305</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>BEBE CON PIJAMA MED BOLSA PVC C4303</t>
+          <t>MUÑECA BEBE GRANDE CON PIJAMA EN BOLSA C4305</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3281,7 +3285,7 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>300</v>
+        <v>144</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
@@ -3290,30 +3294,30 @@
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>300</v>
+        <v>144</v>
       </c>
       <c r="N68" t="n">
-        <v>18016</v>
+        <v>25534</v>
       </c>
       <c r="O68" t="n">
-        <v>5404800</v>
+        <v>3676896</v>
       </c>
       <c r="P68" t="n">
-        <v>29900</v>
+        <v>40900</v>
       </c>
       <c r="Q68" t="n">
-        <v>8970000</v>
+        <v>5889600</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>C4305</t>
+          <t>C4310</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MUÑECA BEBE GRANDE CON PIJAMA EN BOLSA C4305</t>
+          <t>MUÑECA CON CARRO HUMO RECARGABLE C4310</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3327,7 +3331,7 @@
         </is>
       </c>
       <c r="J69" t="n">
-        <v>144</v>
+        <v>32</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
@@ -3336,30 +3340,30 @@
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>144</v>
+        <v>32</v>
       </c>
       <c r="N69" t="n">
-        <v>25534</v>
+        <v>72889</v>
       </c>
       <c r="O69" t="n">
-        <v>3676896</v>
+        <v>2332448</v>
       </c>
       <c r="P69" t="n">
-        <v>40900</v>
+        <v>117500</v>
       </c>
       <c r="Q69" t="n">
-        <v>5889600</v>
+        <v>3760000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>C4310</t>
+          <t>C4545</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MUÑECA CON CARRO HUMO RECARGABLE C4310</t>
+          <t>TAPETE PIANO PARA BEBE C4545</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3373,7 +3377,7 @@
         </is>
       </c>
       <c r="J70" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
@@ -3382,30 +3386,30 @@
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="N70" t="n">
-        <v>72889</v>
+        <v>27186</v>
       </c>
       <c r="O70" t="n">
-        <v>2332448</v>
+        <v>543720</v>
       </c>
       <c r="P70" t="n">
-        <v>117500</v>
+        <v>43900</v>
       </c>
       <c r="Q70" t="n">
-        <v>3760000</v>
+        <v>878000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>C4545</t>
+          <t>C4728</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>TAPETE PIANO PARA BEBE C4545</t>
+          <t>FLIOTADOR DONA DINOSAURIO #60 C4728</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3419,7 +3423,7 @@
         </is>
       </c>
       <c r="J71" t="n">
-        <v>20</v>
+        <v>2160</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
@@ -3428,44 +3432,47 @@
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>20</v>
+        <v>2160</v>
       </c>
       <c r="N71" t="n">
-        <v>27186</v>
+        <v>2454</v>
       </c>
       <c r="O71" t="n">
-        <v>543720</v>
+        <v>5300640</v>
       </c>
       <c r="P71" t="n">
-        <v>43900</v>
+        <v>4200</v>
       </c>
       <c r="Q71" t="n">
-        <v>878000</v>
+        <v>9072000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>C4728</t>
-        </is>
+          <t>C488</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>6554632300006</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>FLIOTADOR DONA DINOSAURIO #60 C4728</t>
+          <t>MALETA JUGUETES</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J72" t="n">
-        <v>2160</v>
+        <v>12</v>
       </c>
       <c r="K72" t="n">
         <v>0</v>
@@ -3474,47 +3481,47 @@
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>2160</v>
+        <v>12</v>
       </c>
       <c r="N72" t="n">
-        <v>2454</v>
+        <v>18491</v>
       </c>
       <c r="O72" t="n">
-        <v>5300640</v>
+        <v>221892</v>
       </c>
       <c r="P72" t="n">
-        <v>4200</v>
+        <v>13500</v>
       </c>
       <c r="Q72" t="n">
-        <v>9072000</v>
+        <v>162000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>C488</t>
+          <t>C5032</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>6554632300006</v>
+        <v>6999899236154</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MALETA JUGUETES</t>
+          <t>INFLABLE TECHITO PIECITOS  FIGURAS STD C5032</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>INFLABLES</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J73" t="n">
-        <v>12</v>
+        <v>937</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -3523,47 +3530,44 @@
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>12</v>
+        <v>937</v>
       </c>
       <c r="N73" t="n">
-        <v>18491</v>
+        <v>8945.379999999999</v>
       </c>
       <c r="O73" t="n">
-        <v>221892</v>
+        <v>8381821.06</v>
       </c>
       <c r="P73" t="n">
-        <v>13500</v>
+        <v>14900</v>
       </c>
       <c r="Q73" t="n">
-        <v>162000</v>
+        <v>13961300</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>C5032</t>
-        </is>
-      </c>
-      <c r="B74" t="n">
-        <v>6999899236154</v>
+          <t>C698</t>
+        </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>INFLABLE TECHITO PIECITOS  FIGURAS STD C5032</t>
+          <t>HELICE 9 LUCES</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>INFLABLES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J74" t="n">
-        <v>937</v>
+        <v>240</v>
       </c>
       <c r="K74" t="n">
         <v>0</v>
@@ -3572,44 +3576,44 @@
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>937</v>
+        <v>240</v>
       </c>
       <c r="N74" t="n">
-        <v>8945.379999999999</v>
+        <v>1567.02</v>
       </c>
       <c r="O74" t="n">
-        <v>8381821.06</v>
+        <v>376084.8</v>
       </c>
       <c r="P74" t="n">
-        <v>14900</v>
+        <v>2900</v>
       </c>
       <c r="Q74" t="n">
-        <v>13961300</v>
+        <v>696000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>C698</t>
+          <t>C7560</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>HELICE 9 LUCES</t>
+          <t>BARRA LUMINOSA 48CM C7560/211</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J75" t="n">
-        <v>240</v>
+        <v>10</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
@@ -3618,35 +3622,38 @@
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>240</v>
+        <v>10</v>
       </c>
       <c r="N75" t="n">
-        <v>1567.02</v>
+        <v>796.3099999999999</v>
       </c>
       <c r="O75" t="n">
-        <v>376084.8</v>
+        <v>7963.099999999999</v>
       </c>
       <c r="P75" t="n">
-        <v>2900</v>
+        <v>2500</v>
       </c>
       <c r="Q75" t="n">
-        <v>696000</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>C7560</t>
-        </is>
+          <t>C7610</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>6999899236093</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>BARRA LUMINOSA 48CM C7560/211</t>
+          <t>BOTE TIMON PISCINA 80X60 C7610</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>INFLABLES</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3655,7 +3662,7 @@
         </is>
       </c>
       <c r="J76" t="n">
-        <v>10</v>
+        <v>480</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
@@ -3664,67 +3671,18 @@
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>10</v>
+        <v>480</v>
       </c>
       <c r="N76" t="n">
-        <v>796.3099999999999</v>
+        <v>7811.9</v>
       </c>
       <c r="O76" t="n">
-        <v>7963.099999999999</v>
+        <v>3749712</v>
       </c>
       <c r="P76" t="n">
-        <v>2500</v>
+        <v>13900</v>
       </c>
       <c r="Q76" t="n">
-        <v>25000</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>C7610</t>
-        </is>
-      </c>
-      <c r="B77" t="n">
-        <v>6999899236093</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>BOTE TIMON PISCINA 80X60 C7610</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>INFLABLES</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J77" t="n">
-        <v>480</v>
-      </c>
-      <c r="K77" t="n">
-        <v>0</v>
-      </c>
-      <c r="L77" t="n">
-        <v>0</v>
-      </c>
-      <c r="M77" t="n">
-        <v>480</v>
-      </c>
-      <c r="N77" t="n">
-        <v>7811.9</v>
-      </c>
-      <c r="O77" t="n">
-        <v>3749712</v>
-      </c>
-      <c r="P77" t="n">
-        <v>13900</v>
-      </c>
-      <c r="Q77" t="n">
         <v>6672000</v>
       </c>
     </row>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-05</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-06</t>
         </is>
       </c>
     </row>
@@ -682,10 +682,10 @@
         <v>12</v>
       </c>
       <c r="N7" t="n">
-        <v>5758.9597797357</v>
+        <v>5784.4419026549</v>
       </c>
       <c r="O7" t="n">
-        <v>69107.51735682841</v>
+        <v>69413.3028318588</v>
       </c>
       <c r="P7" t="n">
         <v>16900</v>
@@ -1077,10 +1077,10 @@
         <v>29</v>
       </c>
       <c r="N16" t="n">
-        <v>1933.3875757576</v>
+        <v>1933.3879908676</v>
       </c>
       <c r="O16" t="n">
-        <v>56068.2396969704</v>
+        <v>56068.2517351604</v>
       </c>
       <c r="P16" t="n">
         <v>4500</v>
@@ -1319,10 +1319,10 @@
         <v>13</v>
       </c>
       <c r="N22" t="n">
-        <v>15403.520494505</v>
+        <v>15403.520852273</v>
       </c>
       <c r="O22" t="n">
-        <v>200245.766428565</v>
+        <v>200245.771079549</v>
       </c>
       <c r="P22" t="n">
         <v>33500</v>
@@ -1358,10 +1358,10 @@
         <v>21</v>
       </c>
       <c r="N23" t="n">
-        <v>3910.628317757</v>
+        <v>3910.628245614</v>
       </c>
       <c r="O23" t="n">
-        <v>82123.19467289699</v>
+        <v>82123.193157894</v>
       </c>
       <c r="P23" t="n">
         <v>9100</v>
@@ -1568,10 +1568,10 @@
         <v>36</v>
       </c>
       <c r="N28" t="n">
-        <v>15711.966317829</v>
+        <v>15834.716054688</v>
       </c>
       <c r="O28" t="n">
-        <v>565630.787441844</v>
+        <v>570049.777968768</v>
       </c>
       <c r="P28" t="n">
         <v>28500</v>
@@ -1973,10 +1973,10 @@
         <v>34</v>
       </c>
       <c r="N37" t="n">
-        <v>200072.19902098</v>
+        <v>200072.19914894</v>
       </c>
       <c r="O37" t="n">
-        <v>6802454.76671332</v>
+        <v>6802454.77106396</v>
       </c>
       <c r="P37" t="n">
         <v>312000</v>
@@ -2015,10 +2015,10 @@
         <v>16</v>
       </c>
       <c r="N38" t="n">
-        <v>174389.78625</v>
+        <v>174389.78666667</v>
       </c>
       <c r="O38" t="n">
-        <v>2790236.58</v>
+        <v>2790236.58666672</v>
       </c>
       <c r="P38" t="n">
         <v>368200</v>
@@ -2062,10 +2062,10 @@
         <v>6</v>
       </c>
       <c r="N39" t="n">
-        <v>251809.29411765</v>
+        <v>251809.29393939</v>
       </c>
       <c r="O39" t="n">
-        <v>1510855.7647059</v>
+        <v>1510855.76363634</v>
       </c>
       <c r="P39" t="n">
         <v>584000</v>
@@ -2389,10 +2389,10 @@
         <v>24</v>
       </c>
       <c r="N47" t="n">
-        <v>4878.2852688172</v>
+        <v>4878.2859036145</v>
       </c>
       <c r="O47" t="n">
-        <v>117078.8464516128</v>
+        <v>117078.861686748</v>
       </c>
       <c r="P47" t="n">
         <v>13500</v>
@@ -2430,10 +2430,10 @@
         <v>12</v>
       </c>
       <c r="N48" t="n">
-        <v>7394.9353846154</v>
+        <v>7477.1013333333</v>
       </c>
       <c r="O48" t="n">
-        <v>88739.2246153848</v>
+        <v>89725.21599999961</v>
       </c>
       <c r="P48" t="n">
         <v>17900</v>
@@ -2625,10 +2625,10 @@
         <v>264</v>
       </c>
       <c r="N53" t="n">
-        <v>3340.6800784314</v>
+        <v>3340.6800808081</v>
       </c>
       <c r="O53" t="n">
-        <v>881939.5407058896</v>
+        <v>881939.5413333384</v>
       </c>
       <c r="P53" t="n">
         <v>7100</v>
@@ -3060,7 +3060,7 @@
         </is>
       </c>
       <c r="J63" t="n">
-        <v>683</v>
+        <v>443</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
@@ -3069,19 +3069,19 @@
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>683</v>
+        <v>443</v>
       </c>
       <c r="N63" t="n">
         <v>3877.89</v>
       </c>
       <c r="O63" t="n">
-        <v>2648598.87</v>
+        <v>1717905.27</v>
       </c>
       <c r="P63" t="n">
         <v>6500</v>
       </c>
       <c r="Q63" t="n">
-        <v>4439500</v>
+        <v>2879500</v>
       </c>
     </row>
     <row r="64">
@@ -3164,10 +3164,10 @@
         <v>48</v>
       </c>
       <c r="N65" t="n">
-        <v>26854</v>
+        <v>27226.972222222</v>
       </c>
       <c r="O65" t="n">
-        <v>1288992</v>
+        <v>1306894.666666656</v>
       </c>
       <c r="P65" t="n">
         <v>43900</v>
@@ -3389,10 +3389,10 @@
         <v>20</v>
       </c>
       <c r="N70" t="n">
-        <v>27186</v>
+        <v>27422.4</v>
       </c>
       <c r="O70" t="n">
-        <v>543720</v>
+        <v>548448</v>
       </c>
       <c r="P70" t="n">
         <v>43900</v>
@@ -3423,7 +3423,7 @@
         </is>
       </c>
       <c r="J71" t="n">
-        <v>2160</v>
+        <v>1800</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
@@ -3432,19 +3432,19 @@
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>2160</v>
+        <v>1800</v>
       </c>
       <c r="N71" t="n">
         <v>2454</v>
       </c>
       <c r="O71" t="n">
-        <v>5300640</v>
+        <v>4417200</v>
       </c>
       <c r="P71" t="n">
         <v>4200</v>
       </c>
       <c r="Q71" t="n">
-        <v>9072000</v>
+        <v>7560000</v>
       </c>
     </row>
     <row r="72">

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -682,10 +682,10 @@
         <v>12</v>
       </c>
       <c r="N7" t="n">
-        <v>5784.4419026549</v>
+        <v>5758.9597787611</v>
       </c>
       <c r="O7" t="n">
-        <v>69413.3028318588</v>
+        <v>69107.51734513321</v>
       </c>
       <c r="P7" t="n">
         <v>16900</v>
@@ -1568,10 +1568,10 @@
         <v>36</v>
       </c>
       <c r="N28" t="n">
-        <v>15834.716054688</v>
+        <v>15711.966289063</v>
       </c>
       <c r="O28" t="n">
-        <v>570049.777968768</v>
+        <v>565630.786406268</v>
       </c>
       <c r="P28" t="n">
         <v>28500</v>
@@ -2430,10 +2430,10 @@
         <v>12</v>
       </c>
       <c r="N48" t="n">
-        <v>7477.1013333333</v>
+        <v>7394.9354444444</v>
       </c>
       <c r="O48" t="n">
-        <v>89725.21599999961</v>
+        <v>88739.2253333328</v>
       </c>
       <c r="P48" t="n">
         <v>17900</v>
@@ -3164,10 +3164,10 @@
         <v>48</v>
       </c>
       <c r="N65" t="n">
-        <v>27226.972222222</v>
+        <v>26854</v>
       </c>
       <c r="O65" t="n">
-        <v>1306894.666666656</v>
+        <v>1288992</v>
       </c>
       <c r="P65" t="n">
         <v>43900</v>
@@ -3389,10 +3389,10 @@
         <v>20</v>
       </c>
       <c r="N70" t="n">
-        <v>27422.4</v>
+        <v>27186</v>
       </c>
       <c r="O70" t="n">
-        <v>548448</v>
+        <v>543720</v>
       </c>
       <c r="P70" t="n">
         <v>43900</v>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-06</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-07</t>
         </is>
       </c>
     </row>
@@ -557,10 +557,10 @@
         <v>12</v>
       </c>
       <c r="N4" t="n">
-        <v>96741.40695121999</v>
+        <v>96741.407037037</v>
       </c>
       <c r="O4" t="n">
-        <v>1160896.88341464</v>
+        <v>1160896.884444444</v>
       </c>
       <c r="P4" t="n">
         <v>188900</v>
@@ -1155,10 +1155,10 @@
         <v>324</v>
       </c>
       <c r="N18" t="n">
-        <v>3926.8371340839</v>
+        <v>3926.8371326165</v>
       </c>
       <c r="O18" t="n">
-        <v>1272295.231443183</v>
+        <v>1272295.230967746</v>
       </c>
       <c r="P18" t="n">
         <v>4800</v>
@@ -1319,10 +1319,10 @@
         <v>13</v>
       </c>
       <c r="N22" t="n">
-        <v>15403.520852273</v>
+        <v>15403.520914286</v>
       </c>
       <c r="O22" t="n">
-        <v>200245.771079549</v>
+        <v>200245.771885718</v>
       </c>
       <c r="P22" t="n">
         <v>33500</v>
@@ -1526,10 +1526,10 @@
         <v>16</v>
       </c>
       <c r="N27" t="n">
-        <v>16486.41027027</v>
+        <v>16486.410204082</v>
       </c>
       <c r="O27" t="n">
-        <v>263782.56432432</v>
+        <v>263782.563265312</v>
       </c>
       <c r="P27" t="n">
         <v>30500</v>
@@ -1568,10 +1568,10 @@
         <v>36</v>
       </c>
       <c r="N28" t="n">
-        <v>15711.966289063</v>
+        <v>15711.966215139</v>
       </c>
       <c r="O28" t="n">
-        <v>565630.786406268</v>
+        <v>565630.783745004</v>
       </c>
       <c r="P28" t="n">
         <v>28500</v>
@@ -1701,10 +1701,10 @@
         <v>4</v>
       </c>
       <c r="N31" t="n">
-        <v>22267.551785714</v>
+        <v>22267.552</v>
       </c>
       <c r="O31" t="n">
-        <v>89070.207142856</v>
+        <v>89070.208</v>
       </c>
       <c r="P31" t="n">
         <v>46300</v>
@@ -1931,10 +1931,10 @@
         <v>56</v>
       </c>
       <c r="N36" t="n">
-        <v>141416.8844586</v>
+        <v>141416.88447284</v>
       </c>
       <c r="O36" t="n">
-        <v>7919345.5296816</v>
+        <v>7919345.53047904</v>
       </c>
       <c r="P36" t="n">
         <v>251900</v>
@@ -2015,10 +2015,10 @@
         <v>16</v>
       </c>
       <c r="N38" t="n">
-        <v>174389.78666667</v>
+        <v>174389.78756757</v>
       </c>
       <c r="O38" t="n">
-        <v>2790236.58666672</v>
+        <v>2790236.60108112</v>
       </c>
       <c r="P38" t="n">
         <v>368200</v>
@@ -2109,10 +2109,10 @@
         <v>6</v>
       </c>
       <c r="N40" t="n">
-        <v>344599.17885246</v>
+        <v>344599.17881356</v>
       </c>
       <c r="O40" t="n">
-        <v>2067595.07311476</v>
+        <v>2067595.07288136</v>
       </c>
       <c r="P40" t="n">
         <v>532900</v>
@@ -2304,10 +2304,10 @@
         <v>340</v>
       </c>
       <c r="N45" t="n">
-        <v>3865.67</v>
+        <v>3872.3234767642</v>
       </c>
       <c r="O45" t="n">
-        <v>1314327.8</v>
+        <v>1316589.982099828</v>
       </c>
       <c r="P45" t="n">
         <v>5500</v>
@@ -2469,10 +2469,10 @@
         <v>402</v>
       </c>
       <c r="N49" t="n">
-        <v>3114.49</v>
+        <v>3126.0967950311</v>
       </c>
       <c r="O49" t="n">
-        <v>1252024.98</v>
+        <v>1256690.911602502</v>
       </c>
       <c r="P49" t="n">
         <v>5500</v>
@@ -2586,10 +2586,10 @@
         <v>183</v>
       </c>
       <c r="N52" t="n">
-        <v>4378</v>
+        <v>4411.4198473282</v>
       </c>
       <c r="O52" t="n">
-        <v>801174</v>
+        <v>807289.8320610607</v>
       </c>
       <c r="P52" t="n">
         <v>3900</v>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -2304,10 +2304,10 @@
         <v>340</v>
       </c>
       <c r="N45" t="n">
-        <v>3872.3234767642</v>
+        <v>3865.67</v>
       </c>
       <c r="O45" t="n">
-        <v>1316589.982099828</v>
+        <v>1314327.8</v>
       </c>
       <c r="P45" t="n">
         <v>5500</v>
@@ -2469,10 +2469,10 @@
         <v>402</v>
       </c>
       <c r="N49" t="n">
-        <v>3126.0967950311</v>
+        <v>3114.49</v>
       </c>
       <c r="O49" t="n">
-        <v>1256690.911602502</v>
+        <v>1252024.98</v>
       </c>
       <c r="P49" t="n">
         <v>5500</v>
@@ -2586,10 +2586,10 @@
         <v>183</v>
       </c>
       <c r="N52" t="n">
-        <v>4411.4198473282</v>
+        <v>4378</v>
       </c>
       <c r="O52" t="n">
-        <v>807289.8320610607</v>
+        <v>801174</v>
       </c>
       <c r="P52" t="n">
         <v>3900</v>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-07</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-08</t>
         </is>
       </c>
     </row>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q76"/>
+  <dimension ref="A1:Q77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -551,22 +551,22 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="N4" t="n">
-        <v>96741.407037037</v>
+        <v>96741.407125</v>
       </c>
       <c r="O4" t="n">
-        <v>1160896.884444444</v>
+        <v>773931.257</v>
       </c>
       <c r="P4" t="n">
         <v>188900</v>
       </c>
       <c r="Q4" t="n">
-        <v>2266800</v>
+        <v>1511200</v>
       </c>
     </row>
     <row r="5">
@@ -604,10 +604,10 @@
         <v>2</v>
       </c>
       <c r="N5" t="n">
-        <v>74676.654222222</v>
+        <v>74676.65386363601</v>
       </c>
       <c r="O5" t="n">
-        <v>149353.308444444</v>
+        <v>149353.307727272</v>
       </c>
       <c r="P5" t="n">
         <v>144900</v>
@@ -763,10 +763,10 @@
         <v>24</v>
       </c>
       <c r="N9" t="n">
-        <v>20826.676136364</v>
+        <v>20826.676585366</v>
       </c>
       <c r="O9" t="n">
-        <v>499840.227272736</v>
+        <v>499840.238048784</v>
       </c>
       <c r="P9" t="n">
         <v>39100</v>
@@ -1155,10 +1155,10 @@
         <v>324</v>
       </c>
       <c r="N18" t="n">
-        <v>3926.8371326165</v>
+        <v>3926.8371296771</v>
       </c>
       <c r="O18" t="n">
-        <v>1272295.230967746</v>
+        <v>1272295.230015381</v>
       </c>
       <c r="P18" t="n">
         <v>4800</v>
@@ -1255,11 +1255,11 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>36405</v>
+        <v>36013</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>FLOTADOR ARO ANIMALES BESTWAY 36PCS</t>
+          <t>FLOTADOR ARO 56CM BESTWAY 36 PCS</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1268,37 +1268,37 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>792</v>
+        <v>118</v>
       </c>
       <c r="N21" t="n">
-        <v>2681</v>
+        <v>2413.0010330579</v>
       </c>
       <c r="O21" t="n">
-        <v>2123352</v>
+        <v>284734.1219008322</v>
       </c>
       <c r="P21" t="n">
-        <v>3500</v>
+        <v>4700</v>
       </c>
       <c r="Q21" t="n">
-        <v>2772000</v>
+        <v>554600</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>41037</v>
+        <v>36405</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>41037 FLOTADOR BALLENA BESTWAY 12PCS</t>
+          <t>FLOTADOR ARO ANIMALES BESTWAY 36PCS</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>13</v>
+        <v>792</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1316,28 +1316,28 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>13</v>
+        <v>792</v>
       </c>
       <c r="N22" t="n">
-        <v>15403.520914286</v>
+        <v>2681</v>
       </c>
       <c r="O22" t="n">
-        <v>200245.771885718</v>
+        <v>2123352</v>
       </c>
       <c r="P22" t="n">
-        <v>33500</v>
+        <v>3500</v>
       </c>
       <c r="Q22" t="n">
-        <v>435500</v>
+        <v>2772000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>44007</v>
+        <v>41037</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>COLCHONETA INFLABLE 69CM BESTWAY</t>
+          <t>41037 FLOTADOR BALLENA BESTWAY 12PCS</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1346,7 +1346,7 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -1355,31 +1355,28 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="N23" t="n">
-        <v>3910.628245614</v>
+        <v>15403.520914286</v>
       </c>
       <c r="O23" t="n">
-        <v>82123.193157894</v>
+        <v>200245.771885718</v>
       </c>
       <c r="P23" t="n">
-        <v>9100</v>
+        <v>33500</v>
       </c>
       <c r="Q23" t="n">
-        <v>191100</v>
+        <v>435500</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>51004</v>
-      </c>
-      <c r="B24" t="n">
-        <v>6941607363478</v>
+        <v>44007</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>51004 PISCINA DEEP DIVE</t>
+          <t>COLCHONETA INFLABLE 69CM BESTWAY</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1388,7 +1385,7 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -1397,31 +1394,31 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="N24" t="n">
-        <v>21338.01</v>
+        <v>3910.628245614</v>
       </c>
       <c r="O24" t="n">
-        <v>21338.01</v>
+        <v>82123.193157894</v>
       </c>
       <c r="P24" t="n">
-        <v>37100</v>
+        <v>9100</v>
       </c>
       <c r="Q24" t="n">
-        <v>37100</v>
+        <v>191100</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>51005</v>
+        <v>51004</v>
       </c>
       <c r="B25" t="n">
-        <v>6941607363485</v>
+        <v>6941607363478</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>51005 PISCINA DEEP DIVE</t>
+          <t>51004 PISCINA DEEP DIVE</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1430,40 +1427,40 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>30708.904814815</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>61417.80962963</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>53500</v>
+        <v>37100</v>
       </c>
       <c r="Q25" t="n">
-        <v>107000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>51008</v>
+        <v>51005</v>
       </c>
       <c r="B26" t="n">
-        <v>6941607367575</v>
+        <v>6941607363485</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>PISCINA CORAL 102 X25CM</t>
+          <t>51005 PISCINA DEEP DIVE</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1472,7 +1469,7 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -1481,31 +1478,31 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="N26" t="n">
-        <v>12837.964861111</v>
+        <v>30708.894545455</v>
       </c>
       <c r="O26" t="n">
-        <v>154055.578333332</v>
+        <v>61417.78909091</v>
       </c>
       <c r="P26" t="n">
-        <v>22900</v>
+        <v>53500</v>
       </c>
       <c r="Q26" t="n">
-        <v>274800</v>
+        <v>107000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>51104</v>
+        <v>51008</v>
       </c>
       <c r="B27" t="n">
-        <v>6942138915815</v>
+        <v>6941607367575</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>PISCINA VERANO 102 X25 CM</t>
+          <t>PISCINA CORAL 102 X25CM</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1514,7 +1511,7 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -1523,31 +1520,31 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="N27" t="n">
-        <v>16486.410204082</v>
+        <v>12837.964861111</v>
       </c>
       <c r="O27" t="n">
-        <v>263782.563265312</v>
+        <v>154055.578333332</v>
       </c>
       <c r="P27" t="n">
-        <v>30500</v>
+        <v>22900</v>
       </c>
       <c r="Q27" t="n">
-        <v>488000</v>
+        <v>274800</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>51124</v>
+        <v>51104</v>
       </c>
       <c r="B28" t="n">
-        <v>6941607325032</v>
+        <v>6942138915815</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>51124 COMBO DE PISCINA Y BALON</t>
+          <t>PISCINA VERANO 102 X25 CM</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1556,54 +1553,49 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M28" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="N28" t="n">
-        <v>15711.966215139</v>
+        <v>16486.410204082</v>
       </c>
       <c r="O28" t="n">
-        <v>565630.783745004</v>
+        <v>164864.10204082</v>
       </c>
       <c r="P28" t="n">
-        <v>28500</v>
+        <v>30500</v>
       </c>
       <c r="Q28" t="n">
-        <v>1026000</v>
+        <v>305000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>51203</v>
+        <v>51124</v>
       </c>
       <c r="B29" t="n">
-        <v>6941607325544</v>
+        <v>6941607325032</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>51203 PISCINA 3 AROS BESTWAY Φ1.68m x H38cm</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>51124 COMBO DE PISCINA Y BALON</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -1612,37 +1604,45 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="N29" t="n">
-        <v>30238.812278481</v>
+        <v>15711.9662</v>
       </c>
       <c r="O29" t="n">
-        <v>302388.12278481</v>
+        <v>565630.7832000001</v>
       </c>
       <c r="P29" t="n">
-        <v>51100</v>
+        <v>28500</v>
       </c>
       <c r="Q29" t="n">
-        <v>511000</v>
+        <v>1026000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>52331</v>
+        <v>51203</v>
+      </c>
+      <c r="B30" t="n">
+        <v>6941607325544</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>PISCINA CANOPY FRUTICAS 8 PCS</t>
+          <t>51203 PISCINA 3 AROS BESTWAY Φ1.68m x H38cm</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -1651,36 +1651,28 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="N30" t="n">
-        <v>20195.32</v>
+        <v>30238.812307692</v>
       </c>
       <c r="O30" t="n">
-        <v>1514649</v>
+        <v>302388.12307692</v>
       </c>
       <c r="P30" t="n">
-        <v>45900</v>
+        <v>51100</v>
       </c>
       <c r="Q30" t="n">
-        <v>3442500</v>
+        <v>511000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>52637</v>
-      </c>
-      <c r="B31" t="n">
-        <v>6941607352212</v>
+        <v>52331</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>52637 PISCINA TECHADA SUNNY BESTWAY</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>PISCINA CANOPY FRUTICAS 8 PCS</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1689,7 +1681,7 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>4</v>
+        <v>75</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -1698,31 +1690,31 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>4</v>
+        <v>75</v>
       </c>
       <c r="N31" t="n">
-        <v>22267.552</v>
+        <v>20195.32</v>
       </c>
       <c r="O31" t="n">
-        <v>89070.208</v>
+        <v>1514649</v>
       </c>
       <c r="P31" t="n">
-        <v>46300</v>
+        <v>45900</v>
       </c>
       <c r="Q31" t="n">
-        <v>185200</v>
+        <v>3442500</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>53157</v>
+        <v>52637</v>
       </c>
       <c r="B32" t="n">
-        <v>6941607352137</v>
+        <v>6941607352212</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>53157 PISCINA FUENTE SHARK BESTWAY</t>
+          <t>52637 PISCINA TECHADA SUNNY BESTWAY</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1748,28 +1740,33 @@
         <v>4</v>
       </c>
       <c r="N32" t="n">
-        <v>36574.852142857</v>
+        <v>22267.552083333</v>
       </c>
       <c r="O32" t="n">
-        <v>146299.408571428</v>
+        <v>89070.208333332</v>
       </c>
       <c r="P32" t="n">
-        <v>65900</v>
+        <v>46300</v>
       </c>
       <c r="Q32" t="n">
-        <v>263600</v>
+        <v>185200</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>54150</v>
+        <v>53157</v>
       </c>
       <c r="B33" t="n">
-        <v>6942138968279</v>
+        <v>6941607352137</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>54150 Piscina familiar rectangular</t>
+          <t>53157 PISCINA FUENTE SHARK BESTWAY</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1790,33 +1787,28 @@
         <v>4</v>
       </c>
       <c r="N33" t="n">
-        <v>80027.73</v>
+        <v>36574.852142857</v>
       </c>
       <c r="O33" t="n">
-        <v>320110.92</v>
+        <v>146299.408571428</v>
       </c>
       <c r="P33" t="n">
-        <v>129900</v>
+        <v>65900</v>
       </c>
       <c r="Q33" t="n">
-        <v>519600</v>
+        <v>263600</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>54370</v>
+        <v>54150</v>
       </c>
       <c r="B34" t="n">
-        <v>6941607312643</v>
+        <v>6942138968279</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>PISCINA CAPITAN 213 X155 X 132CM</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>54150 Piscina familiar rectangular</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1831,34 +1823,34 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>103298.75</v>
+        <v>80027.73</v>
       </c>
       <c r="O34" t="n">
-        <v>413195</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>178900</v>
+        <v>129900</v>
       </c>
       <c r="Q34" t="n">
-        <v>715600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>55031</v>
+        <v>54370</v>
       </c>
       <c r="B35" t="n">
-        <v>6942138913781</v>
+        <v>6941607312643</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>55031 PISCINA DELFIN 2.44mx46cm</t>
+          <t>PISCINA CAPITAN 213 X155 X 132CM</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1872,7 +1864,7 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -1881,31 +1873,31 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N35" t="n">
-        <v>56906.800422535</v>
+        <v>103298.75</v>
       </c>
       <c r="O35" t="n">
-        <v>56906.800422535</v>
+        <v>413195</v>
       </c>
       <c r="P35" t="n">
-        <v>95900</v>
+        <v>178900</v>
       </c>
       <c r="Q35" t="n">
-        <v>95900</v>
+        <v>715600</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>56401</v>
+        <v>55031</v>
       </c>
       <c r="B36" t="n">
-        <v>6941607327951</v>
+        <v>6942138913781</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>56401 PISCINA ESTRUCTURAL RECTANGULAR BESTWAY</t>
+          <t>55031 PISCINA DELFIN 2.44mx46cm</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1919,7 +1911,7 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -1928,40 +1920,45 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="N36" t="n">
-        <v>141416.88447284</v>
+        <v>56906.800571429</v>
       </c>
       <c r="O36" t="n">
-        <v>7919345.53047904</v>
+        <v>56906.800571429</v>
       </c>
       <c r="P36" t="n">
-        <v>251900</v>
+        <v>95900</v>
       </c>
       <c r="Q36" t="n">
-        <v>14106400</v>
+        <v>95900</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>56403</v>
+        <v>56401</v>
       </c>
       <c r="B37" t="n">
-        <v>6941607327982</v>
+        <v>6941607327951</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>PISCINA ESTRUCTURAL 2.59m x 1.70m x 61cm BESTWAY</t>
+          <t>56401 PISCINA ESTRUCTURAL RECTANGULAR BESTWAY</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -1970,40 +1967,40 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="N37" t="n">
-        <v>200072.19914894</v>
+        <v>141416.88453074</v>
       </c>
       <c r="O37" t="n">
-        <v>6802454.77106396</v>
+        <v>7919345.53372144</v>
       </c>
       <c r="P37" t="n">
-        <v>312000</v>
+        <v>251900</v>
       </c>
       <c r="Q37" t="n">
-        <v>10608000</v>
+        <v>14106400</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>56404</v>
+        <v>56403</v>
       </c>
       <c r="B38" t="n">
-        <v>6941607327999</v>
+        <v>6941607327982</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>56404 PISCINA ESTRUCTURAL RECTANGULAR BESTWAY</t>
+          <t>PISCINA ESTRUCTURAL 2.59m x 1.70m x 61cm BESTWAY</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -2012,45 +2009,40 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="N38" t="n">
-        <v>174389.78756757</v>
+        <v>200072.19914894</v>
       </c>
       <c r="O38" t="n">
-        <v>2790236.60108112</v>
+        <v>6802454.77106396</v>
       </c>
       <c r="P38" t="n">
-        <v>368200</v>
+        <v>312000</v>
       </c>
       <c r="Q38" t="n">
-        <v>5891200</v>
+        <v>10608000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>56405</v>
+        <v>56404</v>
       </c>
       <c r="B39" t="n">
-        <v>6941607328002</v>
+        <v>6941607327999</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>PISCINA ESTRUCTURAL RECTAGULAR BESTWAY 4.00mX2.11mX81cm</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>56404 PISCINA ESTRUCTURAL RECTANGULAR BESTWAY</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -2059,31 +2051,31 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="N39" t="n">
-        <v>251809.29393939</v>
+        <v>174389.78756757</v>
       </c>
       <c r="O39" t="n">
-        <v>1510855.76363634</v>
+        <v>2790236.60108112</v>
       </c>
       <c r="P39" t="n">
-        <v>584000</v>
+        <v>368200</v>
       </c>
       <c r="Q39" t="n">
-        <v>3504000</v>
+        <v>5891200</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>56417</v>
+        <v>56405</v>
       </c>
       <c r="B40" t="n">
-        <v>6942138981902</v>
+        <v>6941607328002</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Piscina Estructural Redonda 366 x 76 cm Bomba/Filtro 56417</t>
+          <t>PISCINA ESTRUCTURAL RECTAGULAR BESTWAY 4.00mX2.11mX81cm</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2109,30 +2101,38 @@
         <v>6</v>
       </c>
       <c r="N40" t="n">
-        <v>344599.17881356</v>
+        <v>251809.29393939</v>
       </c>
       <c r="O40" t="n">
-        <v>2067595.07288136</v>
+        <v>1510855.76363634</v>
       </c>
       <c r="P40" t="n">
-        <v>532900</v>
+        <v>584000</v>
       </c>
       <c r="Q40" t="n">
-        <v>3197400</v>
+        <v>3504000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>62068</v>
+        <v>56417</v>
+      </c>
+      <c r="B41" t="n">
+        <v>6942138981902</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>PARCHE PISCINA EXTERIOR BESTWAY</t>
+          <t>Piscina Estructural Redonda 366 x 76 cm Bomba/Filtro 56417</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J41" t="n">
@@ -2148,25 +2148,25 @@
         <v>6</v>
       </c>
       <c r="N41" t="n">
-        <v>1977.88</v>
+        <v>344599.1787931</v>
       </c>
       <c r="O41" t="n">
-        <v>11867.28</v>
+        <v>2067595.0727586</v>
       </c>
       <c r="P41" t="n">
-        <v>2900</v>
+        <v>532900</v>
       </c>
       <c r="Q41" t="n">
-        <v>17400</v>
+        <v>3197400</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>62091</v>
+        <v>62068</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>PARCHE PISCINA A PRUEBA DE AGUA BESTWAY</t>
+          <t>PARCHE PISCINA EXTERIOR BESTWAY</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>217</v>
+        <v>6</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -2184,28 +2184,28 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>217</v>
+        <v>6</v>
       </c>
       <c r="N42" t="n">
-        <v>1141.57</v>
+        <v>1977.88</v>
       </c>
       <c r="O42" t="n">
-        <v>247720.69</v>
+        <v>11867.28</v>
       </c>
       <c r="P42" t="n">
-        <v>3900</v>
+        <v>2900</v>
       </c>
       <c r="Q42" t="n">
-        <v>846300</v>
+        <v>17400</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>67001</v>
+        <v>62091</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>COLCHON INFLABLE SENCILLO BESTWAY 1.88 X 99 CM</t>
+          <t>PARCHE PISCINA A PRUEBA DE AGUA BESTWAY</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2214,7 +2214,7 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>3</v>
+        <v>217</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -2223,28 +2223,28 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3</v>
+        <v>217</v>
       </c>
       <c r="N43" t="n">
-        <v>26280.41</v>
+        <v>1141.57</v>
       </c>
       <c r="O43" t="n">
-        <v>78841.23</v>
+        <v>247720.69</v>
       </c>
       <c r="P43" t="n">
-        <v>46500</v>
+        <v>3900</v>
       </c>
       <c r="Q43" t="n">
-        <v>139500</v>
+        <v>846300</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>67374</v>
+        <v>67001</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>COLCHON INFLABLE DOBLE+ALMOHADAS BESTWAY 2.03mx1.52mx22cm</t>
+          <t>COLCHON INFLABLE SENCILLO BESTWAY 1.88 X 99 CM</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2253,7 +2253,7 @@
         </is>
       </c>
       <c r="J44" t="n">
-        <v>67</v>
+        <v>3</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -2262,28 +2262,28 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>67</v>
+        <v>3</v>
       </c>
       <c r="N44" t="n">
-        <v>61666.873842239</v>
+        <v>26280.41</v>
       </c>
       <c r="O44" t="n">
-        <v>4131680.547430013</v>
+        <v>78841.23</v>
       </c>
       <c r="P44" t="n">
-        <v>98900</v>
+        <v>46500</v>
       </c>
       <c r="Q44" t="n">
-        <v>6626300</v>
+        <v>139500</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>91004</v>
+        <v>67374</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>FLOTADOR DISNEY 56CM 24PCS</t>
+          <t>COLCHON INFLABLE DOBLE+ALMOHADAS BESTWAY 2.03mx1.52mx22cm</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2292,7 +2292,7 @@
         </is>
       </c>
       <c r="J45" t="n">
-        <v>340</v>
+        <v>67</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -2301,74 +2301,67 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>340</v>
+        <v>67</v>
       </c>
       <c r="N45" t="n">
-        <v>3865.67</v>
+        <v>61666.873852041</v>
       </c>
       <c r="O45" t="n">
-        <v>1314327.8</v>
+        <v>4131680.548086747</v>
       </c>
       <c r="P45" t="n">
-        <v>5500</v>
+        <v>98900</v>
       </c>
       <c r="Q45" t="n">
-        <v>1870000</v>
+        <v>6626300</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
+        <v>91004</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>FLOTADOR DISNEY 56CM 24PCS</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>und</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>340</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>340</v>
+      </c>
+      <c r="N46" t="n">
+        <v>3865.67</v>
+      </c>
+      <c r="O46" t="n">
+        <v>1314327.8</v>
+      </c>
+      <c r="P46" t="n">
+        <v>5500</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>1870000</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
         <v>91007</v>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>PISCINA DISNEY 122X25CM 12 PCS</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>und</t>
-        </is>
-      </c>
-      <c r="J46" t="n">
-        <v>24</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>24</v>
-      </c>
-      <c r="N46" t="n">
-        <v>16010.3</v>
-      </c>
-      <c r="O46" t="n">
-        <v>384247.2</v>
-      </c>
-      <c r="P46" t="n">
-        <v>30500</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>732000</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>9103C</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>9103C GAFA ACUATICA SIRENITA BESTWAY</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2389,105 +2382,112 @@
         <v>24</v>
       </c>
       <c r="N47" t="n">
-        <v>4878.2859036145</v>
+        <v>16010.3</v>
       </c>
       <c r="O47" t="n">
-        <v>117078.861686748</v>
+        <v>384247.2</v>
       </c>
       <c r="P47" t="n">
-        <v>13500</v>
+        <v>30500</v>
       </c>
       <c r="Q47" t="n">
-        <v>324000</v>
+        <v>732000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>9103C</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>9103C GAFA ACUATICA SIRENITA BESTWAY</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>und</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>24</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>24</v>
+      </c>
+      <c r="N48" t="n">
+        <v>4878.2859036145</v>
+      </c>
+      <c r="O48" t="n">
+        <v>117078.861686748</v>
+      </c>
+      <c r="P48" t="n">
+        <v>13500</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>324000</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
           <t>9103D</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>9103D CARETA ACUATICA SIRENITA BESTWAY</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>und</t>
-        </is>
-      </c>
-      <c r="J48" t="n">
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>und</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
         <v>12</v>
       </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" t="n">
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
         <v>12</v>
       </c>
-      <c r="N48" t="n">
+      <c r="N49" t="n">
         <v>7394.9354444444</v>
       </c>
-      <c r="O48" t="n">
+      <c r="O49" t="n">
         <v>88739.2253333328</v>
       </c>
-      <c r="P48" t="n">
+      <c r="P49" t="n">
         <v>17900</v>
       </c>
-      <c r="Q48" t="n">
+      <c r="Q49" t="n">
         <v>214800</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>91040</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>FLOTADOR MINNIE 56CM 24 PCS</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>und</t>
-        </is>
-      </c>
-      <c r="J49" t="n">
-        <v>402</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" t="n">
-        <v>402</v>
-      </c>
-      <c r="N49" t="n">
-        <v>3114.49</v>
-      </c>
-      <c r="O49" t="n">
-        <v>1252024.98</v>
-      </c>
-      <c r="P49" t="n">
-        <v>5500</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>2211000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>91042</v>
+        <v>91040</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>PELOTA PISCINA PRINCESAS 24 PCS</t>
+          <t>FLOTADOR MINNIE 56CM 24 PCS</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2496,7 +2496,7 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>120</v>
+        <v>402</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -2505,28 +2505,28 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>120</v>
+        <v>402</v>
       </c>
       <c r="N50" t="n">
-        <v>2791.02</v>
+        <v>3114.49</v>
       </c>
       <c r="O50" t="n">
-        <v>334922.4</v>
+        <v>1252024.98</v>
       </c>
       <c r="P50" t="n">
-        <v>3900</v>
+        <v>5500</v>
       </c>
       <c r="Q50" t="n">
-        <v>468000</v>
+        <v>2211000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>91043</v>
+        <v>91042</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>FLOTADOR PRINCESAS 56CM 24PCS</t>
+          <t>PELOTA PISCINA PRINCESAS 24 PCS</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2535,7 +2535,7 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>58</v>
+        <v>120</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
@@ -2544,28 +2544,28 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>58</v>
+        <v>120</v>
       </c>
       <c r="N51" t="n">
-        <v>3564.14</v>
+        <v>2791.02</v>
       </c>
       <c r="O51" t="n">
-        <v>206720.12</v>
+        <v>334922.4</v>
       </c>
       <c r="P51" t="n">
-        <v>5500</v>
+        <v>3900</v>
       </c>
       <c r="Q51" t="n">
-        <v>319000</v>
+        <v>468000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>91098</v>
+        <v>91043</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>BALON INFLABLE MICKEY 51CM</t>
+          <t>FLOTADOR PRINCESAS 56CM 24PCS</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2574,7 +2574,7 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>183</v>
+        <v>58</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
@@ -2583,28 +2583,28 @@
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>183</v>
+        <v>58</v>
       </c>
       <c r="N52" t="n">
-        <v>4378</v>
+        <v>3564.14</v>
       </c>
       <c r="O52" t="n">
-        <v>801174</v>
+        <v>206720.12</v>
       </c>
       <c r="P52" t="n">
-        <v>3900</v>
+        <v>5500</v>
       </c>
       <c r="Q52" t="n">
-        <v>713700</v>
+        <v>319000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>98002</v>
+        <v>91098</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>PELOTA PISCINA SIPDERMAN  51CM</t>
+          <t>BALON INFLABLE MICKEY 51CM</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="J53" t="n">
-        <v>264</v>
+        <v>183</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
@@ -2622,28 +2622,28 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>264</v>
+        <v>183</v>
       </c>
       <c r="N53" t="n">
-        <v>3340.6800808081</v>
+        <v>4378</v>
       </c>
       <c r="O53" t="n">
-        <v>881939.5413333384</v>
+        <v>801174</v>
       </c>
       <c r="P53" t="n">
-        <v>7100</v>
+        <v>3900</v>
       </c>
       <c r="Q53" t="n">
-        <v>1874400</v>
+        <v>713700</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>98003</v>
+        <v>98002</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>FLOTADOR SPIDER MAN 56CM 24 PCS</t>
+          <t>PELOTA PISCINA SIPDERMAN  51CM</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2652,7 +2652,7 @@
         </is>
       </c>
       <c r="J54" t="n">
-        <v>67</v>
+        <v>264</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
@@ -2661,76 +2661,69 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>67</v>
+        <v>264</v>
       </c>
       <c r="N54" t="n">
-        <v>2903.52</v>
+        <v>3340.6800808081</v>
       </c>
       <c r="O54" t="n">
-        <v>194535.84</v>
+        <v>881939.5413333384</v>
       </c>
       <c r="P54" t="n">
         <v>7100</v>
       </c>
       <c r="Q54" t="n">
+        <v>1874400</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>98003</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>FLOTADOR SPIDER MAN 56CM 24 PCS</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>und</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>67</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>67</v>
+      </c>
+      <c r="N55" t="n">
+        <v>2903.52</v>
+      </c>
+      <c r="O55" t="n">
+        <v>194535.84</v>
+      </c>
+      <c r="P55" t="n">
+        <v>7100</v>
+      </c>
+      <c r="Q55" t="n">
         <v>475700</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>C105</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>SCOOTER COLORES</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>und</t>
-        </is>
-      </c>
-      <c r="J55" t="n">
-        <v>18</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" t="n">
-        <v>18</v>
-      </c>
-      <c r="N55" t="n">
-        <v>39171.85</v>
-      </c>
-      <c r="O55" t="n">
-        <v>705093.2999999999</v>
-      </c>
-      <c r="P55" t="n">
-        <v>68900</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>1240200</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>C1370</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>LLAVERO PELUCHES STD C1370</t>
+          <t>SCOOTER COLORES</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2740,11 +2733,11 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>250</v>
+        <v>18</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -2753,39 +2746,44 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>250</v>
+        <v>18</v>
       </c>
       <c r="N56" t="n">
-        <v>3472</v>
+        <v>39171.85</v>
       </c>
       <c r="O56" t="n">
-        <v>868000</v>
+        <v>705093.2999999999</v>
       </c>
       <c r="P56" t="n">
-        <v>4800</v>
+        <v>68900</v>
       </c>
       <c r="Q56" t="n">
-        <v>1200000</v>
+        <v>1240200</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>C1717</t>
+          <t>C1370</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ESPADA CON LUZ Y SONIDO</t>
+          <t>LLAVERO PELUCHES STD C1370</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>432</v>
+        <v>250</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
@@ -2794,38 +2792,30 @@
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>432</v>
+        <v>250</v>
       </c>
       <c r="N57" t="n">
-        <v>4443</v>
+        <v>3472</v>
       </c>
       <c r="O57" t="n">
-        <v>1919376</v>
+        <v>868000</v>
       </c>
       <c r="P57" t="n">
-        <v>6300</v>
+        <v>4800</v>
       </c>
       <c r="Q57" t="n">
-        <v>2721600</v>
+        <v>1200000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>C1758</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>6914919067549</v>
+          <t>C1717</t>
+        </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>MULA BLISTER SURTIDA</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>ESPADA CON LUZ Y SONIDO</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -2834,7 +2824,7 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>180</v>
+        <v>432</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
@@ -2843,33 +2833,33 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>180</v>
+        <v>432</v>
       </c>
       <c r="N58" t="n">
-        <v>4648.6</v>
+        <v>4443</v>
       </c>
       <c r="O58" t="n">
-        <v>836748.0000000001</v>
+        <v>1919376</v>
       </c>
       <c r="P58" t="n">
-        <v>8900</v>
+        <v>6300</v>
       </c>
       <c r="Q58" t="n">
-        <v>1602000</v>
+        <v>2721600</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>C1897</t>
+          <t>C1758</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>6914919086373</v>
+        <v>6914919067549</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MULA DIDACTICA</t>
+          <t>MULA BLISTER SURTIDA</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2883,7 +2873,7 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
@@ -2892,30 +2882,38 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="N59" t="n">
-        <v>16897</v>
+        <v>4648.6</v>
       </c>
       <c r="O59" t="n">
-        <v>2838696</v>
+        <v>836748.0000000001</v>
       </c>
       <c r="P59" t="n">
-        <v>27900</v>
+        <v>8900</v>
       </c>
       <c r="Q59" t="n">
-        <v>4687200</v>
+        <v>1602000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>C2117</t>
-        </is>
+          <t>C1897</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>6914919086373</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>DISPLAY CARTÓN PEGAJOSOS X 20</t>
+          <t>MULA DIDACTICA</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -2924,7 +2922,7 @@
         </is>
       </c>
       <c r="J60" t="n">
-        <v>1400</v>
+        <v>168</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
@@ -2933,38 +2931,30 @@
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>1400</v>
+        <v>168</v>
       </c>
       <c r="N60" t="n">
-        <v>3751</v>
+        <v>16897</v>
       </c>
       <c r="O60" t="n">
-        <v>5251400</v>
+        <v>2838696</v>
       </c>
       <c r="P60" t="n">
-        <v>6400</v>
+        <v>27900</v>
       </c>
       <c r="Q60" t="n">
-        <v>8960000</v>
+        <v>4687200</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>C342</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>6914919018374</v>
+          <t>C2117</t>
+        </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>COCINA CON VAPOR DE AGUA</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>DISPLAY CARTÓN PEGAJOSOS X 20</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -2973,7 +2963,7 @@
         </is>
       </c>
       <c r="J61" t="n">
-        <v>24</v>
+        <v>1400</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
@@ -2982,30 +2972,38 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>24</v>
+        <v>1400</v>
       </c>
       <c r="N61" t="n">
-        <v>24538.02</v>
+        <v>3751</v>
       </c>
       <c r="O61" t="n">
-        <v>588912.48</v>
+        <v>5251400</v>
       </c>
       <c r="P61" t="n">
-        <v>52900</v>
+        <v>6400</v>
       </c>
       <c r="Q61" t="n">
-        <v>1269600</v>
+        <v>8960000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>C3455</t>
-        </is>
+          <t>C342</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>6914919018374</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>DINOSAURIO BOLSA</t>
+          <t>COCINA CON VAPOR DE AGUA</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3014,7 +3012,7 @@
         </is>
       </c>
       <c r="J62" t="n">
-        <v>288</v>
+        <v>24</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
@@ -3023,35 +3021,30 @@
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>288</v>
+        <v>24</v>
       </c>
       <c r="N62" t="n">
-        <v>5894.64</v>
+        <v>24538.02</v>
       </c>
       <c r="O62" t="n">
-        <v>1697656.32</v>
+        <v>588912.48</v>
       </c>
       <c r="P62" t="n">
-        <v>11000</v>
+        <v>52900</v>
       </c>
       <c r="Q62" t="n">
-        <v>3168000</v>
+        <v>1269600</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>C3638</t>
+          <t>C3455</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>INFLABLE DONA</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>DINOSAURIO BOLSA</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3060,7 +3053,7 @@
         </is>
       </c>
       <c r="J63" t="n">
-        <v>443</v>
+        <v>288</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
@@ -3069,30 +3062,30 @@
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>443</v>
+        <v>288</v>
       </c>
       <c r="N63" t="n">
-        <v>3877.89</v>
+        <v>5894.64</v>
       </c>
       <c r="O63" t="n">
-        <v>1717905.27</v>
+        <v>1697656.32</v>
       </c>
       <c r="P63" t="n">
-        <v>6500</v>
+        <v>11000</v>
       </c>
       <c r="Q63" t="n">
-        <v>2879500</v>
+        <v>3168000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>C3700</t>
+          <t>C3638</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MUNECA CON CARRO RECARGABLE DE CONTROL REMOTO</t>
+          <t>INFLABLE DONA</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3106,7 +3099,7 @@
         </is>
       </c>
       <c r="J64" t="n">
-        <v>6</v>
+        <v>443</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -3115,30 +3108,30 @@
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>6</v>
+        <v>443</v>
       </c>
       <c r="N64" t="n">
-        <v>60174</v>
+        <v>3877.89</v>
       </c>
       <c r="O64" t="n">
-        <v>361044</v>
+        <v>1717905.27</v>
       </c>
       <c r="P64" t="n">
-        <v>96900</v>
+        <v>6500</v>
       </c>
       <c r="Q64" t="n">
-        <v>581400</v>
+        <v>2879500</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>C3970</t>
+          <t>C3700</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>GUITARRAS C3970</t>
+          <t>MUNECA CON CARRO RECARGABLE DE CONTROL REMOTO</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3148,11 +3141,11 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J65" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
@@ -3161,39 +3154,44 @@
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="N65" t="n">
-        <v>26854</v>
+        <v>60174</v>
       </c>
       <c r="O65" t="n">
-        <v>1288992</v>
+        <v>361044</v>
       </c>
       <c r="P65" t="n">
-        <v>43900</v>
+        <v>96900</v>
       </c>
       <c r="Q65" t="n">
-        <v>2107200</v>
+        <v>581400</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>C3988</t>
+          <t>C3970</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>DRAGÓN CAMINA CON LUZ Y SONIDO</t>
+          <t>GUITARRAS C3970</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J66" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>
@@ -3202,44 +3200,39 @@
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="N66" t="n">
-        <v>29700</v>
+        <v>26854</v>
       </c>
       <c r="O66" t="n">
-        <v>356400</v>
+        <v>1288992</v>
       </c>
       <c r="P66" t="n">
-        <v>50500</v>
+        <v>43900</v>
       </c>
       <c r="Q66" t="n">
-        <v>606000</v>
+        <v>2107200</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>C4303</t>
+          <t>C3988</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>BEBE CON PIJAMA MED BOLSA PVC C4303</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>DRAGÓN CAMINA CON LUZ Y SONIDO</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J67" t="n">
-        <v>300</v>
+        <v>12</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
@@ -3248,30 +3241,30 @@
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>300</v>
+        <v>12</v>
       </c>
       <c r="N67" t="n">
-        <v>18016</v>
+        <v>29700</v>
       </c>
       <c r="O67" t="n">
-        <v>5404800</v>
+        <v>356400</v>
       </c>
       <c r="P67" t="n">
-        <v>29900</v>
+        <v>50500</v>
       </c>
       <c r="Q67" t="n">
-        <v>8970000</v>
+        <v>606000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>C4305</t>
+          <t>C4303</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MUÑECA BEBE GRANDE CON PIJAMA EN BOLSA C4305</t>
+          <t>BEBE CON PIJAMA MED BOLSA PVC C4303</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3285,7 +3278,7 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>144</v>
+        <v>300</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
@@ -3294,30 +3287,30 @@
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>144</v>
+        <v>300</v>
       </c>
       <c r="N68" t="n">
-        <v>25534</v>
+        <v>18016</v>
       </c>
       <c r="O68" t="n">
-        <v>3676896</v>
+        <v>5404800</v>
       </c>
       <c r="P68" t="n">
-        <v>40900</v>
+        <v>29900</v>
       </c>
       <c r="Q68" t="n">
-        <v>5889600</v>
+        <v>8970000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>C4310</t>
+          <t>C4305</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MUÑECA CON CARRO HUMO RECARGABLE C4310</t>
+          <t>MUÑECA BEBE GRANDE CON PIJAMA EN BOLSA C4305</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3331,7 +3324,7 @@
         </is>
       </c>
       <c r="J69" t="n">
-        <v>32</v>
+        <v>144</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
@@ -3340,30 +3333,30 @@
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>32</v>
+        <v>144</v>
       </c>
       <c r="N69" t="n">
-        <v>72889</v>
+        <v>25534</v>
       </c>
       <c r="O69" t="n">
-        <v>2332448</v>
+        <v>3676896</v>
       </c>
       <c r="P69" t="n">
-        <v>117500</v>
+        <v>40900</v>
       </c>
       <c r="Q69" t="n">
-        <v>3760000</v>
+        <v>5889600</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>C4545</t>
+          <t>C4310</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>TAPETE PIANO PARA BEBE C4545</t>
+          <t>MUÑECA CON CARRO HUMO RECARGABLE C4310</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3377,7 +3370,7 @@
         </is>
       </c>
       <c r="J70" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
@@ -3386,30 +3379,30 @@
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="N70" t="n">
-        <v>27186</v>
+        <v>72889</v>
       </c>
       <c r="O70" t="n">
-        <v>543720</v>
+        <v>2332448</v>
       </c>
       <c r="P70" t="n">
-        <v>43900</v>
+        <v>117500</v>
       </c>
       <c r="Q70" t="n">
-        <v>878000</v>
+        <v>3760000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>C4728</t>
+          <t>C4545</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>FLIOTADOR DONA DINOSAURIO #60 C4728</t>
+          <t>TAPETE PIANO PARA BEBE C4545</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3423,7 +3416,7 @@
         </is>
       </c>
       <c r="J71" t="n">
-        <v>1800</v>
+        <v>20</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
@@ -3432,47 +3425,44 @@
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>1800</v>
+        <v>20</v>
       </c>
       <c r="N71" t="n">
-        <v>2454</v>
+        <v>27186</v>
       </c>
       <c r="O71" t="n">
-        <v>4417200</v>
+        <v>543720</v>
       </c>
       <c r="P71" t="n">
-        <v>4200</v>
+        <v>43900</v>
       </c>
       <c r="Q71" t="n">
-        <v>7560000</v>
+        <v>878000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>C488</t>
-        </is>
-      </c>
-      <c r="B72" t="n">
-        <v>6554632300006</v>
+          <t>C4728</t>
+        </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MALETA JUGUETES</t>
+          <t>FLIOTADOR DONA DINOSAURIO #60 C4728</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J72" t="n">
-        <v>12</v>
+        <v>1800</v>
       </c>
       <c r="K72" t="n">
         <v>0</v>
@@ -3481,47 +3471,47 @@
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>12</v>
+        <v>1800</v>
       </c>
       <c r="N72" t="n">
-        <v>18491</v>
+        <v>2454</v>
       </c>
       <c r="O72" t="n">
-        <v>221892</v>
+        <v>4417200</v>
       </c>
       <c r="P72" t="n">
-        <v>13500</v>
+        <v>4200</v>
       </c>
       <c r="Q72" t="n">
-        <v>162000</v>
+        <v>7560000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>C5032</t>
+          <t>C488</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>6999899236154</v>
+        <v>6554632300006</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>INFLABLE TECHITO PIECITOS  FIGURAS STD C5032</t>
+          <t>MALETA JUGUETES</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>INFLABLES</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J73" t="n">
-        <v>937</v>
+        <v>12</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -3530,44 +3520,47 @@
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>937</v>
+        <v>12</v>
       </c>
       <c r="N73" t="n">
-        <v>8945.379999999999</v>
+        <v>18491</v>
       </c>
       <c r="O73" t="n">
-        <v>8381821.06</v>
+        <v>221892</v>
       </c>
       <c r="P73" t="n">
-        <v>14900</v>
+        <v>13500</v>
       </c>
       <c r="Q73" t="n">
-        <v>13961300</v>
+        <v>162000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>C698</t>
-        </is>
+          <t>C5032</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>6999899236154</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>HELICE 9 LUCES</t>
+          <t>INFLABLE TECHITO PIECITOS  FIGURAS STD C5032</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>INFLABLES</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J74" t="n">
-        <v>240</v>
+        <v>937</v>
       </c>
       <c r="K74" t="n">
         <v>0</v>
@@ -3576,44 +3569,44 @@
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>240</v>
+        <v>937</v>
       </c>
       <c r="N74" t="n">
-        <v>1567.02</v>
+        <v>8945.379999999999</v>
       </c>
       <c r="O74" t="n">
-        <v>376084.8</v>
+        <v>8381821.06</v>
       </c>
       <c r="P74" t="n">
-        <v>2900</v>
+        <v>14900</v>
       </c>
       <c r="Q74" t="n">
-        <v>696000</v>
+        <v>13961300</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>C7560</t>
+          <t>C698</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>BARRA LUMINOSA 48CM C7560/211</t>
+          <t>HELICE 9 LUCES</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J75" t="n">
-        <v>10</v>
+        <v>240</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
@@ -3622,68 +3615,114 @@
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>10</v>
+        <v>240</v>
       </c>
       <c r="N75" t="n">
-        <v>796.3099999999999</v>
+        <v>1567.02</v>
       </c>
       <c r="O75" t="n">
-        <v>7963.099999999999</v>
+        <v>376084.8</v>
       </c>
       <c r="P75" t="n">
-        <v>2500</v>
+        <v>2900</v>
       </c>
       <c r="Q75" t="n">
-        <v>25000</v>
+        <v>696000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
+          <t>C7560</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>BARRA LUMINOSA 48CM C7560/211</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>PIÑATERIA</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>10</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" t="n">
+        <v>10</v>
+      </c>
+      <c r="N76" t="n">
+        <v>796.3099999999999</v>
+      </c>
+      <c r="O76" t="n">
+        <v>7963.099999999999</v>
+      </c>
+      <c r="P76" t="n">
+        <v>2500</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
           <t>C7610</t>
         </is>
       </c>
-      <c r="B76" t="n">
+      <c r="B77" t="n">
         <v>6999899236093</v>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>BOTE TIMON PISCINA 80X60 C7610</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="E77" t="inlineStr">
         <is>
           <t>INFLABLES</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t>Und</t>
         </is>
       </c>
-      <c r="J76" t="n">
+      <c r="J77" t="n">
         <v>480</v>
       </c>
-      <c r="K76" t="n">
-        <v>0</v>
-      </c>
-      <c r="L76" t="n">
-        <v>0</v>
-      </c>
-      <c r="M76" t="n">
-        <v>480</v>
-      </c>
-      <c r="N76" t="n">
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" t="n">
+        <v>120</v>
+      </c>
+      <c r="M77" t="n">
+        <v>360</v>
+      </c>
+      <c r="N77" t="n">
         <v>7811.9</v>
       </c>
-      <c r="O76" t="n">
-        <v>3749712</v>
-      </c>
-      <c r="P76" t="n">
+      <c r="O77" t="n">
+        <v>2812284</v>
+      </c>
+      <c r="P77" t="n">
         <v>13900</v>
       </c>
-      <c r="Q76" t="n">
-        <v>6672000</v>
+      <c r="Q77" t="n">
+        <v>5004000</v>
       </c>
     </row>
   </sheetData>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q77"/>
+  <dimension ref="A1:Q75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-08</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-09</t>
         </is>
       </c>
     </row>
@@ -545,13 +545,13 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>8</v>
@@ -1268,10 +1268,10 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="K21" t="n">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -1411,14 +1411,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>51004</v>
+        <v>51005</v>
       </c>
       <c r="B25" t="n">
-        <v>6941607363478</v>
+        <v>6941607363485</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>51004 PISCINA DEEP DIVE</t>
+          <t>51005 PISCINA DEEP DIVE</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1427,40 +1427,40 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>30708.894545455</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>61417.78909091</v>
       </c>
       <c r="P25" t="n">
-        <v>37100</v>
+        <v>53500</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>107000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>51005</v>
+        <v>51008</v>
       </c>
       <c r="B26" t="n">
-        <v>6941607363485</v>
+        <v>6941607367575</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>51005 PISCINA DEEP DIVE</t>
+          <t>PISCINA CORAL 102 X25CM</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -1478,31 +1478,31 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="N26" t="n">
-        <v>30708.894545455</v>
+        <v>12837.964861111</v>
       </c>
       <c r="O26" t="n">
-        <v>61417.78909091</v>
+        <v>154055.578333332</v>
       </c>
       <c r="P26" t="n">
-        <v>53500</v>
+        <v>22900</v>
       </c>
       <c r="Q26" t="n">
-        <v>107000</v>
+        <v>274800</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>51008</v>
+        <v>51104</v>
       </c>
       <c r="B27" t="n">
-        <v>6941607367575</v>
+        <v>6942138915815</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>PISCINA CORAL 102 X25CM</t>
+          <t>PISCINA VERANO 102 X25 CM</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1511,7 +1511,7 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -1520,31 +1520,31 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N27" t="n">
-        <v>12837.964861111</v>
+        <v>16486.410204082</v>
       </c>
       <c r="O27" t="n">
-        <v>154055.578333332</v>
+        <v>164864.10204082</v>
       </c>
       <c r="P27" t="n">
-        <v>22900</v>
+        <v>30500</v>
       </c>
       <c r="Q27" t="n">
-        <v>274800</v>
+        <v>305000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>51104</v>
+        <v>51124</v>
       </c>
       <c r="B28" t="n">
-        <v>6942138915815</v>
+        <v>6941607325032</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>PISCINA VERANO 102 X25 CM</t>
+          <t>51124 COMBO DE PISCINA Y BALON</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1553,49 +1553,54 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="N28" t="n">
-        <v>16486.410204082</v>
+        <v>15711.9662</v>
       </c>
       <c r="O28" t="n">
-        <v>164864.10204082</v>
+        <v>565630.7832000001</v>
       </c>
       <c r="P28" t="n">
-        <v>30500</v>
+        <v>28500</v>
       </c>
       <c r="Q28" t="n">
-        <v>305000</v>
+        <v>1026000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>51124</v>
+        <v>51203</v>
       </c>
       <c r="B29" t="n">
-        <v>6941607325032</v>
+        <v>6941607325544</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>51124 COMBO DE PISCINA Y BALON</t>
+          <t>51203 PISCINA 3 AROS BESTWAY Φ1.68m x H38cm</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -1604,45 +1609,37 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="N29" t="n">
-        <v>15711.9662</v>
+        <v>30238.812307692</v>
       </c>
       <c r="O29" t="n">
-        <v>565630.7832000001</v>
+        <v>302388.12307692</v>
       </c>
       <c r="P29" t="n">
-        <v>28500</v>
+        <v>51100</v>
       </c>
       <c r="Q29" t="n">
-        <v>1026000</v>
+        <v>511000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>51203</v>
-      </c>
-      <c r="B30" t="n">
-        <v>6941607325544</v>
+        <v>52331</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>51203 PISCINA 3 AROS BESTWAY Φ1.68m x H38cm</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>PISCINA CANOPY FRUTICAS 8 PCS</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -1651,28 +1648,36 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="N30" t="n">
-        <v>30238.812307692</v>
+        <v>20195.32</v>
       </c>
       <c r="O30" t="n">
-        <v>302388.12307692</v>
+        <v>1514649</v>
       </c>
       <c r="P30" t="n">
-        <v>51100</v>
+        <v>45900</v>
       </c>
       <c r="Q30" t="n">
-        <v>511000</v>
+        <v>3442500</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>52331</v>
+        <v>52637</v>
+      </c>
+      <c r="B31" t="n">
+        <v>6941607352212</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>PISCINA CANOPY FRUTICAS 8 PCS</t>
+          <t>52637 PISCINA TECHADA SUNNY BESTWAY</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1681,7 +1686,7 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>75</v>
+        <v>4</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -1690,31 +1695,31 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>75</v>
+        <v>4</v>
       </c>
       <c r="N31" t="n">
-        <v>20195.32</v>
+        <v>22267.552083333</v>
       </c>
       <c r="O31" t="n">
-        <v>1514649</v>
+        <v>89070.208333332</v>
       </c>
       <c r="P31" t="n">
-        <v>45900</v>
+        <v>46300</v>
       </c>
       <c r="Q31" t="n">
-        <v>3442500</v>
+        <v>185200</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>52637</v>
+        <v>53157</v>
       </c>
       <c r="B32" t="n">
-        <v>6941607352212</v>
+        <v>6941607352137</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>52637 PISCINA TECHADA SUNNY BESTWAY</t>
+          <t>53157 PISCINA FUENTE SHARK BESTWAY</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1740,28 +1745,28 @@
         <v>4</v>
       </c>
       <c r="N32" t="n">
-        <v>22267.552083333</v>
+        <v>36574.852142857</v>
       </c>
       <c r="O32" t="n">
-        <v>89070.208333332</v>
+        <v>146299.408571428</v>
       </c>
       <c r="P32" t="n">
-        <v>46300</v>
+        <v>65900</v>
       </c>
       <c r="Q32" t="n">
-        <v>185200</v>
+        <v>263600</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>53157</v>
+        <v>54370</v>
       </c>
       <c r="B33" t="n">
-        <v>6941607352137</v>
+        <v>6941607312643</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>53157 PISCINA FUENTE SHARK BESTWAY</t>
+          <t>PISCINA CAPITAN 213 X155 X 132CM</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1787,28 +1792,33 @@
         <v>4</v>
       </c>
       <c r="N33" t="n">
-        <v>36574.852142857</v>
+        <v>103298.75</v>
       </c>
       <c r="O33" t="n">
-        <v>146299.408571428</v>
+        <v>413195</v>
       </c>
       <c r="P33" t="n">
-        <v>65900</v>
+        <v>178900</v>
       </c>
       <c r="Q33" t="n">
-        <v>263600</v>
+        <v>715600</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>54150</v>
+        <v>55031</v>
       </c>
       <c r="B34" t="n">
-        <v>6942138968279</v>
+        <v>6942138913781</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>54150 Piscina familiar rectangular</t>
+          <t>55031 PISCINA DELFIN 2.44mx46cm</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1817,40 +1827,40 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N34" t="n">
-        <v>80027.73</v>
+        <v>56906.800571429</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>56906.800571429</v>
       </c>
       <c r="P34" t="n">
-        <v>129900</v>
+        <v>95900</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>95900</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>54370</v>
+        <v>56401</v>
       </c>
       <c r="B35" t="n">
-        <v>6941607312643</v>
+        <v>6941607327951</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>PISCINA CAPITAN 213 X155 X 132CM</t>
+          <t>56401 PISCINA ESTRUCTURAL RECTANGULAR BESTWAY</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1864,7 +1874,7 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -1873,45 +1883,40 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="N35" t="n">
-        <v>103298.75</v>
+        <v>141416.88453074</v>
       </c>
       <c r="O35" t="n">
-        <v>413195</v>
+        <v>7919345.53372144</v>
       </c>
       <c r="P35" t="n">
-        <v>178900</v>
+        <v>251900</v>
       </c>
       <c r="Q35" t="n">
-        <v>715600</v>
+        <v>14106400</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>55031</v>
+        <v>56403</v>
       </c>
       <c r="B36" t="n">
-        <v>6942138913781</v>
+        <v>6941607327982</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>55031 PISCINA DELFIN 2.44mx46cm</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>PISCINA ESTRUCTURAL 2.59m x 1.70m x 61cm BESTWAY</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -1920,36 +1925,31 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="N36" t="n">
-        <v>56906.800571429</v>
+        <v>200072.19914894</v>
       </c>
       <c r="O36" t="n">
-        <v>56906.800571429</v>
+        <v>6802454.77106396</v>
       </c>
       <c r="P36" t="n">
-        <v>95900</v>
+        <v>312000</v>
       </c>
       <c r="Q36" t="n">
-        <v>95900</v>
+        <v>10608000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>56401</v>
+        <v>56404</v>
       </c>
       <c r="B37" t="n">
-        <v>6941607327951</v>
+        <v>6941607327999</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>56401 PISCINA ESTRUCTURAL RECTANGULAR BESTWAY</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>56404 PISCINA ESTRUCTURAL RECTANGULAR BESTWAY</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -1958,7 +1958,7 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -1967,31 +1967,36 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="N37" t="n">
-        <v>141416.88453074</v>
+        <v>174389.78756757</v>
       </c>
       <c r="O37" t="n">
-        <v>7919345.53372144</v>
+        <v>2790236.60108112</v>
       </c>
       <c r="P37" t="n">
-        <v>251900</v>
+        <v>368200</v>
       </c>
       <c r="Q37" t="n">
-        <v>14106400</v>
+        <v>5891200</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>56403</v>
+        <v>56405</v>
       </c>
       <c r="B38" t="n">
-        <v>6941607327982</v>
+        <v>6941607328002</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>PISCINA ESTRUCTURAL 2.59m x 1.70m x 61cm BESTWAY</t>
+          <t>PISCINA ESTRUCTURAL RECTAGULAR BESTWAY 4.00mX2.11mX81cm</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2000,7 +2005,7 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -2009,40 +2014,45 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="N38" t="n">
-        <v>200072.19914894</v>
+        <v>251809.29393939</v>
       </c>
       <c r="O38" t="n">
-        <v>6802454.77106396</v>
+        <v>1510855.76363634</v>
       </c>
       <c r="P38" t="n">
-        <v>312000</v>
+        <v>584000</v>
       </c>
       <c r="Q38" t="n">
-        <v>10608000</v>
+        <v>3504000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>56404</v>
+        <v>56417</v>
       </c>
       <c r="B39" t="n">
-        <v>6941607327999</v>
+        <v>6942138981902</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>56404 PISCINA ESTRUCTURAL RECTANGULAR BESTWAY</t>
+          <t>Piscina Estructural Redonda 366 x 76 cm Bomba/Filtro 56417</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -2051,41 +2061,33 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="N39" t="n">
-        <v>174389.78756757</v>
+        <v>344599.1787931</v>
       </c>
       <c r="O39" t="n">
-        <v>2790236.60108112</v>
+        <v>2067595.0727586</v>
       </c>
       <c r="P39" t="n">
-        <v>368200</v>
+        <v>532900</v>
       </c>
       <c r="Q39" t="n">
-        <v>5891200</v>
+        <v>3197400</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>56405</v>
-      </c>
-      <c r="B40" t="n">
-        <v>6941607328002</v>
+        <v>62068</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>PISCINA ESTRUCTURAL RECTAGULAR BESTWAY 4.00mX2.11mX81cm</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>PARCHE PISCINA EXTERIOR BESTWAY</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J40" t="n">
@@ -2101,42 +2103,34 @@
         <v>6</v>
       </c>
       <c r="N40" t="n">
-        <v>251809.29393939</v>
+        <v>1977.88</v>
       </c>
       <c r="O40" t="n">
-        <v>1510855.76363634</v>
+        <v>11867.28</v>
       </c>
       <c r="P40" t="n">
-        <v>584000</v>
+        <v>2900</v>
       </c>
       <c r="Q40" t="n">
-        <v>3504000</v>
+        <v>17400</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>56417</v>
-      </c>
-      <c r="B41" t="n">
-        <v>6942138981902</v>
+        <v>62091</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Piscina Estructural Redonda 366 x 76 cm Bomba/Filtro 56417</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>PARCHE PISCINA A PRUEBA DE AGUA BESTWAY</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>6</v>
+        <v>217</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -2145,28 +2139,28 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>6</v>
+        <v>217</v>
       </c>
       <c r="N41" t="n">
-        <v>344599.1787931</v>
+        <v>1141.57</v>
       </c>
       <c r="O41" t="n">
-        <v>2067595.0727586</v>
+        <v>247720.69</v>
       </c>
       <c r="P41" t="n">
-        <v>532900</v>
+        <v>3900</v>
       </c>
       <c r="Q41" t="n">
-        <v>3197400</v>
+        <v>846300</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>62068</v>
+        <v>67001</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>PARCHE PISCINA EXTERIOR BESTWAY</t>
+          <t>COLCHON INFLABLE SENCILLO BESTWAY 1.88 X 99 CM</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2175,7 +2169,7 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -2184,28 +2178,28 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N42" t="n">
-        <v>1977.88</v>
+        <v>26280.41</v>
       </c>
       <c r="O42" t="n">
-        <v>11867.28</v>
+        <v>78841.23</v>
       </c>
       <c r="P42" t="n">
-        <v>2900</v>
+        <v>46500</v>
       </c>
       <c r="Q42" t="n">
-        <v>17400</v>
+        <v>139500</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>62091</v>
+        <v>67374</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>PARCHE PISCINA A PRUEBA DE AGUA BESTWAY</t>
+          <t>COLCHON INFLABLE DOBLE+ALMOHADAS BESTWAY 2.03mx1.52mx22cm</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2214,7 +2208,7 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>217</v>
+        <v>67</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -2223,28 +2217,28 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>217</v>
+        <v>67</v>
       </c>
       <c r="N43" t="n">
-        <v>1141.57</v>
+        <v>61666.873852041</v>
       </c>
       <c r="O43" t="n">
-        <v>247720.69</v>
+        <v>4131680.548086747</v>
       </c>
       <c r="P43" t="n">
-        <v>3900</v>
+        <v>98900</v>
       </c>
       <c r="Q43" t="n">
-        <v>846300</v>
+        <v>6626300</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>67001</v>
+        <v>91004</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>COLCHON INFLABLE SENCILLO BESTWAY 1.88 X 99 CM</t>
+          <t>FLOTADOR DISNEY 56CM 24PCS</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2253,7 +2247,7 @@
         </is>
       </c>
       <c r="J44" t="n">
-        <v>3</v>
+        <v>340</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -2262,28 +2256,28 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3</v>
+        <v>340</v>
       </c>
       <c r="N44" t="n">
-        <v>26280.41</v>
+        <v>3865.67</v>
       </c>
       <c r="O44" t="n">
-        <v>78841.23</v>
+        <v>1314327.8</v>
       </c>
       <c r="P44" t="n">
-        <v>46500</v>
+        <v>5500</v>
       </c>
       <c r="Q44" t="n">
-        <v>139500</v>
+        <v>1870000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>67374</v>
+        <v>91007</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>COLCHON INFLABLE DOBLE+ALMOHADAS BESTWAY 2.03mx1.52mx22cm</t>
+          <t>PISCINA DISNEY 122X25CM 12 PCS</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2292,7 +2286,7 @@
         </is>
       </c>
       <c r="J45" t="n">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -2301,28 +2295,35 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="N45" t="n">
-        <v>61666.873852041</v>
+        <v>16010.3</v>
       </c>
       <c r="O45" t="n">
-        <v>4131680.548086747</v>
+        <v>384247.2</v>
       </c>
       <c r="P45" t="n">
-        <v>98900</v>
+        <v>30500</v>
       </c>
       <c r="Q45" t="n">
-        <v>6626300</v>
+        <v>732000</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="n">
-        <v>91004</v>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>9103C</t>
+        </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>FLOTADOR DISNEY 56CM 24PCS</t>
+          <t>9103C GAFA ACUATICA SIRENITA BESTWAY</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2331,7 +2332,7 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>340</v>
+        <v>24</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -2340,115 +2341,108 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>340</v>
+        <v>24</v>
       </c>
       <c r="N46" t="n">
-        <v>3865.67</v>
+        <v>4878.2859036145</v>
       </c>
       <c r="O46" t="n">
-        <v>1314327.8</v>
+        <v>117078.861686748</v>
       </c>
       <c r="P46" t="n">
+        <v>13500</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>324000</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>9103D</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>9103D CARETA ACUATICA SIRENITA BESTWAY</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>und</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>12</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>12</v>
+      </c>
+      <c r="N47" t="n">
+        <v>7394.9354444444</v>
+      </c>
+      <c r="O47" t="n">
+        <v>88739.2253333328</v>
+      </c>
+      <c r="P47" t="n">
+        <v>17900</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>214800</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>91040</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>FLOTADOR MINNIE 56CM 24 PCS</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>und</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>402</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>402</v>
+      </c>
+      <c r="N48" t="n">
+        <v>3114.49</v>
+      </c>
+      <c r="O48" t="n">
+        <v>1252024.98</v>
+      </c>
+      <c r="P48" t="n">
         <v>5500</v>
       </c>
-      <c r="Q46" t="n">
-        <v>1870000</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>91007</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>PISCINA DISNEY 122X25CM 12 PCS</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>und</t>
-        </is>
-      </c>
-      <c r="J47" t="n">
-        <v>24</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" t="n">
-        <v>24</v>
-      </c>
-      <c r="N47" t="n">
-        <v>16010.3</v>
-      </c>
-      <c r="O47" t="n">
-        <v>384247.2</v>
-      </c>
-      <c r="P47" t="n">
-        <v>30500</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>732000</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>9103C</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>9103C GAFA ACUATICA SIRENITA BESTWAY</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>und</t>
-        </is>
-      </c>
-      <c r="J48" t="n">
-        <v>24</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" t="n">
-        <v>24</v>
-      </c>
-      <c r="N48" t="n">
-        <v>4878.2859036145</v>
-      </c>
-      <c r="O48" t="n">
-        <v>117078.861686748</v>
-      </c>
-      <c r="P48" t="n">
-        <v>13500</v>
-      </c>
       <c r="Q48" t="n">
-        <v>324000</v>
+        <v>2211000</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>9103D</t>
-        </is>
+      <c r="A49" t="n">
+        <v>91042</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>9103D CARETA ACUATICA SIRENITA BESTWAY</t>
+          <t>PELOTA PISCINA PRINCESAS 24 PCS</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2457,7 +2451,7 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -2466,28 +2460,28 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="N49" t="n">
-        <v>7394.9354444444</v>
+        <v>2791.02</v>
       </c>
       <c r="O49" t="n">
-        <v>88739.2253333328</v>
+        <v>334922.4</v>
       </c>
       <c r="P49" t="n">
-        <v>17900</v>
+        <v>3900</v>
       </c>
       <c r="Q49" t="n">
-        <v>214800</v>
+        <v>468000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>91040</v>
+        <v>91043</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>FLOTADOR MINNIE 56CM 24 PCS</t>
+          <t>FLOTADOR PRINCESAS 56CM 24PCS</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2496,7 +2490,7 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>402</v>
+        <v>58</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -2505,28 +2499,28 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>402</v>
+        <v>58</v>
       </c>
       <c r="N50" t="n">
-        <v>3114.49</v>
+        <v>3564.14</v>
       </c>
       <c r="O50" t="n">
-        <v>1252024.98</v>
+        <v>206720.12</v>
       </c>
       <c r="P50" t="n">
         <v>5500</v>
       </c>
       <c r="Q50" t="n">
-        <v>2211000</v>
+        <v>319000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>91042</v>
+        <v>91098</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>PELOTA PISCINA PRINCESAS 24 PCS</t>
+          <t>BALON INFLABLE MICKEY 51CM</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2535,7 +2529,7 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>120</v>
+        <v>183</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
@@ -2544,28 +2538,28 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>120</v>
+        <v>183</v>
       </c>
       <c r="N51" t="n">
-        <v>2791.02</v>
+        <v>4378</v>
       </c>
       <c r="O51" t="n">
-        <v>334922.4</v>
+        <v>801174</v>
       </c>
       <c r="P51" t="n">
         <v>3900</v>
       </c>
       <c r="Q51" t="n">
-        <v>468000</v>
+        <v>713700</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>91043</v>
+        <v>98002</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>FLOTADOR PRINCESAS 56CM 24PCS</t>
+          <t>PELOTA PISCINA SIPDERMAN  51CM</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2574,7 +2568,7 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>58</v>
+        <v>264</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
@@ -2583,28 +2577,28 @@
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>58</v>
+        <v>264</v>
       </c>
       <c r="N52" t="n">
-        <v>3564.14</v>
+        <v>3340.6800808081</v>
       </c>
       <c r="O52" t="n">
-        <v>206720.12</v>
+        <v>881939.5413333384</v>
       </c>
       <c r="P52" t="n">
-        <v>5500</v>
+        <v>7100</v>
       </c>
       <c r="Q52" t="n">
-        <v>319000</v>
+        <v>1874400</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>91098</v>
+        <v>98003</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>BALON INFLABLE MICKEY 51CM</t>
+          <t>FLOTADOR SPIDER MAN 56CM 24 PCS</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2613,7 +2607,7 @@
         </is>
       </c>
       <c r="J53" t="n">
-        <v>183</v>
+        <v>67</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
@@ -2622,28 +2616,35 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>183</v>
+        <v>67</v>
       </c>
       <c r="N53" t="n">
-        <v>4378</v>
+        <v>2903.52</v>
       </c>
       <c r="O53" t="n">
-        <v>801174</v>
+        <v>194535.84</v>
       </c>
       <c r="P53" t="n">
-        <v>3900</v>
+        <v>7100</v>
       </c>
       <c r="Q53" t="n">
-        <v>713700</v>
+        <v>475700</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="n">
-        <v>98002</v>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>C105</t>
+        </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>PELOTA PISCINA SIPDERMAN  51CM</t>
+          <t>SCOOTER COLORES</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2652,7 +2653,7 @@
         </is>
       </c>
       <c r="J54" t="n">
-        <v>264</v>
+        <v>18</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
@@ -2661,37 +2662,44 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>264</v>
+        <v>18</v>
       </c>
       <c r="N54" t="n">
-        <v>3340.6800808081</v>
+        <v>39171.85</v>
       </c>
       <c r="O54" t="n">
-        <v>881939.5413333384</v>
+        <v>705093.2999999999</v>
       </c>
       <c r="P54" t="n">
-        <v>7100</v>
+        <v>68900</v>
       </c>
       <c r="Q54" t="n">
-        <v>1874400</v>
+        <v>1240200</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="n">
-        <v>98003</v>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>C1370</t>
+        </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>FLOTADOR SPIDER MAN 56CM 24 PCS</t>
+          <t>LLAVERO PELUCHES STD C1370</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>67</v>
+        <v>250</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
@@ -2700,35 +2708,30 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>67</v>
+        <v>250</v>
       </c>
       <c r="N55" t="n">
-        <v>2903.52</v>
+        <v>3472</v>
       </c>
       <c r="O55" t="n">
-        <v>194535.84</v>
+        <v>868000</v>
       </c>
       <c r="P55" t="n">
-        <v>7100</v>
+        <v>4800</v>
       </c>
       <c r="Q55" t="n">
-        <v>475700</v>
+        <v>1200000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C1717</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>SCOOTER COLORES</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>ESPADA CON LUZ Y SONIDO</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2737,7 +2740,7 @@
         </is>
       </c>
       <c r="J56" t="n">
-        <v>18</v>
+        <v>432</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -2746,30 +2749,33 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>18</v>
+        <v>432</v>
       </c>
       <c r="N56" t="n">
-        <v>39171.85</v>
+        <v>4443</v>
       </c>
       <c r="O56" t="n">
-        <v>705093.2999999999</v>
+        <v>1919376</v>
       </c>
       <c r="P56" t="n">
-        <v>68900</v>
+        <v>6300</v>
       </c>
       <c r="Q56" t="n">
-        <v>1240200</v>
+        <v>2721600</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>C1370</t>
-        </is>
+          <t>C1758</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>6914919067549</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>LLAVERO PELUCHES STD C1370</t>
+          <t>MULA BLISTER SURTIDA</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2779,11 +2785,11 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>250</v>
+        <v>180</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
@@ -2792,30 +2798,38 @@
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>250</v>
+        <v>180</v>
       </c>
       <c r="N57" t="n">
-        <v>3472</v>
+        <v>4648.6</v>
       </c>
       <c r="O57" t="n">
-        <v>868000</v>
+        <v>836748.0000000001</v>
       </c>
       <c r="P57" t="n">
-        <v>4800</v>
+        <v>8900</v>
       </c>
       <c r="Q57" t="n">
-        <v>1200000</v>
+        <v>1602000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>C1717</t>
-        </is>
+          <t>C1897</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>6914919086373</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ESPADA CON LUZ Y SONIDO</t>
+          <t>MULA DIDACTICA</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -2824,7 +2838,7 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>432</v>
+        <v>168</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
@@ -2833,38 +2847,30 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>432</v>
+        <v>168</v>
       </c>
       <c r="N58" t="n">
-        <v>4443</v>
+        <v>16897</v>
       </c>
       <c r="O58" t="n">
-        <v>1919376</v>
+        <v>2838696</v>
       </c>
       <c r="P58" t="n">
-        <v>6300</v>
+        <v>27900</v>
       </c>
       <c r="Q58" t="n">
-        <v>2721600</v>
+        <v>4687200</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>C1758</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>6914919067549</v>
+          <t>C2117</t>
+        </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MULA BLISTER SURTIDA</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>DISPLAY CARTÓN PEGAJOSOS X 20</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -2873,7 +2879,7 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>180</v>
+        <v>1400</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
@@ -2882,33 +2888,33 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>180</v>
+        <v>1400</v>
       </c>
       <c r="N59" t="n">
-        <v>4648.6</v>
+        <v>3751</v>
       </c>
       <c r="O59" t="n">
-        <v>836748.0000000001</v>
+        <v>5251400</v>
       </c>
       <c r="P59" t="n">
-        <v>8900</v>
+        <v>6400</v>
       </c>
       <c r="Q59" t="n">
-        <v>1602000</v>
+        <v>8960000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>C1897</t>
+          <t>C342</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>6914919086373</v>
+        <v>6914919018374</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MULA DIDACTICA</t>
+          <t>COCINA CON VAPOR DE AGUA</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2922,7 +2928,7 @@
         </is>
       </c>
       <c r="J60" t="n">
-        <v>168</v>
+        <v>24</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
@@ -2931,30 +2937,30 @@
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>168</v>
+        <v>24</v>
       </c>
       <c r="N60" t="n">
-        <v>16897</v>
+        <v>24538.02</v>
       </c>
       <c r="O60" t="n">
-        <v>2838696</v>
+        <v>588912.48</v>
       </c>
       <c r="P60" t="n">
-        <v>27900</v>
+        <v>52900</v>
       </c>
       <c r="Q60" t="n">
-        <v>4687200</v>
+        <v>1269600</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>C2117</t>
+          <t>C3455</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>DISPLAY CARTÓN PEGAJOSOS X 20</t>
+          <t>DINOSAURIO BOLSA</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -2963,7 +2969,7 @@
         </is>
       </c>
       <c r="J61" t="n">
-        <v>1400</v>
+        <v>288</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
@@ -2972,33 +2978,30 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>1400</v>
+        <v>288</v>
       </c>
       <c r="N61" t="n">
-        <v>3751</v>
+        <v>5894.64</v>
       </c>
       <c r="O61" t="n">
-        <v>5251400</v>
+        <v>1697656.32</v>
       </c>
       <c r="P61" t="n">
-        <v>6400</v>
+        <v>11000</v>
       </c>
       <c r="Q61" t="n">
-        <v>8960000</v>
+        <v>3168000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>C342</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>6914919018374</v>
+          <t>C3638</t>
+        </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>COCINA CON VAPOR DE AGUA</t>
+          <t>INFLABLE DONA</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3012,7 +3015,7 @@
         </is>
       </c>
       <c r="J62" t="n">
-        <v>24</v>
+        <v>443</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
@@ -3021,30 +3024,35 @@
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>24</v>
+        <v>443</v>
       </c>
       <c r="N62" t="n">
-        <v>24538.02</v>
+        <v>3877.89</v>
       </c>
       <c r="O62" t="n">
-        <v>588912.48</v>
+        <v>1717905.27</v>
       </c>
       <c r="P62" t="n">
-        <v>52900</v>
+        <v>6500</v>
       </c>
       <c r="Q62" t="n">
-        <v>1269600</v>
+        <v>2879500</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>C3455</t>
+          <t>C3700</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>DINOSAURIO BOLSA</t>
+          <t>MUNECA CON CARRO RECARGABLE DE CONTROL REMOTO</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3053,7 +3061,7 @@
         </is>
       </c>
       <c r="J63" t="n">
-        <v>288</v>
+        <v>6</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
@@ -3062,30 +3070,30 @@
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>288</v>
+        <v>6</v>
       </c>
       <c r="N63" t="n">
-        <v>5894.64</v>
+        <v>60174</v>
       </c>
       <c r="O63" t="n">
-        <v>1697656.32</v>
+        <v>361044</v>
       </c>
       <c r="P63" t="n">
-        <v>11000</v>
+        <v>96900</v>
       </c>
       <c r="Q63" t="n">
-        <v>3168000</v>
+        <v>581400</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>C3638</t>
+          <t>C3970</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>INFLABLE DONA</t>
+          <t>GUITARRAS C3970</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3095,11 +3103,11 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>443</v>
+        <v>48</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -3108,35 +3116,30 @@
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>443</v>
+        <v>48</v>
       </c>
       <c r="N64" t="n">
-        <v>3877.89</v>
+        <v>26854</v>
       </c>
       <c r="O64" t="n">
-        <v>1717905.27</v>
+        <v>1288992</v>
       </c>
       <c r="P64" t="n">
-        <v>6500</v>
+        <v>43900</v>
       </c>
       <c r="Q64" t="n">
-        <v>2879500</v>
+        <v>2107200</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>C3700</t>
+          <t>C3988</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MUNECA CON CARRO RECARGABLE DE CONTROL REMOTO</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>DRAGÓN CAMINA CON LUZ Y SONIDO</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3145,7 +3148,7 @@
         </is>
       </c>
       <c r="J65" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
@@ -3154,30 +3157,30 @@
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="N65" t="n">
-        <v>60174</v>
+        <v>29700</v>
       </c>
       <c r="O65" t="n">
-        <v>361044</v>
+        <v>356400</v>
       </c>
       <c r="P65" t="n">
-        <v>96900</v>
+        <v>50500</v>
       </c>
       <c r="Q65" t="n">
-        <v>581400</v>
+        <v>606000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>C3970</t>
+          <t>C4303</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>GUITARRAS C3970</t>
+          <t>BEBE CON PIJAMA MED BOLSA PVC C4303</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3191,7 +3194,7 @@
         </is>
       </c>
       <c r="J66" t="n">
-        <v>48</v>
+        <v>300</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>
@@ -3200,39 +3203,44 @@
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>48</v>
+        <v>300</v>
       </c>
       <c r="N66" t="n">
-        <v>26854</v>
+        <v>18016</v>
       </c>
       <c r="O66" t="n">
-        <v>1288992</v>
+        <v>5404800</v>
       </c>
       <c r="P66" t="n">
-        <v>43900</v>
+        <v>29900</v>
       </c>
       <c r="Q66" t="n">
-        <v>2107200</v>
+        <v>8970000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>C3988</t>
+          <t>C4305</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>DRAGÓN CAMINA CON LUZ Y SONIDO</t>
+          <t>MUÑECA BEBE GRANDE CON PIJAMA EN BOLSA C4305</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J67" t="n">
-        <v>12</v>
+        <v>144</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
@@ -3241,30 +3249,30 @@
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>12</v>
+        <v>144</v>
       </c>
       <c r="N67" t="n">
-        <v>29700</v>
+        <v>25534</v>
       </c>
       <c r="O67" t="n">
-        <v>356400</v>
+        <v>3676896</v>
       </c>
       <c r="P67" t="n">
-        <v>50500</v>
+        <v>40900</v>
       </c>
       <c r="Q67" t="n">
-        <v>606000</v>
+        <v>5889600</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>C4303</t>
+          <t>C4310</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>BEBE CON PIJAMA MED BOLSA PVC C4303</t>
+          <t>MUÑECA CON CARRO HUMO RECARGABLE C4310</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3278,7 +3286,7 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>300</v>
+        <v>32</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
@@ -3287,30 +3295,30 @@
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>300</v>
+        <v>32</v>
       </c>
       <c r="N68" t="n">
-        <v>18016</v>
+        <v>72889</v>
       </c>
       <c r="O68" t="n">
-        <v>5404800</v>
+        <v>2332448</v>
       </c>
       <c r="P68" t="n">
-        <v>29900</v>
+        <v>117500</v>
       </c>
       <c r="Q68" t="n">
-        <v>8970000</v>
+        <v>3760000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>C4305</t>
+          <t>C4545</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MUÑECA BEBE GRANDE CON PIJAMA EN BOLSA C4305</t>
+          <t>TAPETE PIANO PARA BEBE C4545</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3324,7 +3332,7 @@
         </is>
       </c>
       <c r="J69" t="n">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
@@ -3333,30 +3341,30 @@
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="N69" t="n">
-        <v>25534</v>
+        <v>27186</v>
       </c>
       <c r="O69" t="n">
-        <v>3676896</v>
+        <v>543720</v>
       </c>
       <c r="P69" t="n">
-        <v>40900</v>
+        <v>43900</v>
       </c>
       <c r="Q69" t="n">
-        <v>5889600</v>
+        <v>878000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>C4310</t>
+          <t>C4728</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MUÑECA CON CARRO HUMO RECARGABLE C4310</t>
+          <t>FLIOTADOR DONA DINOSAURIO #60 C4728</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3370,7 +3378,7 @@
         </is>
       </c>
       <c r="J70" t="n">
-        <v>32</v>
+        <v>1800</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
@@ -3379,44 +3387,47 @@
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>32</v>
+        <v>1800</v>
       </c>
       <c r="N70" t="n">
-        <v>72889</v>
+        <v>2454</v>
       </c>
       <c r="O70" t="n">
-        <v>2332448</v>
+        <v>4417200</v>
       </c>
       <c r="P70" t="n">
-        <v>117500</v>
+        <v>4200</v>
       </c>
       <c r="Q70" t="n">
-        <v>3760000</v>
+        <v>7560000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>C4545</t>
-        </is>
+          <t>C488</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>6554632300006</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>TAPETE PIANO PARA BEBE C4545</t>
+          <t>MALETA JUGUETES</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J71" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
@@ -3425,35 +3436,38 @@
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="N71" t="n">
-        <v>27186</v>
+        <v>18491</v>
       </c>
       <c r="O71" t="n">
-        <v>543720</v>
+        <v>221892</v>
       </c>
       <c r="P71" t="n">
-        <v>43900</v>
+        <v>13500</v>
       </c>
       <c r="Q71" t="n">
-        <v>878000</v>
+        <v>162000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>C4728</t>
-        </is>
+          <t>C5032</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>6999899236154</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>FLIOTADOR DONA DINOSAURIO #60 C4728</t>
+          <t>INFLABLE TECHITO PIECITOS  FIGURAS STD C5032</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>INFLABLES</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3462,7 +3476,7 @@
         </is>
       </c>
       <c r="J72" t="n">
-        <v>1800</v>
+        <v>937</v>
       </c>
       <c r="K72" t="n">
         <v>0</v>
@@ -3471,38 +3485,35 @@
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>1800</v>
+        <v>937</v>
       </c>
       <c r="N72" t="n">
-        <v>2454</v>
+        <v>8945.379999999999</v>
       </c>
       <c r="O72" t="n">
-        <v>4417200</v>
+        <v>8381821.06</v>
       </c>
       <c r="P72" t="n">
-        <v>4200</v>
+        <v>14900</v>
       </c>
       <c r="Q72" t="n">
-        <v>7560000</v>
+        <v>13961300</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>C488</t>
-        </is>
-      </c>
-      <c r="B73" t="n">
-        <v>6554632300006</v>
+          <t>C698</t>
+        </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MALETA JUGUETES</t>
+          <t>HELICE 9 LUCES</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3511,7 +3522,7 @@
         </is>
       </c>
       <c r="J73" t="n">
-        <v>12</v>
+        <v>240</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -3520,38 +3531,35 @@
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>12</v>
+        <v>240</v>
       </c>
       <c r="N73" t="n">
-        <v>18491</v>
+        <v>1567.02</v>
       </c>
       <c r="O73" t="n">
-        <v>221892</v>
+        <v>376084.8</v>
       </c>
       <c r="P73" t="n">
-        <v>13500</v>
+        <v>2900</v>
       </c>
       <c r="Q73" t="n">
-        <v>162000</v>
+        <v>696000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>C5032</t>
-        </is>
-      </c>
-      <c r="B74" t="n">
-        <v>6999899236154</v>
+          <t>C7560</t>
+        </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>INFLABLE TECHITO PIECITOS  FIGURAS STD C5032</t>
+          <t>BARRA LUMINOSA 48CM C7560/211</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>INFLABLES</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3560,7 +3568,7 @@
         </is>
       </c>
       <c r="J74" t="n">
-        <v>937</v>
+        <v>10</v>
       </c>
       <c r="K74" t="n">
         <v>0</v>
@@ -3569,44 +3577,47 @@
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>937</v>
+        <v>10</v>
       </c>
       <c r="N74" t="n">
-        <v>8945.379999999999</v>
+        <v>796.3099999999999</v>
       </c>
       <c r="O74" t="n">
-        <v>8381821.06</v>
+        <v>7963.099999999999</v>
       </c>
       <c r="P74" t="n">
-        <v>14900</v>
+        <v>2500</v>
       </c>
       <c r="Q74" t="n">
-        <v>13961300</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>C698</t>
-        </is>
+          <t>C7610</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>6999899236093</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>HELICE 9 LUCES</t>
+          <t>BOTE TIMON PISCINA 80X60 C7610</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>INFLABLES</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J75" t="n">
-        <v>240</v>
+        <v>360</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
@@ -3615,113 +3626,18 @@
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>240</v>
+        <v>360</v>
       </c>
       <c r="N75" t="n">
-        <v>1567.02</v>
+        <v>7811.9</v>
       </c>
       <c r="O75" t="n">
-        <v>376084.8</v>
+        <v>2812284</v>
       </c>
       <c r="P75" t="n">
-        <v>2900</v>
+        <v>13900</v>
       </c>
       <c r="Q75" t="n">
-        <v>696000</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>C7560</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>BARRA LUMINOSA 48CM C7560/211</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>PIÑATERIA</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J76" t="n">
-        <v>10</v>
-      </c>
-      <c r="K76" t="n">
-        <v>0</v>
-      </c>
-      <c r="L76" t="n">
-        <v>0</v>
-      </c>
-      <c r="M76" t="n">
-        <v>10</v>
-      </c>
-      <c r="N76" t="n">
-        <v>796.3099999999999</v>
-      </c>
-      <c r="O76" t="n">
-        <v>7963.099999999999</v>
-      </c>
-      <c r="P76" t="n">
-        <v>2500</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>25000</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>C7610</t>
-        </is>
-      </c>
-      <c r="B77" t="n">
-        <v>6999899236093</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>BOTE TIMON PISCINA 80X60 C7610</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>INFLABLES</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J77" t="n">
-        <v>480</v>
-      </c>
-      <c r="K77" t="n">
-        <v>0</v>
-      </c>
-      <c r="L77" t="n">
-        <v>120</v>
-      </c>
-      <c r="M77" t="n">
-        <v>360</v>
-      </c>
-      <c r="N77" t="n">
-        <v>7811.9</v>
-      </c>
-      <c r="O77" t="n">
-        <v>2812284</v>
-      </c>
-      <c r="P77" t="n">
-        <v>13900</v>
-      </c>
-      <c r="Q77" t="n">
         <v>5004000</v>
       </c>
     </row>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-09</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-10</t>
         </is>
       </c>
     </row>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -557,10 +557,10 @@
         <v>8</v>
       </c>
       <c r="N4" t="n">
-        <v>96741.407125</v>
+        <v>96741.407307692</v>
       </c>
       <c r="O4" t="n">
-        <v>773931.257</v>
+        <v>773931.258461536</v>
       </c>
       <c r="P4" t="n">
         <v>188900</v>
@@ -604,10 +604,10 @@
         <v>2</v>
       </c>
       <c r="N5" t="n">
-        <v>74676.65386363601</v>
+        <v>74676.651315789</v>
       </c>
       <c r="O5" t="n">
-        <v>149353.307727272</v>
+        <v>149353.302631578</v>
       </c>
       <c r="P5" t="n">
         <v>144900</v>
@@ -724,10 +724,10 @@
         <v>42</v>
       </c>
       <c r="N8" t="n">
-        <v>27815.961111111</v>
+        <v>27815.961126761</v>
       </c>
       <c r="O8" t="n">
-        <v>1168270.366666662</v>
+        <v>1168270.367323962</v>
       </c>
       <c r="P8" t="n">
         <v>58600</v>
@@ -1523,10 +1523,10 @@
         <v>10</v>
       </c>
       <c r="N27" t="n">
-        <v>16486.410204082</v>
+        <v>16486.41</v>
       </c>
       <c r="O27" t="n">
-        <v>164864.10204082</v>
+        <v>164864.1</v>
       </c>
       <c r="P27" t="n">
         <v>30500</v>
@@ -1565,10 +1565,10 @@
         <v>36</v>
       </c>
       <c r="N28" t="n">
-        <v>15711.9662</v>
+        <v>15711.966184739</v>
       </c>
       <c r="O28" t="n">
-        <v>565630.7832000001</v>
+        <v>565630.782650604</v>
       </c>
       <c r="P28" t="n">
         <v>28500</v>
@@ -1612,10 +1612,10 @@
         <v>10</v>
       </c>
       <c r="N29" t="n">
-        <v>30238.812307692</v>
+        <v>30238.812337662</v>
       </c>
       <c r="O29" t="n">
-        <v>302388.12307692</v>
+        <v>302388.12337662</v>
       </c>
       <c r="P29" t="n">
         <v>51100</v>
@@ -1928,10 +1928,10 @@
         <v>34</v>
       </c>
       <c r="N36" t="n">
-        <v>200072.19914894</v>
+        <v>200072.19977273</v>
       </c>
       <c r="O36" t="n">
-        <v>6802454.77106396</v>
+        <v>6802454.79227282</v>
       </c>
       <c r="P36" t="n">
         <v>312000</v>
@@ -1970,10 +1970,10 @@
         <v>16</v>
       </c>
       <c r="N37" t="n">
-        <v>174389.78756757</v>
+        <v>174389.79096774</v>
       </c>
       <c r="O37" t="n">
-        <v>2790236.60108112</v>
+        <v>2790236.65548384</v>
       </c>
       <c r="P37" t="n">
         <v>368200</v>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-10</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-11</t>
         </is>
       </c>
     </row>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -1155,10 +1155,10 @@
         <v>324</v>
       </c>
       <c r="N18" t="n">
-        <v>3926.8371296771</v>
+        <v>3926.8371267317</v>
       </c>
       <c r="O18" t="n">
-        <v>1272295.230015381</v>
+        <v>1272295.229061071</v>
       </c>
       <c r="P18" t="n">
         <v>4800</v>
@@ -1439,10 +1439,10 @@
         <v>2</v>
       </c>
       <c r="N25" t="n">
-        <v>30708.894545455</v>
+        <v>30708.882222222</v>
       </c>
       <c r="O25" t="n">
-        <v>61417.78909091</v>
+        <v>61417.764444444</v>
       </c>
       <c r="P25" t="n">
         <v>53500</v>
@@ -1481,10 +1481,10 @@
         <v>12</v>
       </c>
       <c r="N26" t="n">
-        <v>12837.964861111</v>
+        <v>12837.965507246</v>
       </c>
       <c r="O26" t="n">
-        <v>154055.578333332</v>
+        <v>154055.586086952</v>
       </c>
       <c r="P26" t="n">
         <v>22900</v>
@@ -1523,10 +1523,10 @@
         <v>10</v>
       </c>
       <c r="N27" t="n">
-        <v>16486.41</v>
+        <v>16486.409489051</v>
       </c>
       <c r="O27" t="n">
-        <v>164864.1</v>
+        <v>164864.09489051</v>
       </c>
       <c r="P27" t="n">
         <v>30500</v>
@@ -1565,10 +1565,10 @@
         <v>36</v>
       </c>
       <c r="N28" t="n">
-        <v>15711.966184739</v>
+        <v>15711.966106557</v>
       </c>
       <c r="O28" t="n">
-        <v>565630.782650604</v>
+        <v>565630.779836052</v>
       </c>
       <c r="P28" t="n">
         <v>28500</v>
@@ -1612,10 +1612,10 @@
         <v>10</v>
       </c>
       <c r="N29" t="n">
-        <v>30238.812337662</v>
+        <v>30238.8124</v>
       </c>
       <c r="O29" t="n">
-        <v>302388.12337662</v>
+        <v>302388.124</v>
       </c>
       <c r="P29" t="n">
         <v>51100</v>
@@ -1970,10 +1970,10 @@
         <v>16</v>
       </c>
       <c r="N37" t="n">
-        <v>174389.79096774</v>
+        <v>174389.79241379</v>
       </c>
       <c r="O37" t="n">
-        <v>2790236.65548384</v>
+        <v>2790236.67862064</v>
       </c>
       <c r="P37" t="n">
         <v>368200</v>
@@ -2064,10 +2064,10 @@
         <v>6</v>
       </c>
       <c r="N39" t="n">
-        <v>344599.1787931</v>
+        <v>344599.17865385</v>
       </c>
       <c r="O39" t="n">
-        <v>2067595.0727586</v>
+        <v>2067595.0719231</v>
       </c>
       <c r="P39" t="n">
         <v>532900</v>
@@ -2220,10 +2220,10 @@
         <v>67</v>
       </c>
       <c r="N43" t="n">
-        <v>61666.873852041</v>
+        <v>61666.873861893</v>
       </c>
       <c r="O43" t="n">
-        <v>4131680.548086747</v>
+        <v>4131680.548746831</v>
       </c>
       <c r="P43" t="n">
         <v>98900</v>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-11</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-12</t>
         </is>
       </c>
     </row>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -557,10 +557,10 @@
         <v>8</v>
       </c>
       <c r="N4" t="n">
-        <v>96741.407307692</v>
+        <v>96741.407402597</v>
       </c>
       <c r="O4" t="n">
-        <v>773931.258461536</v>
+        <v>773931.259220776</v>
       </c>
       <c r="P4" t="n">
         <v>188900</v>
@@ -604,10 +604,10 @@
         <v>2</v>
       </c>
       <c r="N5" t="n">
-        <v>74676.651315789</v>
+        <v>74676.651794872</v>
       </c>
       <c r="O5" t="n">
-        <v>149353.302631578</v>
+        <v>149353.303589744</v>
       </c>
       <c r="P5" t="n">
         <v>144900</v>
@@ -1274,22 +1274,22 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="M21" t="n">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2413.0010330579</v>
+        <v>2413.001059322</v>
       </c>
       <c r="O21" t="n">
-        <v>284734.1219008322</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
         <v>4700</v>
       </c>
       <c r="Q21" t="n">
-        <v>554600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1397,10 +1397,10 @@
         <v>21</v>
       </c>
       <c r="N24" t="n">
-        <v>3910.628245614</v>
+        <v>3910.6282352941</v>
       </c>
       <c r="O24" t="n">
-        <v>82123.193157894</v>
+        <v>82123.19294117609</v>
       </c>
       <c r="P24" t="n">
         <v>9100</v>
@@ -1565,10 +1565,10 @@
         <v>36</v>
       </c>
       <c r="N28" t="n">
-        <v>15711.966106557</v>
+        <v>15711.966058091</v>
       </c>
       <c r="O28" t="n">
-        <v>565630.779836052</v>
+        <v>565630.7780912761</v>
       </c>
       <c r="P28" t="n">
         <v>28500</v>
@@ -1839,10 +1839,10 @@
         <v>1</v>
       </c>
       <c r="N34" t="n">
-        <v>56906.800571429</v>
+        <v>56906.801935484</v>
       </c>
       <c r="O34" t="n">
-        <v>56906.800571429</v>
+        <v>56906.801935484</v>
       </c>
       <c r="P34" t="n">
         <v>95900</v>
@@ -1886,10 +1886,10 @@
         <v>56</v>
       </c>
       <c r="N35" t="n">
-        <v>141416.88453074</v>
+        <v>141416.88454545</v>
       </c>
       <c r="O35" t="n">
-        <v>7919345.53372144</v>
+        <v>7919345.534545201</v>
       </c>
       <c r="P35" t="n">
         <v>251900</v>
@@ -2220,10 +2220,10 @@
         <v>67</v>
       </c>
       <c r="N43" t="n">
-        <v>61666.873861893</v>
+        <v>61666.873932292</v>
       </c>
       <c r="O43" t="n">
-        <v>4131680.548746831</v>
+        <v>4131680.553463564</v>
       </c>
       <c r="P43" t="n">
         <v>98900</v>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q75"/>
+  <dimension ref="A1:Q74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-12</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-13</t>
         </is>
       </c>
     </row>
@@ -1255,11 +1255,11 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>36013</v>
+        <v>36405</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>FLOTADOR ARO 56CM BESTWAY 36 PCS</t>
+          <t>FLOTADOR ARO ANIMALES BESTWAY 36PCS</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1268,37 +1268,37 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>118</v>
+        <v>792</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="N21" t="n">
-        <v>2413.001059322</v>
+        <v>2681</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2123352</v>
       </c>
       <c r="P21" t="n">
-        <v>4700</v>
+        <v>3500</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2772000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>36405</v>
+        <v>41037</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>FLOTADOR ARO ANIMALES BESTWAY 36PCS</t>
+          <t>41037 FLOTADOR BALLENA BESTWAY 12PCS</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>792</v>
+        <v>13</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1316,28 +1316,28 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>792</v>
+        <v>13</v>
       </c>
       <c r="N22" t="n">
-        <v>2681</v>
+        <v>15403.520914286</v>
       </c>
       <c r="O22" t="n">
-        <v>2123352</v>
+        <v>200245.771885718</v>
       </c>
       <c r="P22" t="n">
-        <v>3500</v>
+        <v>33500</v>
       </c>
       <c r="Q22" t="n">
-        <v>2772000</v>
+        <v>435500</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>41037</v>
+        <v>44007</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>41037 FLOTADOR BALLENA BESTWAY 12PCS</t>
+          <t>COLCHONETA INFLABLE 69CM BESTWAY</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1346,7 +1346,7 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -1355,28 +1355,31 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="N23" t="n">
-        <v>15403.520914286</v>
+        <v>3910.6282352941</v>
       </c>
       <c r="O23" t="n">
-        <v>200245.771885718</v>
+        <v>82123.19294117609</v>
       </c>
       <c r="P23" t="n">
-        <v>33500</v>
+        <v>9100</v>
       </c>
       <c r="Q23" t="n">
-        <v>435500</v>
+        <v>191100</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>44007</v>
+        <v>51005</v>
+      </c>
+      <c r="B24" t="n">
+        <v>6941607363485</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>COLCHONETA INFLABLE 69CM BESTWAY</t>
+          <t>51005 PISCINA DEEP DIVE</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1385,7 +1388,7 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -1394,31 +1397,31 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="N24" t="n">
-        <v>3910.6282352941</v>
+        <v>30708.882222222</v>
       </c>
       <c r="O24" t="n">
-        <v>82123.19294117609</v>
+        <v>61417.764444444</v>
       </c>
       <c r="P24" t="n">
-        <v>9100</v>
+        <v>53500</v>
       </c>
       <c r="Q24" t="n">
-        <v>191100</v>
+        <v>107000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>51005</v>
+        <v>51008</v>
       </c>
       <c r="B25" t="n">
-        <v>6941607363485</v>
+        <v>6941607367575</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>51005 PISCINA DEEP DIVE</t>
+          <t>PISCINA CORAL 102 X25CM</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1427,7 +1430,7 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -1436,31 +1439,31 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="N25" t="n">
-        <v>30708.882222222</v>
+        <v>12837.965507246</v>
       </c>
       <c r="O25" t="n">
-        <v>61417.764444444</v>
+        <v>154055.586086952</v>
       </c>
       <c r="P25" t="n">
-        <v>53500</v>
+        <v>22900</v>
       </c>
       <c r="Q25" t="n">
-        <v>107000</v>
+        <v>274800</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>51008</v>
+        <v>51104</v>
       </c>
       <c r="B26" t="n">
-        <v>6941607367575</v>
+        <v>6942138915815</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>PISCINA CORAL 102 X25CM</t>
+          <t>PISCINA VERANO 102 X25 CM</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1469,7 +1472,7 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -1478,31 +1481,31 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N26" t="n">
-        <v>12837.965507246</v>
+        <v>16486.409489051</v>
       </c>
       <c r="O26" t="n">
-        <v>154055.586086952</v>
+        <v>164864.09489051</v>
       </c>
       <c r="P26" t="n">
-        <v>22900</v>
+        <v>30500</v>
       </c>
       <c r="Q26" t="n">
-        <v>274800</v>
+        <v>305000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>51104</v>
+        <v>51124</v>
       </c>
       <c r="B27" t="n">
-        <v>6942138915815</v>
+        <v>6941607325032</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>PISCINA VERANO 102 X25 CM</t>
+          <t>51124 COMBO DE PISCINA Y BALON</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1511,7 +1514,7 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -1520,40 +1523,45 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="N27" t="n">
-        <v>16486.409489051</v>
+        <v>15711.966058091</v>
       </c>
       <c r="O27" t="n">
-        <v>164864.09489051</v>
+        <v>565630.7780912761</v>
       </c>
       <c r="P27" t="n">
-        <v>30500</v>
+        <v>28500</v>
       </c>
       <c r="Q27" t="n">
-        <v>305000</v>
+        <v>1026000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>51124</v>
+        <v>51203</v>
       </c>
       <c r="B28" t="n">
-        <v>6941607325032</v>
+        <v>6941607325544</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>51124 COMBO DE PISCINA Y BALON</t>
+          <t>51203 PISCINA 3 AROS BESTWAY Φ1.68m x H38cm</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -1562,45 +1570,37 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="N28" t="n">
-        <v>15711.966058091</v>
+        <v>30238.8124</v>
       </c>
       <c r="O28" t="n">
-        <v>565630.7780912761</v>
+        <v>302388.124</v>
       </c>
       <c r="P28" t="n">
-        <v>28500</v>
+        <v>51100</v>
       </c>
       <c r="Q28" t="n">
-        <v>1026000</v>
+        <v>511000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>51203</v>
-      </c>
-      <c r="B29" t="n">
-        <v>6941607325544</v>
+        <v>52331</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>51203 PISCINA 3 AROS BESTWAY Φ1.68m x H38cm</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>PISCINA CANOPY FRUTICAS 8 PCS</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -1609,28 +1609,36 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="N29" t="n">
-        <v>30238.8124</v>
+        <v>20195.32</v>
       </c>
       <c r="O29" t="n">
-        <v>302388.124</v>
+        <v>1514649</v>
       </c>
       <c r="P29" t="n">
-        <v>51100</v>
+        <v>45900</v>
       </c>
       <c r="Q29" t="n">
-        <v>511000</v>
+        <v>3442500</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>52331</v>
+        <v>52637</v>
+      </c>
+      <c r="B30" t="n">
+        <v>6941607352212</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>PISCINA CANOPY FRUTICAS 8 PCS</t>
+          <t>52637 PISCINA TECHADA SUNNY BESTWAY</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1639,7 +1647,7 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>75</v>
+        <v>4</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -1648,31 +1656,31 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>75</v>
+        <v>4</v>
       </c>
       <c r="N30" t="n">
-        <v>20195.32</v>
+        <v>22267.552083333</v>
       </c>
       <c r="O30" t="n">
-        <v>1514649</v>
+        <v>89070.208333332</v>
       </c>
       <c r="P30" t="n">
-        <v>45900</v>
+        <v>46300</v>
       </c>
       <c r="Q30" t="n">
-        <v>3442500</v>
+        <v>185200</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>52637</v>
+        <v>53157</v>
       </c>
       <c r="B31" t="n">
-        <v>6941607352212</v>
+        <v>6941607352137</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>52637 PISCINA TECHADA SUNNY BESTWAY</t>
+          <t>53157 PISCINA FUENTE SHARK BESTWAY</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1698,28 +1706,28 @@
         <v>4</v>
       </c>
       <c r="N31" t="n">
-        <v>22267.552083333</v>
+        <v>36574.852142857</v>
       </c>
       <c r="O31" t="n">
-        <v>89070.208333332</v>
+        <v>146299.408571428</v>
       </c>
       <c r="P31" t="n">
-        <v>46300</v>
+        <v>65900</v>
       </c>
       <c r="Q31" t="n">
-        <v>185200</v>
+        <v>263600</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>53157</v>
+        <v>54370</v>
       </c>
       <c r="B32" t="n">
-        <v>6941607352137</v>
+        <v>6941607312643</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>53157 PISCINA FUENTE SHARK BESTWAY</t>
+          <t>PISCINA CAPITAN 213 X155 X 132CM</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1745,28 +1753,28 @@
         <v>4</v>
       </c>
       <c r="N32" t="n">
-        <v>36574.852142857</v>
+        <v>103298.75</v>
       </c>
       <c r="O32" t="n">
-        <v>146299.408571428</v>
+        <v>413195</v>
       </c>
       <c r="P32" t="n">
-        <v>65900</v>
+        <v>178900</v>
       </c>
       <c r="Q32" t="n">
-        <v>263600</v>
+        <v>715600</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>54370</v>
+        <v>55031</v>
       </c>
       <c r="B33" t="n">
-        <v>6941607312643</v>
+        <v>6942138913781</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>PISCINA CAPITAN 213 X155 X 132CM</t>
+          <t>55031 PISCINA DELFIN 2.44mx46cm</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1780,7 +1788,7 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -1789,31 +1797,31 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N33" t="n">
-        <v>103298.75</v>
+        <v>56906.801935484</v>
       </c>
       <c r="O33" t="n">
-        <v>413195</v>
+        <v>56906.801935484</v>
       </c>
       <c r="P33" t="n">
-        <v>178900</v>
+        <v>95900</v>
       </c>
       <c r="Q33" t="n">
-        <v>715600</v>
+        <v>95900</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>55031</v>
+        <v>56401</v>
       </c>
       <c r="B34" t="n">
-        <v>6942138913781</v>
+        <v>6941607327951</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>55031 PISCINA DELFIN 2.44mx46cm</t>
+          <t>56401 PISCINA ESTRUCTURAL RECTANGULAR BESTWAY</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1827,7 +1835,7 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -1836,45 +1844,40 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="N34" t="n">
-        <v>56906.801935484</v>
+        <v>141416.88454545</v>
       </c>
       <c r="O34" t="n">
-        <v>56906.801935484</v>
+        <v>7919345.534545201</v>
       </c>
       <c r="P34" t="n">
-        <v>95900</v>
+        <v>251900</v>
       </c>
       <c r="Q34" t="n">
-        <v>95900</v>
+        <v>14106400</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>56401</v>
+        <v>56403</v>
       </c>
       <c r="B35" t="n">
-        <v>6941607327951</v>
+        <v>6941607327982</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>56401 PISCINA ESTRUCTURAL RECTANGULAR BESTWAY</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>PISCINA ESTRUCTURAL 2.59m x 1.70m x 61cm BESTWAY</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -1883,40 +1886,40 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="N35" t="n">
-        <v>141416.88454545</v>
+        <v>200072.19977273</v>
       </c>
       <c r="O35" t="n">
-        <v>7919345.534545201</v>
+        <v>6802454.79227282</v>
       </c>
       <c r="P35" t="n">
-        <v>251900</v>
+        <v>312000</v>
       </c>
       <c r="Q35" t="n">
-        <v>14106400</v>
+        <v>10608000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>56403</v>
+        <v>56404</v>
       </c>
       <c r="B36" t="n">
-        <v>6941607327982</v>
+        <v>6941607327999</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>PISCINA ESTRUCTURAL 2.59m x 1.70m x 61cm BESTWAY</t>
+          <t>56404 PISCINA ESTRUCTURAL RECTANGULAR BESTWAY</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -1925,40 +1928,45 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="N36" t="n">
-        <v>200072.19977273</v>
+        <v>174389.79241379</v>
       </c>
       <c r="O36" t="n">
-        <v>6802454.79227282</v>
+        <v>2790236.67862064</v>
       </c>
       <c r="P36" t="n">
-        <v>312000</v>
+        <v>368200</v>
       </c>
       <c r="Q36" t="n">
-        <v>10608000</v>
+        <v>5891200</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>56404</v>
+        <v>56405</v>
       </c>
       <c r="B37" t="n">
-        <v>6941607327999</v>
+        <v>6941607328002</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>56404 PISCINA ESTRUCTURAL RECTANGULAR BESTWAY</t>
+          <t>PISCINA ESTRUCTURAL RECTAGULAR BESTWAY 4.00mX2.11mX81cm</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -1967,31 +1975,31 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="N37" t="n">
-        <v>174389.79241379</v>
+        <v>251809.29393939</v>
       </c>
       <c r="O37" t="n">
-        <v>2790236.67862064</v>
+        <v>1510855.76363634</v>
       </c>
       <c r="P37" t="n">
-        <v>368200</v>
+        <v>584000</v>
       </c>
       <c r="Q37" t="n">
-        <v>5891200</v>
+        <v>3504000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>56405</v>
+        <v>56417</v>
       </c>
       <c r="B38" t="n">
-        <v>6941607328002</v>
+        <v>6942138981902</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>PISCINA ESTRUCTURAL RECTAGULAR BESTWAY 4.00mX2.11mX81cm</t>
+          <t>Piscina Estructural Redonda 366 x 76 cm Bomba/Filtro 56417</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2017,38 +2025,30 @@
         <v>6</v>
       </c>
       <c r="N38" t="n">
-        <v>251809.29393939</v>
+        <v>344599.17865385</v>
       </c>
       <c r="O38" t="n">
-        <v>1510855.76363634</v>
+        <v>2067595.0719231</v>
       </c>
       <c r="P38" t="n">
-        <v>584000</v>
+        <v>532900</v>
       </c>
       <c r="Q38" t="n">
-        <v>3504000</v>
+        <v>3197400</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>56417</v>
-      </c>
-      <c r="B39" t="n">
-        <v>6942138981902</v>
+        <v>62068</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Piscina Estructural Redonda 366 x 76 cm Bomba/Filtro 56417</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>PARCHE PISCINA EXTERIOR BESTWAY</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J39" t="n">
@@ -2064,25 +2064,25 @@
         <v>6</v>
       </c>
       <c r="N39" t="n">
-        <v>344599.17865385</v>
+        <v>1977.88</v>
       </c>
       <c r="O39" t="n">
-        <v>2067595.0719231</v>
+        <v>11867.28</v>
       </c>
       <c r="P39" t="n">
-        <v>532900</v>
+        <v>2900</v>
       </c>
       <c r="Q39" t="n">
-        <v>3197400</v>
+        <v>17400</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>62068</v>
+        <v>62091</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>PARCHE PISCINA EXTERIOR BESTWAY</t>
+          <t>PARCHE PISCINA A PRUEBA DE AGUA BESTWAY</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2091,7 +2091,7 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>6</v>
+        <v>217</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -2100,28 +2100,28 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>6</v>
+        <v>217</v>
       </c>
       <c r="N40" t="n">
-        <v>1977.88</v>
+        <v>1141.57</v>
       </c>
       <c r="O40" t="n">
-        <v>11867.28</v>
+        <v>247720.69</v>
       </c>
       <c r="P40" t="n">
-        <v>2900</v>
+        <v>3900</v>
       </c>
       <c r="Q40" t="n">
-        <v>17400</v>
+        <v>846300</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>62091</v>
+        <v>67001</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>PARCHE PISCINA A PRUEBA DE AGUA BESTWAY</t>
+          <t>COLCHON INFLABLE SENCILLO BESTWAY 1.88 X 99 CM</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2130,7 +2130,7 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>217</v>
+        <v>3</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -2139,28 +2139,28 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>217</v>
+        <v>3</v>
       </c>
       <c r="N41" t="n">
-        <v>1141.57</v>
+        <v>26280.41</v>
       </c>
       <c r="O41" t="n">
-        <v>247720.69</v>
+        <v>78841.23</v>
       </c>
       <c r="P41" t="n">
-        <v>3900</v>
+        <v>46500</v>
       </c>
       <c r="Q41" t="n">
-        <v>846300</v>
+        <v>139500</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>67001</v>
+        <v>67374</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>COLCHON INFLABLE SENCILLO BESTWAY 1.88 X 99 CM</t>
+          <t>COLCHON INFLABLE DOBLE+ALMOHADAS BESTWAY 2.03mx1.52mx22cm</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2169,7 +2169,7 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>3</v>
+        <v>67</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -2178,28 +2178,28 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3</v>
+        <v>67</v>
       </c>
       <c r="N42" t="n">
-        <v>26280.41</v>
+        <v>61666.873932292</v>
       </c>
       <c r="O42" t="n">
-        <v>78841.23</v>
+        <v>4131680.553463564</v>
       </c>
       <c r="P42" t="n">
-        <v>46500</v>
+        <v>98900</v>
       </c>
       <c r="Q42" t="n">
-        <v>139500</v>
+        <v>6626300</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>67374</v>
+        <v>91004</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>COLCHON INFLABLE DOBLE+ALMOHADAS BESTWAY 2.03mx1.52mx22cm</t>
+          <t>FLOTADOR DISNEY 56CM 24PCS</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2208,7 +2208,7 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>67</v>
+        <v>340</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -2217,28 +2217,28 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>67</v>
+        <v>340</v>
       </c>
       <c r="N43" t="n">
-        <v>61666.873932292</v>
+        <v>3865.67</v>
       </c>
       <c r="O43" t="n">
-        <v>4131680.553463564</v>
+        <v>1314327.8</v>
       </c>
       <c r="P43" t="n">
-        <v>98900</v>
+        <v>5500</v>
       </c>
       <c r="Q43" t="n">
-        <v>6626300</v>
+        <v>1870000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>91004</v>
+        <v>91007</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>FLOTADOR DISNEY 56CM 24PCS</t>
+          <t>PISCINA DISNEY 122X25CM 12 PCS</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2247,7 +2247,7 @@
         </is>
       </c>
       <c r="J44" t="n">
-        <v>340</v>
+        <v>24</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -2256,28 +2256,35 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>340</v>
+        <v>24</v>
       </c>
       <c r="N44" t="n">
-        <v>3865.67</v>
+        <v>16010.3</v>
       </c>
       <c r="O44" t="n">
-        <v>1314327.8</v>
+        <v>384247.2</v>
       </c>
       <c r="P44" t="n">
-        <v>5500</v>
+        <v>30500</v>
       </c>
       <c r="Q44" t="n">
-        <v>1870000</v>
+        <v>732000</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="n">
-        <v>91007</v>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>9103C</t>
+        </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>PISCINA DISNEY 122X25CM 12 PCS</t>
+          <t>9103C GAFA ACUATICA SIRENITA BESTWAY</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2298,32 +2305,27 @@
         <v>24</v>
       </c>
       <c r="N45" t="n">
-        <v>16010.3</v>
+        <v>4878.2859036145</v>
       </c>
       <c r="O45" t="n">
-        <v>384247.2</v>
+        <v>117078.861686748</v>
       </c>
       <c r="P45" t="n">
-        <v>30500</v>
+        <v>13500</v>
       </c>
       <c r="Q45" t="n">
-        <v>732000</v>
+        <v>324000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>9103C</t>
+          <t>9103D</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>9103C GAFA ACUATICA SIRENITA BESTWAY</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>9103D CARETA ACUATICA SIRENITA BESTWAY</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2332,7 +2334,7 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -2341,30 +2343,28 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="N46" t="n">
-        <v>4878.2859036145</v>
+        <v>7394.9354444444</v>
       </c>
       <c r="O46" t="n">
-        <v>117078.861686748</v>
+        <v>88739.2253333328</v>
       </c>
       <c r="P46" t="n">
-        <v>13500</v>
+        <v>17900</v>
       </c>
       <c r="Q46" t="n">
-        <v>324000</v>
+        <v>214800</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>9103D</t>
-        </is>
+      <c r="A47" t="n">
+        <v>91040</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>9103D CARETA ACUATICA SIRENITA BESTWAY</t>
+          <t>FLOTADOR MINNIE 56CM 24 PCS</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>12</v>
+        <v>402</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -2382,28 +2382,28 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>12</v>
+        <v>402</v>
       </c>
       <c r="N47" t="n">
-        <v>7394.9354444444</v>
+        <v>3114.49</v>
       </c>
       <c r="O47" t="n">
-        <v>88739.2253333328</v>
+        <v>1252024.98</v>
       </c>
       <c r="P47" t="n">
-        <v>17900</v>
+        <v>5500</v>
       </c>
       <c r="Q47" t="n">
-        <v>214800</v>
+        <v>2211000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>91040</v>
+        <v>91042</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>FLOTADOR MINNIE 56CM 24 PCS</t>
+          <t>PELOTA PISCINA PRINCESAS 24 PCS</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2412,7 +2412,7 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>402</v>
+        <v>120</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
@@ -2421,28 +2421,28 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>402</v>
+        <v>120</v>
       </c>
       <c r="N48" t="n">
-        <v>3114.49</v>
+        <v>2791.02</v>
       </c>
       <c r="O48" t="n">
-        <v>1252024.98</v>
+        <v>334922.4</v>
       </c>
       <c r="P48" t="n">
-        <v>5500</v>
+        <v>3900</v>
       </c>
       <c r="Q48" t="n">
-        <v>2211000</v>
+        <v>468000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>91042</v>
+        <v>91043</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>PELOTA PISCINA PRINCESAS 24 PCS</t>
+          <t>FLOTADOR PRINCESAS 56CM 24PCS</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>120</v>
+        <v>58</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -2460,28 +2460,28 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>120</v>
+        <v>58</v>
       </c>
       <c r="N49" t="n">
-        <v>2791.02</v>
+        <v>3564.14</v>
       </c>
       <c r="O49" t="n">
-        <v>334922.4</v>
+        <v>206720.12</v>
       </c>
       <c r="P49" t="n">
-        <v>3900</v>
+        <v>5500</v>
       </c>
       <c r="Q49" t="n">
-        <v>468000</v>
+        <v>319000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>91043</v>
+        <v>91098</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>FLOTADOR PRINCESAS 56CM 24PCS</t>
+          <t>BALON INFLABLE MICKEY 51CM</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2490,7 +2490,7 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>58</v>
+        <v>183</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -2499,28 +2499,28 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>58</v>
+        <v>183</v>
       </c>
       <c r="N50" t="n">
-        <v>3564.14</v>
+        <v>4378</v>
       </c>
       <c r="O50" t="n">
-        <v>206720.12</v>
+        <v>801174</v>
       </c>
       <c r="P50" t="n">
-        <v>5500</v>
+        <v>3900</v>
       </c>
       <c r="Q50" t="n">
-        <v>319000</v>
+        <v>713700</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>91098</v>
+        <v>98002</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>BALON INFLABLE MICKEY 51CM</t>
+          <t>PELOTA PISCINA SIPDERMAN  51CM</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2529,7 +2529,7 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>183</v>
+        <v>264</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
@@ -2538,28 +2538,28 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>183</v>
+        <v>264</v>
       </c>
       <c r="N51" t="n">
-        <v>4378</v>
+        <v>3340.6800808081</v>
       </c>
       <c r="O51" t="n">
-        <v>801174</v>
+        <v>881939.5413333384</v>
       </c>
       <c r="P51" t="n">
-        <v>3900</v>
+        <v>7100</v>
       </c>
       <c r="Q51" t="n">
-        <v>713700</v>
+        <v>1874400</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>98002</v>
+        <v>98003</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>PELOTA PISCINA SIPDERMAN  51CM</t>
+          <t>FLOTADOR SPIDER MAN 56CM 24 PCS</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>264</v>
+        <v>67</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
@@ -2577,28 +2577,35 @@
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>264</v>
+        <v>67</v>
       </c>
       <c r="N52" t="n">
-        <v>3340.6800808081</v>
+        <v>2903.52</v>
       </c>
       <c r="O52" t="n">
-        <v>881939.5413333384</v>
+        <v>194535.84</v>
       </c>
       <c r="P52" t="n">
         <v>7100</v>
       </c>
       <c r="Q52" t="n">
-        <v>1874400</v>
+        <v>475700</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="n">
-        <v>98003</v>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>C105</t>
+        </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>FLOTADOR SPIDER MAN 56CM 24 PCS</t>
+          <t>SCOOTER COLORES</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2607,7 +2614,7 @@
         </is>
       </c>
       <c r="J53" t="n">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
@@ -2616,30 +2623,30 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="N53" t="n">
-        <v>2903.52</v>
+        <v>39171.85</v>
       </c>
       <c r="O53" t="n">
-        <v>194535.84</v>
+        <v>705093.2999999999</v>
       </c>
       <c r="P53" t="n">
-        <v>7100</v>
+        <v>68900</v>
       </c>
       <c r="Q53" t="n">
-        <v>475700</v>
+        <v>1240200</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C1370</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>SCOOTER COLORES</t>
+          <t>LLAVERO PELUCHES STD C1370</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2649,11 +2656,11 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
@@ -2662,44 +2669,39 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="N54" t="n">
-        <v>39171.85</v>
+        <v>3472</v>
       </c>
       <c r="O54" t="n">
-        <v>705093.2999999999</v>
+        <v>868000</v>
       </c>
       <c r="P54" t="n">
-        <v>68900</v>
+        <v>4800</v>
       </c>
       <c r="Q54" t="n">
-        <v>1240200</v>
+        <v>1200000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>C1370</t>
+          <t>C1717</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>LLAVERO PELUCHES STD C1370</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>ESPADA CON LUZ Y SONIDO</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>250</v>
+        <v>432</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
@@ -2708,30 +2710,38 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>250</v>
+        <v>432</v>
       </c>
       <c r="N55" t="n">
-        <v>3472</v>
+        <v>4443</v>
       </c>
       <c r="O55" t="n">
-        <v>868000</v>
+        <v>1919376</v>
       </c>
       <c r="P55" t="n">
-        <v>4800</v>
+        <v>6300</v>
       </c>
       <c r="Q55" t="n">
-        <v>1200000</v>
+        <v>2721600</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>C1717</t>
-        </is>
+          <t>C1758</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>6914919067549</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ESPADA CON LUZ Y SONIDO</t>
+          <t>MULA BLISTER SURTIDA</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2740,7 +2750,7 @@
         </is>
       </c>
       <c r="J56" t="n">
-        <v>432</v>
+        <v>180</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -2749,33 +2759,33 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>432</v>
+        <v>180</v>
       </c>
       <c r="N56" t="n">
-        <v>4443</v>
+        <v>4648.6</v>
       </c>
       <c r="O56" t="n">
-        <v>1919376</v>
+        <v>836748.0000000001</v>
       </c>
       <c r="P56" t="n">
-        <v>6300</v>
+        <v>8900</v>
       </c>
       <c r="Q56" t="n">
-        <v>2721600</v>
+        <v>1602000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>C1758</t>
+          <t>C1897</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>6914919067549</v>
+        <v>6914919086373</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>MULA BLISTER SURTIDA</t>
+          <t>MULA DIDACTICA</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2789,7 +2799,7 @@
         </is>
       </c>
       <c r="J57" t="n">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
@@ -2798,38 +2808,30 @@
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="N57" t="n">
-        <v>4648.6</v>
+        <v>16897</v>
       </c>
       <c r="O57" t="n">
-        <v>836748.0000000001</v>
+        <v>2838696</v>
       </c>
       <c r="P57" t="n">
-        <v>8900</v>
+        <v>27900</v>
       </c>
       <c r="Q57" t="n">
-        <v>1602000</v>
+        <v>4687200</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>C1897</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>6914919086373</v>
+          <t>C2117</t>
+        </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>MULA DIDACTICA</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>DISPLAY CARTÓN PEGAJOSOS X 20</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -2838,7 +2840,7 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>168</v>
+        <v>1400</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
@@ -2847,30 +2849,38 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>168</v>
+        <v>1400</v>
       </c>
       <c r="N58" t="n">
-        <v>16897</v>
+        <v>3751</v>
       </c>
       <c r="O58" t="n">
-        <v>2838696</v>
+        <v>5251400</v>
       </c>
       <c r="P58" t="n">
-        <v>27900</v>
+        <v>6400</v>
       </c>
       <c r="Q58" t="n">
-        <v>4687200</v>
+        <v>8960000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>C2117</t>
-        </is>
+          <t>C342</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>6914919018374</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>DISPLAY CARTÓN PEGAJOSOS X 20</t>
+          <t>COCINA CON VAPOR DE AGUA</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -2879,7 +2889,7 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>1400</v>
+        <v>24</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
@@ -2888,38 +2898,30 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>1400</v>
+        <v>24</v>
       </c>
       <c r="N59" t="n">
-        <v>3751</v>
+        <v>24538.02</v>
       </c>
       <c r="O59" t="n">
-        <v>5251400</v>
+        <v>588912.48</v>
       </c>
       <c r="P59" t="n">
-        <v>6400</v>
+        <v>52900</v>
       </c>
       <c r="Q59" t="n">
-        <v>8960000</v>
+        <v>1269600</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>C342</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>6914919018374</v>
+          <t>C3455</t>
+        </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>COCINA CON VAPOR DE AGUA</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>DINOSAURIO BOLSA</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -2928,7 +2930,7 @@
         </is>
       </c>
       <c r="J60" t="n">
-        <v>24</v>
+        <v>288</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
@@ -2937,30 +2939,35 @@
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>24</v>
+        <v>288</v>
       </c>
       <c r="N60" t="n">
-        <v>24538.02</v>
+        <v>5894.64</v>
       </c>
       <c r="O60" t="n">
-        <v>588912.48</v>
+        <v>1697656.32</v>
       </c>
       <c r="P60" t="n">
-        <v>52900</v>
+        <v>11000</v>
       </c>
       <c r="Q60" t="n">
-        <v>1269600</v>
+        <v>3168000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>C3455</t>
+          <t>C3638</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>DINOSAURIO BOLSA</t>
+          <t>INFLABLE DONA</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -2969,7 +2976,7 @@
         </is>
       </c>
       <c r="J61" t="n">
-        <v>288</v>
+        <v>443</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
@@ -2978,30 +2985,30 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>288</v>
+        <v>443</v>
       </c>
       <c r="N61" t="n">
-        <v>5894.64</v>
+        <v>3877.89</v>
       </c>
       <c r="O61" t="n">
-        <v>1697656.32</v>
+        <v>1717905.27</v>
       </c>
       <c r="P61" t="n">
-        <v>11000</v>
+        <v>6500</v>
       </c>
       <c r="Q61" t="n">
-        <v>3168000</v>
+        <v>2879500</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>C3638</t>
+          <t>C3700</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>INFLABLE DONA</t>
+          <t>MUNECA CON CARRO RECARGABLE DE CONTROL REMOTO</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3015,7 +3022,7 @@
         </is>
       </c>
       <c r="J62" t="n">
-        <v>443</v>
+        <v>6</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
@@ -3024,30 +3031,30 @@
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>443</v>
+        <v>6</v>
       </c>
       <c r="N62" t="n">
-        <v>3877.89</v>
+        <v>60174</v>
       </c>
       <c r="O62" t="n">
-        <v>1717905.27</v>
+        <v>361044</v>
       </c>
       <c r="P62" t="n">
-        <v>6500</v>
+        <v>96900</v>
       </c>
       <c r="Q62" t="n">
-        <v>2879500</v>
+        <v>581400</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>C3700</t>
+          <t>C3970</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>MUNECA CON CARRO RECARGABLE DE CONTROL REMOTO</t>
+          <t>GUITARRAS C3970</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3057,11 +3064,11 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
@@ -3070,44 +3077,39 @@
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="N63" t="n">
-        <v>60174</v>
+        <v>26854</v>
       </c>
       <c r="O63" t="n">
-        <v>361044</v>
+        <v>1288992</v>
       </c>
       <c r="P63" t="n">
-        <v>96900</v>
+        <v>43900</v>
       </c>
       <c r="Q63" t="n">
-        <v>581400</v>
+        <v>2107200</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>C3970</t>
+          <t>C3988</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>GUITARRAS C3970</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>DRAGÓN CAMINA CON LUZ Y SONIDO</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -3116,39 +3118,44 @@
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="N64" t="n">
-        <v>26854</v>
+        <v>29700</v>
       </c>
       <c r="O64" t="n">
-        <v>1288992</v>
+        <v>356400</v>
       </c>
       <c r="P64" t="n">
-        <v>43900</v>
+        <v>50500</v>
       </c>
       <c r="Q64" t="n">
-        <v>2107200</v>
+        <v>606000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>C3988</t>
+          <t>C4303</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>DRAGÓN CAMINA CON LUZ Y SONIDO</t>
+          <t>BEBE CON PIJAMA MED BOLSA PVC C4303</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J65" t="n">
-        <v>12</v>
+        <v>300</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
@@ -3157,30 +3164,30 @@
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>12</v>
+        <v>300</v>
       </c>
       <c r="N65" t="n">
-        <v>29700</v>
+        <v>18016</v>
       </c>
       <c r="O65" t="n">
-        <v>356400</v>
+        <v>5404800</v>
       </c>
       <c r="P65" t="n">
-        <v>50500</v>
+        <v>29900</v>
       </c>
       <c r="Q65" t="n">
-        <v>606000</v>
+        <v>8970000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>C4303</t>
+          <t>C4305</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>BEBE CON PIJAMA MED BOLSA PVC C4303</t>
+          <t>MUÑECA BEBE GRANDE CON PIJAMA EN BOLSA C4305</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3194,7 +3201,7 @@
         </is>
       </c>
       <c r="J66" t="n">
-        <v>300</v>
+        <v>144</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>
@@ -3203,30 +3210,30 @@
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>300</v>
+        <v>144</v>
       </c>
       <c r="N66" t="n">
-        <v>18016</v>
+        <v>25534</v>
       </c>
       <c r="O66" t="n">
-        <v>5404800</v>
+        <v>3676896</v>
       </c>
       <c r="P66" t="n">
-        <v>29900</v>
+        <v>40900</v>
       </c>
       <c r="Q66" t="n">
-        <v>8970000</v>
+        <v>5889600</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>C4305</t>
+          <t>C4310</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>MUÑECA BEBE GRANDE CON PIJAMA EN BOLSA C4305</t>
+          <t>MUÑECA CON CARRO HUMO RECARGABLE C4310</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3240,7 +3247,7 @@
         </is>
       </c>
       <c r="J67" t="n">
-        <v>144</v>
+        <v>32</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
@@ -3249,30 +3256,30 @@
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>144</v>
+        <v>32</v>
       </c>
       <c r="N67" t="n">
-        <v>25534</v>
+        <v>72889</v>
       </c>
       <c r="O67" t="n">
-        <v>3676896</v>
+        <v>2332448</v>
       </c>
       <c r="P67" t="n">
-        <v>40900</v>
+        <v>117500</v>
       </c>
       <c r="Q67" t="n">
-        <v>5889600</v>
+        <v>3760000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>C4310</t>
+          <t>C4545</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MUÑECA CON CARRO HUMO RECARGABLE C4310</t>
+          <t>TAPETE PIANO PARA BEBE C4545</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3286,7 +3293,7 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
@@ -3295,30 +3302,30 @@
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="N68" t="n">
-        <v>72889</v>
+        <v>27186</v>
       </c>
       <c r="O68" t="n">
-        <v>2332448</v>
+        <v>543720</v>
       </c>
       <c r="P68" t="n">
-        <v>117500</v>
+        <v>43900</v>
       </c>
       <c r="Q68" t="n">
-        <v>3760000</v>
+        <v>878000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>C4545</t>
+          <t>C4728</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>TAPETE PIANO PARA BEBE C4545</t>
+          <t>FLIOTADOR DONA DINOSAURIO #60 C4728</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3332,7 +3339,7 @@
         </is>
       </c>
       <c r="J69" t="n">
-        <v>20</v>
+        <v>1800</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
@@ -3341,44 +3348,47 @@
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>20</v>
+        <v>1800</v>
       </c>
       <c r="N69" t="n">
-        <v>27186</v>
+        <v>2454</v>
       </c>
       <c r="O69" t="n">
-        <v>543720</v>
+        <v>4417200</v>
       </c>
       <c r="P69" t="n">
-        <v>43900</v>
+        <v>4200</v>
       </c>
       <c r="Q69" t="n">
-        <v>878000</v>
+        <v>7560000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>C4728</t>
-        </is>
+          <t>C488</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>6554632300006</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>FLIOTADOR DONA DINOSAURIO #60 C4728</t>
+          <t>MALETA JUGUETES</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J70" t="n">
-        <v>1800</v>
+        <v>12</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
@@ -3387,47 +3397,47 @@
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>1800</v>
+        <v>12</v>
       </c>
       <c r="N70" t="n">
-        <v>2454</v>
+        <v>18491</v>
       </c>
       <c r="O70" t="n">
-        <v>4417200</v>
+        <v>221892</v>
       </c>
       <c r="P70" t="n">
-        <v>4200</v>
+        <v>13500</v>
       </c>
       <c r="Q70" t="n">
-        <v>7560000</v>
+        <v>162000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>C488</t>
+          <t>C5032</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>6554632300006</v>
+        <v>6999899236154</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MALETA JUGUETES</t>
+          <t>INFLABLE TECHITO PIECITOS  FIGURAS STD C5032</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>INFLABLES</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J71" t="n">
-        <v>12</v>
+        <v>937</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
@@ -3436,47 +3446,44 @@
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>12</v>
+        <v>937</v>
       </c>
       <c r="N71" t="n">
-        <v>18491</v>
+        <v>8945.379999999999</v>
       </c>
       <c r="O71" t="n">
-        <v>221892</v>
+        <v>8381821.06</v>
       </c>
       <c r="P71" t="n">
-        <v>13500</v>
+        <v>14900</v>
       </c>
       <c r="Q71" t="n">
-        <v>162000</v>
+        <v>13961300</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>C5032</t>
-        </is>
-      </c>
-      <c r="B72" t="n">
-        <v>6999899236154</v>
+          <t>C698</t>
+        </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>INFLABLE TECHITO PIECITOS  FIGURAS STD C5032</t>
+          <t>HELICE 9 LUCES</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>INFLABLES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J72" t="n">
-        <v>937</v>
+        <v>240</v>
       </c>
       <c r="K72" t="n">
         <v>0</v>
@@ -3485,44 +3492,44 @@
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>937</v>
+        <v>240</v>
       </c>
       <c r="N72" t="n">
-        <v>8945.379999999999</v>
+        <v>1567.02</v>
       </c>
       <c r="O72" t="n">
-        <v>8381821.06</v>
+        <v>376084.8</v>
       </c>
       <c r="P72" t="n">
-        <v>14900</v>
+        <v>2900</v>
       </c>
       <c r="Q72" t="n">
-        <v>13961300</v>
+        <v>696000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>C698</t>
+          <t>C7560</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>HELICE 9 LUCES</t>
+          <t>BARRA LUMINOSA 48CM C7560/211</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J73" t="n">
-        <v>240</v>
+        <v>10</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -3531,35 +3538,38 @@
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>240</v>
+        <v>10</v>
       </c>
       <c r="N73" t="n">
-        <v>1567.02</v>
+        <v>796.3099999999999</v>
       </c>
       <c r="O73" t="n">
-        <v>376084.8</v>
+        <v>7963.099999999999</v>
       </c>
       <c r="P73" t="n">
-        <v>2900</v>
+        <v>2500</v>
       </c>
       <c r="Q73" t="n">
-        <v>696000</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>C7560</t>
-        </is>
+          <t>C7610</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>6999899236093</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>BARRA LUMINOSA 48CM C7560/211</t>
+          <t>BOTE TIMON PISCINA 80X60 C7610</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>INFLABLES</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3568,7 +3578,7 @@
         </is>
       </c>
       <c r="J74" t="n">
-        <v>10</v>
+        <v>360</v>
       </c>
       <c r="K74" t="n">
         <v>0</v>
@@ -3577,67 +3587,18 @@
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>10</v>
+        <v>360</v>
       </c>
       <c r="N74" t="n">
-        <v>796.3099999999999</v>
+        <v>7811.9</v>
       </c>
       <c r="O74" t="n">
-        <v>7963.099999999999</v>
+        <v>2812284</v>
       </c>
       <c r="P74" t="n">
-        <v>2500</v>
+        <v>13900</v>
       </c>
       <c r="Q74" t="n">
-        <v>25000</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>C7610</t>
-        </is>
-      </c>
-      <c r="B75" t="n">
-        <v>6999899236093</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>BOTE TIMON PISCINA 80X60 C7610</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>INFLABLES</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J75" t="n">
-        <v>360</v>
-      </c>
-      <c r="K75" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" t="n">
-        <v>0</v>
-      </c>
-      <c r="M75" t="n">
-        <v>360</v>
-      </c>
-      <c r="N75" t="n">
-        <v>7811.9</v>
-      </c>
-      <c r="O75" t="n">
-        <v>2812284</v>
-      </c>
-      <c r="P75" t="n">
-        <v>13900</v>
-      </c>
-      <c r="Q75" t="n">
         <v>5004000</v>
       </c>
     </row>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -1155,10 +1155,10 @@
         <v>324</v>
       </c>
       <c r="N18" t="n">
-        <v>3926.8371267317</v>
+        <v>3926.8371237802</v>
       </c>
       <c r="O18" t="n">
-        <v>1272295.229061071</v>
+        <v>1272295.228104785</v>
       </c>
       <c r="P18" t="n">
         <v>4800</v>
@@ -1358,10 +1358,10 @@
         <v>21</v>
       </c>
       <c r="N23" t="n">
-        <v>3910.6282352941</v>
+        <v>3933.7680473373</v>
       </c>
       <c r="O23" t="n">
-        <v>82123.19294117609</v>
+        <v>82609.12899408329</v>
       </c>
       <c r="P23" t="n">
         <v>9100</v>
@@ -1394,22 +1394,22 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>30708.882222222</v>
+        <v>30708.862857143</v>
       </c>
       <c r="O24" t="n">
-        <v>61417.764444444</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
         <v>53500</v>
       </c>
       <c r="Q24" t="n">
-        <v>107000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1442,10 +1442,10 @@
         <v>12</v>
       </c>
       <c r="N25" t="n">
-        <v>12837.965507246</v>
+        <v>12837.966461538</v>
       </c>
       <c r="O25" t="n">
-        <v>154055.586086952</v>
+        <v>154055.597538456</v>
       </c>
       <c r="P25" t="n">
         <v>22900</v>
@@ -1484,10 +1484,10 @@
         <v>10</v>
       </c>
       <c r="N26" t="n">
-        <v>16486.409489051</v>
+        <v>16486.409172932</v>
       </c>
       <c r="O26" t="n">
-        <v>164864.09489051</v>
+        <v>164864.09172932</v>
       </c>
       <c r="P26" t="n">
         <v>30500</v>
@@ -1567,22 +1567,22 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M28" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="N28" t="n">
-        <v>30238.8124</v>
+        <v>30238.812535211</v>
       </c>
       <c r="O28" t="n">
-        <v>302388.124</v>
+        <v>181432.875211266</v>
       </c>
       <c r="P28" t="n">
         <v>51100</v>
       </c>
       <c r="Q28" t="n">
-        <v>511000</v>
+        <v>306600</v>
       </c>
     </row>
     <row r="29">
@@ -1659,10 +1659,10 @@
         <v>4</v>
       </c>
       <c r="N30" t="n">
-        <v>22267.552083333</v>
+        <v>23235.706521739</v>
       </c>
       <c r="O30" t="n">
-        <v>89070.208333332</v>
+        <v>92942.826086956</v>
       </c>
       <c r="P30" t="n">
         <v>46300</v>
@@ -1883,22 +1883,22 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M35" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="N35" t="n">
-        <v>200072.19977273</v>
+        <v>200072.19992308</v>
       </c>
       <c r="O35" t="n">
-        <v>6802454.79227282</v>
+        <v>6402310.39753856</v>
       </c>
       <c r="P35" t="n">
         <v>312000</v>
       </c>
       <c r="Q35" t="n">
-        <v>10608000</v>
+        <v>9984000</v>
       </c>
     </row>
     <row r="36">
@@ -2025,10 +2025,10 @@
         <v>6</v>
       </c>
       <c r="N38" t="n">
-        <v>344599.17865385</v>
+        <v>344599.17862745</v>
       </c>
       <c r="O38" t="n">
-        <v>2067595.0719231</v>
+        <v>2067595.0717647</v>
       </c>
       <c r="P38" t="n">
         <v>532900</v>
@@ -2181,10 +2181,10 @@
         <v>67</v>
       </c>
       <c r="N42" t="n">
-        <v>61666.873932292</v>
+        <v>61666.873994709</v>
       </c>
       <c r="O42" t="n">
-        <v>4131680.553463564</v>
+        <v>4131680.557645503</v>
       </c>
       <c r="P42" t="n">
         <v>98900</v>
@@ -2811,10 +2811,10 @@
         <v>168</v>
       </c>
       <c r="N57" t="n">
-        <v>16897</v>
+        <v>17010.976391231</v>
       </c>
       <c r="O57" t="n">
-        <v>2838696</v>
+        <v>2857844.033726808</v>
       </c>
       <c r="P57" t="n">
         <v>27900</v>
@@ -3449,10 +3449,10 @@
         <v>937</v>
       </c>
       <c r="N71" t="n">
-        <v>8945.379999999999</v>
+        <v>8947.9898847557</v>
       </c>
       <c r="O71" t="n">
-        <v>8381821.06</v>
+        <v>8384266.52201609</v>
       </c>
       <c r="P71" t="n">
         <v>14900</v>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q74"/>
+  <dimension ref="A1:Q73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-13</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-14</t>
         </is>
       </c>
     </row>
@@ -1358,10 +1358,10 @@
         <v>21</v>
       </c>
       <c r="N23" t="n">
-        <v>3933.7680473373</v>
+        <v>3910.6282248521</v>
       </c>
       <c r="O23" t="n">
-        <v>82609.12899408329</v>
+        <v>82123.1927218941</v>
       </c>
       <c r="P23" t="n">
         <v>9100</v>
@@ -1372,14 +1372,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>51005</v>
+        <v>51008</v>
       </c>
       <c r="B24" t="n">
-        <v>6941607363485</v>
+        <v>6941607367575</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>51005 PISCINA DEEP DIVE</t>
+          <t>PISCINA CORAL 102 X25CM</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1388,40 +1388,40 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N24" t="n">
-        <v>30708.862857143</v>
+        <v>12837.966461538</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>154055.597538456</v>
       </c>
       <c r="P24" t="n">
-        <v>53500</v>
+        <v>22900</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>274800</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>51008</v>
+        <v>51104</v>
       </c>
       <c r="B25" t="n">
-        <v>6941607367575</v>
+        <v>6942138915815</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>PISCINA CORAL 102 X25CM</t>
+          <t>PISCINA VERANO 102 X25 CM</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1430,7 +1430,7 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -1439,31 +1439,31 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N25" t="n">
-        <v>12837.966461538</v>
+        <v>16486.409172932</v>
       </c>
       <c r="O25" t="n">
-        <v>154055.597538456</v>
+        <v>164864.09172932</v>
       </c>
       <c r="P25" t="n">
-        <v>22900</v>
+        <v>30500</v>
       </c>
       <c r="Q25" t="n">
-        <v>274800</v>
+        <v>305000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>51104</v>
+        <v>51124</v>
       </c>
       <c r="B26" t="n">
-        <v>6942138915815</v>
+        <v>6941607325032</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>PISCINA VERANO 102 X25 CM</t>
+          <t>51124 COMBO DE PISCINA Y BALON</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1472,7 +1472,7 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -1481,40 +1481,45 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="N26" t="n">
-        <v>16486.409172932</v>
+        <v>15711.966058091</v>
       </c>
       <c r="O26" t="n">
-        <v>164864.09172932</v>
+        <v>565630.7780912761</v>
       </c>
       <c r="P26" t="n">
-        <v>30500</v>
+        <v>28500</v>
       </c>
       <c r="Q26" t="n">
-        <v>305000</v>
+        <v>1026000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>51124</v>
+        <v>51203</v>
       </c>
       <c r="B27" t="n">
-        <v>6941607325032</v>
+        <v>6941607325544</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>51124 COMBO DE PISCINA Y BALON</t>
+          <t>51203 PISCINA 3 AROS BESTWAY Φ1.68m x H38cm</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -1523,75 +1528,75 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="N27" t="n">
-        <v>15711.966058091</v>
+        <v>30238.812535211</v>
       </c>
       <c r="O27" t="n">
-        <v>565630.7780912761</v>
+        <v>181432.875211266</v>
       </c>
       <c r="P27" t="n">
-        <v>28500</v>
+        <v>51100</v>
       </c>
       <c r="Q27" t="n">
-        <v>1026000</v>
+        <v>306600</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>51203</v>
-      </c>
-      <c r="B28" t="n">
-        <v>6941607325544</v>
+        <v>52331</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>51203 PISCINA 3 AROS BESTWAY Φ1.68m x H38cm</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>PISCINA CANOPY FRUTICAS 8 PCS</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>6</v>
+        <v>75</v>
       </c>
       <c r="N28" t="n">
-        <v>30238.812535211</v>
+        <v>20195.32</v>
       </c>
       <c r="O28" t="n">
-        <v>181432.875211266</v>
+        <v>1514649</v>
       </c>
       <c r="P28" t="n">
-        <v>51100</v>
+        <v>45900</v>
       </c>
       <c r="Q28" t="n">
-        <v>306600</v>
+        <v>3442500</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>52331</v>
+        <v>52637</v>
+      </c>
+      <c r="B29" t="n">
+        <v>6941607352212</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>PISCINA CANOPY FRUTICAS 8 PCS</t>
+          <t>52637 PISCINA TECHADA SUNNY BESTWAY</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1600,7 +1605,7 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>75</v>
+        <v>4</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -1609,31 +1614,31 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>75</v>
+        <v>4</v>
       </c>
       <c r="N29" t="n">
-        <v>20195.32</v>
+        <v>22267.552173913</v>
       </c>
       <c r="O29" t="n">
-        <v>1514649</v>
+        <v>89070.20869565201</v>
       </c>
       <c r="P29" t="n">
-        <v>45900</v>
+        <v>46300</v>
       </c>
       <c r="Q29" t="n">
-        <v>3442500</v>
+        <v>185200</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>52637</v>
+        <v>53157</v>
       </c>
       <c r="B30" t="n">
-        <v>6941607352212</v>
+        <v>6941607352137</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>52637 PISCINA TECHADA SUNNY BESTWAY</t>
+          <t>53157 PISCINA FUENTE SHARK BESTWAY</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1659,28 +1664,28 @@
         <v>4</v>
       </c>
       <c r="N30" t="n">
-        <v>23235.706521739</v>
+        <v>36574.852142857</v>
       </c>
       <c r="O30" t="n">
-        <v>92942.826086956</v>
+        <v>146299.408571428</v>
       </c>
       <c r="P30" t="n">
-        <v>46300</v>
+        <v>65900</v>
       </c>
       <c r="Q30" t="n">
-        <v>185200</v>
+        <v>263600</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>53157</v>
+        <v>54370</v>
       </c>
       <c r="B31" t="n">
-        <v>6941607352137</v>
+        <v>6941607312643</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>53157 PISCINA FUENTE SHARK BESTWAY</t>
+          <t>PISCINA CAPITAN 213 X155 X 132CM</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1706,28 +1711,28 @@
         <v>4</v>
       </c>
       <c r="N31" t="n">
-        <v>36574.852142857</v>
+        <v>103298.75</v>
       </c>
       <c r="O31" t="n">
-        <v>146299.408571428</v>
+        <v>413195</v>
       </c>
       <c r="P31" t="n">
-        <v>65900</v>
+        <v>178900</v>
       </c>
       <c r="Q31" t="n">
-        <v>263600</v>
+        <v>715600</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>54370</v>
+        <v>55031</v>
       </c>
       <c r="B32" t="n">
-        <v>6941607312643</v>
+        <v>6942138913781</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>PISCINA CAPITAN 213 X155 X 132CM</t>
+          <t>55031 PISCINA DELFIN 2.44mx46cm</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1741,7 +1746,7 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -1750,31 +1755,31 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N32" t="n">
-        <v>103298.75</v>
+        <v>56906.801935484</v>
       </c>
       <c r="O32" t="n">
-        <v>413195</v>
+        <v>56906.801935484</v>
       </c>
       <c r="P32" t="n">
-        <v>178900</v>
+        <v>95900</v>
       </c>
       <c r="Q32" t="n">
-        <v>715600</v>
+        <v>95900</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>55031</v>
+        <v>56401</v>
       </c>
       <c r="B33" t="n">
-        <v>6942138913781</v>
+        <v>6941607327951</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>55031 PISCINA DELFIN 2.44mx46cm</t>
+          <t>56401 PISCINA ESTRUCTURAL RECTANGULAR BESTWAY</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1788,7 +1793,7 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -1797,45 +1802,40 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="N33" t="n">
-        <v>56906.801935484</v>
+        <v>141416.88454545</v>
       </c>
       <c r="O33" t="n">
-        <v>56906.801935484</v>
+        <v>7919345.534545201</v>
       </c>
       <c r="P33" t="n">
-        <v>95900</v>
+        <v>251900</v>
       </c>
       <c r="Q33" t="n">
-        <v>95900</v>
+        <v>14106400</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>56401</v>
+        <v>56403</v>
       </c>
       <c r="B34" t="n">
-        <v>6941607327951</v>
+        <v>6941607327982</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>56401 PISCINA ESTRUCTURAL RECTANGULAR BESTWAY</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>PISCINA ESTRUCTURAL 2.59m x 1.70m x 61cm BESTWAY</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -1844,82 +1844,87 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="N34" t="n">
-        <v>141416.88454545</v>
+        <v>200072.19992308</v>
       </c>
       <c r="O34" t="n">
-        <v>7919345.534545201</v>
+        <v>6402310.39753856</v>
       </c>
       <c r="P34" t="n">
-        <v>251900</v>
+        <v>312000</v>
       </c>
       <c r="Q34" t="n">
-        <v>14106400</v>
+        <v>9984000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>56403</v>
+        <v>56404</v>
       </c>
       <c r="B35" t="n">
-        <v>6941607327982</v>
+        <v>6941607327999</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>PISCINA ESTRUCTURAL 2.59m x 1.70m x 61cm BESTWAY</t>
+          <t>56404 PISCINA ESTRUCTURAL RECTANGULAR BESTWAY</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="N35" t="n">
-        <v>200072.19992308</v>
+        <v>174389.79241379</v>
       </c>
       <c r="O35" t="n">
-        <v>6402310.39753856</v>
+        <v>2790236.67862064</v>
       </c>
       <c r="P35" t="n">
-        <v>312000</v>
+        <v>368200</v>
       </c>
       <c r="Q35" t="n">
-        <v>9984000</v>
+        <v>5891200</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>56404</v>
+        <v>56405</v>
       </c>
       <c r="B36" t="n">
-        <v>6941607327999</v>
+        <v>6941607328002</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>56404 PISCINA ESTRUCTURAL RECTANGULAR BESTWAY</t>
+          <t>PISCINA ESTRUCTURAL RECTAGULAR BESTWAY 4.00mX2.11mX81cm</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -1928,31 +1933,31 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="N36" t="n">
-        <v>174389.79241379</v>
+        <v>251809.29393939</v>
       </c>
       <c r="O36" t="n">
-        <v>2790236.67862064</v>
+        <v>1510855.76363634</v>
       </c>
       <c r="P36" t="n">
-        <v>368200</v>
+        <v>584000</v>
       </c>
       <c r="Q36" t="n">
-        <v>5891200</v>
+        <v>3504000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>56405</v>
+        <v>56417</v>
       </c>
       <c r="B37" t="n">
-        <v>6941607328002</v>
+        <v>6942138981902</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>PISCINA ESTRUCTURAL RECTAGULAR BESTWAY 4.00mX2.11mX81cm</t>
+          <t>Piscina Estructural Redonda 366 x 76 cm Bomba/Filtro 56417</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1978,38 +1983,30 @@
         <v>6</v>
       </c>
       <c r="N37" t="n">
-        <v>251809.29393939</v>
+        <v>344599.17862745</v>
       </c>
       <c r="O37" t="n">
-        <v>1510855.76363634</v>
+        <v>2067595.0717647</v>
       </c>
       <c r="P37" t="n">
-        <v>584000</v>
+        <v>532900</v>
       </c>
       <c r="Q37" t="n">
-        <v>3504000</v>
+        <v>3197400</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>56417</v>
-      </c>
-      <c r="B38" t="n">
-        <v>6942138981902</v>
+        <v>62068</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Piscina Estructural Redonda 366 x 76 cm Bomba/Filtro 56417</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>PARCHE PISCINA EXTERIOR BESTWAY</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J38" t="n">
@@ -2025,25 +2022,25 @@
         <v>6</v>
       </c>
       <c r="N38" t="n">
-        <v>344599.17862745</v>
+        <v>1977.88</v>
       </c>
       <c r="O38" t="n">
-        <v>2067595.0717647</v>
+        <v>11867.28</v>
       </c>
       <c r="P38" t="n">
-        <v>532900</v>
+        <v>2900</v>
       </c>
       <c r="Q38" t="n">
-        <v>3197400</v>
+        <v>17400</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>62068</v>
+        <v>62091</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>PARCHE PISCINA EXTERIOR BESTWAY</t>
+          <t>PARCHE PISCINA A PRUEBA DE AGUA BESTWAY</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2052,7 +2049,7 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>6</v>
+        <v>217</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -2061,28 +2058,28 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>6</v>
+        <v>217</v>
       </c>
       <c r="N39" t="n">
-        <v>1977.88</v>
+        <v>1141.57</v>
       </c>
       <c r="O39" t="n">
-        <v>11867.28</v>
+        <v>247720.69</v>
       </c>
       <c r="P39" t="n">
-        <v>2900</v>
+        <v>3900</v>
       </c>
       <c r="Q39" t="n">
-        <v>17400</v>
+        <v>846300</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>62091</v>
+        <v>67001</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>PARCHE PISCINA A PRUEBA DE AGUA BESTWAY</t>
+          <t>COLCHON INFLABLE SENCILLO BESTWAY 1.88 X 99 CM</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2091,7 +2088,7 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>217</v>
+        <v>3</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -2100,28 +2097,28 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>217</v>
+        <v>3</v>
       </c>
       <c r="N40" t="n">
-        <v>1141.57</v>
+        <v>26280.41</v>
       </c>
       <c r="O40" t="n">
-        <v>247720.69</v>
+        <v>78841.23</v>
       </c>
       <c r="P40" t="n">
-        <v>3900</v>
+        <v>46500</v>
       </c>
       <c r="Q40" t="n">
-        <v>846300</v>
+        <v>139500</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>67001</v>
+        <v>67374</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>COLCHON INFLABLE SENCILLO BESTWAY 1.88 X 99 CM</t>
+          <t>COLCHON INFLABLE DOBLE+ALMOHADAS BESTWAY 2.03mx1.52mx22cm</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2130,7 +2127,7 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>3</v>
+        <v>67</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -2139,28 +2136,28 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3</v>
+        <v>67</v>
       </c>
       <c r="N41" t="n">
-        <v>26280.41</v>
+        <v>61666.873994709</v>
       </c>
       <c r="O41" t="n">
-        <v>78841.23</v>
+        <v>4131680.557645503</v>
       </c>
       <c r="P41" t="n">
-        <v>46500</v>
+        <v>98900</v>
       </c>
       <c r="Q41" t="n">
-        <v>139500</v>
+        <v>6626300</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>67374</v>
+        <v>91004</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>COLCHON INFLABLE DOBLE+ALMOHADAS BESTWAY 2.03mx1.52mx22cm</t>
+          <t>FLOTADOR DISNEY 56CM 24PCS</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2169,7 +2166,7 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>67</v>
+        <v>340</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -2178,28 +2175,28 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>67</v>
+        <v>340</v>
       </c>
       <c r="N42" t="n">
-        <v>61666.873994709</v>
+        <v>3865.67</v>
       </c>
       <c r="O42" t="n">
-        <v>4131680.557645503</v>
+        <v>1314327.8</v>
       </c>
       <c r="P42" t="n">
-        <v>98900</v>
+        <v>5500</v>
       </c>
       <c r="Q42" t="n">
-        <v>6626300</v>
+        <v>1870000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>91004</v>
+        <v>91007</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>FLOTADOR DISNEY 56CM 24PCS</t>
+          <t>PISCINA DISNEY 122X25CM 12 PCS</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2208,7 +2205,7 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>340</v>
+        <v>24</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -2217,28 +2214,35 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>340</v>
+        <v>24</v>
       </c>
       <c r="N43" t="n">
-        <v>3865.67</v>
+        <v>16010.3</v>
       </c>
       <c r="O43" t="n">
-        <v>1314327.8</v>
+        <v>384247.2</v>
       </c>
       <c r="P43" t="n">
-        <v>5500</v>
+        <v>30500</v>
       </c>
       <c r="Q43" t="n">
-        <v>1870000</v>
+        <v>732000</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="n">
-        <v>91007</v>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>9103C</t>
+        </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>PISCINA DISNEY 122X25CM 12 PCS</t>
+          <t>9103C GAFA ACUATICA SIRENITA BESTWAY</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2259,32 +2263,27 @@
         <v>24</v>
       </c>
       <c r="N44" t="n">
-        <v>16010.3</v>
+        <v>4878.2859036145</v>
       </c>
       <c r="O44" t="n">
-        <v>384247.2</v>
+        <v>117078.861686748</v>
       </c>
       <c r="P44" t="n">
-        <v>30500</v>
+        <v>13500</v>
       </c>
       <c r="Q44" t="n">
-        <v>732000</v>
+        <v>324000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>9103C</t>
+          <t>9103D</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>9103C GAFA ACUATICA SIRENITA BESTWAY</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>9103D CARETA ACUATICA SIRENITA BESTWAY</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2293,7 +2292,7 @@
         </is>
       </c>
       <c r="J45" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -2302,30 +2301,28 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="N45" t="n">
-        <v>4878.2859036145</v>
+        <v>7394.9354444444</v>
       </c>
       <c r="O45" t="n">
-        <v>117078.861686748</v>
+        <v>88739.2253333328</v>
       </c>
       <c r="P45" t="n">
-        <v>13500</v>
+        <v>17900</v>
       </c>
       <c r="Q45" t="n">
-        <v>324000</v>
+        <v>214800</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>9103D</t>
-        </is>
+      <c r="A46" t="n">
+        <v>91040</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>9103D CARETA ACUATICA SIRENITA BESTWAY</t>
+          <t>FLOTADOR MINNIE 56CM 24 PCS</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2334,7 +2331,7 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>12</v>
+        <v>402</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -2343,28 +2340,28 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>12</v>
+        <v>402</v>
       </c>
       <c r="N46" t="n">
-        <v>7394.9354444444</v>
+        <v>3114.49</v>
       </c>
       <c r="O46" t="n">
-        <v>88739.2253333328</v>
+        <v>1252024.98</v>
       </c>
       <c r="P46" t="n">
-        <v>17900</v>
+        <v>5500</v>
       </c>
       <c r="Q46" t="n">
-        <v>214800</v>
+        <v>2211000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>91040</v>
+        <v>91042</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>FLOTADOR MINNIE 56CM 24 PCS</t>
+          <t>PELOTA PISCINA PRINCESAS 24 PCS</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2373,7 +2370,7 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>402</v>
+        <v>120</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -2382,28 +2379,28 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>402</v>
+        <v>120</v>
       </c>
       <c r="N47" t="n">
-        <v>3114.49</v>
+        <v>2791.02</v>
       </c>
       <c r="O47" t="n">
-        <v>1252024.98</v>
+        <v>334922.4</v>
       </c>
       <c r="P47" t="n">
-        <v>5500</v>
+        <v>3900</v>
       </c>
       <c r="Q47" t="n">
-        <v>2211000</v>
+        <v>468000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>91042</v>
+        <v>91043</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>PELOTA PISCINA PRINCESAS 24 PCS</t>
+          <t>FLOTADOR PRINCESAS 56CM 24PCS</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2412,7 +2409,7 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>120</v>
+        <v>58</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
@@ -2421,28 +2418,28 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>120</v>
+        <v>58</v>
       </c>
       <c r="N48" t="n">
-        <v>2791.02</v>
+        <v>3564.14</v>
       </c>
       <c r="O48" t="n">
-        <v>334922.4</v>
+        <v>206720.12</v>
       </c>
       <c r="P48" t="n">
-        <v>3900</v>
+        <v>5500</v>
       </c>
       <c r="Q48" t="n">
-        <v>468000</v>
+        <v>319000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>91043</v>
+        <v>91098</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>FLOTADOR PRINCESAS 56CM 24PCS</t>
+          <t>BALON INFLABLE MICKEY 51CM</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2451,7 +2448,7 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>58</v>
+        <v>183</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -2460,28 +2457,28 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>58</v>
+        <v>183</v>
       </c>
       <c r="N49" t="n">
-        <v>3564.14</v>
+        <v>4378</v>
       </c>
       <c r="O49" t="n">
-        <v>206720.12</v>
+        <v>801174</v>
       </c>
       <c r="P49" t="n">
-        <v>5500</v>
+        <v>3900</v>
       </c>
       <c r="Q49" t="n">
-        <v>319000</v>
+        <v>713700</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>91098</v>
+        <v>98002</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>BALON INFLABLE MICKEY 51CM</t>
+          <t>PELOTA PISCINA SIPDERMAN  51CM</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2490,7 +2487,7 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>183</v>
+        <v>264</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -2499,28 +2496,28 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>183</v>
+        <v>264</v>
       </c>
       <c r="N50" t="n">
-        <v>4378</v>
+        <v>3340.6800808081</v>
       </c>
       <c r="O50" t="n">
-        <v>801174</v>
+        <v>881939.5413333384</v>
       </c>
       <c r="P50" t="n">
-        <v>3900</v>
+        <v>7100</v>
       </c>
       <c r="Q50" t="n">
-        <v>713700</v>
+        <v>1874400</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>98002</v>
+        <v>98003</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>PELOTA PISCINA SIPDERMAN  51CM</t>
+          <t>FLOTADOR SPIDER MAN 56CM 24 PCS</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2529,7 +2526,7 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>264</v>
+        <v>67</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
@@ -2538,28 +2535,35 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>264</v>
+        <v>67</v>
       </c>
       <c r="N51" t="n">
-        <v>3340.6800808081</v>
+        <v>2903.52</v>
       </c>
       <c r="O51" t="n">
-        <v>881939.5413333384</v>
+        <v>194535.84</v>
       </c>
       <c r="P51" t="n">
         <v>7100</v>
       </c>
       <c r="Q51" t="n">
-        <v>1874400</v>
+        <v>475700</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="n">
-        <v>98003</v>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>C105</t>
+        </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>FLOTADOR SPIDER MAN 56CM 24 PCS</t>
+          <t>SCOOTER COLORES</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2568,7 +2572,7 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
@@ -2577,30 +2581,30 @@
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="N52" t="n">
-        <v>2903.52</v>
+        <v>39171.85</v>
       </c>
       <c r="O52" t="n">
-        <v>194535.84</v>
+        <v>705093.2999999999</v>
       </c>
       <c r="P52" t="n">
-        <v>7100</v>
+        <v>68900</v>
       </c>
       <c r="Q52" t="n">
-        <v>475700</v>
+        <v>1240200</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C1370</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>SCOOTER COLORES</t>
+          <t>LLAVERO PELUCHES STD C1370</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2610,11 +2614,11 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J53" t="n">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
@@ -2623,44 +2627,39 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="N53" t="n">
-        <v>39171.85</v>
+        <v>3472</v>
       </c>
       <c r="O53" t="n">
-        <v>705093.2999999999</v>
+        <v>868000</v>
       </c>
       <c r="P53" t="n">
-        <v>68900</v>
+        <v>4800</v>
       </c>
       <c r="Q53" t="n">
-        <v>1240200</v>
+        <v>1200000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>C1370</t>
+          <t>C1717</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>LLAVERO PELUCHES STD C1370</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>ESPADA CON LUZ Y SONIDO</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>250</v>
+        <v>432</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
@@ -2669,30 +2668,38 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>250</v>
+        <v>432</v>
       </c>
       <c r="N54" t="n">
-        <v>3472</v>
+        <v>4443</v>
       </c>
       <c r="O54" t="n">
-        <v>868000</v>
+        <v>1919376</v>
       </c>
       <c r="P54" t="n">
-        <v>4800</v>
+        <v>6300</v>
       </c>
       <c r="Q54" t="n">
-        <v>1200000</v>
+        <v>2721600</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>C1717</t>
-        </is>
+          <t>C1758</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>6914919067549</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ESPADA CON LUZ Y SONIDO</t>
+          <t>MULA BLISTER SURTIDA</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2701,7 +2708,7 @@
         </is>
       </c>
       <c r="J55" t="n">
-        <v>432</v>
+        <v>180</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
@@ -2710,33 +2717,33 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>432</v>
+        <v>180</v>
       </c>
       <c r="N55" t="n">
-        <v>4443</v>
+        <v>4648.6</v>
       </c>
       <c r="O55" t="n">
-        <v>1919376</v>
+        <v>836748.0000000001</v>
       </c>
       <c r="P55" t="n">
-        <v>6300</v>
+        <v>8900</v>
       </c>
       <c r="Q55" t="n">
-        <v>2721600</v>
+        <v>1602000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>C1758</t>
+          <t>C1897</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>6914919067549</v>
+        <v>6914919086373</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>MULA BLISTER SURTIDA</t>
+          <t>MULA DIDACTICA</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2750,7 +2757,7 @@
         </is>
       </c>
       <c r="J56" t="n">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -2759,38 +2766,30 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="N56" t="n">
-        <v>4648.6</v>
+        <v>16897</v>
       </c>
       <c r="O56" t="n">
-        <v>836748.0000000001</v>
+        <v>2838696</v>
       </c>
       <c r="P56" t="n">
-        <v>8900</v>
+        <v>27900</v>
       </c>
       <c r="Q56" t="n">
-        <v>1602000</v>
+        <v>4687200</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>C1897</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>6914919086373</v>
+          <t>C2117</t>
+        </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>MULA DIDACTICA</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>DISPLAY CARTÓN PEGAJOSOS X 20</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -2799,7 +2798,7 @@
         </is>
       </c>
       <c r="J57" t="n">
-        <v>168</v>
+        <v>1400</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
@@ -2808,30 +2807,38 @@
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>168</v>
+        <v>1400</v>
       </c>
       <c r="N57" t="n">
-        <v>17010.976391231</v>
+        <v>3751</v>
       </c>
       <c r="O57" t="n">
-        <v>2857844.033726808</v>
+        <v>5251400</v>
       </c>
       <c r="P57" t="n">
-        <v>27900</v>
+        <v>6400</v>
       </c>
       <c r="Q57" t="n">
-        <v>4687200</v>
+        <v>8960000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>C2117</t>
-        </is>
+          <t>C342</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>6914919018374</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>DISPLAY CARTÓN PEGAJOSOS X 20</t>
+          <t>COCINA CON VAPOR DE AGUA</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -2840,7 +2847,7 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>1400</v>
+        <v>24</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
@@ -2849,38 +2856,30 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>1400</v>
+        <v>24</v>
       </c>
       <c r="N58" t="n">
-        <v>3751</v>
+        <v>24538.02</v>
       </c>
       <c r="O58" t="n">
-        <v>5251400</v>
+        <v>588912.48</v>
       </c>
       <c r="P58" t="n">
-        <v>6400</v>
+        <v>52900</v>
       </c>
       <c r="Q58" t="n">
-        <v>8960000</v>
+        <v>1269600</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>C342</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>6914919018374</v>
+          <t>C3455</t>
+        </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>COCINA CON VAPOR DE AGUA</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>DINOSAURIO BOLSA</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -2889,7 +2888,7 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>24</v>
+        <v>288</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
@@ -2898,30 +2897,35 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>24</v>
+        <v>288</v>
       </c>
       <c r="N59" t="n">
-        <v>24538.02</v>
+        <v>5894.64</v>
       </c>
       <c r="O59" t="n">
-        <v>588912.48</v>
+        <v>1697656.32</v>
       </c>
       <c r="P59" t="n">
-        <v>52900</v>
+        <v>11000</v>
       </c>
       <c r="Q59" t="n">
-        <v>1269600</v>
+        <v>3168000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>C3455</t>
+          <t>C3638</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>DINOSAURIO BOLSA</t>
+          <t>INFLABLE DONA</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -2930,7 +2934,7 @@
         </is>
       </c>
       <c r="J60" t="n">
-        <v>288</v>
+        <v>443</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
@@ -2939,30 +2943,30 @@
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>288</v>
+        <v>443</v>
       </c>
       <c r="N60" t="n">
-        <v>5894.64</v>
+        <v>3877.89</v>
       </c>
       <c r="O60" t="n">
-        <v>1697656.32</v>
+        <v>1717905.27</v>
       </c>
       <c r="P60" t="n">
-        <v>11000</v>
+        <v>6500</v>
       </c>
       <c r="Q60" t="n">
-        <v>3168000</v>
+        <v>2879500</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>C3638</t>
+          <t>C3700</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>INFLABLE DONA</t>
+          <t>MUNECA CON CARRO RECARGABLE DE CONTROL REMOTO</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2976,7 +2980,7 @@
         </is>
       </c>
       <c r="J61" t="n">
-        <v>443</v>
+        <v>6</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
@@ -2985,30 +2989,30 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>443</v>
+        <v>6</v>
       </c>
       <c r="N61" t="n">
-        <v>3877.89</v>
+        <v>60174</v>
       </c>
       <c r="O61" t="n">
-        <v>1717905.27</v>
+        <v>361044</v>
       </c>
       <c r="P61" t="n">
-        <v>6500</v>
+        <v>96900</v>
       </c>
       <c r="Q61" t="n">
-        <v>2879500</v>
+        <v>581400</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>C3700</t>
+          <t>C3970</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>MUNECA CON CARRO RECARGABLE DE CONTROL REMOTO</t>
+          <t>GUITARRAS C3970</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3018,11 +3022,11 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J62" t="n">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
@@ -3031,44 +3035,39 @@
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="N62" t="n">
-        <v>60174</v>
+        <v>26854</v>
       </c>
       <c r="O62" t="n">
-        <v>361044</v>
+        <v>1288992</v>
       </c>
       <c r="P62" t="n">
-        <v>96900</v>
+        <v>43900</v>
       </c>
       <c r="Q62" t="n">
-        <v>581400</v>
+        <v>2107200</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>C3970</t>
+          <t>C3988</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>GUITARRAS C3970</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>DRAGÓN CAMINA CON LUZ Y SONIDO</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
@@ -3077,39 +3076,44 @@
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="N63" t="n">
-        <v>26854</v>
+        <v>29700</v>
       </c>
       <c r="O63" t="n">
-        <v>1288992</v>
+        <v>356400</v>
       </c>
       <c r="P63" t="n">
-        <v>43900</v>
+        <v>50500</v>
       </c>
       <c r="Q63" t="n">
-        <v>2107200</v>
+        <v>606000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>C3988</t>
+          <t>C4303</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>DRAGÓN CAMINA CON LUZ Y SONIDO</t>
+          <t>BEBE CON PIJAMA MED BOLSA PVC C4303</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>12</v>
+        <v>300</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -3118,30 +3122,30 @@
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>12</v>
+        <v>300</v>
       </c>
       <c r="N64" t="n">
-        <v>29700</v>
+        <v>18016</v>
       </c>
       <c r="O64" t="n">
-        <v>356400</v>
+        <v>5404800</v>
       </c>
       <c r="P64" t="n">
-        <v>50500</v>
+        <v>29900</v>
       </c>
       <c r="Q64" t="n">
-        <v>606000</v>
+        <v>8970000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>C4303</t>
+          <t>C4305</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>BEBE CON PIJAMA MED BOLSA PVC C4303</t>
+          <t>MUÑECA BEBE GRANDE CON PIJAMA EN BOLSA C4305</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3155,7 +3159,7 @@
         </is>
       </c>
       <c r="J65" t="n">
-        <v>300</v>
+        <v>144</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
@@ -3164,30 +3168,30 @@
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>300</v>
+        <v>144</v>
       </c>
       <c r="N65" t="n">
-        <v>18016</v>
+        <v>25534</v>
       </c>
       <c r="O65" t="n">
-        <v>5404800</v>
+        <v>3676896</v>
       </c>
       <c r="P65" t="n">
-        <v>29900</v>
+        <v>40900</v>
       </c>
       <c r="Q65" t="n">
-        <v>8970000</v>
+        <v>5889600</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>C4305</t>
+          <t>C4310</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MUÑECA BEBE GRANDE CON PIJAMA EN BOLSA C4305</t>
+          <t>MUÑECA CON CARRO HUMO RECARGABLE C4310</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3201,7 +3205,7 @@
         </is>
       </c>
       <c r="J66" t="n">
-        <v>144</v>
+        <v>32</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>
@@ -3210,30 +3214,30 @@
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>144</v>
+        <v>32</v>
       </c>
       <c r="N66" t="n">
-        <v>25534</v>
+        <v>72889</v>
       </c>
       <c r="O66" t="n">
-        <v>3676896</v>
+        <v>2332448</v>
       </c>
       <c r="P66" t="n">
-        <v>40900</v>
+        <v>117500</v>
       </c>
       <c r="Q66" t="n">
-        <v>5889600</v>
+        <v>3760000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>C4310</t>
+          <t>C4545</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>MUÑECA CON CARRO HUMO RECARGABLE C4310</t>
+          <t>TAPETE PIANO PARA BEBE C4545</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3247,7 +3251,7 @@
         </is>
       </c>
       <c r="J67" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
@@ -3256,30 +3260,30 @@
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="N67" t="n">
-        <v>72889</v>
+        <v>27186</v>
       </c>
       <c r="O67" t="n">
-        <v>2332448</v>
+        <v>543720</v>
       </c>
       <c r="P67" t="n">
-        <v>117500</v>
+        <v>43900</v>
       </c>
       <c r="Q67" t="n">
-        <v>3760000</v>
+        <v>878000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>C4545</t>
+          <t>C4728</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>TAPETE PIANO PARA BEBE C4545</t>
+          <t>FLIOTADOR DONA DINOSAURIO #60 C4728</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3293,7 +3297,7 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>20</v>
+        <v>1800</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
@@ -3302,44 +3306,47 @@
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>20</v>
+        <v>1800</v>
       </c>
       <c r="N68" t="n">
-        <v>27186</v>
+        <v>2454</v>
       </c>
       <c r="O68" t="n">
-        <v>543720</v>
+        <v>4417200</v>
       </c>
       <c r="P68" t="n">
-        <v>43900</v>
+        <v>4200</v>
       </c>
       <c r="Q68" t="n">
-        <v>878000</v>
+        <v>7560000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>C4728</t>
-        </is>
+          <t>C488</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>6554632300006</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>FLIOTADOR DONA DINOSAURIO #60 C4728</t>
+          <t>MALETA JUGUETES</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J69" t="n">
-        <v>1800</v>
+        <v>12</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
@@ -3348,47 +3355,47 @@
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>1800</v>
+        <v>12</v>
       </c>
       <c r="N69" t="n">
-        <v>2454</v>
+        <v>18491</v>
       </c>
       <c r="O69" t="n">
-        <v>4417200</v>
+        <v>221892</v>
       </c>
       <c r="P69" t="n">
-        <v>4200</v>
+        <v>13500</v>
       </c>
       <c r="Q69" t="n">
-        <v>7560000</v>
+        <v>162000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>C488</t>
+          <t>C5032</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>6554632300006</v>
+        <v>6999899236154</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MALETA JUGUETES</t>
+          <t>INFLABLE TECHITO PIECITOS  FIGURAS STD C5032</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>INFLABLES</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J70" t="n">
-        <v>12</v>
+        <v>937</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
@@ -3397,47 +3404,44 @@
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>12</v>
+        <v>937</v>
       </c>
       <c r="N70" t="n">
-        <v>18491</v>
+        <v>8945.379999999999</v>
       </c>
       <c r="O70" t="n">
-        <v>221892</v>
+        <v>8381821.06</v>
       </c>
       <c r="P70" t="n">
-        <v>13500</v>
+        <v>14900</v>
       </c>
       <c r="Q70" t="n">
-        <v>162000</v>
+        <v>13961300</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>C5032</t>
-        </is>
-      </c>
-      <c r="B71" t="n">
-        <v>6999899236154</v>
+          <t>C698</t>
+        </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>INFLABLE TECHITO PIECITOS  FIGURAS STD C5032</t>
+          <t>HELICE 9 LUCES</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>INFLABLES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J71" t="n">
-        <v>937</v>
+        <v>240</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
@@ -3446,44 +3450,44 @@
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>937</v>
+        <v>240</v>
       </c>
       <c r="N71" t="n">
-        <v>8947.9898847557</v>
+        <v>1567.02</v>
       </c>
       <c r="O71" t="n">
-        <v>8384266.52201609</v>
+        <v>376084.8</v>
       </c>
       <c r="P71" t="n">
-        <v>14900</v>
+        <v>2900</v>
       </c>
       <c r="Q71" t="n">
-        <v>13961300</v>
+        <v>696000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>C698</t>
+          <t>C7560</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>HELICE 9 LUCES</t>
+          <t>BARRA LUMINOSA 48CM C7560/211</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J72" t="n">
-        <v>240</v>
+        <v>10</v>
       </c>
       <c r="K72" t="n">
         <v>0</v>
@@ -3492,35 +3496,38 @@
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>240</v>
+        <v>10</v>
       </c>
       <c r="N72" t="n">
-        <v>1567.02</v>
+        <v>796.3099999999999</v>
       </c>
       <c r="O72" t="n">
-        <v>376084.8</v>
+        <v>7963.099999999999</v>
       </c>
       <c r="P72" t="n">
-        <v>2900</v>
+        <v>2500</v>
       </c>
       <c r="Q72" t="n">
-        <v>696000</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>C7560</t>
-        </is>
+          <t>C7610</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>6999899236093</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>BARRA LUMINOSA 48CM C7560/211</t>
+          <t>BOTE TIMON PISCINA 80X60 C7610</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>INFLABLES</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3529,7 +3536,7 @@
         </is>
       </c>
       <c r="J73" t="n">
-        <v>10</v>
+        <v>360</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -3538,67 +3545,18 @@
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>10</v>
+        <v>360</v>
       </c>
       <c r="N73" t="n">
-        <v>796.3099999999999</v>
+        <v>7811.9</v>
       </c>
       <c r="O73" t="n">
-        <v>7963.099999999999</v>
+        <v>2812284</v>
       </c>
       <c r="P73" t="n">
-        <v>2500</v>
+        <v>13900</v>
       </c>
       <c r="Q73" t="n">
-        <v>25000</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>C7610</t>
-        </is>
-      </c>
-      <c r="B74" t="n">
-        <v>6999899236093</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>BOTE TIMON PISCINA 80X60 C7610</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>INFLABLES</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J74" t="n">
-        <v>360</v>
-      </c>
-      <c r="K74" t="n">
-        <v>0</v>
-      </c>
-      <c r="L74" t="n">
-        <v>0</v>
-      </c>
-      <c r="M74" t="n">
-        <v>360</v>
-      </c>
-      <c r="N74" t="n">
-        <v>7811.9</v>
-      </c>
-      <c r="O74" t="n">
-        <v>2812284</v>
-      </c>
-      <c r="P74" t="n">
-        <v>13900</v>
-      </c>
-      <c r="Q74" t="n">
         <v>5004000</v>
       </c>
     </row>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -763,10 +763,10 @@
         <v>24</v>
       </c>
       <c r="N9" t="n">
-        <v>20826.676585366</v>
+        <v>20826.676923077</v>
       </c>
       <c r="O9" t="n">
-        <v>499840.238048784</v>
+        <v>499840.246153848</v>
       </c>
       <c r="P9" t="n">
         <v>39100</v>
@@ -1358,10 +1358,10 @@
         <v>21</v>
       </c>
       <c r="N23" t="n">
-        <v>3910.6282248521</v>
+        <v>3910.6281963928</v>
       </c>
       <c r="O23" t="n">
-        <v>82123.1927218941</v>
+        <v>82123.1921242488</v>
       </c>
       <c r="P23" t="n">
         <v>9100</v>
@@ -1847,10 +1847,10 @@
         <v>32</v>
       </c>
       <c r="N34" t="n">
-        <v>200072.19992308</v>
+        <v>200072.2</v>
       </c>
       <c r="O34" t="n">
-        <v>6402310.39753856</v>
+        <v>6402310.4</v>
       </c>
       <c r="P34" t="n">
         <v>312000</v>
@@ -2499,10 +2499,10 @@
         <v>264</v>
       </c>
       <c r="N50" t="n">
-        <v>3340.6800808081</v>
+        <v>3340.6800817996</v>
       </c>
       <c r="O50" t="n">
-        <v>881939.5413333384</v>
+        <v>881939.5415950944</v>
       </c>
       <c r="P50" t="n">
         <v>7100</v>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-14</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-15</t>
         </is>
       </c>
     </row>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -1358,10 +1358,10 @@
         <v>21</v>
       </c>
       <c r="N23" t="n">
-        <v>3910.6281963928</v>
+        <v>3910.6281927711</v>
       </c>
       <c r="O23" t="n">
-        <v>82123.1921242488</v>
+        <v>82123.1920481931</v>
       </c>
       <c r="P23" t="n">
         <v>9100</v>
@@ -1847,10 +1847,10 @@
         <v>32</v>
       </c>
       <c r="N34" t="n">
-        <v>200072.2</v>
+        <v>200072.20007812</v>
       </c>
       <c r="O34" t="n">
-        <v>6402310.4</v>
+        <v>6402310.40249984</v>
       </c>
       <c r="P34" t="n">
         <v>312000</v>
@@ -2139,10 +2139,10 @@
         <v>67</v>
       </c>
       <c r="N41" t="n">
-        <v>61666.873994709</v>
+        <v>61666.874005305</v>
       </c>
       <c r="O41" t="n">
-        <v>4131680.557645503</v>
+        <v>4131680.558355435</v>
       </c>
       <c r="P41" t="n">
         <v>98900</v>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-15</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-16</t>
         </is>
       </c>
     </row>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-16</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-17</t>
         </is>
       </c>
     </row>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-17</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-18</t>
         </is>
       </c>
     </row>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -1155,10 +1155,10 @@
         <v>324</v>
       </c>
       <c r="N18" t="n">
-        <v>3926.8371237802</v>
+        <v>3926.8371059432</v>
       </c>
       <c r="O18" t="n">
-        <v>1272295.228104785</v>
+        <v>1272295.222325597</v>
       </c>
       <c r="P18" t="n">
         <v>4800</v>
@@ -1358,10 +1358,10 @@
         <v>21</v>
       </c>
       <c r="N23" t="n">
-        <v>3910.6281927711</v>
+        <v>3910.6281818182</v>
       </c>
       <c r="O23" t="n">
-        <v>82123.1920481931</v>
+        <v>82123.1918181822</v>
       </c>
       <c r="P23" t="n">
         <v>9100</v>
@@ -1442,10 +1442,10 @@
         <v>10</v>
       </c>
       <c r="N25" t="n">
-        <v>16486.409172932</v>
+        <v>16486.409090909</v>
       </c>
       <c r="O25" t="n">
-        <v>164864.09172932</v>
+        <v>164864.09090909</v>
       </c>
       <c r="P25" t="n">
         <v>30500</v>
@@ -1847,10 +1847,10 @@
         <v>32</v>
       </c>
       <c r="N34" t="n">
-        <v>200072.20007812</v>
+        <v>200072.20015748</v>
       </c>
       <c r="O34" t="n">
-        <v>6402310.40249984</v>
+        <v>6402310.40503936</v>
       </c>
       <c r="P34" t="n">
         <v>312000</v>
@@ -2139,10 +2139,10 @@
         <v>67</v>
       </c>
       <c r="N41" t="n">
-        <v>61666.874005305</v>
+        <v>61666.874015957</v>
       </c>
       <c r="O41" t="n">
-        <v>4131680.558355435</v>
+        <v>4131680.559069119</v>
       </c>
       <c r="P41" t="n">
         <v>98900</v>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-18</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-19</t>
         </is>
       </c>
     </row>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -1531,10 +1531,10 @@
         <v>6</v>
       </c>
       <c r="N27" t="n">
-        <v>30238.812535211</v>
+        <v>30238.812571429</v>
       </c>
       <c r="O27" t="n">
-        <v>181432.875211266</v>
+        <v>181432.875428574</v>
       </c>
       <c r="P27" t="n">
         <v>51100</v>
@@ -1664,10 +1664,10 @@
         <v>4</v>
       </c>
       <c r="N30" t="n">
-        <v>36574.852142857</v>
+        <v>36574.852195122</v>
       </c>
       <c r="O30" t="n">
-        <v>146299.408571428</v>
+        <v>146299.408780488</v>
       </c>
       <c r="P30" t="n">
         <v>65900</v>
@@ -1805,10 +1805,10 @@
         <v>56</v>
       </c>
       <c r="N33" t="n">
-        <v>141416.88454545</v>
+        <v>141416.88456026</v>
       </c>
       <c r="O33" t="n">
-        <v>7919345.534545201</v>
+        <v>7919345.535374559</v>
       </c>
       <c r="P33" t="n">
         <v>251900</v>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-19</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-20</t>
         </is>
       </c>
     </row>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -551,22 +551,22 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N4" t="n">
-        <v>96741.407402597</v>
+        <v>96741.407702703</v>
       </c>
       <c r="O4" t="n">
-        <v>773931.259220776</v>
+        <v>483707.038513515</v>
       </c>
       <c r="P4" t="n">
         <v>188900</v>
       </c>
       <c r="Q4" t="n">
-        <v>1511200</v>
+        <v>944500</v>
       </c>
     </row>
     <row r="5">
@@ -1758,10 +1758,10 @@
         <v>1</v>
       </c>
       <c r="N32" t="n">
-        <v>56906.801935484</v>
+        <v>56906.802333333</v>
       </c>
       <c r="O32" t="n">
-        <v>56906.801935484</v>
+        <v>56906.802333333</v>
       </c>
       <c r="P32" t="n">
         <v>95900</v>
@@ -1841,22 +1841,22 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M34" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="N34" t="n">
-        <v>200072.20015748</v>
+        <v>200072.20040323</v>
       </c>
       <c r="O34" t="n">
-        <v>6402310.40503936</v>
+        <v>5802093.81169367</v>
       </c>
       <c r="P34" t="n">
         <v>312000</v>
       </c>
       <c r="Q34" t="n">
-        <v>9984000</v>
+        <v>9048000</v>
       </c>
     </row>
     <row r="35">
@@ -1883,22 +1883,22 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M35" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N35" t="n">
-        <v>174389.79241379</v>
+        <v>174389.79407407</v>
       </c>
       <c r="O35" t="n">
-        <v>2790236.67862064</v>
+        <v>2441457.11703698</v>
       </c>
       <c r="P35" t="n">
         <v>368200</v>
       </c>
       <c r="Q35" t="n">
-        <v>5891200</v>
+        <v>5154800</v>
       </c>
     </row>
     <row r="36">
@@ -2763,22 +2763,22 @@
         <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M56" t="n">
-        <v>168</v>
+        <v>144</v>
       </c>
       <c r="N56" t="n">
         <v>16897</v>
       </c>
       <c r="O56" t="n">
-        <v>2838696</v>
+        <v>2433168</v>
       </c>
       <c r="P56" t="n">
         <v>27900</v>
       </c>
       <c r="Q56" t="n">
-        <v>4687200</v>
+        <v>4017600</v>
       </c>
     </row>
     <row r="57">

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-20</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-21</t>
         </is>
       </c>
     </row>
@@ -545,13 +545,13 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>5</v>
@@ -1835,13 +1835,13 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
         <v>29</v>
@@ -1877,13 +1877,13 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
         <v>14</v>
@@ -2757,13 +2757,13 @@
         </is>
       </c>
       <c r="J56" t="n">
-        <v>168</v>
+        <v>144</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
         <v>144</v>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-21</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-22</t>
         </is>
       </c>
     </row>
@@ -604,10 +604,10 @@
         <v>2</v>
       </c>
       <c r="N5" t="n">
-        <v>74676.651794872</v>
+        <v>74676.651315789</v>
       </c>
       <c r="O5" t="n">
-        <v>149353.303589744</v>
+        <v>149353.302631578</v>
       </c>
       <c r="P5" t="n">
         <v>144900</v>
@@ -763,10 +763,10 @@
         <v>24</v>
       </c>
       <c r="N9" t="n">
-        <v>20826.676923077</v>
+        <v>20826.677105263</v>
       </c>
       <c r="O9" t="n">
-        <v>499840.246153848</v>
+        <v>499840.250526312</v>
       </c>
       <c r="P9" t="n">
         <v>39100</v>
@@ -1442,10 +1442,10 @@
         <v>10</v>
       </c>
       <c r="N25" t="n">
-        <v>16486.409090909</v>
+        <v>16486.408923077</v>
       </c>
       <c r="O25" t="n">
-        <v>164864.09090909</v>
+        <v>164864.08923077</v>
       </c>
       <c r="P25" t="n">
         <v>30500</v>
@@ -1484,10 +1484,10 @@
         <v>36</v>
       </c>
       <c r="N26" t="n">
-        <v>15711.966058091</v>
+        <v>15711.966041667</v>
       </c>
       <c r="O26" t="n">
-        <v>565630.7780912761</v>
+        <v>565630.777500012</v>
       </c>
       <c r="P26" t="n">
         <v>28500</v>
@@ -1758,10 +1758,10 @@
         <v>1</v>
       </c>
       <c r="N32" t="n">
-        <v>56906.802333333</v>
+        <v>56906.802542373</v>
       </c>
       <c r="O32" t="n">
-        <v>56906.802333333</v>
+        <v>56906.802542373</v>
       </c>
       <c r="P32" t="n">
         <v>95900</v>
@@ -1847,10 +1847,10 @@
         <v>29</v>
       </c>
       <c r="N34" t="n">
-        <v>200072.20040323</v>
+        <v>200072.2004878</v>
       </c>
       <c r="O34" t="n">
-        <v>5802093.81169367</v>
+        <v>5802093.8141462</v>
       </c>
       <c r="P34" t="n">
         <v>312000</v>
@@ -2139,10 +2139,10 @@
         <v>67</v>
       </c>
       <c r="N41" t="n">
-        <v>61666.874015957</v>
+        <v>61666.874026667</v>
       </c>
       <c r="O41" t="n">
-        <v>4131680.559069119</v>
+        <v>4131680.559786689</v>
       </c>
       <c r="P41" t="n">
         <v>98900</v>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -682,10 +682,10 @@
         <v>12</v>
       </c>
       <c r="N7" t="n">
-        <v>5758.9597787611</v>
+        <v>5758.9597782705</v>
       </c>
       <c r="O7" t="n">
-        <v>69107.51734513321</v>
+        <v>69107.517339246</v>
       </c>
       <c r="P7" t="n">
         <v>16900</v>
@@ -1358,10 +1358,10 @@
         <v>21</v>
       </c>
       <c r="N23" t="n">
-        <v>3910.6281818182</v>
+        <v>3910.6281707317</v>
       </c>
       <c r="O23" t="n">
-        <v>82123.1918181822</v>
+        <v>82123.1915853657</v>
       </c>
       <c r="P23" t="n">
         <v>9100</v>
@@ -1394,22 +1394,22 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M24" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>12837.966461538</v>
+        <v>12837.967258065</v>
       </c>
       <c r="O24" t="n">
-        <v>154055.597538456</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
         <v>22900</v>
       </c>
       <c r="Q24" t="n">
-        <v>274800</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1484,10 +1484,10 @@
         <v>36</v>
       </c>
       <c r="N26" t="n">
-        <v>15711.966041667</v>
+        <v>15711.966008403</v>
       </c>
       <c r="O26" t="n">
-        <v>565630.777500012</v>
+        <v>565630.776302508</v>
       </c>
       <c r="P26" t="n">
         <v>28500</v>
@@ -1752,22 +1752,22 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>56906.802542373</v>
+        <v>56906.802982456</v>
       </c>
       <c r="O32" t="n">
-        <v>56906.802542373</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
         <v>95900</v>
       </c>
       <c r="Q32" t="n">
-        <v>95900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -1841,22 +1841,22 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N34" t="n">
-        <v>200072.2004878</v>
+        <v>200072.20057377</v>
       </c>
       <c r="O34" t="n">
-        <v>5802093.8141462</v>
+        <v>5602021.61606556</v>
       </c>
       <c r="P34" t="n">
         <v>312000</v>
       </c>
       <c r="Q34" t="n">
-        <v>9048000</v>
+        <v>8736000</v>
       </c>
     </row>
     <row r="35">

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q73"/>
+  <dimension ref="A1:Q71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-22</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-23</t>
         </is>
       </c>
     </row>
@@ -1372,14 +1372,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>51008</v>
+        <v>51104</v>
       </c>
       <c r="B24" t="n">
-        <v>6941607367575</v>
+        <v>6942138915815</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>PISCINA CORAL 102 X25CM</t>
+          <t>PISCINA VERANO 102 X25 CM</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1388,40 +1388,40 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N24" t="n">
-        <v>12837.967258065</v>
+        <v>16486.408923077</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>164864.08923077</v>
       </c>
       <c r="P24" t="n">
-        <v>22900</v>
+        <v>30500</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>305000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>51104</v>
+        <v>51124</v>
       </c>
       <c r="B25" t="n">
-        <v>6942138915815</v>
+        <v>6941607325032</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>PISCINA VERANO 102 X25 CM</t>
+          <t>51124 COMBO DE PISCINA Y BALON</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1430,7 +1430,7 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -1439,40 +1439,45 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="N25" t="n">
-        <v>16486.408923077</v>
+        <v>15711.966008403</v>
       </c>
       <c r="O25" t="n">
-        <v>164864.08923077</v>
+        <v>565630.776302508</v>
       </c>
       <c r="P25" t="n">
-        <v>30500</v>
+        <v>28500</v>
       </c>
       <c r="Q25" t="n">
-        <v>305000</v>
+        <v>1026000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>51124</v>
+        <v>51203</v>
       </c>
       <c r="B26" t="n">
-        <v>6941607325032</v>
+        <v>6941607325544</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>51124 COMBO DE PISCINA Y BALON</t>
+          <t>51203 PISCINA 3 AROS BESTWAY Φ1.68m x H38cm</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -1481,45 +1486,37 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="N26" t="n">
-        <v>15711.966008403</v>
+        <v>30238.812571429</v>
       </c>
       <c r="O26" t="n">
-        <v>565630.776302508</v>
+        <v>181432.875428574</v>
       </c>
       <c r="P26" t="n">
-        <v>28500</v>
+        <v>51100</v>
       </c>
       <c r="Q26" t="n">
-        <v>1026000</v>
+        <v>306600</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>51203</v>
-      </c>
-      <c r="B27" t="n">
-        <v>6941607325544</v>
+        <v>52331</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>51203 PISCINA 3 AROS BESTWAY Φ1.68m x H38cm</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>PISCINA CANOPY FRUTICAS 8 PCS</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>6</v>
+        <v>75</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -1528,28 +1525,36 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>6</v>
+        <v>75</v>
       </c>
       <c r="N27" t="n">
-        <v>30238.812571429</v>
+        <v>20195.32</v>
       </c>
       <c r="O27" t="n">
-        <v>181432.875428574</v>
+        <v>1514649</v>
       </c>
       <c r="P27" t="n">
-        <v>51100</v>
+        <v>45900</v>
       </c>
       <c r="Q27" t="n">
-        <v>306600</v>
+        <v>3442500</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>52331</v>
+        <v>52637</v>
+      </c>
+      <c r="B28" t="n">
+        <v>6941607352212</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>PISCINA CANOPY FRUTICAS 8 PCS</t>
+          <t>52637 PISCINA TECHADA SUNNY BESTWAY</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1558,7 +1563,7 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>75</v>
+        <v>4</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -1567,31 +1572,31 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>75</v>
+        <v>4</v>
       </c>
       <c r="N28" t="n">
-        <v>20195.32</v>
+        <v>22267.552173913</v>
       </c>
       <c r="O28" t="n">
-        <v>1514649</v>
+        <v>89070.20869565201</v>
       </c>
       <c r="P28" t="n">
-        <v>45900</v>
+        <v>46300</v>
       </c>
       <c r="Q28" t="n">
-        <v>3442500</v>
+        <v>185200</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>52637</v>
+        <v>53157</v>
       </c>
       <c r="B29" t="n">
-        <v>6941607352212</v>
+        <v>6941607352137</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>52637 PISCINA TECHADA SUNNY BESTWAY</t>
+          <t>53157 PISCINA FUENTE SHARK BESTWAY</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1617,28 +1622,28 @@
         <v>4</v>
       </c>
       <c r="N29" t="n">
-        <v>22267.552173913</v>
+        <v>36574.852195122</v>
       </c>
       <c r="O29" t="n">
-        <v>89070.20869565201</v>
+        <v>146299.408780488</v>
       </c>
       <c r="P29" t="n">
-        <v>46300</v>
+        <v>65900</v>
       </c>
       <c r="Q29" t="n">
-        <v>185200</v>
+        <v>263600</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>53157</v>
+        <v>54370</v>
       </c>
       <c r="B30" t="n">
-        <v>6941607352137</v>
+        <v>6941607312643</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>53157 PISCINA FUENTE SHARK BESTWAY</t>
+          <t>PISCINA CAPITAN 213 X155 X 132CM</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1664,28 +1669,28 @@
         <v>4</v>
       </c>
       <c r="N30" t="n">
-        <v>36574.852195122</v>
+        <v>103298.75</v>
       </c>
       <c r="O30" t="n">
-        <v>146299.408780488</v>
+        <v>413195</v>
       </c>
       <c r="P30" t="n">
-        <v>65900</v>
+        <v>178900</v>
       </c>
       <c r="Q30" t="n">
-        <v>263600</v>
+        <v>715600</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>54370</v>
+        <v>56401</v>
       </c>
       <c r="B31" t="n">
-        <v>6941607312643</v>
+        <v>6941607327951</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>PISCINA CAPITAN 213 X155 X 132CM</t>
+          <t>56401 PISCINA ESTRUCTURAL RECTANGULAR BESTWAY</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1699,7 +1704,7 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -1708,83 +1713,73 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="N31" t="n">
-        <v>103298.75</v>
+        <v>141416.88456026</v>
       </c>
       <c r="O31" t="n">
-        <v>413195</v>
+        <v>7919345.535374559</v>
       </c>
       <c r="P31" t="n">
-        <v>178900</v>
+        <v>251900</v>
       </c>
       <c r="Q31" t="n">
-        <v>715600</v>
+        <v>14106400</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>55031</v>
+        <v>56403</v>
       </c>
       <c r="B32" t="n">
-        <v>6942138913781</v>
+        <v>6941607327982</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>55031 PISCINA DELFIN 2.44mx46cm</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>PISCINA ESTRUCTURAL 2.59m x 1.70m x 61cm BESTWAY</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="N32" t="n">
-        <v>56906.802982456</v>
+        <v>200072.20057377</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>5602021.61606556</v>
       </c>
       <c r="P32" t="n">
-        <v>95900</v>
+        <v>312000</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>8736000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>56401</v>
+        <v>56404</v>
       </c>
       <c r="B33" t="n">
-        <v>6941607327951</v>
+        <v>6941607327999</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>56401 PISCINA ESTRUCTURAL RECTANGULAR BESTWAY</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>56404 PISCINA ESTRUCTURAL RECTANGULAR BESTWAY</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1793,7 +1788,7 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -1802,31 +1797,36 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="N33" t="n">
-        <v>141416.88456026</v>
+        <v>174389.79407407</v>
       </c>
       <c r="O33" t="n">
-        <v>7919345.535374559</v>
+        <v>2441457.11703698</v>
       </c>
       <c r="P33" t="n">
-        <v>251900</v>
+        <v>368200</v>
       </c>
       <c r="Q33" t="n">
-        <v>14106400</v>
+        <v>5154800</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>56403</v>
+        <v>56405</v>
       </c>
       <c r="B34" t="n">
-        <v>6941607327982</v>
+        <v>6941607328002</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>PISCINA ESTRUCTURAL 2.59m x 1.70m x 61cm BESTWAY</t>
+          <t>PISCINA ESTRUCTURAL RECTAGULAR BESTWAY 4.00mX2.11mX81cm</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1835,49 +1835,54 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="N34" t="n">
-        <v>200072.20057377</v>
+        <v>251809.29393939</v>
       </c>
       <c r="O34" t="n">
-        <v>5602021.61606556</v>
+        <v>1510855.76363634</v>
       </c>
       <c r="P34" t="n">
-        <v>312000</v>
+        <v>584000</v>
       </c>
       <c r="Q34" t="n">
-        <v>8736000</v>
+        <v>3504000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>56404</v>
+        <v>56417</v>
       </c>
       <c r="B35" t="n">
-        <v>6941607327999</v>
+        <v>6942138981902</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>56404 PISCINA ESTRUCTURAL RECTANGULAR BESTWAY</t>
+          <t>Piscina Estructural Redonda 366 x 76 cm Bomba/Filtro 56417</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -1886,41 +1891,33 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="N35" t="n">
-        <v>174389.79407407</v>
+        <v>344599.17862745</v>
       </c>
       <c r="O35" t="n">
-        <v>2441457.11703698</v>
+        <v>2067595.0717647</v>
       </c>
       <c r="P35" t="n">
-        <v>368200</v>
+        <v>532900</v>
       </c>
       <c r="Q35" t="n">
-        <v>5154800</v>
+        <v>3197400</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>56405</v>
-      </c>
-      <c r="B36" t="n">
-        <v>6941607328002</v>
+        <v>62068</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>PISCINA ESTRUCTURAL RECTAGULAR BESTWAY 4.00mX2.11mX81cm</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>PARCHE PISCINA EXTERIOR BESTWAY</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J36" t="n">
@@ -1936,42 +1933,34 @@
         <v>6</v>
       </c>
       <c r="N36" t="n">
-        <v>251809.29393939</v>
+        <v>1977.88</v>
       </c>
       <c r="O36" t="n">
-        <v>1510855.76363634</v>
+        <v>11867.28</v>
       </c>
       <c r="P36" t="n">
-        <v>584000</v>
+        <v>2900</v>
       </c>
       <c r="Q36" t="n">
-        <v>3504000</v>
+        <v>17400</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>56417</v>
-      </c>
-      <c r="B37" t="n">
-        <v>6942138981902</v>
+        <v>62091</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Piscina Estructural Redonda 366 x 76 cm Bomba/Filtro 56417</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>PARCHE PISCINA A PRUEBA DE AGUA BESTWAY</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>6</v>
+        <v>217</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -1980,28 +1969,28 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>6</v>
+        <v>217</v>
       </c>
       <c r="N37" t="n">
-        <v>344599.17862745</v>
+        <v>1141.57</v>
       </c>
       <c r="O37" t="n">
-        <v>2067595.0717647</v>
+        <v>247720.69</v>
       </c>
       <c r="P37" t="n">
-        <v>532900</v>
+        <v>3900</v>
       </c>
       <c r="Q37" t="n">
-        <v>3197400</v>
+        <v>846300</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>62068</v>
+        <v>67001</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>PARCHE PISCINA EXTERIOR BESTWAY</t>
+          <t>COLCHON INFLABLE SENCILLO BESTWAY 1.88 X 99 CM</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2010,7 +1999,7 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -2019,28 +2008,28 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N38" t="n">
-        <v>1977.88</v>
+        <v>26280.41</v>
       </c>
       <c r="O38" t="n">
-        <v>11867.28</v>
+        <v>78841.23</v>
       </c>
       <c r="P38" t="n">
-        <v>2900</v>
+        <v>46500</v>
       </c>
       <c r="Q38" t="n">
-        <v>17400</v>
+        <v>139500</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>62091</v>
+        <v>67374</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>PARCHE PISCINA A PRUEBA DE AGUA BESTWAY</t>
+          <t>COLCHON INFLABLE DOBLE+ALMOHADAS BESTWAY 2.03mx1.52mx22cm</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2049,7 +2038,7 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>217</v>
+        <v>67</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -2058,28 +2047,28 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>217</v>
+        <v>67</v>
       </c>
       <c r="N39" t="n">
-        <v>1141.57</v>
+        <v>61666.874026667</v>
       </c>
       <c r="O39" t="n">
-        <v>247720.69</v>
+        <v>4131680.559786689</v>
       </c>
       <c r="P39" t="n">
-        <v>3900</v>
+        <v>98900</v>
       </c>
       <c r="Q39" t="n">
-        <v>846300</v>
+        <v>6626300</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>67001</v>
+        <v>91004</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>COLCHON INFLABLE SENCILLO BESTWAY 1.88 X 99 CM</t>
+          <t>FLOTADOR DISNEY 56CM 24PCS</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2088,7 +2077,7 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>3</v>
+        <v>340</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -2097,28 +2086,28 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3</v>
+        <v>340</v>
       </c>
       <c r="N40" t="n">
-        <v>26280.41</v>
+        <v>3865.67</v>
       </c>
       <c r="O40" t="n">
-        <v>78841.23</v>
+        <v>1314327.8</v>
       </c>
       <c r="P40" t="n">
-        <v>46500</v>
+        <v>5500</v>
       </c>
       <c r="Q40" t="n">
-        <v>139500</v>
+        <v>1870000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>67374</v>
+        <v>91007</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>COLCHON INFLABLE DOBLE+ALMOHADAS BESTWAY 2.03mx1.52mx22cm</t>
+          <t>PISCINA DISNEY 122X25CM 12 PCS</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2127,7 +2116,7 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -2136,28 +2125,35 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="N41" t="n">
-        <v>61666.874026667</v>
+        <v>16010.3</v>
       </c>
       <c r="O41" t="n">
-        <v>4131680.559786689</v>
+        <v>384247.2</v>
       </c>
       <c r="P41" t="n">
-        <v>98900</v>
+        <v>30500</v>
       </c>
       <c r="Q41" t="n">
-        <v>6626300</v>
+        <v>732000</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="n">
-        <v>91004</v>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>9103C</t>
+        </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>FLOTADOR DISNEY 56CM 24PCS</t>
+          <t>9103C GAFA ACUATICA SIRENITA BESTWAY</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2166,7 +2162,7 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>340</v>
+        <v>24</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -2175,115 +2171,108 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>340</v>
+        <v>24</v>
       </c>
       <c r="N42" t="n">
-        <v>3865.67</v>
+        <v>4878.2859036145</v>
       </c>
       <c r="O42" t="n">
-        <v>1314327.8</v>
+        <v>117078.861686748</v>
       </c>
       <c r="P42" t="n">
+        <v>13500</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>324000</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>9103D</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>9103D CARETA ACUATICA SIRENITA BESTWAY</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>und</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>12</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>12</v>
+      </c>
+      <c r="N43" t="n">
+        <v>7394.9354444444</v>
+      </c>
+      <c r="O43" t="n">
+        <v>88739.2253333328</v>
+      </c>
+      <c r="P43" t="n">
+        <v>17900</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>214800</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>91040</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>FLOTADOR MINNIE 56CM 24 PCS</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>und</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>402</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>402</v>
+      </c>
+      <c r="N44" t="n">
+        <v>3114.49</v>
+      </c>
+      <c r="O44" t="n">
+        <v>1252024.98</v>
+      </c>
+      <c r="P44" t="n">
         <v>5500</v>
       </c>
-      <c r="Q42" t="n">
-        <v>1870000</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>91007</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>PISCINA DISNEY 122X25CM 12 PCS</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>und</t>
-        </is>
-      </c>
-      <c r="J43" t="n">
-        <v>24</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" t="n">
-        <v>24</v>
-      </c>
-      <c r="N43" t="n">
-        <v>16010.3</v>
-      </c>
-      <c r="O43" t="n">
-        <v>384247.2</v>
-      </c>
-      <c r="P43" t="n">
-        <v>30500</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>732000</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>9103C</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>9103C GAFA ACUATICA SIRENITA BESTWAY</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>und</t>
-        </is>
-      </c>
-      <c r="J44" t="n">
-        <v>24</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" t="n">
-        <v>24</v>
-      </c>
-      <c r="N44" t="n">
-        <v>4878.2859036145</v>
-      </c>
-      <c r="O44" t="n">
-        <v>117078.861686748</v>
-      </c>
-      <c r="P44" t="n">
-        <v>13500</v>
-      </c>
       <c r="Q44" t="n">
-        <v>324000</v>
+        <v>2211000</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>9103D</t>
-        </is>
+      <c r="A45" t="n">
+        <v>91042</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>9103D CARETA ACUATICA SIRENITA BESTWAY</t>
+          <t>PELOTA PISCINA PRINCESAS 24 PCS</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2292,7 +2281,7 @@
         </is>
       </c>
       <c r="J45" t="n">
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -2301,28 +2290,28 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="N45" t="n">
-        <v>7394.9354444444</v>
+        <v>2791.02</v>
       </c>
       <c r="O45" t="n">
-        <v>88739.2253333328</v>
+        <v>334922.4</v>
       </c>
       <c r="P45" t="n">
-        <v>17900</v>
+        <v>3900</v>
       </c>
       <c r="Q45" t="n">
-        <v>214800</v>
+        <v>468000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>91040</v>
+        <v>91043</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>FLOTADOR MINNIE 56CM 24 PCS</t>
+          <t>FLOTADOR PRINCESAS 56CM 24PCS</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2331,7 +2320,7 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>402</v>
+        <v>58</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -2340,28 +2329,28 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>402</v>
+        <v>58</v>
       </c>
       <c r="N46" t="n">
-        <v>3114.49</v>
+        <v>3564.14</v>
       </c>
       <c r="O46" t="n">
-        <v>1252024.98</v>
+        <v>206720.12</v>
       </c>
       <c r="P46" t="n">
         <v>5500</v>
       </c>
       <c r="Q46" t="n">
-        <v>2211000</v>
+        <v>319000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>91042</v>
+        <v>91098</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>PELOTA PISCINA PRINCESAS 24 PCS</t>
+          <t>BALON INFLABLE MICKEY 51CM</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2370,7 +2359,7 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>120</v>
+        <v>183</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -2379,28 +2368,28 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>120</v>
+        <v>183</v>
       </c>
       <c r="N47" t="n">
-        <v>2791.02</v>
+        <v>4378</v>
       </c>
       <c r="O47" t="n">
-        <v>334922.4</v>
+        <v>801174</v>
       </c>
       <c r="P47" t="n">
         <v>3900</v>
       </c>
       <c r="Q47" t="n">
-        <v>468000</v>
+        <v>713700</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>91043</v>
+        <v>98002</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>FLOTADOR PRINCESAS 56CM 24PCS</t>
+          <t>PELOTA PISCINA SIPDERMAN  51CM</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2409,7 +2398,7 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>58</v>
+        <v>264</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
@@ -2418,28 +2407,28 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>58</v>
+        <v>264</v>
       </c>
       <c r="N48" t="n">
-        <v>3564.14</v>
+        <v>3340.6800817996</v>
       </c>
       <c r="O48" t="n">
-        <v>206720.12</v>
+        <v>881939.5415950944</v>
       </c>
       <c r="P48" t="n">
-        <v>5500</v>
+        <v>7100</v>
       </c>
       <c r="Q48" t="n">
-        <v>319000</v>
+        <v>1874400</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>91098</v>
+        <v>98003</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>BALON INFLABLE MICKEY 51CM</t>
+          <t>FLOTADOR SPIDER MAN 56CM 24 PCS</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2448,7 +2437,7 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>183</v>
+        <v>67</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -2457,28 +2446,35 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>183</v>
+        <v>67</v>
       </c>
       <c r="N49" t="n">
-        <v>4378</v>
+        <v>2903.52</v>
       </c>
       <c r="O49" t="n">
-        <v>801174</v>
+        <v>194535.84</v>
       </c>
       <c r="P49" t="n">
-        <v>3900</v>
+        <v>7100</v>
       </c>
       <c r="Q49" t="n">
-        <v>713700</v>
+        <v>475700</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="n">
-        <v>98002</v>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>C105</t>
+        </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>PELOTA PISCINA SIPDERMAN  51CM</t>
+          <t>SCOOTER COLORES</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2487,7 +2483,7 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>264</v>
+        <v>18</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -2496,37 +2492,44 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>264</v>
+        <v>18</v>
       </c>
       <c r="N50" t="n">
-        <v>3340.6800817996</v>
+        <v>39171.85</v>
       </c>
       <c r="O50" t="n">
-        <v>881939.5415950944</v>
+        <v>705093.2999999999</v>
       </c>
       <c r="P50" t="n">
-        <v>7100</v>
+        <v>68900</v>
       </c>
       <c r="Q50" t="n">
-        <v>1874400</v>
+        <v>1240200</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="n">
-        <v>98003</v>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>C1370</t>
+        </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>FLOTADOR SPIDER MAN 56CM 24 PCS</t>
+          <t>LLAVERO PELUCHES STD C1370</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>67</v>
+        <v>250</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
@@ -2535,35 +2538,30 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>67</v>
+        <v>250</v>
       </c>
       <c r="N51" t="n">
-        <v>2903.52</v>
+        <v>3472</v>
       </c>
       <c r="O51" t="n">
-        <v>194535.84</v>
+        <v>868000</v>
       </c>
       <c r="P51" t="n">
-        <v>7100</v>
+        <v>4800</v>
       </c>
       <c r="Q51" t="n">
-        <v>475700</v>
+        <v>1200000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C1717</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>SCOOTER COLORES</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>ESPADA CON LUZ Y SONIDO</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2572,7 +2570,7 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>18</v>
+        <v>432</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
@@ -2581,30 +2579,33 @@
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>18</v>
+        <v>432</v>
       </c>
       <c r="N52" t="n">
-        <v>39171.85</v>
+        <v>4443</v>
       </c>
       <c r="O52" t="n">
-        <v>705093.2999999999</v>
+        <v>1919376</v>
       </c>
       <c r="P52" t="n">
-        <v>68900</v>
+        <v>6300</v>
       </c>
       <c r="Q52" t="n">
-        <v>1240200</v>
+        <v>2721600</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>C1370</t>
-        </is>
+          <t>C1758</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>6914919067549</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>LLAVERO PELUCHES STD C1370</t>
+          <t>MULA BLISTER SURTIDA</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2614,11 +2615,11 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J53" t="n">
-        <v>250</v>
+        <v>180</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
@@ -2627,30 +2628,38 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>250</v>
+        <v>180</v>
       </c>
       <c r="N53" t="n">
-        <v>3472</v>
+        <v>4648.6</v>
       </c>
       <c r="O53" t="n">
-        <v>868000</v>
+        <v>836748.0000000001</v>
       </c>
       <c r="P53" t="n">
-        <v>4800</v>
+        <v>8900</v>
       </c>
       <c r="Q53" t="n">
-        <v>1200000</v>
+        <v>1602000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>C1717</t>
-        </is>
+          <t>C1897</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>6914919086373</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ESPADA CON LUZ Y SONIDO</t>
+          <t>MULA DIDACTICA</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2659,7 +2668,7 @@
         </is>
       </c>
       <c r="J54" t="n">
-        <v>432</v>
+        <v>144</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
@@ -2668,38 +2677,30 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>432</v>
+        <v>144</v>
       </c>
       <c r="N54" t="n">
-        <v>4443</v>
+        <v>16897</v>
       </c>
       <c r="O54" t="n">
-        <v>1919376</v>
+        <v>2433168</v>
       </c>
       <c r="P54" t="n">
-        <v>6300</v>
+        <v>27900</v>
       </c>
       <c r="Q54" t="n">
-        <v>2721600</v>
+        <v>4017600</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>C1758</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>6914919067549</v>
+          <t>C2117</t>
+        </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>MULA BLISTER SURTIDA</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>DISPLAY CARTÓN PEGAJOSOS X 20</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2708,7 +2709,7 @@
         </is>
       </c>
       <c r="J55" t="n">
-        <v>180</v>
+        <v>1400</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
@@ -2717,33 +2718,33 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>180</v>
+        <v>1400</v>
       </c>
       <c r="N55" t="n">
-        <v>4648.6</v>
+        <v>3751</v>
       </c>
       <c r="O55" t="n">
-        <v>836748.0000000001</v>
+        <v>5251400</v>
       </c>
       <c r="P55" t="n">
-        <v>8900</v>
+        <v>6400</v>
       </c>
       <c r="Q55" t="n">
-        <v>1602000</v>
+        <v>8960000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>C1897</t>
+          <t>C342</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>6914919086373</v>
+        <v>6914919018374</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>MULA DIDACTICA</t>
+          <t>COCINA CON VAPOR DE AGUA</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2757,7 +2758,7 @@
         </is>
       </c>
       <c r="J56" t="n">
-        <v>144</v>
+        <v>24</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -2766,30 +2767,30 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>144</v>
+        <v>24</v>
       </c>
       <c r="N56" t="n">
-        <v>16897</v>
+        <v>24538.02</v>
       </c>
       <c r="O56" t="n">
-        <v>2433168</v>
+        <v>588912.48</v>
       </c>
       <c r="P56" t="n">
-        <v>27900</v>
+        <v>52900</v>
       </c>
       <c r="Q56" t="n">
-        <v>4017600</v>
+        <v>1269600</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>C2117</t>
+          <t>C3455</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>DISPLAY CARTÓN PEGAJOSOS X 20</t>
+          <t>DINOSAURIO BOLSA</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -2798,7 +2799,7 @@
         </is>
       </c>
       <c r="J57" t="n">
-        <v>1400</v>
+        <v>288</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
@@ -2807,33 +2808,30 @@
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>1400</v>
+        <v>288</v>
       </c>
       <c r="N57" t="n">
-        <v>3751</v>
+        <v>5894.64</v>
       </c>
       <c r="O57" t="n">
-        <v>5251400</v>
+        <v>1697656.32</v>
       </c>
       <c r="P57" t="n">
-        <v>6400</v>
+        <v>11000</v>
       </c>
       <c r="Q57" t="n">
-        <v>8960000</v>
+        <v>3168000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>C342</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>6914919018374</v>
+          <t>C3638</t>
+        </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>COCINA CON VAPOR DE AGUA</t>
+          <t>INFLABLE DONA</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2847,7 +2845,7 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>24</v>
+        <v>443</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
@@ -2856,30 +2854,35 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>24</v>
+        <v>443</v>
       </c>
       <c r="N58" t="n">
-        <v>24538.02</v>
+        <v>3877.89</v>
       </c>
       <c r="O58" t="n">
-        <v>588912.48</v>
+        <v>1717905.27</v>
       </c>
       <c r="P58" t="n">
-        <v>52900</v>
+        <v>6500</v>
       </c>
       <c r="Q58" t="n">
-        <v>1269600</v>
+        <v>2879500</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>C3455</t>
+          <t>C3700</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>DINOSAURIO BOLSA</t>
+          <t>MUNECA CON CARRO RECARGABLE DE CONTROL REMOTO</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -2888,7 +2891,7 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>288</v>
+        <v>6</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
@@ -2897,30 +2900,30 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>288</v>
+        <v>6</v>
       </c>
       <c r="N59" t="n">
-        <v>5894.64</v>
+        <v>60174</v>
       </c>
       <c r="O59" t="n">
-        <v>1697656.32</v>
+        <v>361044</v>
       </c>
       <c r="P59" t="n">
-        <v>11000</v>
+        <v>96900</v>
       </c>
       <c r="Q59" t="n">
-        <v>3168000</v>
+        <v>581400</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>C3638</t>
+          <t>C3970</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>INFLABLE DONA</t>
+          <t>GUITARRAS C3970</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2930,11 +2933,11 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>443</v>
+        <v>48</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
@@ -2943,35 +2946,30 @@
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>443</v>
+        <v>48</v>
       </c>
       <c r="N60" t="n">
-        <v>3877.89</v>
+        <v>26854</v>
       </c>
       <c r="O60" t="n">
-        <v>1717905.27</v>
+        <v>1288992</v>
       </c>
       <c r="P60" t="n">
-        <v>6500</v>
+        <v>43900</v>
       </c>
       <c r="Q60" t="n">
-        <v>2879500</v>
+        <v>2107200</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>C3700</t>
+          <t>C3988</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MUNECA CON CARRO RECARGABLE DE CONTROL REMOTO</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>DRAGÓN CAMINA CON LUZ Y SONIDO</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -2980,7 +2978,7 @@
         </is>
       </c>
       <c r="J61" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
@@ -2989,30 +2987,30 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="N61" t="n">
-        <v>60174</v>
+        <v>29700</v>
       </c>
       <c r="O61" t="n">
-        <v>361044</v>
+        <v>356400</v>
       </c>
       <c r="P61" t="n">
-        <v>96900</v>
+        <v>50500</v>
       </c>
       <c r="Q61" t="n">
-        <v>581400</v>
+        <v>606000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>C3970</t>
+          <t>C4303</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>GUITARRAS C3970</t>
+          <t>BEBE CON PIJAMA MED BOLSA PVC C4303</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3026,7 +3024,7 @@
         </is>
       </c>
       <c r="J62" t="n">
-        <v>48</v>
+        <v>300</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
@@ -3035,39 +3033,44 @@
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>48</v>
+        <v>300</v>
       </c>
       <c r="N62" t="n">
-        <v>26854</v>
+        <v>18016</v>
       </c>
       <c r="O62" t="n">
-        <v>1288992</v>
+        <v>5404800</v>
       </c>
       <c r="P62" t="n">
-        <v>43900</v>
+        <v>29900</v>
       </c>
       <c r="Q62" t="n">
-        <v>2107200</v>
+        <v>8970000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>C3988</t>
+          <t>C4305</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>DRAGÓN CAMINA CON LUZ Y SONIDO</t>
+          <t>MUÑECA BEBE GRANDE CON PIJAMA EN BOLSA C4305</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>12</v>
+        <v>144</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
@@ -3076,30 +3079,30 @@
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>12</v>
+        <v>144</v>
       </c>
       <c r="N63" t="n">
-        <v>29700</v>
+        <v>25534</v>
       </c>
       <c r="O63" t="n">
-        <v>356400</v>
+        <v>3676896</v>
       </c>
       <c r="P63" t="n">
-        <v>50500</v>
+        <v>40900</v>
       </c>
       <c r="Q63" t="n">
-        <v>606000</v>
+        <v>5889600</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>C4303</t>
+          <t>C4310</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>BEBE CON PIJAMA MED BOLSA PVC C4303</t>
+          <t>MUÑECA CON CARRO HUMO RECARGABLE C4310</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3113,7 +3116,7 @@
         </is>
       </c>
       <c r="J64" t="n">
-        <v>300</v>
+        <v>32</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -3122,30 +3125,30 @@
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>300</v>
+        <v>32</v>
       </c>
       <c r="N64" t="n">
-        <v>18016</v>
+        <v>72889</v>
       </c>
       <c r="O64" t="n">
-        <v>5404800</v>
+        <v>2332448</v>
       </c>
       <c r="P64" t="n">
-        <v>29900</v>
+        <v>117500</v>
       </c>
       <c r="Q64" t="n">
-        <v>8970000</v>
+        <v>3760000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>C4305</t>
+          <t>C4545</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MUÑECA BEBE GRANDE CON PIJAMA EN BOLSA C4305</t>
+          <t>TAPETE PIANO PARA BEBE C4545</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3159,7 +3162,7 @@
         </is>
       </c>
       <c r="J65" t="n">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
@@ -3168,30 +3171,30 @@
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="N65" t="n">
-        <v>25534</v>
+        <v>27186</v>
       </c>
       <c r="O65" t="n">
-        <v>3676896</v>
+        <v>543720</v>
       </c>
       <c r="P65" t="n">
-        <v>40900</v>
+        <v>43900</v>
       </c>
       <c r="Q65" t="n">
-        <v>5889600</v>
+        <v>878000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>C4310</t>
+          <t>C4728</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MUÑECA CON CARRO HUMO RECARGABLE C4310</t>
+          <t>FLIOTADOR DONA DINOSAURIO #60 C4728</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3205,7 +3208,7 @@
         </is>
       </c>
       <c r="J66" t="n">
-        <v>32</v>
+        <v>1800</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>
@@ -3214,44 +3217,47 @@
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>32</v>
+        <v>1800</v>
       </c>
       <c r="N66" t="n">
-        <v>72889</v>
+        <v>2454</v>
       </c>
       <c r="O66" t="n">
-        <v>2332448</v>
+        <v>4417200</v>
       </c>
       <c r="P66" t="n">
-        <v>117500</v>
+        <v>4200</v>
       </c>
       <c r="Q66" t="n">
-        <v>3760000</v>
+        <v>7560000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>C4545</t>
-        </is>
+          <t>C488</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>6554632300006</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>TAPETE PIANO PARA BEBE C4545</t>
+          <t>MALETA JUGUETES</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J67" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
@@ -3260,35 +3266,38 @@
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="N67" t="n">
-        <v>27186</v>
+        <v>18491</v>
       </c>
       <c r="O67" t="n">
-        <v>543720</v>
+        <v>221892</v>
       </c>
       <c r="P67" t="n">
-        <v>43900</v>
+        <v>13500</v>
       </c>
       <c r="Q67" t="n">
-        <v>878000</v>
+        <v>162000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>C4728</t>
-        </is>
+          <t>C5032</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>6999899236154</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>FLIOTADOR DONA DINOSAURIO #60 C4728</t>
+          <t>INFLABLE TECHITO PIECITOS  FIGURAS STD C5032</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>INFLABLES</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3297,7 +3306,7 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>1800</v>
+        <v>937</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
@@ -3306,38 +3315,35 @@
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>1800</v>
+        <v>937</v>
       </c>
       <c r="N68" t="n">
-        <v>2454</v>
+        <v>8945.379999999999</v>
       </c>
       <c r="O68" t="n">
-        <v>4417200</v>
+        <v>8381821.06</v>
       </c>
       <c r="P68" t="n">
-        <v>4200</v>
+        <v>14900</v>
       </c>
       <c r="Q68" t="n">
-        <v>7560000</v>
+        <v>13961300</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>C488</t>
-        </is>
-      </c>
-      <c r="B69" t="n">
-        <v>6554632300006</v>
+          <t>C698</t>
+        </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MALETA JUGUETES</t>
+          <t>HELICE 9 LUCES</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3346,7 +3352,7 @@
         </is>
       </c>
       <c r="J69" t="n">
-        <v>12</v>
+        <v>240</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
@@ -3355,38 +3361,35 @@
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>12</v>
+        <v>240</v>
       </c>
       <c r="N69" t="n">
-        <v>18491</v>
+        <v>1567.02</v>
       </c>
       <c r="O69" t="n">
-        <v>221892</v>
+        <v>376084.8</v>
       </c>
       <c r="P69" t="n">
-        <v>13500</v>
+        <v>2900</v>
       </c>
       <c r="Q69" t="n">
-        <v>162000</v>
+        <v>696000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>C5032</t>
-        </is>
-      </c>
-      <c r="B70" t="n">
-        <v>6999899236154</v>
+          <t>C7560</t>
+        </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>INFLABLE TECHITO PIECITOS  FIGURAS STD C5032</t>
+          <t>BARRA LUMINOSA 48CM C7560/211</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>INFLABLES</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3395,7 +3398,7 @@
         </is>
       </c>
       <c r="J70" t="n">
-        <v>937</v>
+        <v>10</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
@@ -3404,44 +3407,47 @@
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>937</v>
+        <v>10</v>
       </c>
       <c r="N70" t="n">
-        <v>8945.379999999999</v>
+        <v>796.3099999999999</v>
       </c>
       <c r="O70" t="n">
-        <v>8381821.06</v>
+        <v>7963.099999999999</v>
       </c>
       <c r="P70" t="n">
-        <v>14900</v>
+        <v>2500</v>
       </c>
       <c r="Q70" t="n">
-        <v>13961300</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>C698</t>
-        </is>
+          <t>C7610</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>6999899236093</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>HELICE 9 LUCES</t>
+          <t>BOTE TIMON PISCINA 80X60 C7610</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>INFLABLES</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J71" t="n">
-        <v>240</v>
+        <v>360</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
@@ -3450,113 +3456,18 @@
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>240</v>
+        <v>360</v>
       </c>
       <c r="N71" t="n">
-        <v>1567.02</v>
+        <v>7811.9</v>
       </c>
       <c r="O71" t="n">
-        <v>376084.8</v>
+        <v>2812284</v>
       </c>
       <c r="P71" t="n">
-        <v>2900</v>
+        <v>13900</v>
       </c>
       <c r="Q71" t="n">
-        <v>696000</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>C7560</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>BARRA LUMINOSA 48CM C7560/211</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>PIÑATERIA</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J72" t="n">
-        <v>10</v>
-      </c>
-      <c r="K72" t="n">
-        <v>0</v>
-      </c>
-      <c r="L72" t="n">
-        <v>0</v>
-      </c>
-      <c r="M72" t="n">
-        <v>10</v>
-      </c>
-      <c r="N72" t="n">
-        <v>796.3099999999999</v>
-      </c>
-      <c r="O72" t="n">
-        <v>7963.099999999999</v>
-      </c>
-      <c r="P72" t="n">
-        <v>2500</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>25000</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>C7610</t>
-        </is>
-      </c>
-      <c r="B73" t="n">
-        <v>6999899236093</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>BOTE TIMON PISCINA 80X60 C7610</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>INFLABLES</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J73" t="n">
-        <v>360</v>
-      </c>
-      <c r="K73" t="n">
-        <v>0</v>
-      </c>
-      <c r="L73" t="n">
-        <v>0</v>
-      </c>
-      <c r="M73" t="n">
-        <v>360</v>
-      </c>
-      <c r="N73" t="n">
-        <v>7811.9</v>
-      </c>
-      <c r="O73" t="n">
-        <v>2812284</v>
-      </c>
-      <c r="P73" t="n">
-        <v>13900</v>
-      </c>
-      <c r="Q73" t="n">
         <v>5004000</v>
       </c>
     </row>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-23</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-24</t>
         </is>
       </c>
     </row>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -682,10 +682,10 @@
         <v>12</v>
       </c>
       <c r="N7" t="n">
-        <v>5758.9597782705</v>
+        <v>5758.9597777778</v>
       </c>
       <c r="O7" t="n">
-        <v>69107.517339246</v>
+        <v>69107.5173333336</v>
       </c>
       <c r="P7" t="n">
         <v>16900</v>
@@ -763,10 +763,10 @@
         <v>24</v>
       </c>
       <c r="N9" t="n">
-        <v>20826.677105263</v>
+        <v>20826.677297297</v>
       </c>
       <c r="O9" t="n">
-        <v>499840.250526312</v>
+        <v>499840.255135128</v>
       </c>
       <c r="P9" t="n">
         <v>39100</v>
@@ -1400,10 +1400,10 @@
         <v>10</v>
       </c>
       <c r="N24" t="n">
-        <v>16486.408923077</v>
+        <v>16614.210542636</v>
       </c>
       <c r="O24" t="n">
-        <v>164864.08923077</v>
+        <v>166142.10542636</v>
       </c>
       <c r="P24" t="n">
         <v>30500</v>
@@ -1442,10 +1442,10 @@
         <v>36</v>
       </c>
       <c r="N25" t="n">
-        <v>15711.966008403</v>
+        <v>15711.965957447</v>
       </c>
       <c r="O25" t="n">
-        <v>565630.776302508</v>
+        <v>565630.774468092</v>
       </c>
       <c r="P25" t="n">
         <v>28500</v>
@@ -1622,10 +1622,10 @@
         <v>4</v>
       </c>
       <c r="N29" t="n">
-        <v>36574.852195122</v>
+        <v>36574.852307692</v>
       </c>
       <c r="O29" t="n">
-        <v>146299.408780488</v>
+        <v>146299.409230768</v>
       </c>
       <c r="P29" t="n">
         <v>65900</v>
@@ -2128,10 +2128,10 @@
         <v>24</v>
       </c>
       <c r="N41" t="n">
-        <v>16010.3</v>
+        <v>16128.022794118</v>
       </c>
       <c r="O41" t="n">
-        <v>384247.2</v>
+        <v>387072.547058832</v>
       </c>
       <c r="P41" t="n">
         <v>30500</v>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-24</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-25</t>
         </is>
       </c>
     </row>
@@ -1400,10 +1400,10 @@
         <v>10</v>
       </c>
       <c r="N24" t="n">
-        <v>16614.210542636</v>
+        <v>16486.408837209</v>
       </c>
       <c r="O24" t="n">
-        <v>166142.10542636</v>
+        <v>164864.08837209</v>
       </c>
       <c r="P24" t="n">
         <v>30500</v>
@@ -2128,10 +2128,10 @@
         <v>24</v>
       </c>
       <c r="N41" t="n">
-        <v>16128.022794118</v>
+        <v>16010.3</v>
       </c>
       <c r="O41" t="n">
-        <v>387072.547058832</v>
+        <v>384247.2</v>
       </c>
       <c r="P41" t="n">
         <v>30500</v>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -757,22 +757,22 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="N9" t="n">
         <v>20826.677297297</v>
       </c>
       <c r="O9" t="n">
-        <v>499840.255135128</v>
+        <v>249920.127567564</v>
       </c>
       <c r="P9" t="n">
         <v>39100</v>
       </c>
       <c r="Q9" t="n">
-        <v>938400</v>
+        <v>469200</v>
       </c>
     </row>
     <row r="10">
@@ -1358,10 +1358,10 @@
         <v>21</v>
       </c>
       <c r="N23" t="n">
-        <v>3910.6281707317</v>
+        <v>3910.6281632653</v>
       </c>
       <c r="O23" t="n">
-        <v>82123.1915853657</v>
+        <v>82123.1914285713</v>
       </c>
       <c r="P23" t="n">
         <v>9100</v>
@@ -2050,10 +2050,10 @@
         <v>67</v>
       </c>
       <c r="N39" t="n">
-        <v>61666.874026667</v>
+        <v>61666.874048257</v>
       </c>
       <c r="O39" t="n">
-        <v>4131680.559786689</v>
+        <v>4131680.561233219</v>
       </c>
       <c r="P39" t="n">
         <v>98900</v>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-25</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-26</t>
         </is>
       </c>
     </row>
@@ -751,13 +751,13 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>12</v>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-26</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-27</t>
         </is>
       </c>
     </row>
@@ -604,10 +604,10 @@
         <v>2</v>
       </c>
       <c r="N5" t="n">
-        <v>74676.651315789</v>
+        <v>74676.64464285701</v>
       </c>
       <c r="O5" t="n">
-        <v>149353.302631578</v>
+        <v>149353.289285714</v>
       </c>
       <c r="P5" t="n">
         <v>144900</v>
@@ -1358,10 +1358,10 @@
         <v>21</v>
       </c>
       <c r="N23" t="n">
-        <v>3910.6281632653</v>
+        <v>3910.6281595092</v>
       </c>
       <c r="O23" t="n">
-        <v>82123.1914285713</v>
+        <v>82123.1913496932</v>
       </c>
       <c r="P23" t="n">
         <v>9100</v>
@@ -1442,10 +1442,10 @@
         <v>36</v>
       </c>
       <c r="N25" t="n">
-        <v>15711.965957447</v>
+        <v>15711.965922747</v>
       </c>
       <c r="O25" t="n">
-        <v>565630.774468092</v>
+        <v>565630.773218892</v>
       </c>
       <c r="P25" t="n">
         <v>28500</v>
@@ -1575,10 +1575,10 @@
         <v>4</v>
       </c>
       <c r="N28" t="n">
-        <v>22267.552173913</v>
+        <v>22267.5525</v>
       </c>
       <c r="O28" t="n">
-        <v>89070.20869565201</v>
+        <v>89070.21000000001</v>
       </c>
       <c r="P28" t="n">
         <v>46300</v>
@@ -1758,10 +1758,10 @@
         <v>28</v>
       </c>
       <c r="N32" t="n">
-        <v>200072.20057377</v>
+        <v>200072.20066116</v>
       </c>
       <c r="O32" t="n">
-        <v>5602021.61606556</v>
+        <v>5602021.61851248</v>
       </c>
       <c r="P32" t="n">
         <v>312000</v>
@@ -1800,10 +1800,10 @@
         <v>14</v>
       </c>
       <c r="N33" t="n">
-        <v>174389.79407407</v>
+        <v>174389.795</v>
       </c>
       <c r="O33" t="n">
-        <v>2441457.11703698</v>
+        <v>2441457.13</v>
       </c>
       <c r="P33" t="n">
         <v>368200</v>
@@ -1847,10 +1847,10 @@
         <v>6</v>
       </c>
       <c r="N34" t="n">
-        <v>251809.29393939</v>
+        <v>251809.29375</v>
       </c>
       <c r="O34" t="n">
-        <v>1510855.76363634</v>
+        <v>1510855.7625</v>
       </c>
       <c r="P34" t="n">
         <v>584000</v>
@@ -2050,10 +2050,10 @@
         <v>67</v>
       </c>
       <c r="N39" t="n">
-        <v>61666.874048257</v>
+        <v>61666.874070081</v>
       </c>
       <c r="O39" t="n">
-        <v>4131680.561233219</v>
+        <v>4131680.562695427</v>
       </c>
       <c r="P39" t="n">
         <v>98900</v>
@@ -2174,10 +2174,10 @@
         <v>24</v>
       </c>
       <c r="N42" t="n">
-        <v>4878.2859036145</v>
+        <v>4878.2859393939</v>
       </c>
       <c r="O42" t="n">
-        <v>117078.861686748</v>
+        <v>117078.8625454536</v>
       </c>
       <c r="P42" t="n">
         <v>13500</v>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -604,10 +604,10 @@
         <v>2</v>
       </c>
       <c r="N5" t="n">
-        <v>74676.64464285701</v>
+        <v>87122.75208333301</v>
       </c>
       <c r="O5" t="n">
-        <v>149353.289285714</v>
+        <v>174245.504166666</v>
       </c>
       <c r="P5" t="n">
         <v>144900</v>
@@ -763,10 +763,10 @@
         <v>12</v>
       </c>
       <c r="N9" t="n">
-        <v>20826.677297297</v>
+        <v>20826.6775</v>
       </c>
       <c r="O9" t="n">
-        <v>249920.127567564</v>
+        <v>249920.13</v>
       </c>
       <c r="P9" t="n">
         <v>39100</v>
@@ -1110,22 +1110,22 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M17" t="n">
-        <v>432</v>
+        <v>360</v>
       </c>
       <c r="N17" t="n">
         <v>3585</v>
       </c>
       <c r="O17" t="n">
-        <v>1548720</v>
+        <v>1290600</v>
       </c>
       <c r="P17" t="n">
         <v>4500</v>
       </c>
       <c r="Q17" t="n">
-        <v>1944000</v>
+        <v>1620000</v>
       </c>
     </row>
     <row r="18">
@@ -1358,10 +1358,10 @@
         <v>21</v>
       </c>
       <c r="N23" t="n">
-        <v>3910.6281595092</v>
+        <v>3910.6281481481</v>
       </c>
       <c r="O23" t="n">
-        <v>82123.1913496932</v>
+        <v>82123.19111111011</v>
       </c>
       <c r="P23" t="n">
         <v>9100</v>
@@ -2050,10 +2050,10 @@
         <v>67</v>
       </c>
       <c r="N39" t="n">
-        <v>61666.874070081</v>
+        <v>61666.874081081</v>
       </c>
       <c r="O39" t="n">
-        <v>4131680.562695427</v>
+        <v>4131680.563432427</v>
       </c>
       <c r="P39" t="n">
         <v>98900</v>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-27</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-28</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -554,19 +554,19 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N4" t="n">
         <v>96741.407702703</v>
       </c>
       <c r="O4" t="n">
-        <v>483707.038513515</v>
+        <v>193482.815405406</v>
       </c>
       <c r="P4" t="n">
         <v>188900</v>
       </c>
       <c r="Q4" t="n">
-        <v>944500</v>
+        <v>377800</v>
       </c>
     </row>
     <row r="5">
@@ -604,10 +604,10 @@
         <v>2</v>
       </c>
       <c r="N5" t="n">
-        <v>87122.75208333301</v>
+        <v>74676.64464285701</v>
       </c>
       <c r="O5" t="n">
-        <v>174245.504166666</v>
+        <v>149353.289285714</v>
       </c>
       <c r="P5" t="n">
         <v>144900</v>
@@ -1077,10 +1077,10 @@
         <v>29</v>
       </c>
       <c r="N16" t="n">
-        <v>1933.3879908676</v>
+        <v>1933.3880645161</v>
       </c>
       <c r="O16" t="n">
-        <v>56068.2517351604</v>
+        <v>56068.2538709669</v>
       </c>
       <c r="P16" t="n">
         <v>4500</v>
@@ -1104,13 +1104,13 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>432</v>
+        <v>360</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>360</v>
@@ -1155,10 +1155,10 @@
         <v>324</v>
       </c>
       <c r="N18" t="n">
-        <v>3926.8371059432</v>
+        <v>3926.8370969414</v>
       </c>
       <c r="O18" t="n">
-        <v>1272295.222325597</v>
+        <v>1272295.219409014</v>
       </c>
       <c r="P18" t="n">
         <v>4800</v>
@@ -1319,10 +1319,10 @@
         <v>13</v>
       </c>
       <c r="N22" t="n">
-        <v>15403.520914286</v>
+        <v>15403.520977011</v>
       </c>
       <c r="O22" t="n">
-        <v>200245.771885718</v>
+        <v>200245.772701143</v>
       </c>
       <c r="P22" t="n">
         <v>33500</v>
@@ -1358,10 +1358,10 @@
         <v>21</v>
       </c>
       <c r="N23" t="n">
-        <v>3910.6281481481</v>
+        <v>3910.6281404959</v>
       </c>
       <c r="O23" t="n">
-        <v>82123.19111111011</v>
+        <v>82123.1909504139</v>
       </c>
       <c r="P23" t="n">
         <v>9100</v>
@@ -1489,10 +1489,10 @@
         <v>6</v>
       </c>
       <c r="N26" t="n">
-        <v>30238.812571429</v>
+        <v>30238.812608696</v>
       </c>
       <c r="O26" t="n">
-        <v>181432.875428574</v>
+        <v>181432.875652176</v>
       </c>
       <c r="P26" t="n">
         <v>51100</v>
@@ -1788,7 +1788,7 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -1797,19 +1797,19 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="N33" t="n">
-        <v>174389.795</v>
+        <v>174389.79826087</v>
       </c>
       <c r="O33" t="n">
-        <v>2441457.13</v>
+        <v>1743897.9826087</v>
       </c>
       <c r="P33" t="n">
         <v>368200</v>
       </c>
       <c r="Q33" t="n">
-        <v>5154800</v>
+        <v>3682000</v>
       </c>
     </row>
     <row r="34">
@@ -2050,10 +2050,10 @@
         <v>67</v>
       </c>
       <c r="N39" t="n">
-        <v>61666.874081081</v>
+        <v>61666.874092141</v>
       </c>
       <c r="O39" t="n">
-        <v>4131680.563432427</v>
+        <v>4131680.564173447</v>
       </c>
       <c r="P39" t="n">
         <v>98900</v>
@@ -2410,10 +2410,10 @@
         <v>264</v>
       </c>
       <c r="N48" t="n">
-        <v>3340.6800817996</v>
+        <v>3340.6800821355</v>
       </c>
       <c r="O48" t="n">
-        <v>881939.5415950944</v>
+        <v>881939.541683772</v>
       </c>
       <c r="P48" t="n">
         <v>7100</v>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -1202,10 +1202,10 @@
         <v>12</v>
       </c>
       <c r="N19" t="n">
-        <v>22510.483333333</v>
+        <v>22510.483207547</v>
       </c>
       <c r="O19" t="n">
-        <v>270125.799999996</v>
+        <v>270125.798490564</v>
       </c>
       <c r="P19" t="n">
         <v>44900</v>
@@ -1716,10 +1716,10 @@
         <v>56</v>
       </c>
       <c r="N31" t="n">
-        <v>141416.88456026</v>
+        <v>141416.88457516</v>
       </c>
       <c r="O31" t="n">
-        <v>7919345.535374559</v>
+        <v>7919345.536208959</v>
       </c>
       <c r="P31" t="n">
         <v>251900</v>
@@ -2050,10 +2050,10 @@
         <v>67</v>
       </c>
       <c r="N39" t="n">
-        <v>61666.874092141</v>
+        <v>61666.874114441</v>
       </c>
       <c r="O39" t="n">
-        <v>4131680.564173447</v>
+        <v>4131680.565667547</v>
       </c>
       <c r="P39" t="n">
         <v>98900</v>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-28</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-29</t>
         </is>
       </c>
     </row>
@@ -1358,10 +1358,10 @@
         <v>21</v>
       </c>
       <c r="N23" t="n">
-        <v>3910.6281404959</v>
+        <v>3910.628136646</v>
       </c>
       <c r="O23" t="n">
-        <v>82123.1909504139</v>
+        <v>82123.19086956599</v>
       </c>
       <c r="P23" t="n">
         <v>9100</v>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -1155,10 +1155,10 @@
         <v>324</v>
       </c>
       <c r="N18" t="n">
-        <v>3926.8370969414</v>
+        <v>3926.8370954357</v>
       </c>
       <c r="O18" t="n">
-        <v>1272295.219409014</v>
+        <v>1272295.218921167</v>
       </c>
       <c r="P18" t="n">
         <v>4800</v>
@@ -1442,10 +1442,10 @@
         <v>36</v>
       </c>
       <c r="N25" t="n">
-        <v>15711.965922747</v>
+        <v>15711.965905172</v>
       </c>
       <c r="O25" t="n">
-        <v>565630.773218892</v>
+        <v>565630.772586192</v>
       </c>
       <c r="P25" t="n">
         <v>28500</v>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-29</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-30</t>
         </is>
       </c>
     </row>
@@ -1035,10 +1035,10 @@
         <v>18</v>
       </c>
       <c r="N15" t="n">
-        <v>31658.725454545</v>
+        <v>31658.725660377</v>
       </c>
       <c r="O15" t="n">
-        <v>569857.0581818101</v>
+        <v>569857.061886786</v>
       </c>
       <c r="P15" t="n">
         <v>62900</v>
@@ -1358,10 +1358,10 @@
         <v>21</v>
       </c>
       <c r="N23" t="n">
-        <v>3910.628136646</v>
+        <v>3910.628089172</v>
       </c>
       <c r="O23" t="n">
-        <v>82123.19086956599</v>
+        <v>82123.189872612</v>
       </c>
       <c r="P23" t="n">
         <v>9100</v>
@@ -1400,10 +1400,10 @@
         <v>10</v>
       </c>
       <c r="N24" t="n">
-        <v>16486.408837209</v>
+        <v>16486.40875</v>
       </c>
       <c r="O24" t="n">
-        <v>164864.08837209</v>
+        <v>164864.0875</v>
       </c>
       <c r="P24" t="n">
         <v>30500</v>
@@ -1442,10 +1442,10 @@
         <v>36</v>
       </c>
       <c r="N25" t="n">
-        <v>15711.965905172</v>
+        <v>15711.965869565</v>
       </c>
       <c r="O25" t="n">
-        <v>565630.772586192</v>
+        <v>565630.77130434</v>
       </c>
       <c r="P25" t="n">
         <v>28500</v>
@@ -1489,10 +1489,10 @@
         <v>6</v>
       </c>
       <c r="N26" t="n">
-        <v>30238.812608696</v>
+        <v>30238.812647059</v>
       </c>
       <c r="O26" t="n">
-        <v>181432.875652176</v>
+        <v>181432.875882354</v>
       </c>
       <c r="P26" t="n">
         <v>51100</v>
@@ -1894,10 +1894,10 @@
         <v>6</v>
       </c>
       <c r="N35" t="n">
-        <v>344599.17862745</v>
+        <v>344599.1786</v>
       </c>
       <c r="O35" t="n">
-        <v>2067595.0717647</v>
+        <v>2067595.0716</v>
       </c>
       <c r="P35" t="n">
         <v>532900</v>
@@ -2410,10 +2410,10 @@
         <v>264</v>
       </c>
       <c r="N48" t="n">
-        <v>3340.6800821355</v>
+        <v>3340.6800824742</v>
       </c>
       <c r="O48" t="n">
-        <v>881939.541683772</v>
+        <v>881939.5417731887</v>
       </c>
       <c r="P48" t="n">
         <v>7100</v>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-30</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-31</t>
         </is>
       </c>
     </row>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -557,10 +557,10 @@
         <v>2</v>
       </c>
       <c r="N4" t="n">
-        <v>96741.407702703</v>
+        <v>96741.42375</v>
       </c>
       <c r="O4" t="n">
-        <v>193482.815405406</v>
+        <v>193482.8475</v>
       </c>
       <c r="P4" t="n">
         <v>188900</v>
@@ -1400,10 +1400,10 @@
         <v>10</v>
       </c>
       <c r="N24" t="n">
-        <v>16486.40875</v>
+        <v>16486.408661417</v>
       </c>
       <c r="O24" t="n">
-        <v>164864.0875</v>
+        <v>164864.08661417</v>
       </c>
       <c r="P24" t="n">
         <v>30500</v>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-31</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-01</t>
         </is>
       </c>
     </row>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -1442,10 +1442,10 @@
         <v>36</v>
       </c>
       <c r="N25" t="n">
-        <v>15711.965869565</v>
+        <v>15711.965851528</v>
       </c>
       <c r="O25" t="n">
-        <v>565630.77130434</v>
+        <v>565630.770655008</v>
       </c>
       <c r="P25" t="n">
         <v>28500</v>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-01</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-02</t>
         </is>
       </c>
     </row>
@@ -1358,10 +1358,10 @@
         <v>21</v>
       </c>
       <c r="N23" t="n">
-        <v>3910.628089172</v>
+        <v>3910.6280686695</v>
       </c>
       <c r="O23" t="n">
-        <v>82123.189872612</v>
+        <v>82123.18944205951</v>
       </c>
       <c r="P23" t="n">
         <v>9100</v>
@@ -1442,10 +1442,10 @@
         <v>36</v>
       </c>
       <c r="N25" t="n">
-        <v>15711.965851528</v>
+        <v>15711.965814978</v>
       </c>
       <c r="O25" t="n">
-        <v>565630.770655008</v>
+        <v>565630.769339208</v>
       </c>
       <c r="P25" t="n">
         <v>28500</v>
@@ -1758,10 +1758,10 @@
         <v>28</v>
       </c>
       <c r="N32" t="n">
-        <v>200072.20066116</v>
+        <v>200072.20075</v>
       </c>
       <c r="O32" t="n">
-        <v>5602021.61851248</v>
+        <v>5602021.620999999</v>
       </c>
       <c r="P32" t="n">
         <v>312000</v>
@@ -2410,10 +2410,10 @@
         <v>264</v>
       </c>
       <c r="N48" t="n">
-        <v>3340.6800824742</v>
+        <v>3340.6800833333</v>
       </c>
       <c r="O48" t="n">
-        <v>881939.5417731887</v>
+        <v>881939.5419999912</v>
       </c>
       <c r="P48" t="n">
         <v>7100</v>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -1400,10 +1400,10 @@
         <v>10</v>
       </c>
       <c r="N24" t="n">
-        <v>16486.408661417</v>
+        <v>16486.408571429</v>
       </c>
       <c r="O24" t="n">
-        <v>164864.08661417</v>
+        <v>164864.08571429</v>
       </c>
       <c r="P24" t="n">
         <v>30500</v>
@@ -1442,10 +1442,10 @@
         <v>36</v>
       </c>
       <c r="N25" t="n">
-        <v>15711.965814978</v>
+        <v>15711.96579646</v>
       </c>
       <c r="O25" t="n">
-        <v>565630.769339208</v>
+        <v>565630.76867256</v>
       </c>
       <c r="P25" t="n">
         <v>28500</v>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q71"/>
+  <dimension ref="A1:Q68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-02</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-03</t>
         </is>
       </c>
     </row>
@@ -524,14 +524,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>10471</v>
+        <v>10473</v>
       </c>
       <c r="B4" t="n">
-        <v>6941607380819</v>
+        <v>6941607380833</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>PISCINA ESTRUCTURAL 228X159X42cm</t>
+          <t>PISCINA RIGIDA 190X130X42cm</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -557,42 +557,34 @@
         <v>2</v>
       </c>
       <c r="N4" t="n">
-        <v>96741.42375</v>
+        <v>74676.64464285701</v>
       </c>
       <c r="O4" t="n">
-        <v>193482.8475</v>
+        <v>149353.289285714</v>
       </c>
       <c r="P4" t="n">
-        <v>188900</v>
+        <v>144900</v>
       </c>
       <c r="Q4" t="n">
-        <v>377800</v>
+        <v>289800</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>10473</v>
-      </c>
-      <c r="B5" t="n">
-        <v>6941607380833</v>
+        <v>22057</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>PISCINA RIGIDA 190X130X42cm</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>22057 CARETA NATACION NIÑOS BESTWAY</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -601,28 +593,28 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="N5" t="n">
-        <v>74676.64464285701</v>
+        <v>6338</v>
       </c>
       <c r="O5" t="n">
-        <v>149353.289285714</v>
+        <v>304224</v>
       </c>
       <c r="P5" t="n">
-        <v>144900</v>
+        <v>10900</v>
       </c>
       <c r="Q5" t="n">
-        <v>289800</v>
+        <v>523200</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>22057</v>
+        <v>22064</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>22057 CARETA NATACION NIÑOS BESTWAY</t>
+          <t>22064 GAFA NATACION  INFANTIL BESTWAY</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -631,7 +623,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -640,28 +632,31 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="N6" t="n">
-        <v>6338</v>
+        <v>5758.9597777778</v>
       </c>
       <c r="O6" t="n">
-        <v>304224</v>
+        <v>69107.5173333336</v>
       </c>
       <c r="P6" t="n">
-        <v>10900</v>
+        <v>16900</v>
       </c>
       <c r="Q6" t="n">
-        <v>523200</v>
+        <v>202800</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>22064</v>
+        <v>24021</v>
+      </c>
+      <c r="B7" t="n">
+        <v>6941607331156</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>22064 GAFA NATACION  INFANTIL BESTWAY</t>
+          <t>HYDRO-PRO BLACKSEA MASK  SNORKEL SET 6 PCS</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -670,7 +665,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -679,31 +674,28 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="N7" t="n">
-        <v>5758.9597777778</v>
+        <v>27815.961126761</v>
       </c>
       <c r="O7" t="n">
-        <v>69107.5173333336</v>
+        <v>1168270.367323962</v>
       </c>
       <c r="P7" t="n">
-        <v>16900</v>
+        <v>58600</v>
       </c>
       <c r="Q7" t="n">
-        <v>202800</v>
+        <v>2461200</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>24021</v>
-      </c>
-      <c r="B8" t="n">
-        <v>6941607331156</v>
+        <v>24029</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>HYDRO-PRO BLACKSEA MASK  SNORKEL SET 6 PCS</t>
+          <t>HYDRO-SWIM BLACKSTRIPE SET</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -712,7 +704,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -721,37 +713,45 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="N8" t="n">
-        <v>27815.961126761</v>
+        <v>20826.6775</v>
       </c>
       <c r="O8" t="n">
-        <v>1168270.367323962</v>
+        <v>249920.13</v>
       </c>
       <c r="P8" t="n">
-        <v>58600</v>
+        <v>39100</v>
       </c>
       <c r="Q8" t="n">
-        <v>2461200</v>
+        <v>469200</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24029</v>
+        <v>24035</v>
+      </c>
+      <c r="B9" t="n">
+        <v>6941607331217</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>HYDRO-SWIM BLACKSTRIPE SET</t>
+          <t>Equipo de Buceo Bestway, Essential Freestyle, +7 Años, 35x13cm, 24035</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -760,31 +760,31 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="N9" t="n">
-        <v>20826.6775</v>
+        <v>13386</v>
       </c>
       <c r="O9" t="n">
-        <v>249920.13</v>
+        <v>321264</v>
       </c>
       <c r="P9" t="n">
-        <v>39100</v>
+        <v>23900</v>
       </c>
       <c r="Q9" t="n">
-        <v>469200</v>
+        <v>573600</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>24035</v>
+        <v>24058</v>
       </c>
       <c r="B10" t="n">
-        <v>6941607331217</v>
+        <v>6941607331255</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Equipo de Buceo Bestway, Essential Freestyle, +7 Años, 35x13cm, 24035</t>
+          <t>Máscara de esnórquel - 24058 L/XL</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -807,31 +807,31 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="N10" t="n">
-        <v>13386</v>
+        <v>73300</v>
       </c>
       <c r="O10" t="n">
-        <v>321264</v>
+        <v>293200</v>
       </c>
       <c r="P10" t="n">
-        <v>23900</v>
+        <v>119900</v>
       </c>
       <c r="Q10" t="n">
-        <v>573600</v>
+        <v>479600</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>24058</v>
+        <v>24060</v>
       </c>
       <c r="B11" t="n">
-        <v>6941607331255</v>
+        <v>6941607331286</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Máscara de esnórquel - 24058 L/XL</t>
+          <t>Máscara Buceo Snorkel con 2 Tubos Hydro Pro Talla S/M Bestway 24060</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -857,10 +857,10 @@
         <v>4</v>
       </c>
       <c r="N11" t="n">
-        <v>73300</v>
+        <v>73940</v>
       </c>
       <c r="O11" t="n">
-        <v>293200</v>
+        <v>295760</v>
       </c>
       <c r="P11" t="n">
         <v>119900</v>
@@ -871,14 +871,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>24060</v>
+        <v>24068</v>
       </c>
       <c r="B12" t="n">
-        <v>6941607331286</v>
+        <v>6941607331149</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Máscara Buceo Snorkel con 2 Tubos Hydro Pro Talla S/M Bestway 24060</t>
+          <t>Máscara de Buceo Snorkel +14 Bestway Spark Wave</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -892,7 +892,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -901,41 +901,36 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="N12" t="n">
-        <v>73940</v>
+        <v>18934</v>
       </c>
       <c r="O12" t="n">
-        <v>295760</v>
+        <v>227208</v>
       </c>
       <c r="P12" t="n">
-        <v>119900</v>
+        <v>32900</v>
       </c>
       <c r="Q12" t="n">
-        <v>479600</v>
+        <v>394800</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>24068</v>
+        <v>24069</v>
       </c>
       <c r="B13" t="n">
-        <v>6941607331149</v>
+        <v>6941607331125</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Máscara de Buceo Snorkel +14 Bestway Spark Wave</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>24069 SET SNORKEL ADULTO BESTWAY</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -951,28 +946,28 @@
         <v>12</v>
       </c>
       <c r="N13" t="n">
-        <v>18934</v>
+        <v>30240.861395349</v>
       </c>
       <c r="O13" t="n">
-        <v>227208</v>
+        <v>362890.336744188</v>
       </c>
       <c r="P13" t="n">
-        <v>32900</v>
+        <v>56900</v>
       </c>
       <c r="Q13" t="n">
-        <v>394800</v>
+        <v>682800</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>24069</v>
+        <v>25020</v>
       </c>
       <c r="B14" t="n">
-        <v>6941607331125</v>
+        <v>6941607331309</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>24069 SET SNORKEL ADULTO BESTWAY</t>
+          <t>25020 SET SNORKEL-ALETAD ADULTO BESTWAY</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -981,7 +976,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -990,31 +985,31 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="N14" t="n">
-        <v>30240.861395349</v>
+        <v>31658.725660377</v>
       </c>
       <c r="O14" t="n">
-        <v>362890.336744188</v>
+        <v>569857.061886786</v>
       </c>
       <c r="P14" t="n">
-        <v>56900</v>
+        <v>62900</v>
       </c>
       <c r="Q14" t="n">
-        <v>682800</v>
+        <v>1132200</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>25020</v>
+        <v>31036</v>
       </c>
       <c r="B15" t="n">
-        <v>6941607331309</v>
+        <v>6942138967142</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>25020 SET SNORKEL-ALETAD ADULTO BESTWAY</t>
+          <t>31036 BALON PLAYERO 51CM  DISEÑOS   BESTWAY 36 PCS</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1023,7 +1018,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1032,31 +1027,28 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="N15" t="n">
-        <v>31658.725660377</v>
+        <v>1933.3880645161</v>
       </c>
       <c r="O15" t="n">
-        <v>569857.061886786</v>
+        <v>56068.2538709669</v>
       </c>
       <c r="P15" t="n">
-        <v>62900</v>
+        <v>4500</v>
       </c>
       <c r="Q15" t="n">
-        <v>1132200</v>
+        <v>130500</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>31036</v>
-      </c>
-      <c r="B16" t="n">
-        <v>6942138967142</v>
+        <v>32033</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>31036 BALON PLAYERO 51CM  DISEÑOS   BESTWAY 36 PCS</t>
+          <t>BRAZOS INFLABLES  25 CM BESTWAY 36PCS</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1065,7 +1057,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>29</v>
+        <v>360</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1074,28 +1066,28 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>29</v>
+        <v>360</v>
       </c>
       <c r="N16" t="n">
-        <v>1933.3880645161</v>
+        <v>3585</v>
       </c>
       <c r="O16" t="n">
-        <v>56068.2538709669</v>
+        <v>1290600</v>
       </c>
       <c r="P16" t="n">
         <v>4500</v>
       </c>
       <c r="Q16" t="n">
-        <v>130500</v>
+        <v>1620000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>32033</v>
+        <v>32110</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BRAZOS INFLABLES  25 CM BESTWAY 36PCS</t>
+          <t>BRAZOS INFLEBLES 30 CM BESTWAY 36PCS</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1104,7 +1096,7 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>360</v>
+        <v>324</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1113,28 +1105,36 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>360</v>
+        <v>324</v>
       </c>
       <c r="N17" t="n">
-        <v>3585</v>
+        <v>3926.8370954357</v>
       </c>
       <c r="O17" t="n">
-        <v>1290600</v>
+        <v>1272295.218921167</v>
       </c>
       <c r="P17" t="n">
-        <v>4500</v>
+        <v>4800</v>
       </c>
       <c r="Q17" t="n">
-        <v>1620000</v>
+        <v>1555200</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>32110</v>
+        <v>34149</v>
+      </c>
+      <c r="B18" t="n">
+        <v>6941607308462</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>BRAZOS INFLEBLES 30 CM BESTWAY 36PCS</t>
+          <t>34149 FLOTADOR TECHO COHETE BESTWAY</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1143,7 +1143,7 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>324</v>
+        <v>12</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1152,36 +1152,28 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>324</v>
+        <v>12</v>
       </c>
       <c r="N18" t="n">
-        <v>3926.8370954357</v>
+        <v>22510.483207547</v>
       </c>
       <c r="O18" t="n">
-        <v>1272295.218921167</v>
+        <v>270125.798490564</v>
       </c>
       <c r="P18" t="n">
-        <v>4800</v>
+        <v>44900</v>
       </c>
       <c r="Q18" t="n">
-        <v>1555200</v>
+        <v>538800</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>34149</v>
-      </c>
-      <c r="B19" t="n">
-        <v>6941607308462</v>
+        <v>34180</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>34149 FLOTADOR TECHO COHETE BESTWAY</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>FLOTADOR ANIMALES PIES BESTWAY 24PCS</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1190,7 +1182,7 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>12</v>
+        <v>384</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1199,28 +1191,28 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>12</v>
+        <v>384</v>
       </c>
       <c r="N19" t="n">
-        <v>22510.483207547</v>
+        <v>11256</v>
       </c>
       <c r="O19" t="n">
-        <v>270125.798490564</v>
+        <v>4322304</v>
       </c>
       <c r="P19" t="n">
-        <v>44900</v>
+        <v>18400</v>
       </c>
       <c r="Q19" t="n">
-        <v>538800</v>
+        <v>7065600</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>34180</v>
+        <v>36405</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>FLOTADOR ANIMALES PIES BESTWAY 24PCS</t>
+          <t>FLOTADOR ARO ANIMALES BESTWAY 36PCS</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1229,7 +1221,7 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>384</v>
+        <v>792</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1238,28 +1230,28 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>384</v>
+        <v>792</v>
       </c>
       <c r="N20" t="n">
-        <v>11256</v>
+        <v>2681</v>
       </c>
       <c r="O20" t="n">
-        <v>4322304</v>
+        <v>2123352</v>
       </c>
       <c r="P20" t="n">
-        <v>18400</v>
+        <v>3500</v>
       </c>
       <c r="Q20" t="n">
-        <v>7065600</v>
+        <v>2772000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>36405</v>
+        <v>41037</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>FLOTADOR ARO ANIMALES BESTWAY 36PCS</t>
+          <t>41037 FLOTADOR BALLENA BESTWAY 12PCS</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1268,7 +1260,7 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>792</v>
+        <v>13</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1277,28 +1269,28 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>792</v>
+        <v>13</v>
       </c>
       <c r="N21" t="n">
-        <v>2681</v>
+        <v>15403.520977011</v>
       </c>
       <c r="O21" t="n">
-        <v>2123352</v>
+        <v>200245.772701143</v>
       </c>
       <c r="P21" t="n">
-        <v>3500</v>
+        <v>33500</v>
       </c>
       <c r="Q21" t="n">
-        <v>2772000</v>
+        <v>435500</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>41037</v>
+        <v>44007</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>41037 FLOTADOR BALLENA BESTWAY 12PCS</t>
+          <t>COLCHONETA INFLABLE 69CM BESTWAY</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1307,7 +1299,7 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1316,28 +1308,31 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="N22" t="n">
-        <v>15403.520977011</v>
+        <v>3910.6280519481</v>
       </c>
       <c r="O22" t="n">
-        <v>200245.772701143</v>
+        <v>82123.18909091011</v>
       </c>
       <c r="P22" t="n">
-        <v>33500</v>
+        <v>9100</v>
       </c>
       <c r="Q22" t="n">
-        <v>435500</v>
+        <v>191100</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>44007</v>
+        <v>51124</v>
+      </c>
+      <c r="B23" t="n">
+        <v>6941607325032</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>COLCHONETA INFLABLE 69CM BESTWAY</t>
+          <t>51124 COMBO DE PISCINA Y BALON</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1346,7 +1341,7 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -1355,31 +1350,28 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="N23" t="n">
-        <v>3910.6280686695</v>
+        <v>15711.965777778</v>
       </c>
       <c r="O23" t="n">
-        <v>82123.18944205951</v>
+        <v>565630.768000008</v>
       </c>
       <c r="P23" t="n">
-        <v>9100</v>
+        <v>28500</v>
       </c>
       <c r="Q23" t="n">
-        <v>191100</v>
+        <v>1026000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>51104</v>
-      </c>
-      <c r="B24" t="n">
-        <v>6942138915815</v>
+        <v>52331</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>PISCINA VERANO 102 X25 CM</t>
+          <t>PISCINA CANOPY FRUTICAS 8 PCS</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1388,7 +1380,7 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -1397,31 +1389,36 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="N24" t="n">
-        <v>16486.408571429</v>
+        <v>20195.32</v>
       </c>
       <c r="O24" t="n">
-        <v>164864.08571429</v>
+        <v>1514649</v>
       </c>
       <c r="P24" t="n">
-        <v>30500</v>
+        <v>45900</v>
       </c>
       <c r="Q24" t="n">
-        <v>305000</v>
+        <v>3442500</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>51124</v>
+        <v>52637</v>
       </c>
       <c r="B25" t="n">
-        <v>6941607325032</v>
+        <v>6941607352212</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>51124 COMBO DE PISCINA Y BALON</t>
+          <t>52637 PISCINA TECHADA SUNNY BESTWAY</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1430,7 +1427,7 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -1439,31 +1436,31 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="N25" t="n">
-        <v>15711.96579646</v>
+        <v>22267.5525</v>
       </c>
       <c r="O25" t="n">
-        <v>565630.76867256</v>
+        <v>89070.21000000001</v>
       </c>
       <c r="P25" t="n">
-        <v>28500</v>
+        <v>46300</v>
       </c>
       <c r="Q25" t="n">
-        <v>1026000</v>
+        <v>185200</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>51203</v>
+        <v>53157</v>
       </c>
       <c r="B26" t="n">
-        <v>6941607325544</v>
+        <v>6941607352137</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>51203 PISCINA 3 AROS BESTWAY Φ1.68m x H38cm</t>
+          <t>53157 PISCINA FUENTE SHARK BESTWAY</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1473,11 +1470,11 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -1486,28 +1483,36 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N26" t="n">
-        <v>30238.812647059</v>
+        <v>36574.852307692</v>
       </c>
       <c r="O26" t="n">
-        <v>181432.875882354</v>
+        <v>146299.409230768</v>
       </c>
       <c r="P26" t="n">
-        <v>51100</v>
+        <v>65900</v>
       </c>
       <c r="Q26" t="n">
-        <v>306600</v>
+        <v>263600</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>52331</v>
+        <v>54370</v>
+      </c>
+      <c r="B27" t="n">
+        <v>6941607312643</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>PISCINA CANOPY FRUTICAS 8 PCS</t>
+          <t>PISCINA CAPITAN 213 X155 X 132CM</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1516,7 +1521,7 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>75</v>
+        <v>4</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -1525,31 +1530,31 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>75</v>
+        <v>4</v>
       </c>
       <c r="N27" t="n">
-        <v>20195.32</v>
+        <v>103298.75</v>
       </c>
       <c r="O27" t="n">
-        <v>1514649</v>
+        <v>413195</v>
       </c>
       <c r="P27" t="n">
-        <v>45900</v>
+        <v>178900</v>
       </c>
       <c r="Q27" t="n">
-        <v>3442500</v>
+        <v>715600</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>52637</v>
+        <v>56401</v>
       </c>
       <c r="B28" t="n">
-        <v>6941607352212</v>
+        <v>6941607327951</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>52637 PISCINA TECHADA SUNNY BESTWAY</t>
+          <t>56401 PISCINA ESTRUCTURAL RECTANGULAR BESTWAY</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1563,7 +1568,7 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -1572,45 +1577,40 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="N28" t="n">
-        <v>22267.5525</v>
+        <v>141416.88457516</v>
       </c>
       <c r="O28" t="n">
-        <v>89070.21000000001</v>
+        <v>7919345.536208959</v>
       </c>
       <c r="P28" t="n">
-        <v>46300</v>
+        <v>251900</v>
       </c>
       <c r="Q28" t="n">
-        <v>185200</v>
+        <v>14106400</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>53157</v>
+        <v>56403</v>
       </c>
       <c r="B29" t="n">
-        <v>6941607352137</v>
+        <v>6941607327982</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>53157 PISCINA FUENTE SHARK BESTWAY</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>PISCINA ESTRUCTURAL 2.59m x 1.70m x 61cm BESTWAY</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -1619,36 +1619,31 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="N29" t="n">
-        <v>36574.852307692</v>
+        <v>200072.20075</v>
       </c>
       <c r="O29" t="n">
-        <v>146299.409230768</v>
+        <v>4601660.61725</v>
       </c>
       <c r="P29" t="n">
-        <v>65900</v>
+        <v>312000</v>
       </c>
       <c r="Q29" t="n">
-        <v>263600</v>
+        <v>7176000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>54370</v>
+        <v>56404</v>
       </c>
       <c r="B30" t="n">
-        <v>6941607312643</v>
+        <v>6941607327999</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>PISCINA CAPITAN 213 X155 X 132CM</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>56404 PISCINA ESTRUCTURAL RECTANGULAR BESTWAY</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1657,7 +1652,7 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -1666,31 +1661,31 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="N30" t="n">
-        <v>103298.75</v>
+        <v>174389.79826087</v>
       </c>
       <c r="O30" t="n">
-        <v>413195</v>
+        <v>1743897.9826087</v>
       </c>
       <c r="P30" t="n">
-        <v>178900</v>
+        <v>368200</v>
       </c>
       <c r="Q30" t="n">
-        <v>715600</v>
+        <v>3682000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>56401</v>
+        <v>56405</v>
       </c>
       <c r="B31" t="n">
-        <v>6941607327951</v>
+        <v>6941607328002</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>56401 PISCINA ESTRUCTURAL RECTANGULAR BESTWAY</t>
+          <t>PISCINA ESTRUCTURAL RECTAGULAR BESTWAY 4.00mX2.11mX81cm</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1700,11 +1695,11 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>56</v>
+        <v>6</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -1713,31 +1708,36 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>56</v>
+        <v>6</v>
       </c>
       <c r="N31" t="n">
-        <v>141416.88457516</v>
+        <v>251809.29375</v>
       </c>
       <c r="O31" t="n">
-        <v>7919345.536208959</v>
+        <v>1510855.7625</v>
       </c>
       <c r="P31" t="n">
-        <v>251900</v>
+        <v>584000</v>
       </c>
       <c r="Q31" t="n">
-        <v>14106400</v>
+        <v>3504000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>56403</v>
+        <v>56417</v>
       </c>
       <c r="B32" t="n">
-        <v>6941607327982</v>
+        <v>6942138981902</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>PISCINA ESTRUCTURAL 2.59m x 1.70m x 61cm BESTWAY</t>
+          <t>Piscina Estructural Redonda 366 x 76 cm Bomba/Filtro 56417</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -1755,31 +1755,28 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="N32" t="n">
-        <v>200072.20075</v>
+        <v>344599.1786</v>
       </c>
       <c r="O32" t="n">
-        <v>5602021.620999999</v>
+        <v>2067595.0716</v>
       </c>
       <c r="P32" t="n">
-        <v>312000</v>
+        <v>532900</v>
       </c>
       <c r="Q32" t="n">
-        <v>8736000</v>
+        <v>3197400</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>56404</v>
-      </c>
-      <c r="B33" t="n">
-        <v>6941607327999</v>
+        <v>62068</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>56404 PISCINA ESTRUCTURAL RECTANGULAR BESTWAY</t>
+          <t>PARCHE PISCINA EXTERIOR BESTWAY</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1788,7 +1785,7 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -1797,45 +1794,37 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="N33" t="n">
-        <v>174389.79826087</v>
+        <v>1977.88</v>
       </c>
       <c r="O33" t="n">
-        <v>1743897.9826087</v>
+        <v>11867.28</v>
       </c>
       <c r="P33" t="n">
-        <v>368200</v>
+        <v>2900</v>
       </c>
       <c r="Q33" t="n">
-        <v>3682000</v>
+        <v>17400</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>56405</v>
-      </c>
-      <c r="B34" t="n">
-        <v>6941607328002</v>
+        <v>62091</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>PISCINA ESTRUCTURAL RECTAGULAR BESTWAY 4.00mX2.11mX81cm</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>PARCHE PISCINA A PRUEBA DE AGUA BESTWAY</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>6</v>
+        <v>217</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -1844,45 +1833,37 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>6</v>
+        <v>217</v>
       </c>
       <c r="N34" t="n">
-        <v>251809.29375</v>
+        <v>1141.57</v>
       </c>
       <c r="O34" t="n">
-        <v>1510855.7625</v>
+        <v>247720.69</v>
       </c>
       <c r="P34" t="n">
-        <v>584000</v>
+        <v>3900</v>
       </c>
       <c r="Q34" t="n">
-        <v>3504000</v>
+        <v>846300</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>56417</v>
-      </c>
-      <c r="B35" t="n">
-        <v>6942138981902</v>
+        <v>67001</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Piscina Estructural Redonda 366 x 76 cm Bomba/Filtro 56417</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>COLCHON INFLABLE SENCILLO BESTWAY 1.88 X 99 CM</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -1891,28 +1872,28 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N35" t="n">
-        <v>344599.1786</v>
+        <v>26280.41</v>
       </c>
       <c r="O35" t="n">
-        <v>2067595.0716</v>
+        <v>78841.23</v>
       </c>
       <c r="P35" t="n">
-        <v>532900</v>
+        <v>46500</v>
       </c>
       <c r="Q35" t="n">
-        <v>3197400</v>
+        <v>139500</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>62068</v>
+        <v>67374</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>PARCHE PISCINA EXTERIOR BESTWAY</t>
+          <t>COLCHON INFLABLE DOBLE+ALMOHADAS BESTWAY 2.03mx1.52mx22cm</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -1921,7 +1902,7 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -1930,28 +1911,28 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="N36" t="n">
-        <v>1977.88</v>
+        <v>61666.874114441</v>
       </c>
       <c r="O36" t="n">
-        <v>11867.28</v>
+        <v>4131680.565667547</v>
       </c>
       <c r="P36" t="n">
-        <v>2900</v>
+        <v>98900</v>
       </c>
       <c r="Q36" t="n">
-        <v>17400</v>
+        <v>6626300</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>62091</v>
+        <v>91004</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>PARCHE PISCINA A PRUEBA DE AGUA BESTWAY</t>
+          <t>FLOTADOR DISNEY 56CM 24PCS</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -1960,7 +1941,7 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>217</v>
+        <v>340</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -1969,28 +1950,28 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>217</v>
+        <v>340</v>
       </c>
       <c r="N37" t="n">
-        <v>1141.57</v>
+        <v>3865.67</v>
       </c>
       <c r="O37" t="n">
-        <v>247720.69</v>
+        <v>1314327.8</v>
       </c>
       <c r="P37" t="n">
-        <v>3900</v>
+        <v>5500</v>
       </c>
       <c r="Q37" t="n">
-        <v>846300</v>
+        <v>1870000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>67001</v>
+        <v>91007</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>COLCHON INFLABLE SENCILLO BESTWAY 1.88 X 99 CM</t>
+          <t>PISCINA DISNEY 122X25CM 12 PCS</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -1999,7 +1980,7 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -2008,28 +1989,35 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="N38" t="n">
-        <v>26280.41</v>
+        <v>16010.3</v>
       </c>
       <c r="O38" t="n">
-        <v>78841.23</v>
+        <v>384247.2</v>
       </c>
       <c r="P38" t="n">
-        <v>46500</v>
+        <v>30500</v>
       </c>
       <c r="Q38" t="n">
-        <v>139500</v>
+        <v>732000</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="n">
-        <v>67374</v>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>9103C</t>
+        </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>COLCHON INFLABLE DOBLE+ALMOHADAS BESTWAY 2.03mx1.52mx22cm</t>
+          <t>9103C GAFA ACUATICA SIRENITA BESTWAY</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2038,7 +2026,7 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -2047,28 +2035,30 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="N39" t="n">
-        <v>61666.874114441</v>
+        <v>4878.2859393939</v>
       </c>
       <c r="O39" t="n">
-        <v>4131680.565667547</v>
+        <v>117078.8625454536</v>
       </c>
       <c r="P39" t="n">
-        <v>98900</v>
+        <v>13500</v>
       </c>
       <c r="Q39" t="n">
-        <v>6626300</v>
+        <v>324000</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="n">
-        <v>91004</v>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>9103D</t>
+        </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>FLOTADOR DISNEY 56CM 24PCS</t>
+          <t>9103D CARETA ACUATICA SIRENITA BESTWAY</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2077,7 +2067,7 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>340</v>
+        <v>12</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -2086,28 +2076,28 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>340</v>
+        <v>12</v>
       </c>
       <c r="N40" t="n">
-        <v>3865.67</v>
+        <v>7394.9354444444</v>
       </c>
       <c r="O40" t="n">
-        <v>1314327.8</v>
+        <v>88739.2253333328</v>
       </c>
       <c r="P40" t="n">
-        <v>5500</v>
+        <v>17900</v>
       </c>
       <c r="Q40" t="n">
-        <v>1870000</v>
+        <v>214800</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>91007</v>
+        <v>91040</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>PISCINA DISNEY 122X25CM 12 PCS</t>
+          <t>FLOTADOR MINNIE 56CM 24 PCS</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2116,7 +2106,7 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>24</v>
+        <v>402</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -2125,35 +2115,28 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>24</v>
+        <v>402</v>
       </c>
       <c r="N41" t="n">
-        <v>16010.3</v>
+        <v>3114.49</v>
       </c>
       <c r="O41" t="n">
-        <v>384247.2</v>
+        <v>1252024.98</v>
       </c>
       <c r="P41" t="n">
-        <v>30500</v>
+        <v>5500</v>
       </c>
       <c r="Q41" t="n">
-        <v>732000</v>
+        <v>2211000</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>9103C</t>
-        </is>
+      <c r="A42" t="n">
+        <v>91042</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>9103C GAFA ACUATICA SIRENITA BESTWAY</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>PELOTA PISCINA PRINCESAS 24 PCS</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2162,7 +2145,7 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -2171,30 +2154,28 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="N42" t="n">
-        <v>4878.2859393939</v>
+        <v>2791.02</v>
       </c>
       <c r="O42" t="n">
-        <v>117078.8625454536</v>
+        <v>334922.4</v>
       </c>
       <c r="P42" t="n">
-        <v>13500</v>
+        <v>3900</v>
       </c>
       <c r="Q42" t="n">
-        <v>324000</v>
+        <v>468000</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>9103D</t>
-        </is>
+      <c r="A43" t="n">
+        <v>91043</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>9103D CARETA ACUATICA SIRENITA BESTWAY</t>
+          <t>FLOTADOR PRINCESAS 56CM 24PCS</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2203,7 +2184,7 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -2212,28 +2193,28 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="N43" t="n">
-        <v>7394.9354444444</v>
+        <v>3564.14</v>
       </c>
       <c r="O43" t="n">
-        <v>88739.2253333328</v>
+        <v>206720.12</v>
       </c>
       <c r="P43" t="n">
-        <v>17900</v>
+        <v>5500</v>
       </c>
       <c r="Q43" t="n">
-        <v>214800</v>
+        <v>319000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>91040</v>
+        <v>91098</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>FLOTADOR MINNIE 56CM 24 PCS</t>
+          <t>BALON INFLABLE MICKEY 51CM</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2242,7 +2223,7 @@
         </is>
       </c>
       <c r="J44" t="n">
-        <v>402</v>
+        <v>183</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -2251,28 +2232,28 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>402</v>
+        <v>183</v>
       </c>
       <c r="N44" t="n">
-        <v>3114.49</v>
+        <v>4378</v>
       </c>
       <c r="O44" t="n">
-        <v>1252024.98</v>
+        <v>801174</v>
       </c>
       <c r="P44" t="n">
-        <v>5500</v>
+        <v>3900</v>
       </c>
       <c r="Q44" t="n">
-        <v>2211000</v>
+        <v>713700</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>91042</v>
+        <v>98002</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>PELOTA PISCINA PRINCESAS 24 PCS</t>
+          <t>PELOTA PISCINA SIPDERMAN  51CM</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2281,7 +2262,7 @@
         </is>
       </c>
       <c r="J45" t="n">
-        <v>120</v>
+        <v>264</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -2290,28 +2271,28 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>120</v>
+        <v>264</v>
       </c>
       <c r="N45" t="n">
-        <v>2791.02</v>
+        <v>3340.6800835073</v>
       </c>
       <c r="O45" t="n">
-        <v>334922.4</v>
+        <v>881939.5420459271</v>
       </c>
       <c r="P45" t="n">
-        <v>3900</v>
+        <v>7100</v>
       </c>
       <c r="Q45" t="n">
-        <v>468000</v>
+        <v>1874400</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>91043</v>
+        <v>98003</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>FLOTADOR PRINCESAS 56CM 24PCS</t>
+          <t>FLOTADOR SPIDER MAN 56CM 24 PCS</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2320,7 +2301,7 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -2329,28 +2310,35 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="N46" t="n">
-        <v>3564.14</v>
+        <v>2903.52</v>
       </c>
       <c r="O46" t="n">
-        <v>206720.12</v>
+        <v>194535.84</v>
       </c>
       <c r="P46" t="n">
-        <v>5500</v>
+        <v>7100</v>
       </c>
       <c r="Q46" t="n">
-        <v>319000</v>
+        <v>475700</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="n">
-        <v>91098</v>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>C105</t>
+        </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>BALON INFLABLE MICKEY 51CM</t>
+          <t>SCOOTER COLORES</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2359,7 +2347,7 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>183</v>
+        <v>18</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -2368,37 +2356,44 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>183</v>
+        <v>18</v>
       </c>
       <c r="N47" t="n">
-        <v>4378</v>
+        <v>39171.85</v>
       </c>
       <c r="O47" t="n">
-        <v>801174</v>
+        <v>705093.2999999999</v>
       </c>
       <c r="P47" t="n">
-        <v>3900</v>
+        <v>68900</v>
       </c>
       <c r="Q47" t="n">
-        <v>713700</v>
+        <v>1240200</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="n">
-        <v>98002</v>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>C1370</t>
+        </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>PELOTA PISCINA SIPDERMAN  51CM</t>
+          <t>LLAVERO PELUCHES STD C1370</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
@@ -2407,28 +2402,30 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c r="N48" t="n">
-        <v>3340.6800833333</v>
+        <v>3472</v>
       </c>
       <c r="O48" t="n">
-        <v>881939.5419999912</v>
+        <v>868000</v>
       </c>
       <c r="P48" t="n">
-        <v>7100</v>
+        <v>4800</v>
       </c>
       <c r="Q48" t="n">
-        <v>1874400</v>
+        <v>1200000</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="n">
-        <v>98003</v>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>C1717</t>
+        </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>FLOTADOR SPIDER MAN 56CM 24 PCS</t>
+          <t>ESPADA CON LUZ Y SONIDO</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2437,7 +2434,7 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>67</v>
+        <v>432</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -2446,30 +2443,33 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>67</v>
+        <v>432</v>
       </c>
       <c r="N49" t="n">
-        <v>2903.52</v>
+        <v>4443</v>
       </c>
       <c r="O49" t="n">
-        <v>194535.84</v>
+        <v>1919376</v>
       </c>
       <c r="P49" t="n">
-        <v>7100</v>
+        <v>6300</v>
       </c>
       <c r="Q49" t="n">
-        <v>475700</v>
+        <v>2721600</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>C105</t>
-        </is>
+          <t>C1758</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>6914919067549</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SCOOTER COLORES</t>
+          <t>MULA BLISTER SURTIDA</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>18</v>
+        <v>180</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -2492,30 +2492,33 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>18</v>
+        <v>180</v>
       </c>
       <c r="N50" t="n">
-        <v>39171.85</v>
+        <v>4648.6</v>
       </c>
       <c r="O50" t="n">
-        <v>705093.2999999999</v>
+        <v>836748.0000000001</v>
       </c>
       <c r="P50" t="n">
-        <v>68900</v>
+        <v>8900</v>
       </c>
       <c r="Q50" t="n">
-        <v>1240200</v>
+        <v>1602000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>C1370</t>
-        </is>
+          <t>C1897</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>6914919086373</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>LLAVERO PELUCHES STD C1370</t>
+          <t>MULA DIDACTICA</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2525,11 +2528,11 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>250</v>
+        <v>144</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
@@ -2538,30 +2541,30 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>250</v>
+        <v>144</v>
       </c>
       <c r="N51" t="n">
-        <v>3472</v>
+        <v>16897</v>
       </c>
       <c r="O51" t="n">
-        <v>868000</v>
+        <v>2433168</v>
       </c>
       <c r="P51" t="n">
-        <v>4800</v>
+        <v>27900</v>
       </c>
       <c r="Q51" t="n">
-        <v>1200000</v>
+        <v>4017600</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>C1717</t>
+          <t>C2117</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ESPADA CON LUZ Y SONIDO</t>
+          <t>DISPLAY CARTÓN PEGAJOSOS X 20</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2570,7 +2573,7 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>432</v>
+        <v>1400</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
@@ -2579,33 +2582,33 @@
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>432</v>
+        <v>1400</v>
       </c>
       <c r="N52" t="n">
-        <v>4443</v>
+        <v>3751</v>
       </c>
       <c r="O52" t="n">
-        <v>1919376</v>
+        <v>5251400</v>
       </c>
       <c r="P52" t="n">
-        <v>6300</v>
+        <v>6400</v>
       </c>
       <c r="Q52" t="n">
-        <v>2721600</v>
+        <v>8960000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>C1758</t>
+          <t>C342</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>6914919067549</v>
+        <v>6914919018374</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>MULA BLISTER SURTIDA</t>
+          <t>COCINA CON VAPOR DE AGUA</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2619,7 +2622,7 @@
         </is>
       </c>
       <c r="J53" t="n">
-        <v>180</v>
+        <v>24</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
@@ -2628,38 +2631,30 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>180</v>
+        <v>24</v>
       </c>
       <c r="N53" t="n">
-        <v>4648.6</v>
+        <v>24538.02</v>
       </c>
       <c r="O53" t="n">
-        <v>836748.0000000001</v>
+        <v>588912.48</v>
       </c>
       <c r="P53" t="n">
-        <v>8900</v>
+        <v>52900</v>
       </c>
       <c r="Q53" t="n">
-        <v>1602000</v>
+        <v>1269600</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>C1897</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>6914919086373</v>
+          <t>C3455</t>
+        </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>MULA DIDACTICA</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>DINOSAURIO BOLSA</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2668,7 +2663,7 @@
         </is>
       </c>
       <c r="J54" t="n">
-        <v>144</v>
+        <v>288</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
@@ -2677,30 +2672,35 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>144</v>
+        <v>288</v>
       </c>
       <c r="N54" t="n">
-        <v>16897</v>
+        <v>5894.64</v>
       </c>
       <c r="O54" t="n">
-        <v>2433168</v>
+        <v>1697656.32</v>
       </c>
       <c r="P54" t="n">
-        <v>27900</v>
+        <v>11000</v>
       </c>
       <c r="Q54" t="n">
-        <v>4017600</v>
+        <v>3168000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>C2117</t>
+          <t>C3638</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>DISPLAY CARTÓN PEGAJOSOS X 20</t>
+          <t>INFLABLE DONA</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2709,7 +2709,7 @@
         </is>
       </c>
       <c r="J55" t="n">
-        <v>1400</v>
+        <v>443</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
@@ -2718,33 +2718,30 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>1400</v>
+        <v>443</v>
       </c>
       <c r="N55" t="n">
-        <v>3751</v>
+        <v>3877.89</v>
       </c>
       <c r="O55" t="n">
-        <v>5251400</v>
+        <v>1717905.27</v>
       </c>
       <c r="P55" t="n">
-        <v>6400</v>
+        <v>6500</v>
       </c>
       <c r="Q55" t="n">
-        <v>8960000</v>
+        <v>2879500</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>C342</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>6914919018374</v>
+          <t>C3700</t>
+        </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>COCINA CON VAPOR DE AGUA</t>
+          <t>MUNECA CON CARRO RECARGABLE DE CONTROL REMOTO</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2758,7 +2755,7 @@
         </is>
       </c>
       <c r="J56" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -2767,39 +2764,44 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="N56" t="n">
-        <v>24538.02</v>
+        <v>60174</v>
       </c>
       <c r="O56" t="n">
-        <v>588912.48</v>
+        <v>361044</v>
       </c>
       <c r="P56" t="n">
-        <v>52900</v>
+        <v>96900</v>
       </c>
       <c r="Q56" t="n">
-        <v>1269600</v>
+        <v>581400</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>C3455</t>
+          <t>C3970</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>DINOSAURIO BOLSA</t>
+          <t>GUITARRAS C3970</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>288</v>
+        <v>48</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
@@ -2808,35 +2810,30 @@
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>288</v>
+        <v>48</v>
       </c>
       <c r="N57" t="n">
-        <v>5894.64</v>
+        <v>26854</v>
       </c>
       <c r="O57" t="n">
-        <v>1697656.32</v>
+        <v>1288992</v>
       </c>
       <c r="P57" t="n">
-        <v>11000</v>
+        <v>43900</v>
       </c>
       <c r="Q57" t="n">
-        <v>3168000</v>
+        <v>2107200</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>C3638</t>
+          <t>C3988</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>INFLABLE DONA</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>DRAGÓN CAMINA CON LUZ Y SONIDO</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -2845,7 +2842,7 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>443</v>
+        <v>12</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
@@ -2854,30 +2851,30 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>443</v>
+        <v>12</v>
       </c>
       <c r="N58" t="n">
-        <v>3877.89</v>
+        <v>29700</v>
       </c>
       <c r="O58" t="n">
-        <v>1717905.27</v>
+        <v>356400</v>
       </c>
       <c r="P58" t="n">
-        <v>6500</v>
+        <v>50500</v>
       </c>
       <c r="Q58" t="n">
-        <v>2879500</v>
+        <v>606000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>C3700</t>
+          <t>C4303</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MUNECA CON CARRO RECARGABLE DE CONTROL REMOTO</t>
+          <t>BEBE CON PIJAMA MED BOLSA PVC C4303</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2887,11 +2884,11 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J59" t="n">
-        <v>6</v>
+        <v>300</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
@@ -2900,30 +2897,30 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>6</v>
+        <v>300</v>
       </c>
       <c r="N59" t="n">
-        <v>60174</v>
+        <v>18016</v>
       </c>
       <c r="O59" t="n">
-        <v>361044</v>
+        <v>5404800</v>
       </c>
       <c r="P59" t="n">
-        <v>96900</v>
+        <v>29900</v>
       </c>
       <c r="Q59" t="n">
-        <v>581400</v>
+        <v>8970000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>C3970</t>
+          <t>C4305</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>GUITARRAS C3970</t>
+          <t>MUÑECA BEBE GRANDE CON PIJAMA EN BOLSA C4305</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2937,7 +2934,7 @@
         </is>
       </c>
       <c r="J60" t="n">
-        <v>48</v>
+        <v>144</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
@@ -2946,39 +2943,44 @@
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>48</v>
+        <v>144</v>
       </c>
       <c r="N60" t="n">
-        <v>26854</v>
+        <v>25534</v>
       </c>
       <c r="O60" t="n">
-        <v>1288992</v>
+        <v>3676896</v>
       </c>
       <c r="P60" t="n">
-        <v>43900</v>
+        <v>40900</v>
       </c>
       <c r="Q60" t="n">
-        <v>2107200</v>
+        <v>5889600</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>C3988</t>
+          <t>C4310</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>DRAGÓN CAMINA CON LUZ Y SONIDO</t>
+          <t>MUÑECA CON CARRO HUMO RECARGABLE C4310</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
@@ -2987,30 +2989,30 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="N61" t="n">
-        <v>29700</v>
+        <v>72889</v>
       </c>
       <c r="O61" t="n">
-        <v>356400</v>
+        <v>2332448</v>
       </c>
       <c r="P61" t="n">
-        <v>50500</v>
+        <v>117500</v>
       </c>
       <c r="Q61" t="n">
-        <v>606000</v>
+        <v>3760000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>C4303</t>
+          <t>C4545</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>BEBE CON PIJAMA MED BOLSA PVC C4303</t>
+          <t>TAPETE PIANO PARA BEBE C4545</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3024,7 +3026,7 @@
         </is>
       </c>
       <c r="J62" t="n">
-        <v>300</v>
+        <v>20</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
@@ -3033,30 +3035,30 @@
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>300</v>
+        <v>20</v>
       </c>
       <c r="N62" t="n">
-        <v>18016</v>
+        <v>27186</v>
       </c>
       <c r="O62" t="n">
-        <v>5404800</v>
+        <v>543720</v>
       </c>
       <c r="P62" t="n">
-        <v>29900</v>
+        <v>43900</v>
       </c>
       <c r="Q62" t="n">
-        <v>8970000</v>
+        <v>878000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>C4305</t>
+          <t>C4728</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>MUÑECA BEBE GRANDE CON PIJAMA EN BOLSA C4305</t>
+          <t>FLIOTADOR DONA DINOSAURIO #60 C4728</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3070,7 +3072,7 @@
         </is>
       </c>
       <c r="J63" t="n">
-        <v>144</v>
+        <v>1800</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
@@ -3079,44 +3081,47 @@
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>144</v>
+        <v>1800</v>
       </c>
       <c r="N63" t="n">
-        <v>25534</v>
+        <v>2454</v>
       </c>
       <c r="O63" t="n">
-        <v>3676896</v>
+        <v>4417200</v>
       </c>
       <c r="P63" t="n">
-        <v>40900</v>
+        <v>4200</v>
       </c>
       <c r="Q63" t="n">
-        <v>5889600</v>
+        <v>7560000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>C4310</t>
-        </is>
+          <t>C488</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>6554632300006</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MUÑECA CON CARRO HUMO RECARGABLE C4310</t>
+          <t>MALETA JUGUETES</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -3125,35 +3130,38 @@
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="N64" t="n">
-        <v>72889</v>
+        <v>18491</v>
       </c>
       <c r="O64" t="n">
-        <v>2332448</v>
+        <v>221892</v>
       </c>
       <c r="P64" t="n">
-        <v>117500</v>
+        <v>13500</v>
       </c>
       <c r="Q64" t="n">
-        <v>3760000</v>
+        <v>162000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>C4545</t>
-        </is>
+          <t>C5032</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>6999899236154</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>TAPETE PIANO PARA BEBE C4545</t>
+          <t>INFLABLE TECHITO PIECITOS  FIGURAS STD C5032</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>INFLABLES</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3162,7 +3170,7 @@
         </is>
       </c>
       <c r="J65" t="n">
-        <v>20</v>
+        <v>937</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
@@ -3171,30 +3179,30 @@
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>20</v>
+        <v>937</v>
       </c>
       <c r="N65" t="n">
-        <v>27186</v>
+        <v>8945.379999999999</v>
       </c>
       <c r="O65" t="n">
-        <v>543720</v>
+        <v>8381821.06</v>
       </c>
       <c r="P65" t="n">
-        <v>43900</v>
+        <v>14900</v>
       </c>
       <c r="Q65" t="n">
-        <v>878000</v>
+        <v>13961300</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>C4728</t>
+          <t>C698</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>FLIOTADOR DONA DINOSAURIO #60 C4728</t>
+          <t>HELICE 9 LUCES</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3204,11 +3212,11 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J66" t="n">
-        <v>1800</v>
+        <v>240</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>
@@ -3217,33 +3225,30 @@
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>1800</v>
+        <v>240</v>
       </c>
       <c r="N66" t="n">
-        <v>2454</v>
+        <v>1567.02</v>
       </c>
       <c r="O66" t="n">
-        <v>4417200</v>
+        <v>376084.8</v>
       </c>
       <c r="P66" t="n">
-        <v>4200</v>
+        <v>2900</v>
       </c>
       <c r="Q66" t="n">
-        <v>7560000</v>
+        <v>696000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>C488</t>
-        </is>
-      </c>
-      <c r="B67" t="n">
-        <v>6554632300006</v>
+          <t>C7560</t>
+        </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>MALETA JUGUETES</t>
+          <t>BARRA LUMINOSA 48CM C7560/211</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3253,11 +3258,11 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J67" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
@@ -3266,33 +3271,33 @@
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N67" t="n">
-        <v>18491</v>
+        <v>796.3099999999999</v>
       </c>
       <c r="O67" t="n">
-        <v>221892</v>
+        <v>7963.099999999999</v>
       </c>
       <c r="P67" t="n">
-        <v>13500</v>
+        <v>2500</v>
       </c>
       <c r="Q67" t="n">
-        <v>162000</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>C5032</t>
+          <t>C7610</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>6999899236154</v>
+        <v>6999899236093</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>INFLABLE TECHITO PIECITOS  FIGURAS STD C5032</t>
+          <t>BOTE TIMON PISCINA 80X60 C7610</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3306,7 +3311,7 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>937</v>
+        <v>360</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
@@ -3315,159 +3320,18 @@
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>937</v>
+        <v>360</v>
       </c>
       <c r="N68" t="n">
-        <v>8945.379999999999</v>
+        <v>7811.9</v>
       </c>
       <c r="O68" t="n">
-        <v>8381821.06</v>
+        <v>2812284</v>
       </c>
       <c r="P68" t="n">
-        <v>14900</v>
+        <v>13900</v>
       </c>
       <c r="Q68" t="n">
-        <v>13961300</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>C698</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>HELICE 9 LUCES</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>und</t>
-        </is>
-      </c>
-      <c r="J69" t="n">
-        <v>240</v>
-      </c>
-      <c r="K69" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" t="n">
-        <v>0</v>
-      </c>
-      <c r="M69" t="n">
-        <v>240</v>
-      </c>
-      <c r="N69" t="n">
-        <v>1567.02</v>
-      </c>
-      <c r="O69" t="n">
-        <v>376084.8</v>
-      </c>
-      <c r="P69" t="n">
-        <v>2900</v>
-      </c>
-      <c r="Q69" t="n">
-        <v>696000</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>C7560</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>BARRA LUMINOSA 48CM C7560/211</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>PIÑATERIA</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J70" t="n">
-        <v>10</v>
-      </c>
-      <c r="K70" t="n">
-        <v>0</v>
-      </c>
-      <c r="L70" t="n">
-        <v>0</v>
-      </c>
-      <c r="M70" t="n">
-        <v>10</v>
-      </c>
-      <c r="N70" t="n">
-        <v>796.3099999999999</v>
-      </c>
-      <c r="O70" t="n">
-        <v>7963.099999999999</v>
-      </c>
-      <c r="P70" t="n">
-        <v>2500</v>
-      </c>
-      <c r="Q70" t="n">
-        <v>25000</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>C7610</t>
-        </is>
-      </c>
-      <c r="B71" t="n">
-        <v>6999899236093</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>BOTE TIMON PISCINA 80X60 C7610</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>INFLABLES</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J71" t="n">
-        <v>360</v>
-      </c>
-      <c r="K71" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" t="n">
-        <v>0</v>
-      </c>
-      <c r="M71" t="n">
-        <v>360</v>
-      </c>
-      <c r="N71" t="n">
-        <v>7811.9</v>
-      </c>
-      <c r="O71" t="n">
-        <v>2812284</v>
-      </c>
-      <c r="P71" t="n">
-        <v>13900</v>
-      </c>
-      <c r="Q71" t="n">
         <v>5004000</v>
       </c>
     </row>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q68"/>
+  <dimension ref="A1:Q67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-03</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-04</t>
         </is>
       </c>
     </row>
@@ -1108,10 +1108,10 @@
         <v>324</v>
       </c>
       <c r="N17" t="n">
-        <v>3926.8370954357</v>
+        <v>3926.8370909091</v>
       </c>
       <c r="O17" t="n">
-        <v>1272295.218921167</v>
+        <v>1272295.217454548</v>
       </c>
       <c r="P17" t="n">
         <v>4800</v>
@@ -1272,10 +1272,10 @@
         <v>13</v>
       </c>
       <c r="N21" t="n">
-        <v>15403.520977011</v>
+        <v>15403.521040462</v>
       </c>
       <c r="O21" t="n">
-        <v>200245.772701143</v>
+        <v>200245.773526006</v>
       </c>
       <c r="P21" t="n">
         <v>33500</v>
@@ -1286,11 +1286,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>44007</v>
+        <v>51124</v>
+      </c>
+      <c r="B22" t="n">
+        <v>6941607325032</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>COLCHONETA INFLABLE 69CM BESTWAY</t>
+          <t>51124 COMBO DE PISCINA Y BALON</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1299,7 +1302,7 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1308,31 +1311,28 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="N22" t="n">
-        <v>3910.6280519481</v>
+        <v>15711.96573991</v>
       </c>
       <c r="O22" t="n">
-        <v>82123.18909091011</v>
+        <v>565630.76663676</v>
       </c>
       <c r="P22" t="n">
-        <v>9100</v>
+        <v>28500</v>
       </c>
       <c r="Q22" t="n">
-        <v>191100</v>
+        <v>1026000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>51124</v>
-      </c>
-      <c r="B23" t="n">
-        <v>6941607325032</v>
+        <v>52331</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>51124 COMBO DE PISCINA Y BALON</t>
+          <t>PISCINA CANOPY FRUTICAS 8 PCS</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1341,7 +1341,7 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -1350,28 +1350,36 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="N23" t="n">
-        <v>15711.965777778</v>
+        <v>20195.32</v>
       </c>
       <c r="O23" t="n">
-        <v>565630.768000008</v>
+        <v>1514649</v>
       </c>
       <c r="P23" t="n">
-        <v>28500</v>
+        <v>45900</v>
       </c>
       <c r="Q23" t="n">
-        <v>1026000</v>
+        <v>3442500</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>52331</v>
+        <v>52637</v>
+      </c>
+      <c r="B24" t="n">
+        <v>6941607352212</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>PISCINA CANOPY FRUTICAS 8 PCS</t>
+          <t>52637 PISCINA TECHADA SUNNY BESTWAY</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1380,7 +1388,7 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>75</v>
+        <v>4</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -1389,31 +1397,31 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>75</v>
+        <v>4</v>
       </c>
       <c r="N24" t="n">
-        <v>20195.32</v>
+        <v>22267.5525</v>
       </c>
       <c r="O24" t="n">
-        <v>1514649</v>
+        <v>89070.21000000001</v>
       </c>
       <c r="P24" t="n">
-        <v>45900</v>
+        <v>46300</v>
       </c>
       <c r="Q24" t="n">
-        <v>3442500</v>
+        <v>185200</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>52637</v>
+        <v>53157</v>
       </c>
       <c r="B25" t="n">
-        <v>6941607352212</v>
+        <v>6941607352137</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>52637 PISCINA TECHADA SUNNY BESTWAY</t>
+          <t>53157 PISCINA FUENTE SHARK BESTWAY</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1439,28 +1447,28 @@
         <v>4</v>
       </c>
       <c r="N25" t="n">
-        <v>22267.5525</v>
+        <v>36574.852307692</v>
       </c>
       <c r="O25" t="n">
-        <v>89070.21000000001</v>
+        <v>146299.409230768</v>
       </c>
       <c r="P25" t="n">
-        <v>46300</v>
+        <v>65900</v>
       </c>
       <c r="Q25" t="n">
-        <v>185200</v>
+        <v>263600</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>53157</v>
+        <v>54370</v>
       </c>
       <c r="B26" t="n">
-        <v>6941607352137</v>
+        <v>6941607312643</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>53157 PISCINA FUENTE SHARK BESTWAY</t>
+          <t>PISCINA CAPITAN 213 X155 X 132CM</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1486,28 +1494,28 @@
         <v>4</v>
       </c>
       <c r="N26" t="n">
-        <v>36574.852307692</v>
+        <v>103298.75</v>
       </c>
       <c r="O26" t="n">
-        <v>146299.409230768</v>
+        <v>413195</v>
       </c>
       <c r="P26" t="n">
-        <v>65900</v>
+        <v>178900</v>
       </c>
       <c r="Q26" t="n">
-        <v>263600</v>
+        <v>715600</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>54370</v>
+        <v>56401</v>
       </c>
       <c r="B27" t="n">
-        <v>6941607312643</v>
+        <v>6941607327951</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>PISCINA CAPITAN 213 X155 X 132CM</t>
+          <t>56401 PISCINA ESTRUCTURAL RECTANGULAR BESTWAY</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1521,7 +1529,7 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -1530,45 +1538,40 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="N27" t="n">
-        <v>103298.75</v>
+        <v>141416.88457516</v>
       </c>
       <c r="O27" t="n">
-        <v>413195</v>
+        <v>7919345.536208959</v>
       </c>
       <c r="P27" t="n">
-        <v>178900</v>
+        <v>251900</v>
       </c>
       <c r="Q27" t="n">
-        <v>715600</v>
+        <v>14106400</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>56401</v>
+        <v>56403</v>
       </c>
       <c r="B28" t="n">
-        <v>6941607327951</v>
+        <v>6941607327982</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>56401 PISCINA ESTRUCTURAL RECTANGULAR BESTWAY</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>PISCINA ESTRUCTURAL 2.59m x 1.70m x 61cm BESTWAY</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -1577,40 +1580,40 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="N28" t="n">
-        <v>141416.88457516</v>
+        <v>200072.20121739</v>
       </c>
       <c r="O28" t="n">
-        <v>7919345.536208959</v>
+        <v>4601660.62799997</v>
       </c>
       <c r="P28" t="n">
-        <v>251900</v>
+        <v>312000</v>
       </c>
       <c r="Q28" t="n">
-        <v>14106400</v>
+        <v>7176000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>56403</v>
+        <v>56404</v>
       </c>
       <c r="B29" t="n">
-        <v>6941607327982</v>
+        <v>6941607327999</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>PISCINA ESTRUCTURAL 2.59m x 1.70m x 61cm BESTWAY</t>
+          <t>56404 PISCINA ESTRUCTURAL RECTANGULAR BESTWAY</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -1619,40 +1622,45 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="N29" t="n">
-        <v>200072.20075</v>
+        <v>174389.79826087</v>
       </c>
       <c r="O29" t="n">
-        <v>4601660.61725</v>
+        <v>1743897.9826087</v>
       </c>
       <c r="P29" t="n">
-        <v>312000</v>
+        <v>368200</v>
       </c>
       <c r="Q29" t="n">
-        <v>7176000</v>
+        <v>3682000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>56404</v>
+        <v>56405</v>
       </c>
       <c r="B30" t="n">
-        <v>6941607327999</v>
+        <v>6941607328002</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>56404 PISCINA ESTRUCTURAL RECTANGULAR BESTWAY</t>
+          <t>PISCINA ESTRUCTURAL RECTAGULAR BESTWAY 4.00mX2.11mX81cm</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -1661,31 +1669,31 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="N30" t="n">
-        <v>174389.79826087</v>
+        <v>251809.29375</v>
       </c>
       <c r="O30" t="n">
-        <v>1743897.9826087</v>
+        <v>1510855.7625</v>
       </c>
       <c r="P30" t="n">
-        <v>368200</v>
+        <v>584000</v>
       </c>
       <c r="Q30" t="n">
-        <v>3682000</v>
+        <v>3504000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>56405</v>
+        <v>56417</v>
       </c>
       <c r="B31" t="n">
-        <v>6941607328002</v>
+        <v>6942138981902</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>PISCINA ESTRUCTURAL RECTAGULAR BESTWAY 4.00mX2.11mX81cm</t>
+          <t>Piscina Estructural Redonda 366 x 76 cm Bomba/Filtro 56417</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1711,38 +1719,30 @@
         <v>6</v>
       </c>
       <c r="N31" t="n">
-        <v>251809.29375</v>
+        <v>344599.1786</v>
       </c>
       <c r="O31" t="n">
-        <v>1510855.7625</v>
+        <v>2067595.0716</v>
       </c>
       <c r="P31" t="n">
-        <v>584000</v>
+        <v>532900</v>
       </c>
       <c r="Q31" t="n">
-        <v>3504000</v>
+        <v>3197400</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>56417</v>
-      </c>
-      <c r="B32" t="n">
-        <v>6942138981902</v>
+        <v>62068</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Piscina Estructural Redonda 366 x 76 cm Bomba/Filtro 56417</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>PARCHE PISCINA EXTERIOR BESTWAY</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J32" t="n">
@@ -1758,25 +1758,25 @@
         <v>6</v>
       </c>
       <c r="N32" t="n">
-        <v>344599.1786</v>
+        <v>1977.88</v>
       </c>
       <c r="O32" t="n">
-        <v>2067595.0716</v>
+        <v>11867.28</v>
       </c>
       <c r="P32" t="n">
-        <v>532900</v>
+        <v>2900</v>
       </c>
       <c r="Q32" t="n">
-        <v>3197400</v>
+        <v>17400</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>62068</v>
+        <v>62091</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>PARCHE PISCINA EXTERIOR BESTWAY</t>
+          <t>PARCHE PISCINA A PRUEBA DE AGUA BESTWAY</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>6</v>
+        <v>217</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -1794,28 +1794,28 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>6</v>
+        <v>217</v>
       </c>
       <c r="N33" t="n">
-        <v>1977.88</v>
+        <v>1141.57</v>
       </c>
       <c r="O33" t="n">
-        <v>11867.28</v>
+        <v>247720.69</v>
       </c>
       <c r="P33" t="n">
-        <v>2900</v>
+        <v>3900</v>
       </c>
       <c r="Q33" t="n">
-        <v>17400</v>
+        <v>846300</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>62091</v>
+        <v>67001</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>PARCHE PISCINA A PRUEBA DE AGUA BESTWAY</t>
+          <t>COLCHON INFLABLE SENCILLO BESTWAY 1.88 X 99 CM</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>217</v>
+        <v>3</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -1833,28 +1833,28 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>217</v>
+        <v>3</v>
       </c>
       <c r="N34" t="n">
-        <v>1141.57</v>
+        <v>26280.41</v>
       </c>
       <c r="O34" t="n">
-        <v>247720.69</v>
+        <v>78841.23</v>
       </c>
       <c r="P34" t="n">
-        <v>3900</v>
+        <v>46500</v>
       </c>
       <c r="Q34" t="n">
-        <v>846300</v>
+        <v>139500</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>67001</v>
+        <v>67374</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>COLCHON INFLABLE SENCILLO BESTWAY 1.88 X 99 CM</t>
+          <t>COLCHON INFLABLE DOBLE+ALMOHADAS BESTWAY 2.03mx1.52mx22cm</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>3</v>
+        <v>67</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -1872,28 +1872,28 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3</v>
+        <v>67</v>
       </c>
       <c r="N35" t="n">
-        <v>26280.41</v>
+        <v>61666.874114441</v>
       </c>
       <c r="O35" t="n">
-        <v>78841.23</v>
+        <v>4131680.565667547</v>
       </c>
       <c r="P35" t="n">
-        <v>46500</v>
+        <v>98900</v>
       </c>
       <c r="Q35" t="n">
-        <v>139500</v>
+        <v>6626300</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>67374</v>
+        <v>91004</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>COLCHON INFLABLE DOBLE+ALMOHADAS BESTWAY 2.03mx1.52mx22cm</t>
+          <t>FLOTADOR DISNEY 56CM 24PCS</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -1902,7 +1902,7 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>67</v>
+        <v>340</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -1911,28 +1911,28 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>67</v>
+        <v>340</v>
       </c>
       <c r="N36" t="n">
-        <v>61666.874114441</v>
+        <v>3865.67</v>
       </c>
       <c r="O36" t="n">
-        <v>4131680.565667547</v>
+        <v>1314327.8</v>
       </c>
       <c r="P36" t="n">
-        <v>98900</v>
+        <v>5500</v>
       </c>
       <c r="Q36" t="n">
-        <v>6626300</v>
+        <v>1870000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>91004</v>
+        <v>91007</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>FLOTADOR DISNEY 56CM 24PCS</t>
+          <t>PISCINA DISNEY 122X25CM 12 PCS</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -1941,7 +1941,7 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>340</v>
+        <v>24</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -1950,28 +1950,35 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>340</v>
+        <v>24</v>
       </c>
       <c r="N37" t="n">
-        <v>3865.67</v>
+        <v>16010.3</v>
       </c>
       <c r="O37" t="n">
-        <v>1314327.8</v>
+        <v>384247.2</v>
       </c>
       <c r="P37" t="n">
-        <v>5500</v>
+        <v>30500</v>
       </c>
       <c r="Q37" t="n">
-        <v>1870000</v>
+        <v>732000</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="n">
-        <v>91007</v>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>9103C</t>
+        </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>PISCINA DISNEY 122X25CM 12 PCS</t>
+          <t>9103C GAFA ACUATICA SIRENITA BESTWAY</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -1992,32 +1999,27 @@
         <v>24</v>
       </c>
       <c r="N38" t="n">
-        <v>16010.3</v>
+        <v>4878.2859393939</v>
       </c>
       <c r="O38" t="n">
-        <v>384247.2</v>
+        <v>117078.8625454536</v>
       </c>
       <c r="P38" t="n">
-        <v>30500</v>
+        <v>13500</v>
       </c>
       <c r="Q38" t="n">
-        <v>732000</v>
+        <v>324000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>9103C</t>
+          <t>9103D</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>9103C GAFA ACUATICA SIRENITA BESTWAY</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>9103D CARETA ACUATICA SIRENITA BESTWAY</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2026,7 +2028,7 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -2035,30 +2037,28 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="N39" t="n">
-        <v>4878.2859393939</v>
+        <v>7394.9354444444</v>
       </c>
       <c r="O39" t="n">
-        <v>117078.8625454536</v>
+        <v>88739.2253333328</v>
       </c>
       <c r="P39" t="n">
-        <v>13500</v>
+        <v>17900</v>
       </c>
       <c r="Q39" t="n">
-        <v>324000</v>
+        <v>214800</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>9103D</t>
-        </is>
+      <c r="A40" t="n">
+        <v>91040</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>9103D CARETA ACUATICA SIRENITA BESTWAY</t>
+          <t>FLOTADOR MINNIE 56CM 24 PCS</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>12</v>
+        <v>402</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -2076,28 +2076,28 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>12</v>
+        <v>402</v>
       </c>
       <c r="N40" t="n">
-        <v>7394.9354444444</v>
+        <v>3114.49</v>
       </c>
       <c r="O40" t="n">
-        <v>88739.2253333328</v>
+        <v>1252024.98</v>
       </c>
       <c r="P40" t="n">
-        <v>17900</v>
+        <v>5500</v>
       </c>
       <c r="Q40" t="n">
-        <v>214800</v>
+        <v>2211000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>91040</v>
+        <v>91042</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>FLOTADOR MINNIE 56CM 24 PCS</t>
+          <t>PELOTA PISCINA PRINCESAS 24 PCS</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>402</v>
+        <v>120</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -2115,28 +2115,28 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>402</v>
+        <v>120</v>
       </c>
       <c r="N41" t="n">
-        <v>3114.49</v>
+        <v>2791.02</v>
       </c>
       <c r="O41" t="n">
-        <v>1252024.98</v>
+        <v>334922.4</v>
       </c>
       <c r="P41" t="n">
-        <v>5500</v>
+        <v>3900</v>
       </c>
       <c r="Q41" t="n">
-        <v>2211000</v>
+        <v>468000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>91042</v>
+        <v>91043</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>PELOTA PISCINA PRINCESAS 24 PCS</t>
+          <t>FLOTADOR PRINCESAS 56CM 24PCS</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>120</v>
+        <v>58</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>120</v>
+        <v>58</v>
       </c>
       <c r="N42" t="n">
-        <v>2791.02</v>
+        <v>3564.14</v>
       </c>
       <c r="O42" t="n">
-        <v>334922.4</v>
+        <v>206720.12</v>
       </c>
       <c r="P42" t="n">
-        <v>3900</v>
+        <v>5500</v>
       </c>
       <c r="Q42" t="n">
-        <v>468000</v>
+        <v>319000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>91043</v>
+        <v>91098</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>FLOTADOR PRINCESAS 56CM 24PCS</t>
+          <t>BALON INFLABLE MICKEY 51CM</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2184,7 +2184,7 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>58</v>
+        <v>183</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -2193,28 +2193,28 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>58</v>
+        <v>183</v>
       </c>
       <c r="N43" t="n">
-        <v>3564.14</v>
+        <v>4378</v>
       </c>
       <c r="O43" t="n">
-        <v>206720.12</v>
+        <v>801174</v>
       </c>
       <c r="P43" t="n">
-        <v>5500</v>
+        <v>3900</v>
       </c>
       <c r="Q43" t="n">
-        <v>319000</v>
+        <v>713700</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>91098</v>
+        <v>98002</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>BALON INFLABLE MICKEY 51CM</t>
+          <t>PELOTA PISCINA SIPDERMAN  51CM</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="J44" t="n">
-        <v>183</v>
+        <v>264</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -2232,28 +2232,28 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>183</v>
+        <v>264</v>
       </c>
       <c r="N44" t="n">
-        <v>4378</v>
+        <v>3340.680083682</v>
       </c>
       <c r="O44" t="n">
-        <v>801174</v>
+        <v>881939.542092048</v>
       </c>
       <c r="P44" t="n">
-        <v>3900</v>
+        <v>7100</v>
       </c>
       <c r="Q44" t="n">
-        <v>713700</v>
+        <v>1874400</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>98002</v>
+        <v>98003</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>PELOTA PISCINA SIPDERMAN  51CM</t>
+          <t>FLOTADOR SPIDER MAN 56CM 24 PCS</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2262,7 +2262,7 @@
         </is>
       </c>
       <c r="J45" t="n">
-        <v>264</v>
+        <v>67</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -2271,28 +2271,35 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>264</v>
+        <v>67</v>
       </c>
       <c r="N45" t="n">
-        <v>3340.6800835073</v>
+        <v>2903.52</v>
       </c>
       <c r="O45" t="n">
-        <v>881939.5420459271</v>
+        <v>194535.84</v>
       </c>
       <c r="P45" t="n">
         <v>7100</v>
       </c>
       <c r="Q45" t="n">
-        <v>1874400</v>
+        <v>475700</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="n">
-        <v>98003</v>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>C105</t>
+        </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>FLOTADOR SPIDER MAN 56CM 24 PCS</t>
+          <t>SCOOTER COLORES</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2301,7 +2308,7 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -2310,30 +2317,30 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="N46" t="n">
-        <v>2903.52</v>
+        <v>39171.85</v>
       </c>
       <c r="O46" t="n">
-        <v>194535.84</v>
+        <v>705093.2999999999</v>
       </c>
       <c r="P46" t="n">
-        <v>7100</v>
+        <v>68900</v>
       </c>
       <c r="Q46" t="n">
-        <v>475700</v>
+        <v>1240200</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C1370</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SCOOTER COLORES</t>
+          <t>LLAVERO PELUCHES STD C1370</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2343,11 +2350,11 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -2356,44 +2363,39 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="N47" t="n">
-        <v>39171.85</v>
+        <v>3472</v>
       </c>
       <c r="O47" t="n">
-        <v>705093.2999999999</v>
+        <v>868000</v>
       </c>
       <c r="P47" t="n">
-        <v>68900</v>
+        <v>4800</v>
       </c>
       <c r="Q47" t="n">
-        <v>1240200</v>
+        <v>1200000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>C1370</t>
+          <t>C1717</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>LLAVERO PELUCHES STD C1370</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>ESPADA CON LUZ Y SONIDO</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>250</v>
+        <v>432</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
@@ -2402,30 +2404,38 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>250</v>
+        <v>432</v>
       </c>
       <c r="N48" t="n">
-        <v>3472</v>
+        <v>4443</v>
       </c>
       <c r="O48" t="n">
-        <v>868000</v>
+        <v>1919376</v>
       </c>
       <c r="P48" t="n">
-        <v>4800</v>
+        <v>6300</v>
       </c>
       <c r="Q48" t="n">
-        <v>1200000</v>
+        <v>2721600</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>C1717</t>
-        </is>
+          <t>C1758</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>6914919067549</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ESPADA CON LUZ Y SONIDO</t>
+          <t>MULA BLISTER SURTIDA</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2434,7 +2444,7 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>432</v>
+        <v>180</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -2443,33 +2453,33 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>432</v>
+        <v>180</v>
       </c>
       <c r="N49" t="n">
-        <v>4443</v>
+        <v>4648.6</v>
       </c>
       <c r="O49" t="n">
-        <v>1919376</v>
+        <v>836748.0000000001</v>
       </c>
       <c r="P49" t="n">
-        <v>6300</v>
+        <v>8900</v>
       </c>
       <c r="Q49" t="n">
-        <v>2721600</v>
+        <v>1602000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>C1758</t>
+          <t>C1897</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>6914919067549</v>
+        <v>6914919086373</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MULA BLISTER SURTIDA</t>
+          <t>MULA DIDACTICA</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2483,7 +2493,7 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>180</v>
+        <v>144</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -2492,38 +2502,30 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>180</v>
+        <v>144</v>
       </c>
       <c r="N50" t="n">
-        <v>4648.6</v>
+        <v>16897</v>
       </c>
       <c r="O50" t="n">
-        <v>836748.0000000001</v>
+        <v>2433168</v>
       </c>
       <c r="P50" t="n">
-        <v>8900</v>
+        <v>27900</v>
       </c>
       <c r="Q50" t="n">
-        <v>1602000</v>
+        <v>4017600</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>C1897</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>6914919086373</v>
+          <t>C2117</t>
+        </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MULA DIDACTICA</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>DISPLAY CARTÓN PEGAJOSOS X 20</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2532,7 +2534,7 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>144</v>
+        <v>1400</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
@@ -2541,30 +2543,38 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>144</v>
+        <v>1400</v>
       </c>
       <c r="N51" t="n">
-        <v>16897</v>
+        <v>3751</v>
       </c>
       <c r="O51" t="n">
-        <v>2433168</v>
+        <v>5251400</v>
       </c>
       <c r="P51" t="n">
-        <v>27900</v>
+        <v>6400</v>
       </c>
       <c r="Q51" t="n">
-        <v>4017600</v>
+        <v>8960000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>C2117</t>
-        </is>
+          <t>C342</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>6914919018374</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>DISPLAY CARTÓN PEGAJOSOS X 20</t>
+          <t>COCINA CON VAPOR DE AGUA</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2573,7 +2583,7 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>1400</v>
+        <v>24</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
@@ -2582,38 +2592,30 @@
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>1400</v>
+        <v>24</v>
       </c>
       <c r="N52" t="n">
-        <v>3751</v>
+        <v>24538.02</v>
       </c>
       <c r="O52" t="n">
-        <v>5251400</v>
+        <v>588912.48</v>
       </c>
       <c r="P52" t="n">
-        <v>6400</v>
+        <v>52900</v>
       </c>
       <c r="Q52" t="n">
-        <v>8960000</v>
+        <v>1269600</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>C342</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>6914919018374</v>
+          <t>C3455</t>
+        </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>COCINA CON VAPOR DE AGUA</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>DINOSAURIO BOLSA</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2622,7 +2624,7 @@
         </is>
       </c>
       <c r="J53" t="n">
-        <v>24</v>
+        <v>288</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
@@ -2631,30 +2633,35 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>24</v>
+        <v>288</v>
       </c>
       <c r="N53" t="n">
-        <v>24538.02</v>
+        <v>5894.64</v>
       </c>
       <c r="O53" t="n">
-        <v>588912.48</v>
+        <v>1697656.32</v>
       </c>
       <c r="P53" t="n">
-        <v>52900</v>
+        <v>11000</v>
       </c>
       <c r="Q53" t="n">
-        <v>1269600</v>
+        <v>3168000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>C3455</t>
+          <t>C3638</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>DINOSAURIO BOLSA</t>
+          <t>INFLABLE DONA</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2663,7 +2670,7 @@
         </is>
       </c>
       <c r="J54" t="n">
-        <v>288</v>
+        <v>443</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
@@ -2672,30 +2679,30 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>288</v>
+        <v>443</v>
       </c>
       <c r="N54" t="n">
-        <v>5894.64</v>
+        <v>3877.89</v>
       </c>
       <c r="O54" t="n">
-        <v>1697656.32</v>
+        <v>1717905.27</v>
       </c>
       <c r="P54" t="n">
-        <v>11000</v>
+        <v>6500</v>
       </c>
       <c r="Q54" t="n">
-        <v>3168000</v>
+        <v>2879500</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>C3638</t>
+          <t>C3700</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>INFLABLE DONA</t>
+          <t>MUNECA CON CARRO RECARGABLE DE CONTROL REMOTO</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2709,7 +2716,7 @@
         </is>
       </c>
       <c r="J55" t="n">
-        <v>443</v>
+        <v>6</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
@@ -2718,30 +2725,30 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>443</v>
+        <v>6</v>
       </c>
       <c r="N55" t="n">
-        <v>3877.89</v>
+        <v>60174</v>
       </c>
       <c r="O55" t="n">
-        <v>1717905.27</v>
+        <v>361044</v>
       </c>
       <c r="P55" t="n">
-        <v>6500</v>
+        <v>96900</v>
       </c>
       <c r="Q55" t="n">
-        <v>2879500</v>
+        <v>581400</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>C3700</t>
+          <t>C3970</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>MUNECA CON CARRO RECARGABLE DE CONTROL REMOTO</t>
+          <t>GUITARRAS C3970</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2751,11 +2758,11 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -2764,44 +2771,39 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="N56" t="n">
-        <v>60174</v>
+        <v>26854</v>
       </c>
       <c r="O56" t="n">
-        <v>361044</v>
+        <v>1288992</v>
       </c>
       <c r="P56" t="n">
-        <v>96900</v>
+        <v>43900</v>
       </c>
       <c r="Q56" t="n">
-        <v>581400</v>
+        <v>2107200</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>C3970</t>
+          <t>C3988</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>GUITARRAS C3970</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>DRAGÓN CAMINA CON LUZ Y SONIDO</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
@@ -2810,39 +2812,44 @@
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="N57" t="n">
-        <v>26854</v>
+        <v>29700</v>
       </c>
       <c r="O57" t="n">
-        <v>1288992</v>
+        <v>356400</v>
       </c>
       <c r="P57" t="n">
-        <v>43900</v>
+        <v>50500</v>
       </c>
       <c r="Q57" t="n">
-        <v>2107200</v>
+        <v>606000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>C3988</t>
+          <t>C4303</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>DRAGÓN CAMINA CON LUZ Y SONIDO</t>
+          <t>BEBE CON PIJAMA MED BOLSA PVC C4303</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>12</v>
+        <v>300</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
@@ -2851,30 +2858,30 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>12</v>
+        <v>300</v>
       </c>
       <c r="N58" t="n">
-        <v>29700</v>
+        <v>18016</v>
       </c>
       <c r="O58" t="n">
-        <v>356400</v>
+        <v>5404800</v>
       </c>
       <c r="P58" t="n">
-        <v>50500</v>
+        <v>29900</v>
       </c>
       <c r="Q58" t="n">
-        <v>606000</v>
+        <v>8970000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>C4303</t>
+          <t>C4305</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>BEBE CON PIJAMA MED BOLSA PVC C4303</t>
+          <t>MUÑECA BEBE GRANDE CON PIJAMA EN BOLSA C4305</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2888,7 +2895,7 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>300</v>
+        <v>144</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
@@ -2897,30 +2904,30 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>300</v>
+        <v>144</v>
       </c>
       <c r="N59" t="n">
-        <v>18016</v>
+        <v>25534</v>
       </c>
       <c r="O59" t="n">
-        <v>5404800</v>
+        <v>3676896</v>
       </c>
       <c r="P59" t="n">
-        <v>29900</v>
+        <v>40900</v>
       </c>
       <c r="Q59" t="n">
-        <v>8970000</v>
+        <v>5889600</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>C4305</t>
+          <t>C4310</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MUÑECA BEBE GRANDE CON PIJAMA EN BOLSA C4305</t>
+          <t>MUÑECA CON CARRO HUMO RECARGABLE C4310</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2934,7 +2941,7 @@
         </is>
       </c>
       <c r="J60" t="n">
-        <v>144</v>
+        <v>32</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
@@ -2943,30 +2950,30 @@
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>144</v>
+        <v>32</v>
       </c>
       <c r="N60" t="n">
-        <v>25534</v>
+        <v>72889</v>
       </c>
       <c r="O60" t="n">
-        <v>3676896</v>
+        <v>2332448</v>
       </c>
       <c r="P60" t="n">
-        <v>40900</v>
+        <v>117500</v>
       </c>
       <c r="Q60" t="n">
-        <v>5889600</v>
+        <v>3760000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>C4310</t>
+          <t>C4545</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MUÑECA CON CARRO HUMO RECARGABLE C4310</t>
+          <t>TAPETE PIANO PARA BEBE C4545</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2980,7 +2987,7 @@
         </is>
       </c>
       <c r="J61" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
@@ -2989,30 +2996,30 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="N61" t="n">
-        <v>72889</v>
+        <v>27186</v>
       </c>
       <c r="O61" t="n">
-        <v>2332448</v>
+        <v>543720</v>
       </c>
       <c r="P61" t="n">
-        <v>117500</v>
+        <v>43900</v>
       </c>
       <c r="Q61" t="n">
-        <v>3760000</v>
+        <v>878000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>C4545</t>
+          <t>C4728</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>TAPETE PIANO PARA BEBE C4545</t>
+          <t>FLIOTADOR DONA DINOSAURIO #60 C4728</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3026,7 +3033,7 @@
         </is>
       </c>
       <c r="J62" t="n">
-        <v>20</v>
+        <v>1800</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
@@ -3035,44 +3042,47 @@
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>20</v>
+        <v>1800</v>
       </c>
       <c r="N62" t="n">
-        <v>27186</v>
+        <v>2454</v>
       </c>
       <c r="O62" t="n">
-        <v>543720</v>
+        <v>4417200</v>
       </c>
       <c r="P62" t="n">
-        <v>43900</v>
+        <v>4200</v>
       </c>
       <c r="Q62" t="n">
-        <v>878000</v>
+        <v>7560000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>C4728</t>
-        </is>
+          <t>C488</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>6554632300006</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>FLIOTADOR DONA DINOSAURIO #60 C4728</t>
+          <t>MALETA JUGUETES</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>1800</v>
+        <v>12</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
@@ -3081,47 +3091,47 @@
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>1800</v>
+        <v>12</v>
       </c>
       <c r="N63" t="n">
-        <v>2454</v>
+        <v>18491</v>
       </c>
       <c r="O63" t="n">
-        <v>4417200</v>
+        <v>221892</v>
       </c>
       <c r="P63" t="n">
-        <v>4200</v>
+        <v>13500</v>
       </c>
       <c r="Q63" t="n">
-        <v>7560000</v>
+        <v>162000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>C488</t>
+          <t>C5032</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>6554632300006</v>
+        <v>6999899236154</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MALETA JUGUETES</t>
+          <t>INFLABLE TECHITO PIECITOS  FIGURAS STD C5032</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>INFLABLES</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>12</v>
+        <v>937</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -3130,47 +3140,44 @@
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>12</v>
+        <v>937</v>
       </c>
       <c r="N64" t="n">
-        <v>18491</v>
+        <v>8945.379999999999</v>
       </c>
       <c r="O64" t="n">
-        <v>221892</v>
+        <v>8381821.06</v>
       </c>
       <c r="P64" t="n">
-        <v>13500</v>
+        <v>14900</v>
       </c>
       <c r="Q64" t="n">
-        <v>162000</v>
+        <v>13961300</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>C5032</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>6999899236154</v>
+          <t>C698</t>
+        </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>INFLABLE TECHITO PIECITOS  FIGURAS STD C5032</t>
+          <t>HELICE 9 LUCES</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>INFLABLES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J65" t="n">
-        <v>937</v>
+        <v>240</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
@@ -3179,44 +3186,44 @@
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>937</v>
+        <v>240</v>
       </c>
       <c r="N65" t="n">
-        <v>8945.379999999999</v>
+        <v>1567.02</v>
       </c>
       <c r="O65" t="n">
-        <v>8381821.06</v>
+        <v>376084.8</v>
       </c>
       <c r="P65" t="n">
-        <v>14900</v>
+        <v>2900</v>
       </c>
       <c r="Q65" t="n">
-        <v>13961300</v>
+        <v>696000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>C698</t>
+          <t>C7560</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>HELICE 9 LUCES</t>
+          <t>BARRA LUMINOSA 48CM C7560/211</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J66" t="n">
-        <v>240</v>
+        <v>10</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>
@@ -3225,35 +3232,38 @@
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>240</v>
+        <v>10</v>
       </c>
       <c r="N66" t="n">
-        <v>1567.02</v>
+        <v>796.3099999999999</v>
       </c>
       <c r="O66" t="n">
-        <v>376084.8</v>
+        <v>7963.099999999999</v>
       </c>
       <c r="P66" t="n">
-        <v>2900</v>
+        <v>2500</v>
       </c>
       <c r="Q66" t="n">
-        <v>696000</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>C7560</t>
-        </is>
+          <t>C7610</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>6999899236093</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>BARRA LUMINOSA 48CM C7560/211</t>
+          <t>BOTE TIMON PISCINA 80X60 C7610</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>INFLABLES</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3262,7 +3272,7 @@
         </is>
       </c>
       <c r="J67" t="n">
-        <v>10</v>
+        <v>360</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
@@ -3271,67 +3281,18 @@
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>10</v>
+        <v>360</v>
       </c>
       <c r="N67" t="n">
-        <v>796.3099999999999</v>
+        <v>7811.9</v>
       </c>
       <c r="O67" t="n">
-        <v>7963.099999999999</v>
+        <v>2812284</v>
       </c>
       <c r="P67" t="n">
-        <v>2500</v>
+        <v>13900</v>
       </c>
       <c r="Q67" t="n">
-        <v>25000</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>C7610</t>
-        </is>
-      </c>
-      <c r="B68" t="n">
-        <v>6999899236093</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>BOTE TIMON PISCINA 80X60 C7610</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>INFLABLES</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J68" t="n">
-        <v>360</v>
-      </c>
-      <c r="K68" t="n">
-        <v>0</v>
-      </c>
-      <c r="L68" t="n">
-        <v>0</v>
-      </c>
-      <c r="M68" t="n">
-        <v>360</v>
-      </c>
-      <c r="N68" t="n">
-        <v>7811.9</v>
-      </c>
-      <c r="O68" t="n">
-        <v>2812284</v>
-      </c>
-      <c r="P68" t="n">
-        <v>13900</v>
-      </c>
-      <c r="Q68" t="n">
         <v>5004000</v>
       </c>
     </row>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-04</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-05</t>
         </is>
       </c>
     </row>
@@ -1030,10 +1030,10 @@
         <v>29</v>
       </c>
       <c r="N15" t="n">
-        <v>1933.3880645161</v>
+        <v>1933.3881018519</v>
       </c>
       <c r="O15" t="n">
-        <v>56068.2538709669</v>
+        <v>56068.2549537051</v>
       </c>
       <c r="P15" t="n">
         <v>4500</v>
@@ -1314,10 +1314,10 @@
         <v>36</v>
       </c>
       <c r="N22" t="n">
-        <v>15711.96573991</v>
+        <v>15711.96562212</v>
       </c>
       <c r="O22" t="n">
-        <v>565630.76663676</v>
+        <v>565630.76239632</v>
       </c>
       <c r="P22" t="n">
         <v>28500</v>
@@ -1583,10 +1583,10 @@
         <v>23</v>
       </c>
       <c r="N28" t="n">
-        <v>200072.20121739</v>
+        <v>200072.20172727</v>
       </c>
       <c r="O28" t="n">
-        <v>4601660.62799997</v>
+        <v>4601660.63972721</v>
       </c>
       <c r="P28" t="n">
         <v>312000</v>
@@ -1719,10 +1719,10 @@
         <v>6</v>
       </c>
       <c r="N31" t="n">
-        <v>344599.1786</v>
+        <v>344599.17851064</v>
       </c>
       <c r="O31" t="n">
-        <v>2067595.0716</v>
+        <v>2067595.07106384</v>
       </c>
       <c r="P31" t="n">
         <v>532900</v>
@@ -2235,10 +2235,10 @@
         <v>264</v>
       </c>
       <c r="N44" t="n">
-        <v>3340.680083682</v>
+        <v>3340.6800838574</v>
       </c>
       <c r="O44" t="n">
-        <v>881939.542092048</v>
+        <v>881939.5421383536</v>
       </c>
       <c r="P44" t="n">
         <v>7100</v>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-05</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-06</t>
         </is>
       </c>
     </row>
@@ -1030,10 +1030,10 @@
         <v>29</v>
       </c>
       <c r="N15" t="n">
-        <v>1933.3881018519</v>
+        <v>1933.3882159624</v>
       </c>
       <c r="O15" t="n">
-        <v>56068.2549537051</v>
+        <v>56068.2582629096</v>
       </c>
       <c r="P15" t="n">
         <v>4500</v>
@@ -1541,10 +1541,10 @@
         <v>56</v>
       </c>
       <c r="N27" t="n">
-        <v>141416.88457516</v>
+        <v>141416.88459016</v>
       </c>
       <c r="O27" t="n">
-        <v>7919345.536208959</v>
+        <v>7919345.537048961</v>
       </c>
       <c r="P27" t="n">
         <v>251900</v>
@@ -1583,10 +1583,10 @@
         <v>23</v>
       </c>
       <c r="N28" t="n">
-        <v>200072.20172727</v>
+        <v>200072.20183486</v>
       </c>
       <c r="O28" t="n">
-        <v>4601660.63972721</v>
+        <v>4601660.64220178</v>
       </c>
       <c r="P28" t="n">
         <v>312000</v>
@@ -1625,10 +1625,10 @@
         <v>10</v>
       </c>
       <c r="N29" t="n">
-        <v>174389.79826087</v>
+        <v>174389.79954545</v>
       </c>
       <c r="O29" t="n">
-        <v>1743897.9826087</v>
+        <v>1743897.9954545</v>
       </c>
       <c r="P29" t="n">
         <v>368200</v>
@@ -1875,10 +1875,10 @@
         <v>67</v>
       </c>
       <c r="N35" t="n">
-        <v>61666.874114441</v>
+        <v>61666.874148352</v>
       </c>
       <c r="O35" t="n">
-        <v>4131680.565667547</v>
+        <v>4131680.567939584</v>
       </c>
       <c r="P35" t="n">
         <v>98900</v>
@@ -3094,10 +3094,10 @@
         <v>12</v>
       </c>
       <c r="N63" t="n">
-        <v>18491</v>
+        <v>18654.637168142</v>
       </c>
       <c r="O63" t="n">
-        <v>221892</v>
+        <v>223855.646017704</v>
       </c>
       <c r="P63" t="n">
         <v>13500</v>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -3094,10 +3094,10 @@
         <v>12</v>
       </c>
       <c r="N63" t="n">
-        <v>18654.637168142</v>
+        <v>18491</v>
       </c>
       <c r="O63" t="n">
-        <v>223855.646017704</v>
+        <v>221892</v>
       </c>
       <c r="P63" t="n">
         <v>13500</v>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-06</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-07</t>
         </is>
       </c>
     </row>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -1314,10 +1314,10 @@
         <v>36</v>
       </c>
       <c r="N22" t="n">
-        <v>15711.96562212</v>
+        <v>15711.965560748</v>
       </c>
       <c r="O22" t="n">
-        <v>565630.76239632</v>
+        <v>565630.760186928</v>
       </c>
       <c r="P22" t="n">
         <v>28500</v>
@@ -1400,10 +1400,10 @@
         <v>4</v>
       </c>
       <c r="N24" t="n">
-        <v>22267.5525</v>
+        <v>22267.552777778</v>
       </c>
       <c r="O24" t="n">
-        <v>89070.21000000001</v>
+        <v>89070.211111112</v>
       </c>
       <c r="P24" t="n">
         <v>46300</v>
@@ -1541,10 +1541,10 @@
         <v>56</v>
       </c>
       <c r="N27" t="n">
-        <v>141416.88459016</v>
+        <v>141416.88460526</v>
       </c>
       <c r="O27" t="n">
-        <v>7919345.537048961</v>
+        <v>7919345.537894561</v>
       </c>
       <c r="P27" t="n">
         <v>251900</v>
@@ -1583,10 +1583,10 @@
         <v>23</v>
       </c>
       <c r="N28" t="n">
-        <v>200072.20183486</v>
+        <v>200072.20194444</v>
       </c>
       <c r="O28" t="n">
-        <v>4601660.64220178</v>
+        <v>4601660.64472212</v>
       </c>
       <c r="P28" t="n">
         <v>312000</v>
@@ -1625,10 +1625,10 @@
         <v>10</v>
       </c>
       <c r="N29" t="n">
-        <v>174389.79954545</v>
+        <v>174389.80095238</v>
       </c>
       <c r="O29" t="n">
-        <v>1743897.9954545</v>
+        <v>1743898.0095238</v>
       </c>
       <c r="P29" t="n">
         <v>368200</v>
@@ -1719,10 +1719,10 @@
         <v>6</v>
       </c>
       <c r="N31" t="n">
-        <v>344599.17851064</v>
+        <v>344599.17844444</v>
       </c>
       <c r="O31" t="n">
-        <v>2067595.07106384</v>
+        <v>2067595.07066664</v>
       </c>
       <c r="P31" t="n">
         <v>532900</v>
@@ -1875,10 +1875,10 @@
         <v>67</v>
       </c>
       <c r="N35" t="n">
-        <v>61666.874148352</v>
+        <v>61666.87415978</v>
       </c>
       <c r="O35" t="n">
-        <v>4131680.567939584</v>
+        <v>4131680.56870526</v>
       </c>
       <c r="P35" t="n">
         <v>98900</v>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-07</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-08</t>
         </is>
       </c>
     </row>
@@ -2040,10 +2040,10 @@
         <v>12</v>
       </c>
       <c r="N39" t="n">
-        <v>7394.9354444444</v>
+        <v>7394.9355367232</v>
       </c>
       <c r="O39" t="n">
-        <v>88739.2253333328</v>
+        <v>88739.22644067841</v>
       </c>
       <c r="P39" t="n">
         <v>17900</v>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -2999,10 +2999,10 @@
         <v>20</v>
       </c>
       <c r="N61" t="n">
-        <v>27186</v>
+        <v>27309.572727273</v>
       </c>
       <c r="O61" t="n">
-        <v>543720</v>
+        <v>546191.4545454599</v>
       </c>
       <c r="P61" t="n">
         <v>43900</v>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-08</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-09</t>
         </is>
       </c>
     </row>
@@ -557,10 +557,10 @@
         <v>2</v>
       </c>
       <c r="N4" t="n">
-        <v>74676.64464285701</v>
+        <v>74676.643703704</v>
       </c>
       <c r="O4" t="n">
-        <v>149353.289285714</v>
+        <v>149353.287407408</v>
       </c>
       <c r="P4" t="n">
         <v>144900</v>
@@ -1314,10 +1314,10 @@
         <v>36</v>
       </c>
       <c r="N22" t="n">
-        <v>15711.965560748</v>
+        <v>15711.96478022</v>
       </c>
       <c r="O22" t="n">
-        <v>565630.760186928</v>
+        <v>565630.73208792</v>
       </c>
       <c r="P22" t="n">
         <v>28500</v>
@@ -1400,10 +1400,10 @@
         <v>4</v>
       </c>
       <c r="N24" t="n">
-        <v>22267.552777778</v>
+        <v>23504.638888889</v>
       </c>
       <c r="O24" t="n">
-        <v>89070.211111112</v>
+        <v>94018.555555556</v>
       </c>
       <c r="P24" t="n">
         <v>46300</v>
@@ -1583,10 +1583,10 @@
         <v>23</v>
       </c>
       <c r="N28" t="n">
-        <v>200072.20194444</v>
+        <v>200072.20205607</v>
       </c>
       <c r="O28" t="n">
-        <v>4601660.64472212</v>
+        <v>4601660.64728961</v>
       </c>
       <c r="P28" t="n">
         <v>312000</v>
@@ -1719,10 +1719,10 @@
         <v>6</v>
       </c>
       <c r="N31" t="n">
-        <v>344599.17844444</v>
+        <v>344599.17851064</v>
       </c>
       <c r="O31" t="n">
-        <v>2067595.07066664</v>
+        <v>2067595.07106384</v>
       </c>
       <c r="P31" t="n">
         <v>532900</v>
@@ -2040,10 +2040,10 @@
         <v>12</v>
       </c>
       <c r="N39" t="n">
-        <v>7394.9355367232</v>
+        <v>7394.9355681818</v>
       </c>
       <c r="O39" t="n">
-        <v>88739.22644067841</v>
+        <v>88739.2268181816</v>
       </c>
       <c r="P39" t="n">
         <v>17900</v>
@@ -2505,10 +2505,10 @@
         <v>144</v>
       </c>
       <c r="N50" t="n">
-        <v>16897</v>
+        <v>16960.16635514</v>
       </c>
       <c r="O50" t="n">
-        <v>2433168</v>
+        <v>2442263.95514016</v>
       </c>
       <c r="P50" t="n">
         <v>27900</v>
@@ -2999,10 +2999,10 @@
         <v>20</v>
       </c>
       <c r="N61" t="n">
-        <v>27309.572727273</v>
+        <v>27186</v>
       </c>
       <c r="O61" t="n">
-        <v>546191.4545454599</v>
+        <v>543720</v>
       </c>
       <c r="P61" t="n">
         <v>43900</v>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -1400,10 +1400,10 @@
         <v>4</v>
       </c>
       <c r="N24" t="n">
-        <v>23504.638888889</v>
+        <v>22267.552777778</v>
       </c>
       <c r="O24" t="n">
-        <v>94018.555555556</v>
+        <v>89070.211111112</v>
       </c>
       <c r="P24" t="n">
         <v>46300</v>
@@ -2505,10 +2505,10 @@
         <v>144</v>
       </c>
       <c r="N50" t="n">
-        <v>16960.16635514</v>
+        <v>16897</v>
       </c>
       <c r="O50" t="n">
-        <v>2442263.95514016</v>
+        <v>2433168</v>
       </c>
       <c r="P50" t="n">
         <v>27900</v>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-09</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-10</t>
         </is>
       </c>
     </row>
@@ -1314,10 +1314,10 @@
         <v>36</v>
       </c>
       <c r="N22" t="n">
-        <v>15711.96478022</v>
+        <v>15711.964751381</v>
       </c>
       <c r="O22" t="n">
-        <v>565630.73208792</v>
+        <v>565630.731049716</v>
       </c>
       <c r="P22" t="n">
         <v>28500</v>
@@ -1541,10 +1541,10 @@
         <v>56</v>
       </c>
       <c r="N27" t="n">
-        <v>141416.88460526</v>
+        <v>141416.88462046</v>
       </c>
       <c r="O27" t="n">
-        <v>7919345.537894561</v>
+        <v>7919345.538745761</v>
       </c>
       <c r="P27" t="n">
         <v>251900</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -1580,19 +1580,19 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N28" t="n">
-        <v>200072.20205607</v>
+        <v>200072.20216981</v>
       </c>
       <c r="O28" t="n">
-        <v>4601660.64728961</v>
+        <v>4401588.44773582</v>
       </c>
       <c r="P28" t="n">
         <v>312000</v>
       </c>
       <c r="Q28" t="n">
-        <v>7176000</v>
+        <v>6864000</v>
       </c>
     </row>
     <row r="29">
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -1622,19 +1622,19 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N29" t="n">
-        <v>174389.80095238</v>
+        <v>174389.8025</v>
       </c>
       <c r="O29" t="n">
-        <v>1743898.0095238</v>
+        <v>1395118.42</v>
       </c>
       <c r="P29" t="n">
         <v>368200</v>
       </c>
       <c r="Q29" t="n">
-        <v>3682000</v>
+        <v>2945600</v>
       </c>
     </row>
     <row r="30">
@@ -2670,7 +2670,7 @@
         </is>
       </c>
       <c r="J54" t="n">
-        <v>443</v>
+        <v>203</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
@@ -2679,19 +2679,19 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>443</v>
+        <v>203</v>
       </c>
       <c r="N54" t="n">
         <v>3877.89</v>
       </c>
       <c r="O54" t="n">
-        <v>1717905.27</v>
+        <v>787211.6699999999</v>
       </c>
       <c r="P54" t="n">
         <v>6500</v>
       </c>
       <c r="Q54" t="n">
-        <v>2879500</v>
+        <v>1319500</v>
       </c>
     </row>
     <row r="55">

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-10</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-11</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -554,19 +554,19 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N4" t="n">
-        <v>74676.643703704</v>
+        <v>74676.628235294</v>
       </c>
       <c r="O4" t="n">
-        <v>149353.287407408</v>
+        <v>74676.628235294</v>
       </c>
       <c r="P4" t="n">
         <v>144900</v>
       </c>
       <c r="Q4" t="n">
-        <v>289800</v>
+        <v>144900</v>
       </c>
     </row>
     <row r="5">
@@ -635,10 +635,10 @@
         <v>12</v>
       </c>
       <c r="N6" t="n">
-        <v>5758.9597777778</v>
+        <v>5758.9597772829</v>
       </c>
       <c r="O6" t="n">
-        <v>69107.5173333336</v>
+        <v>69107.5173273948</v>
       </c>
       <c r="P6" t="n">
         <v>16900</v>
@@ -1108,10 +1108,10 @@
         <v>324</v>
       </c>
       <c r="N17" t="n">
-        <v>3926.8370909091</v>
+        <v>3926.8370787689</v>
       </c>
       <c r="O17" t="n">
-        <v>1272295.217454548</v>
+        <v>1272295.213521124</v>
       </c>
       <c r="P17" t="n">
         <v>4800</v>
@@ -1314,10 +1314,10 @@
         <v>36</v>
       </c>
       <c r="N22" t="n">
-        <v>15711.964751381</v>
+        <v>15711.964662921</v>
       </c>
       <c r="O22" t="n">
-        <v>565630.731049716</v>
+        <v>565630.727865156</v>
       </c>
       <c r="P22" t="n">
         <v>28500</v>
@@ -1625,10 +1625,10 @@
         <v>8</v>
       </c>
       <c r="N29" t="n">
-        <v>174389.8025</v>
+        <v>174389.81333333</v>
       </c>
       <c r="O29" t="n">
-        <v>1395118.42</v>
+        <v>1395118.50666664</v>
       </c>
       <c r="P29" t="n">
         <v>368200</v>
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -1669,19 +1669,19 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N30" t="n">
-        <v>251809.29375</v>
+        <v>251809.29259259</v>
       </c>
       <c r="O30" t="n">
-        <v>1510855.7625</v>
+        <v>1259046.46296295</v>
       </c>
       <c r="P30" t="n">
         <v>584000</v>
       </c>
       <c r="Q30" t="n">
-        <v>3504000</v>
+        <v>2920000</v>
       </c>
     </row>
     <row r="31">
@@ -1875,10 +1875,10 @@
         <v>67</v>
       </c>
       <c r="N35" t="n">
-        <v>61666.87415978</v>
+        <v>61666.874171271</v>
       </c>
       <c r="O35" t="n">
-        <v>4131680.56870526</v>
+        <v>4131680.569475157</v>
       </c>
       <c r="P35" t="n">
         <v>98900</v>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q67"/>
+  <dimension ref="A1:Q66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-11</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-12</t>
         </is>
       </c>
     </row>
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1311,19 +1311,19 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="N22" t="n">
-        <v>15711.964662921</v>
+        <v>15711.964632768</v>
       </c>
       <c r="O22" t="n">
-        <v>565630.727865156</v>
+        <v>392799.1158192</v>
       </c>
       <c r="P22" t="n">
         <v>28500</v>
       </c>
       <c r="Q22" t="n">
-        <v>1026000</v>
+        <v>712500</v>
       </c>
     </row>
     <row r="23">
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -1622,19 +1622,19 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N29" t="n">
         <v>174389.81333333</v>
       </c>
       <c r="O29" t="n">
-        <v>1395118.50666664</v>
+        <v>1220728.69333331</v>
       </c>
       <c r="P29" t="n">
         <v>368200</v>
       </c>
       <c r="Q29" t="n">
-        <v>2945600</v>
+        <v>2577400</v>
       </c>
     </row>
     <row r="30">
@@ -2335,26 +2335,21 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>C1370</t>
+          <t>C1717</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>LLAVERO PELUCHES STD C1370</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>ESPADA CON LUZ Y SONIDO</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>250</v>
+        <v>432</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -2363,30 +2358,38 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>250</v>
+        <v>432</v>
       </c>
       <c r="N47" t="n">
-        <v>3472</v>
+        <v>4443</v>
       </c>
       <c r="O47" t="n">
-        <v>868000</v>
+        <v>1919376</v>
       </c>
       <c r="P47" t="n">
-        <v>4800</v>
+        <v>6300</v>
       </c>
       <c r="Q47" t="n">
-        <v>1200000</v>
+        <v>2721600</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>C1717</t>
-        </is>
+          <t>C1758</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>6914919067549</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ESPADA CON LUZ Y SONIDO</t>
+          <t>MULA BLISTER SURTIDA</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2395,7 +2398,7 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>432</v>
+        <v>180</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
@@ -2404,33 +2407,33 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>432</v>
+        <v>180</v>
       </c>
       <c r="N48" t="n">
-        <v>4443</v>
+        <v>4648.6</v>
       </c>
       <c r="O48" t="n">
-        <v>1919376</v>
+        <v>836748.0000000001</v>
       </c>
       <c r="P48" t="n">
-        <v>6300</v>
+        <v>8900</v>
       </c>
       <c r="Q48" t="n">
-        <v>2721600</v>
+        <v>1602000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>C1758</t>
+          <t>C1897</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>6914919067549</v>
+        <v>6914919086373</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MULA BLISTER SURTIDA</t>
+          <t>MULA DIDACTICA</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2444,7 +2447,7 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>180</v>
+        <v>144</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -2453,38 +2456,30 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>180</v>
+        <v>144</v>
       </c>
       <c r="N49" t="n">
-        <v>4648.6</v>
+        <v>16897</v>
       </c>
       <c r="O49" t="n">
-        <v>836748.0000000001</v>
+        <v>2433168</v>
       </c>
       <c r="P49" t="n">
-        <v>8900</v>
+        <v>27900</v>
       </c>
       <c r="Q49" t="n">
-        <v>1602000</v>
+        <v>4017600</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>C1897</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>6914919086373</v>
+          <t>C2117</t>
+        </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MULA DIDACTICA</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>DISPLAY CARTÓN PEGAJOSOS X 20</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2493,7 +2488,7 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>144</v>
+        <v>1400</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -2502,30 +2497,38 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>144</v>
+        <v>1400</v>
       </c>
       <c r="N50" t="n">
-        <v>16897</v>
+        <v>3751</v>
       </c>
       <c r="O50" t="n">
-        <v>2433168</v>
+        <v>5251400</v>
       </c>
       <c r="P50" t="n">
-        <v>27900</v>
+        <v>6400</v>
       </c>
       <c r="Q50" t="n">
-        <v>4017600</v>
+        <v>8960000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>C2117</t>
-        </is>
+          <t>C342</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>6914919018374</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>DISPLAY CARTÓN PEGAJOSOS X 20</t>
+          <t>COCINA CON VAPOR DE AGUA</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2534,7 +2537,7 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>1400</v>
+        <v>24</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
@@ -2543,38 +2546,30 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>1400</v>
+        <v>24</v>
       </c>
       <c r="N51" t="n">
-        <v>3751</v>
+        <v>24573.894298246</v>
       </c>
       <c r="O51" t="n">
-        <v>5251400</v>
+        <v>589773.463157904</v>
       </c>
       <c r="P51" t="n">
-        <v>6400</v>
+        <v>52900</v>
       </c>
       <c r="Q51" t="n">
-        <v>8960000</v>
+        <v>1269600</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>C342</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>6914919018374</v>
+          <t>C3455</t>
+        </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>COCINA CON VAPOR DE AGUA</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>DINOSAURIO BOLSA</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2583,7 +2578,7 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>24</v>
+        <v>288</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
@@ -2592,30 +2587,35 @@
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>24</v>
+        <v>288</v>
       </c>
       <c r="N52" t="n">
-        <v>24538.02</v>
+        <v>5894.64</v>
       </c>
       <c r="O52" t="n">
-        <v>588912.48</v>
+        <v>1697656.32</v>
       </c>
       <c r="P52" t="n">
-        <v>52900</v>
+        <v>11000</v>
       </c>
       <c r="Q52" t="n">
-        <v>1269600</v>
+        <v>3168000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>C3455</t>
+          <t>C3638</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>DINOSAURIO BOLSA</t>
+          <t>INFLABLE DONA</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2624,7 +2624,7 @@
         </is>
       </c>
       <c r="J53" t="n">
-        <v>288</v>
+        <v>203</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
@@ -2633,30 +2633,30 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>288</v>
+        <v>203</v>
       </c>
       <c r="N53" t="n">
-        <v>5894.64</v>
+        <v>3877.89</v>
       </c>
       <c r="O53" t="n">
-        <v>1697656.32</v>
+        <v>787211.6699999999</v>
       </c>
       <c r="P53" t="n">
-        <v>11000</v>
+        <v>6500</v>
       </c>
       <c r="Q53" t="n">
-        <v>3168000</v>
+        <v>1319500</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>C3638</t>
+          <t>C3700</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>INFLABLE DONA</t>
+          <t>MUNECA CON CARRO RECARGABLE DE CONTROL REMOTO</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2670,7 +2670,7 @@
         </is>
       </c>
       <c r="J54" t="n">
-        <v>203</v>
+        <v>6</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
@@ -2679,30 +2679,30 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>203</v>
+        <v>6</v>
       </c>
       <c r="N54" t="n">
-        <v>3877.89</v>
+        <v>60174</v>
       </c>
       <c r="O54" t="n">
-        <v>787211.6699999999</v>
+        <v>361044</v>
       </c>
       <c r="P54" t="n">
-        <v>6500</v>
+        <v>96900</v>
       </c>
       <c r="Q54" t="n">
-        <v>1319500</v>
+        <v>581400</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>C3700</t>
+          <t>C3970</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>MUNECA CON CARRO RECARGABLE DE CONTROL REMOTO</t>
+          <t>GUITARRAS C3970</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2712,11 +2712,11 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
@@ -2725,44 +2725,39 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="N55" t="n">
-        <v>60174</v>
+        <v>27011.040935673</v>
       </c>
       <c r="O55" t="n">
-        <v>361044</v>
+        <v>1296529.964912304</v>
       </c>
       <c r="P55" t="n">
-        <v>96900</v>
+        <v>43900</v>
       </c>
       <c r="Q55" t="n">
-        <v>581400</v>
+        <v>2107200</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>C3970</t>
+          <t>C3988</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>GUITARRAS C3970</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>DRAGÓN CAMINA CON LUZ Y SONIDO</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -2771,39 +2766,44 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="N56" t="n">
-        <v>26854</v>
+        <v>29700</v>
       </c>
       <c r="O56" t="n">
-        <v>1288992</v>
+        <v>356400</v>
       </c>
       <c r="P56" t="n">
-        <v>43900</v>
+        <v>50500</v>
       </c>
       <c r="Q56" t="n">
-        <v>2107200</v>
+        <v>606000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>C3988</t>
+          <t>C4303</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>DRAGÓN CAMINA CON LUZ Y SONIDO</t>
+          <t>BEBE CON PIJAMA MED BOLSA PVC C4303</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>12</v>
+        <v>300</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
@@ -2812,30 +2812,30 @@
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>12</v>
+        <v>300</v>
       </c>
       <c r="N57" t="n">
-        <v>29700</v>
+        <v>18016</v>
       </c>
       <c r="O57" t="n">
-        <v>356400</v>
+        <v>5404800</v>
       </c>
       <c r="P57" t="n">
-        <v>50500</v>
+        <v>29900</v>
       </c>
       <c r="Q57" t="n">
-        <v>606000</v>
+        <v>8970000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>C4303</t>
+          <t>C4305</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>BEBE CON PIJAMA MED BOLSA PVC C4303</t>
+          <t>MUÑECA BEBE GRANDE CON PIJAMA EN BOLSA C4305</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2849,7 +2849,7 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>300</v>
+        <v>144</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
@@ -2858,30 +2858,30 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>300</v>
+        <v>144</v>
       </c>
       <c r="N58" t="n">
-        <v>18016</v>
+        <v>25534</v>
       </c>
       <c r="O58" t="n">
-        <v>5404800</v>
+        <v>3676896</v>
       </c>
       <c r="P58" t="n">
-        <v>29900</v>
+        <v>40900</v>
       </c>
       <c r="Q58" t="n">
-        <v>8970000</v>
+        <v>5889600</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>C4305</t>
+          <t>C4310</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MUÑECA BEBE GRANDE CON PIJAMA EN BOLSA C4305</t>
+          <t>MUÑECA CON CARRO HUMO RECARGABLE C4310</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2895,7 +2895,7 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>144</v>
+        <v>32</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
@@ -2904,30 +2904,30 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>144</v>
+        <v>32</v>
       </c>
       <c r="N59" t="n">
-        <v>25534</v>
+        <v>72889</v>
       </c>
       <c r="O59" t="n">
-        <v>3676896</v>
+        <v>2332448</v>
       </c>
       <c r="P59" t="n">
-        <v>40900</v>
+        <v>117500</v>
       </c>
       <c r="Q59" t="n">
-        <v>5889600</v>
+        <v>3760000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>C4310</t>
+          <t>C4545</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MUÑECA CON CARRO HUMO RECARGABLE C4310</t>
+          <t>TAPETE PIANO PARA BEBE C4545</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2941,7 +2941,7 @@
         </is>
       </c>
       <c r="J60" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
@@ -2950,30 +2950,30 @@
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="N60" t="n">
-        <v>72889</v>
+        <v>27186</v>
       </c>
       <c r="O60" t="n">
-        <v>2332448</v>
+        <v>543720</v>
       </c>
       <c r="P60" t="n">
-        <v>117500</v>
+        <v>43900</v>
       </c>
       <c r="Q60" t="n">
-        <v>3760000</v>
+        <v>878000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>C4545</t>
+          <t>C4728</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>TAPETE PIANO PARA BEBE C4545</t>
+          <t>FLIOTADOR DONA DINOSAURIO #60 C4728</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="J61" t="n">
-        <v>20</v>
+        <v>1800</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
@@ -2996,44 +2996,47 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>20</v>
+        <v>1800</v>
       </c>
       <c r="N61" t="n">
-        <v>27186</v>
+        <v>2454</v>
       </c>
       <c r="O61" t="n">
-        <v>543720</v>
+        <v>4417200</v>
       </c>
       <c r="P61" t="n">
-        <v>43900</v>
+        <v>4200</v>
       </c>
       <c r="Q61" t="n">
-        <v>878000</v>
+        <v>7560000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>C4728</t>
-        </is>
+          <t>C488</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>6554632300006</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>FLIOTADOR DONA DINOSAURIO #60 C4728</t>
+          <t>MALETA JUGUETES</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J62" t="n">
-        <v>1800</v>
+        <v>12</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
@@ -3042,47 +3045,47 @@
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>1800</v>
+        <v>12</v>
       </c>
       <c r="N62" t="n">
-        <v>2454</v>
+        <v>18491</v>
       </c>
       <c r="O62" t="n">
-        <v>4417200</v>
+        <v>221892</v>
       </c>
       <c r="P62" t="n">
-        <v>4200</v>
+        <v>13500</v>
       </c>
       <c r="Q62" t="n">
-        <v>7560000</v>
+        <v>162000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>C488</t>
+          <t>C5032</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>6554632300006</v>
+        <v>6999899236154</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>MALETA JUGUETES</t>
+          <t>INFLABLE TECHITO PIECITOS  FIGURAS STD C5032</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>INFLABLES</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>12</v>
+        <v>937</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
@@ -3091,47 +3094,44 @@
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>12</v>
+        <v>937</v>
       </c>
       <c r="N63" t="n">
-        <v>18491</v>
+        <v>8945.379999999999</v>
       </c>
       <c r="O63" t="n">
-        <v>221892</v>
+        <v>8381821.06</v>
       </c>
       <c r="P63" t="n">
-        <v>13500</v>
+        <v>14900</v>
       </c>
       <c r="Q63" t="n">
-        <v>162000</v>
+        <v>13961300</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>C5032</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>6999899236154</v>
+          <t>C698</t>
+        </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>INFLABLE TECHITO PIECITOS  FIGURAS STD C5032</t>
+          <t>HELICE 9 LUCES</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>INFLABLES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>937</v>
+        <v>240</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -3140,44 +3140,44 @@
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>937</v>
+        <v>240</v>
       </c>
       <c r="N64" t="n">
-        <v>8945.379999999999</v>
+        <v>1567.02</v>
       </c>
       <c r="O64" t="n">
-        <v>8381821.06</v>
+        <v>376084.8</v>
       </c>
       <c r="P64" t="n">
-        <v>14900</v>
+        <v>2900</v>
       </c>
       <c r="Q64" t="n">
-        <v>13961300</v>
+        <v>696000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>C698</t>
+          <t>C7560</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>HELICE 9 LUCES</t>
+          <t>BARRA LUMINOSA 48CM C7560/211</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J65" t="n">
-        <v>240</v>
+        <v>10</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
@@ -3186,35 +3186,38 @@
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>240</v>
+        <v>10</v>
       </c>
       <c r="N65" t="n">
-        <v>1567.02</v>
+        <v>796.3099999999999</v>
       </c>
       <c r="O65" t="n">
-        <v>376084.8</v>
+        <v>7963.099999999999</v>
       </c>
       <c r="P65" t="n">
-        <v>2900</v>
+        <v>2500</v>
       </c>
       <c r="Q65" t="n">
-        <v>696000</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>C7560</t>
-        </is>
+          <t>C7610</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>6999899236093</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>BARRA LUMINOSA 48CM C7560/211</t>
+          <t>BOTE TIMON PISCINA 80X60 C7610</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>INFLABLES</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3223,7 +3226,7 @@
         </is>
       </c>
       <c r="J66" t="n">
-        <v>10</v>
+        <v>360</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>
@@ -3232,67 +3235,18 @@
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>10</v>
+        <v>360</v>
       </c>
       <c r="N66" t="n">
-        <v>796.3099999999999</v>
+        <v>7811.9</v>
       </c>
       <c r="O66" t="n">
-        <v>7963.099999999999</v>
+        <v>2812284</v>
       </c>
       <c r="P66" t="n">
-        <v>2500</v>
+        <v>13900</v>
       </c>
       <c r="Q66" t="n">
-        <v>25000</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>C7610</t>
-        </is>
-      </c>
-      <c r="B67" t="n">
-        <v>6999899236093</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>BOTE TIMON PISCINA 80X60 C7610</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>INFLABLES</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J67" t="n">
-        <v>360</v>
-      </c>
-      <c r="K67" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" t="n">
-        <v>0</v>
-      </c>
-      <c r="M67" t="n">
-        <v>360</v>
-      </c>
-      <c r="N67" t="n">
-        <v>7811.9</v>
-      </c>
-      <c r="O67" t="n">
-        <v>2812284</v>
-      </c>
-      <c r="P67" t="n">
-        <v>13900</v>
-      </c>
-      <c r="Q67" t="n">
         <v>5004000</v>
       </c>
     </row>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -2549,10 +2549,10 @@
         <v>24</v>
       </c>
       <c r="N51" t="n">
-        <v>24573.894298246</v>
+        <v>24538.02</v>
       </c>
       <c r="O51" t="n">
-        <v>589773.463157904</v>
+        <v>588912.48</v>
       </c>
       <c r="P51" t="n">
         <v>52900</v>
@@ -2728,10 +2728,10 @@
         <v>48</v>
       </c>
       <c r="N55" t="n">
-        <v>27011.040935673</v>
+        <v>26854</v>
       </c>
       <c r="O55" t="n">
-        <v>1296529.964912304</v>
+        <v>1288992</v>
       </c>
       <c r="P55" t="n">
         <v>43900</v>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-12</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-13</t>
         </is>
       </c>
     </row>
@@ -1314,10 +1314,10 @@
         <v>25</v>
       </c>
       <c r="N22" t="n">
-        <v>15711.964632768</v>
+        <v>15711.964602273</v>
       </c>
       <c r="O22" t="n">
-        <v>392799.1158192</v>
+        <v>392799.115056825</v>
       </c>
       <c r="P22" t="n">
         <v>28500</v>
